--- a/excel/游戏新闻50篇.xlsx
+++ b/excel/游戏新闻50篇.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="游戏新闻50篇" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="游戏新闻" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -504,14 +504,14 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>每经编辑：肖芮冬
-8月12日，A股三大指数集体上涨，市场情绪回暖。截至14:47，创业板指涨幅达1.58%，领涨两市，深证成指与上证指数分别上涨1.12%和0.34%。在此背景下，游戏板块表现活跃，跟踪板块表现的游戏ETF国泰（516010）场内价格上涨0.80%，成交额达8207.29万元。
-资金流向显示，市场对游戏板块的关注度正在升温。最新数据显示，游戏ETF国泰（516010）已连续3个交易日获得资金净流入，近30日累计资金净流入达3.27亿元，其管理规模也随之增至27.42亿元，显示出资金对该领域的积极布局。
-近期市场风格出现了明显的轮动迹象，前期调整较多的科技成长方向重获资金青睐。中信建投指出，本周A股市场成长与小盘风格强势反弹，行业层面电子、有色金属、机械设备领涨，市场资金偏好前期回调较多的科技成长方向。游戏板块作为TMT产业的重要组成部分，同样受益于此轮风格切换和情绪修复。
-从宏观和盈利预期来看，当前时点为布局相关板块提供了窗口期。光大证券策略观点认为，国内外科技盈利高增长且PPI带动整体盈利回升，8月中报密集披露期或成市场从估值消化切换至盈利驱动的拐点，财报季可能是下半年最好的配置窗口。在市场逻辑有望转向盈利驱动的背景下，游戏行业凭借其内生的内容创新周期和技术迭代（如AIGC）带来的降本增效，其基本面价值值得关注。
-对于希望便捷布局游戏产业的投资者而言，游戏ETF国泰（516010）提供了高效的配置工具。该ETF紧密跟踪中证动漫游戏指数，指数样本选取主营业务涉及动画、漫画、游戏等相关细分娱乐产业的上市公司。从估值角度看，最新数据显示，当前中证动漫游戏指数市盈率（PE）为25.36倍，处于近一年20%的较低分位水平，估值具备吸引力，配置价值凸显。
-风险提示：提及个股仅用于行业事件分析，不构成任何个股推荐或投资建议。指数等短期涨跌仅供参考，不代表其未来表现，亦不构成对基金业绩的承诺或保证。观点可能随市场环境变化而调整，不构成投资建议或承诺。提及基金风险收益特征各不相同，敬请投资者仔细阅读基金法律文件，充分了解产品要素、风险等级及收益分配原则，选择与自身风险承受能力匹配的产品，谨慎投资。涉及基金费率请查阅法律文件。
-每日经济新闻</t>
+          <t>&lt;p&gt;　　每经编辑：肖芮冬&lt;/p&gt;
+&lt;p&gt;　　8月12日，A股三大指数集体上涨，市场情绪回暖。截至14:47，创业板指涨幅达1.58%，领涨两市，深证成指与上证指数分别上涨1.12%和0.34%。在此背景下，游戏板块表现活跃，跟踪板块表现的游戏ETF国泰（516010）场内价格上涨0.80%，成交额达8207.29万元。&lt;/p&gt;
+&lt;p&gt;　　资金流向显示，市场对游戏板块的关注度正在升温。最新数据显示，游戏ETF国泰（516010）已连续3个交易日获得资金净流入，近30日累计资金净流入达3.27亿元，其管理规模也随之增至27.42亿元，显示出资金对该领域的积极布局。&lt;/p&gt;
+&lt;p&gt;　　近期市场风格出现了明显的轮动迹象，前期调整较多的科技成长方向重获资金青睐。中信建投指出，本周A股市场成长与小盘风格强势反弹，行业层面电子、有色金属、机械设备领涨，市场资金偏好前期回调较多的科技成长方向。游戏板块作为TMT产业的重要组成部分，同样受益于此轮风格切换和情绪修复。&lt;/p&gt;
+&lt;p&gt;　　从宏观和盈利预期来看，当前时点为布局相关板块提供了窗口期。光大证券策略观点认为，国内外科技盈利高增长且PPI带动整体盈利回升，8月中报密集披露期或成市场从估值消化切换至盈利驱动的拐点，财报季可能是下半年最好的配置窗口。在市场逻辑有望转向盈利驱动的背景下，游戏行业凭借其内生的内容创新周期和技术迭代（如AIGC）带来的降本增效，其基本面价值值得关注。&lt;/p&gt;
+&lt;p&gt;　　对于希望便捷布局游戏产业的投资者而言，游戏ETF国泰（516010）提供了高效的配置工具。该ETF紧密跟踪中证动漫游戏指数，指数样本选取主营业务涉及动画、漫画、游戏等相关细分娱乐产业的上市公司。从估值角度看，最新数据显示，当前中证动漫游戏指数市盈率（PE）为25.36倍，处于近一年20%的较低分位水平，估值具备吸引力，配置价值凸显。&lt;/p&gt;
+&lt;p&gt;　　风险提示：提及个股仅用于行业事件分析，不构成任何个股推荐或投资建议。指数等短期涨跌仅供参考，不代表其未来表现，亦不构成对基金业绩的承诺或保证。观点可能随市场环境变化而调整，不构成投资建议或承诺。提及基金风险收益特征各不相同，敬请投资者仔细阅读基金法律文件，充分了解产品要素、风险等级及收益分配原则，选择与自身风险承受能力匹配的产品，谨慎投资。涉及基金费率请查阅法律文件。&lt;/p&gt;
+&lt;p&gt;　　每日经济新闻&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -519,7 +519,7 @@
       <c r="A3" s="2" t="inlineStr"/>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>游戏科学杨奇：《黑神话：钟馗》设计阶段将远离AIGC；Square Enix第一财季游戏业务营收利润双增｜游戏早参</t>
+          <t>米哈游AI陪伴产品《BSide: Olivia Lin》上线不足一月宣布停运；《影之刃零》开启全平台预售｜游戏早参</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -529,31 +529,27 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>每经记者：李宇彤    每经编辑：余婷婷
-｜2026年8月11日  星期二｜
-NO.1 游戏科学杨奇：《黑神话：钟馗》设计阶段将远离AIGC
-8月10日，游戏科学联合创始人、《黑神话：悟空》美术总监杨奇，在社交平台回应网友询问AI（人工智能）能否加快《黑神话：钟馗》的开发进度时称：“设计和资产阶段会远离AIGC（人工智能生成内容），倒不是抵触，只是为了站好最后一班岗？”他以诺兰新作《奥德赛》采用胶片等技术手段为例，表示“没有什么末班车是非赶不可的，况且AI啥的有的是时间，不急”。《黑神话：钟馗》是游戏科学继《悟空》后的新作，目标是延续写实美术风格并追求更高画面水准。
-点评：游戏科学在《黑神话：钟馗》开发中主动远离AIGC，体现其对人工创作价值与画面品质的坚持，有助于维持品牌在核心玩家群体中的口碑预期。此举也向市场传递了精品化研发路径的信号，即不盲目追求技术捷径换取速度。
-NO.2 Square Enix第一财季游戏业务营收利润双增
-8月10日，Square Enix公布本财年第一季度财报（2026年4月1日至2026年6月30日），游戏业务销售额同比增长51.8%，营业利润同比增长91.8%。整体净销售额达784亿日元，同比增长32.3%；营业利润170亿日元，同比增长89%，远超市场预期。业绩增长主要得益于NS2/Xbox版《最终幻想7：重生》及新作《冒险家艾略特的千年奇谭》销量稳健，叠加过往作品持续销售与手游增收。数据显示，本季度Square Enix的数字版销量占比达90.1%。
-点评：Square Enix游戏业务营收利润双增，验证了多平台移植与经典IP（具有商业价值的创意内容或品牌）续作组合策略的有效性，对产品储备丰富的日系厂商板块构成积极参照。数字版占比突破九成，表明实体向数字的渠道迁移在成熟市场已接近完成，对实体分销依赖度较高的产业链环节形成结构压力。
-NO.3 PlayStation官网新增提示：2028年起新作终止实体光盘发售
-8月10日消息，索尼PlayStation官方商店已正式加入提示，告知购买PS5光驱版的用户：从2028年1月起将不再支持新游戏的光盘发行，届时新作仅以数字版形式发售。此前，索尼已宣布自2028年1月起停止为所有PlayStation新游戏生产实体光盘。PS5主机包装盒及外接光驱产品页面也已陆续加入相同提示。
-点评：索尼在官方渠道系统性地嵌入停发实体光盘提示，标志着从2028年起全面转向数字发行的计划已进入实质性推进阶段。此举将加速游戏零售渠道的结构性变革，对实体分销商及二手交易市场的长期预期构成冲击。
-免责声明：本文内容与数据仅供参考，不构成投资建议，使用前请核实。据此操作，风险自担。
-每日经济新闻</t>
+          <t>&lt;p&gt;　　每经记者：李宇彤    每经编辑：廖丹&lt;/p&gt;
+&lt;p&gt;　　|2026年8月12日 星期三|&lt;/p&gt;
+&lt;p&gt;　　NO.1 《影之刃零》8月12日开启全平台预售&lt;/p&gt;
+&lt;p&gt;　　8月12日，灵游坊旗下黑暗武侠题材单机动作游戏《影之刃零》将在PS5、Steam、Epic、WeGame及TapTap开启预售。此前官方曾表示整体研发工作已全部完成，预售当天将公布游戏售价及PC（个人电脑）版详细配置需求，并放出11分钟全新实机演示视频。本作是灵游坊采用虚幻引擎5打造的3A大作，定位为暗黑武侠题材第三人称动作冒险游戏，融合中国武术与蒸汽朋克元素。&lt;/p&gt;
+&lt;p&gt;　　点评：灵游坊携国产单机大作开启全平台预售，标志着《影之刃零》正式进入商业化兑现阶段，对公司现金流与品牌价值构成积极预期。虚幻引擎5的品质呈现与暗黑武侠的差异化定位，有望在全球市场建立品类认知。对国产单机板块而言，头部产品的预售热度与最终销量表现，将成为验证国内3A单机研发能力与市场空间的重要参照。&lt;/p&gt;
+&lt;p&gt;　　NO.2 米哈游AI陪伴产品《BSide: Olivia Lin》上线不足一月宣布停运&lt;/p&gt;
+&lt;p&gt;　　8月11日，米哈游发布公告，宣布旗下AI（人工智能）陪伴产品《BSide:Olivia Lin》将正式停止线上运营。该产品于7月13日登陆Steam开启抢先体验，运营时间不足一个月。官方表示基于产品阶段性规划与后续安排作出该决定，并将于2026年8月27日15:00上线离线版本，届时停止“写信”“上传MIDI”等在线服务功能。8月31日15:00，产品将从Steam商店下架，服务器正式关闭。离线版本支持用户继续聆听角色演奏并使用桌面动态壁纸等功能。&lt;/p&gt;
+&lt;p&gt;　　点评：米哈游AI陪伴产品快速停运，反映出AI互动工具类产品在用户留存与商业化路径上面临的现实挑战，对公司探索新交互形态的试错成本构成短期扰动。离线版本保留了部分功能，一定程度体现了对早期用户的基本关照。对游戏板块而言，此案例提示AI赋能消费级产品的落地仍需在场景适配与用户价值间找到更精准的平衡点。&lt;/p&gt;
+&lt;p&gt;　　NO.3 《王者荣耀世界》宣布S1赛季延长，集中优化新手与战斗体验&lt;/p&gt;
+&lt;p&gt;　　8月11日，《王者荣耀世界》制作组发布公告，决定投入一段时间重点优化基础体验，S1赛季将继续延长，S2赛季将围绕新手体验、战斗机制和基础内容进行调整。新手体验方面将重新设计新手流程并新增主线难度选择——“故事模式”降低怪物难度，“冒险模式”保持正常挑战。前期剧情将重新编排，部分内容移出主线，同时完善教学与引导设计。战斗机制方面将调整共鸣养成与双共鸣战斗系统，降低理解门槛。移动端将继续优化发热、掉帧等问题，重点改善多人同屏战斗及中低配设备表现。&lt;/p&gt;
+&lt;p&gt;　　点评：腾讯《王者荣耀世界》主动放缓赛季节奏以集中优化基础体验，有助于降低新玩家进入门槛并改善核心战斗反馈，对产品长线留存与口碑修复形成正向支撑。此举虽短期推迟了内容更新带来的流水增量，但长期有利于提升用户生命周期价值。对开放世界品类而言，头部产品对新手引导与性能优化的持续投入，正在抬升赛道整体的体验基准。&lt;/p&gt;
+&lt;p&gt;　　免责声明：本文内容与数据仅供参考，不构成投资建议，使用前请核实。据此操作，风险自担。&lt;/p&gt;
+&lt;p&gt;　　每日经济新闻&lt;/p&gt;</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>https://inews.gtimg.com/om_bt/OjLlhhDNX_5LYooS2swAZvxL8qQsEY36Cb-kq5RxPizjkAA/641</t>
-        </is>
-      </c>
+      <c r="A4" s="2" t="inlineStr"/>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>“悟空”之后，中国游戏继续闯世界</t>
+          <t>估值处历史低位，资金逆市布局游戏ETF国泰（516010），连续3日迎资金净流入</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
@@ -563,45 +559,25 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>原标题：与科技同游 与文化同行
-“悟空”之后，中国游戏继续闯世界
-观众在2026 ChinaJoy上体验国产游戏。受访者供图
-灵珠子驾驭法宝，在天地之间与上古巨神交锋；锦衣卫在刀光剑影中见招拆招；少女剑客闪身避开锋芒、顺势反击……这些充满东方想象的游戏场景背后，是游戏引擎、动作捕捉、实时渲染、流体解算和人工智能等数字技术的共同支撑。
-以“与AI同游”为主题的2026年中国国际数码互动娱乐展览会（ChinaJoy）期间，来自39个国家和地区的近900家企业参展，千余款游戏产品集中亮相。
-两年前，《黑神话：悟空》的成功，见证了中国游戏的新高度。热潮之后，一个更为现实的问题摆在从业者面前：从一款现象级作品，到更多游戏持续走向世界，中间还有多远的路？为此，记者采访了多位国产单机游戏制作人及海外发行商。
-一颗种子，打开一扇门
-《黑神话：悟空》发售后，濮冠楠用了不到两天的时间通关游戏。
-“《黑神话》是一颗种子，它会激励成千上万的人。”濮冠楠说。在此之前，他所创办的星辰无双主要从事弹幕互动游戏业务。通关不久，他作出决定：转向大型单机游戏开发，启动科幻动作游戏《时空低语》。
-《黑神话：悟空》的风靡，带动国内主机游戏市场的增长。中国音像与数字出版协会发布的报告显示，2025年国内主机游戏市场实际销售收入达到83.62亿元，同比增长86.33%，实现了连续3年的高速增长。
-本届ChinaJoy期间，一批开发多年的国产单机游戏作品集中亮相，这是中国游戏从业者多年技术积累和创作探索的集中显现。
-成都剑猫熊网络创始人、游戏制作人武侠曾参与多款国际知名3A游戏的开发。2022年，他回到家乡创办团队，制作游戏《猿公剑》。
-“我们等了20多年，终于等到了这个机会。”武侠说，许多国产单机游戏早在《黑神话：悟空》发售前就已启动，“一个大型游戏制作往往要耗费5年甚至更长时间，不可能看到一款游戏成功，第二年就拿出新的作品。”
-游戏《一盏秋声：锦衣卫》的开发同样在“悟空”风靡之前。90后游戏制作人刘启威早年在手游行业工作，后来聚集几名志同道合的伙伴，逐渐搭建起完整团队。
-在刘启威看来，近年来国产单机游戏集中涌现，一方面是技术、人才和工业化能力积累到了一定阶段，另一方面是《黑神话：悟空》以产品结果验证了这条道路的可行性。积压已久的表达欲与逐渐成熟的产业条件相遇，让更多从业者向着高质量的作品努力。
-技术，让文化更有“可玩性”
-剑锋迎面袭来，主人公没有向远处翻滚，而是侧身避开锋芒，并在擦身而过的一瞬间切入反击……这是《猿公剑》设计的一套战斗机制——“避青入红”。
-武侠曾学习传统武术。在他看来，中国剑术并不总是依靠力量硬碰硬，而是强调观察、身法、时机与攻守转换。游戏据此把“避其锋芒、乘隙而入”的理念转化成了具体操作。
-“通过身体上的锻炼和修炼，达到精神上的升华，这是我特别想在游戏里表达的东西。”武侠说。
-随着国产游戏工业化水平提升，传统文化正借助画面、动作和玩法，直接形成面向全球玩家的吸引力。如今，从上古神话、中国历史，到传统武术、地方民俗，越来越多国产单机游戏从中华文化中寻找创作灵感和资源，尝试将文化内涵融入战斗机制、角色成长和世界构建之中。
-盘古魂游戏创始人、《古神：风里希》制作人刘洋，尝试用数字技术表现古人想象中的“神仙打架”场景。游戏从女娲造人等华夏创世神话中寻找灵感。刘洋带领开发团队运用流体解算、动态特效和空地双架势系统，将飞天遁地、呼风唤雨的神话想象，转化为能够实时运行、由玩家亲手操作的战斗体验。
-《一盏秋声：锦衣卫》试图呈现武侠故事中“高手过招”的感觉。游戏围绕真气、内息、破绽和招式克制构建战斗体系，实现“见招拆招、以招破招”。
-“中国文化是‘好食材’，但首先要把‘香味’激发出来，让人愿意走近、品尝。”刘启威认为，只有游戏的操作、画面和战斗能够吸引玩家，隐藏在背后的历史和文化才有机会被进一步感知。
-从“被看见”到“被记住”
-在同海外游戏从业者交流时，刘洋曾多次尝试解释：游戏中的女娲是谁？
-刘洋将女娲抟土造人的故事与中国瓷器联系起来，把主角的成长设计为从土和水塑造的“器物”，逐渐成长为人、走向神；游戏海外名称则突出“哪吒”这一认知度相对较高的形象，由此引导玩家理解更久远的中国创世神话。
-2025年，中国自主研发游戏海外市场实际销售收入达到204.55亿美元，同比增长10.23%，连续第6年超过1000亿元人民币。其中，移动游戏仍占主要部分。对于主机和单机产品而言，如何在全球市场建立认知，仍是一条需要探索的路径。
-一款游戏从完成开发到真正抵达海外玩家，中间还有一条由资金、市场、本地化、媒体传播和销售渠道共同组成的产业链。
-新加坡游戏发行及分销企业嘉仕尔（GCL）旗下的4Divinity，曾承担《黑神话：悟空》海外发行工作。嘉仕尔中国区商务负责人吕晟认为，中国游戏团队的研发和技术能力已经接近国际一线，但部分团队在全球市场经验、原创IP塑造、本地化和全流程发行等方面仍有不足。为此，GCL在游戏项目较早阶段介入，在提供资金支持的同时，与团队共同讨论产品方向、剧本、本地化和海外传播策略，再通过海外展会、媒体和销售渠道完成落地。
-“悟空”证明了中国文化题材能够进入全球主流游戏市场，但并没有缩短一款好游戏必须经历的漫长创作过程。中国游戏还需要在一次次创作和市场检验中，把科技、文化和产业能力结合起来，做出让全球玩家愿意拿起手柄、走进其中，并在游戏结束后依然记得的中国故事。
-濮冠楠打了一个比方：初唐有了王勃，但几十年后才出现李白和杜甫。“单机游戏不是增加算力、堆积数据就能批量生产的产品。技术可以拓展创作边界，却不能代替时间、经验和创作者自身的表达。”他说。</t>
+          <t>&lt;p&gt;　　每经编辑：肖芮冬&lt;/p&gt;
+&lt;p&gt;　　数据显示，近期资金持续借道相关ETF产品布局游戏板块。截至最新数据，游戏ETF国泰（516010）连续3日迎资金净流入，近30日资金净流入额高达3.27亿元，显示出投资者对该板块未来修复行情的看好。在持续的资金流入推动下，该ETF最新规模已达到27.42亿元。&lt;/p&gt;
+&lt;p&gt;　　从产业基本面与估值水平来看，游戏板块当前的配置价值正逐步凸显。游戏ETF国泰所跟踪的中证动漫游戏指数，其样本股选取主营业务涉及动画、漫画、游戏等相关细分娱乐产业的优质上市公司，能够较好地反映我国动漫游戏产业的整体发展态势。&lt;/p&gt;
+&lt;p&gt;　　当前，该指数的估值水平处于历史相对低位。最新数据显示，中证动漫游戏指数的市盈率（PE）为25.36倍，位于近一年估值区间的20%分位数，显著低于历史高点。在行业经历了前期调整后，较低的估值水平为投资者提供了更宽裕的安全边际和潜在的上涨空间。随着暑期档的来临、重点游戏产品的上线以及AI等新技术对游戏内容生产和玩法的赋能，行业景气度有望得到提振，龙头公司的业绩增长潜力值得关注。&lt;/p&gt;
+&lt;p&gt;　　对于希望便捷把握动漫游戏行业投资机遇的投资者而言，游戏ETF国泰（516010）提供了一个高效的配置工具。通过投资该ETF，投资者可一键布局多只动漫游戏核心企业，有效分散个股风险，分享行业整体增长所带来的红利。在板块估值处于低位、资金持续流入的背景下，该产品的配置价值值得密切关注。&lt;/p&gt;
+&lt;p&gt;　　风险提示：提及个股仅用于行业事件分析，不构成任何个股推荐或投资建议。指数等短期涨跌仅供参考，不代表其未来表现，亦不构成对基金业绩的承诺或保证。观点可能随市场环境变化而调整，不构成投资建议或承诺。提及基金风险收益特征各不相同，敬请投资者仔细阅读基金法律文件，充分了解产品要素、风险等级及收益分配原则，选择与自身风险承受能力匹配的产品，谨慎投资。涉及基金费率请查阅法律文件。&lt;/p&gt;
+&lt;p&gt;　　每日经济新闻&lt;/p&gt;</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr"/>
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>https://inews.gtimg.com/om_bt/OH7P4hd_x3Bg5IcjhZ2cdRSlsTpoXe3R39kXVoU_mmbnMAA/641</t>
+        </is>
+      </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>腾讯Q2游戏收入重回双位数增长</t>
+          <t>游戏科学杨奇回应《黑神话：钟馗》进度：暂不用AI，坚持“手搓”</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -611,7 +587,24 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>8月12日，腾讯控股发布2026年第二季度财报。网络游戏业务总收入659亿元，同比增长11%，整体重回双位数增长态势。本土市场收入473亿元，同比增长17%。增长动力主要来自四款核心产品：《三角洲行动》、《无畏契约》、《无畏契约：能源行动》及《洛克王国：世界》。其中《三角洲行动》与《无畏契约》平均日活跃用户均在本季度创下历史新高。国际市场收入186亿元，按固定汇率计算同比增长4%，主要受《鸣潮》《VALORANT》驱动。</t>
+          <t>&lt;p&gt;　　8月10日，游戏科学联合创始人、《黑神话》系列美术总监杨奇在社交平台分享团队新作研发思路，明确现阶段正在开发的《黑神话：钟馗》，将会在设计、游戏资产制作环节主动避开AIGC生成式工具。&lt;/p&gt;
+&lt;p&gt;　　事件起因源自杨奇分享的观影感悟，他在自己微博账号发贴，称诺兰全新影片《奥德赛》是“史诗电影的标准答案，深受启发”。随后有网友在评论区提问，当下AI工具的水平，能否帮助提速《黑神话：钟馗》整体研发进度，缩短新作上线周期。&lt;/p&gt;
+&lt;p&gt;　　对此，杨奇直接回应：设计和资产阶段会远离aigc，倒不是抵触，只是为了站好最后一班岗？顺道点个题啊，数字电影和3d后期看似穷途末路的今天，诺兰这不红光满面，用着更老的技术手段搅动风云… 没有什么末班车是非赶不可的，找个小旅馆住一住也行，况且ai啥的有的是时间，不急。&lt;/p&gt;
+&lt;img src="https://inews.gtimg.com/om_bt/OH7P4hd_x3Bg5IcjhZ2cdRSlsTpoXe3R39kXVoU_mmbnMAA/641" alt="https://inews.gtimg.com/om_bt/OH7P4hd_x3Bg5IcjhZ2cdRSlsTpoXe3R39kXVoU_mmbnMAA/641" /&gt;
+&lt;p&gt;　　现如今生成式AI已经成为全球游戏行业的主流辅助工具，大量厂商依靠AI快速产出原画、场景素材、贴图、音效素材，压缩人力成本、拉长项目产出速度。但 AIGC 批量产出的素材普遍存在细节空洞、风格同质化、缺少人文情绪等短板。&lt;/p&gt;
+&lt;p&gt;　　从杨奇的回应看来，即便当下AI能够大幅提速，游戏科学依旧拥有充足时间后续尝试新技术，新作开发不必急于求成。&lt;/p&gt;
+&lt;p&gt;　　而且，对于主打传统东方神话、精细化写实国风美术的黑神话系列而言，人工手绘、手工建模依旧是把控作品气质的关键。&lt;/p&gt;
+&lt;p&gt;　　据公开资料，《黑神话：钟馗》自2025年6月正式立项开工，项目至今仍处在早期研发周期。此前游戏科学曾在洛杉矶《黑神话：悟空》交响音乐会后接受采访，披露新作规划，本作脱离《黑神话：悟空》热血厚重的史诗基调，转向市井烟火的诙谐风格；战斗系统围绕钟馗佩剑、折扇、葫芦等特色器物搭建；画面渲染标准全面高于前作，团队目标打造照片级别的国风场景与角色建模，同时优化叙事门槛，适配海内外玩家的审美习惯。&lt;/p&gt;
+&lt;p&gt;　　截至目前，游戏科学未对外公布《黑神话：钟馗》预计发售时间，仅在科隆游戏展、新春短片放出过两段项目预热。2025年8月20日，在科隆游戏展开幕之夜上，游戏科学公布了旗下最新作品《黑神话：钟馗》，本作官网现已上线，并正式进入开发状态。&lt;/p&gt;
+&lt;p&gt;　　当时，游戏科学创始人、CEO，《黑神话：悟空》制作人冯骥曾发文解释为何推出新作。他表示，《黑神话：悟空》发售后有相当长一段时间。此时此刻，他们更想先做一款黑神话的新作——新的英雄，新的玩法，新的视觉，新的技术，新的故事。&lt;/p&gt;
+&lt;p&gt;　　作为黑神话系列的第二作，《黑神话:钟馗》依然取材于中国的古代神话与民俗传说；它依然是一款标准的单机·动作·角色扮演游戏，商业模式与前作一样。&lt;/p&gt;
+&lt;p&gt;　　按照前作漫长的打磨周期，以及主创不急着追赶AI风口的表态，估计这款全新神话题材作品依旧还有漫长的深耕之路。&lt;/p&gt;
+&lt;p&gt;　　由游戏科学开发的《黑神话：悟空》是一款以《西游记》中的孙悟空为原型的动作冒险游戏，它被业内视为国内真正意义上的第一款3A游戏。&lt;/p&gt;
+&lt;p&gt;　　《黑神话：悟空》2024年8月20日全球上线，上线当天热度席卷各大社交平台，同时在线人数超百万，实现了现象级破圈。据统计机构VG Insights在当年11月披露的数据，《黑神话：悟空》在Steam平台上的销量已经突破了2200万份，收入约11亿美元。&lt;/p&gt;
+&lt;p&gt;　　据公开数据，截至今年6月《黑神话：悟空》全平台全球累计销量已经突破3000万份，海外地区销量占比超过50%，海外售出份额突破1500万份，Steam长期稳定维持95%以上好评率，欧洲多国实体光盘销量持续走高，仅西班牙地区实体版销量已经突破4万份。&lt;/p&gt;
+&lt;p&gt;　　今年8月5日，即将迎来发售两周年的《黑神话：悟空》宣布，所有数字版本（标准版、豪华版、豪华升级包）即将开启七折优惠活动。PlayStation Store打折时间为8月12日-8月26日；微软商店、Steam、Epic游戏商城、WeGame打折时间为8月12日0时-8月25日24时。因平台政策影响，PS5不同时区打折活动的具体开启和结束时间略有不同，洪都拉斯、墨西哥和尼加拉瓜暂不参与本轮PS5促销。&lt;/p&gt;
+&lt;p&gt;　　此外，去年9月，黑神话首家线下零售店开启运营，并同步上线店铺服务号。线下店位于浙江省杭州市西湖区转塘街道艺创小镇，面积约1000平方米，展品有黑神话游戏中的大圣、牛魔王、黄眉、杨戬等关键角色；商品覆盖手办摆件、服装、玩偶、配饰、家居、包袋6个品类。开业当天，店铺多款产品就已售罄。&lt;/p&gt;
+&lt;p&gt;　　当时，杨奇曾在社交平台发布线下店的招聘公告，招聘店员和店长。招聘中强调应聘者需 “热爱艺术文化，具备审美与时尚敏感度，形象穿搭符合品牌调性”。&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -619,7 +612,7 @@
       <c r="A6" s="2" t="inlineStr"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>实探ChinaJoy：消费端丰富体验，商务端深化AI落地</t>
+          <t>AI退烧？米哈游AI产品停运，黑神话“手搓”游戏拒绝速成</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -629,21 +622,21 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>N1馆索尼PlayStation国风展台吸引大量观众驻足，南都记者现场看到，青瓦飞檐搭配科技蓝调拱门，中式美学元素与主机硬件视觉结合，往来观众不断，各试玩机位全程排起长队。
-展台带来8款海内外游戏试玩，三款“中国之星计划”三期国产新作开放专属试玩关卡，明末武侠《一盏秋声：锦衣卫》、古格文明题材《达巴：水痕之地》、末世射击《潜阈限界》展现本土主机多元创作实力；海外大作涵盖竞速、格斗、科幻射击多品类，《跑车浪漫旅7》模拟驾驶区、《漫威斗魂：格斗之魂》对战台前聚集不少观众。现场工作人员表示，第四期“中国之星计划”扩大招募规模，加大资金与全球化渠道扶持，支持国产主机拓展海外市场。南都记者留意到，武侠、星际主题Coser定时巡游全场，打卡集章可兑换限定周边，赛车挑战优胜者可领取仰望U9专属车模。
-恺英网络多馆联动打造沉浸式线下实景体验，南都记者在N3馆看到，996传奇盒子五周年游园会复刻沙巴克城池，6米高“天下第一战”雕像矗立展厅中央，七大传奇神兵整齐陈列于神兵库；展台特设非遗合作专区，非遗匠人在现场展示传统雕刻工艺复刻传奇兵器，网游IP与传统匠艺跨界融合。
-南都记者在N1馆看到，恺英网络以今年4月上线的SLG游戏《三国：天下归心》为主题，打造了仿古归心城池场景，魏蜀吴三面旌旗分列，全新S3赛季跨服玩法开放现场试玩，多场三国主题模特大秀轮番上演，到场观众通过打卡、互动等，领取了CJ限定电子纪念票、国风周边。
-同在N1馆的顺网科技以“江湖任我游”打造国风沉浸式展区，七大体验区域集结数十家独立工作室与硬件厂商，覆盖武侠、休闲、幻想各类题材。南都记者现场观察到，本次参展亮点为顺网云电脑全场景落地，工作人员向记者介绍，个人版支持手机、平板、PC多端云端畅玩3A大作，CITY版将游戏体验延伸至社区、电竞舱、客厅等线下场景，突破线下试玩的设备与空间限制。观众领取通关云牒打卡全展区即可兑换主题周边，主舞台全天开启趣味挑战赛，吸引观众参与。
-此外，南都记者在N4馆世纪华通旗下点点互动展台看到，《无尽冬日》《奔奔王国》两大产品展区客流持续稳定。据悉，爆款SLG《无尽冬日》第三次参展，展区复刻游戏冰雪场景，打造极寒合影屋，吉祥物大白熊、角色Coser互动吸引玩家打卡，现场可参与活动兑换白熊系列周边。《奔奔王国》迎来CJ首秀，搭建中世纪城邦主题空间，设置国王雕塑打卡点，配套射箭、淘金等互动小游戏，舞台持续开展走秀、扭蛋抽奖活动。
-相较于N馆展台面向普通玩家展现游戏娱乐消费端产品，W区商务馆中三七互娱、智冠集团、飞书深诺、波克科技等企业则针对行业需求，带来系统化AI工具，分别应对厂商出海增长、内容工业化生产、知识产权风控需求，吸引行业从业者驻足洽谈。
-三七互娱在B端展区展出自研四大AI产业工具，覆盖游戏研发、营销视频、版权风控全流程，用于企业内部提效及外部服务。南都记者逐一体验展台工具后发现，AI小游戏生成平台支持自然语言输入，无需编程即可快速生成可上线的H5小游戏；AI动作动画师仅需单张角色原画与文字指令，就能自动生成成套游戏动作资产，降低美术逐帧绘制成本；灵栩栩AI视频创作平台适配游戏广告、短剧、漫剧生产，单人单日可完成一整部剧集制作，据展台工作人员介绍，成本约为实景拍摄的十分之一，效率提升约十倍；灵察察智能风控平台依托自研大模型，提供舆情监测、侵权识别、AI内容合规管控一体化服务，为游戏厂商出海、线上运营提供版权与品牌安全保障。整套工具链展示游戏厂商自研AI技术商业化落地路径，南都记者看到，不少研发、出海企业从业者驻足展台，与工作人员洽谈合作。
-老牌华文游戏厂商智冠集团今年的展区设于BTOB的W5馆。据悉，智冠集团是深耕华文数字娱乐多年的综合服务商，旗下拥有MyCard支付平台，自研《吞食天地》《飘流幻境》《武林群侠传》《炎龙骑士团》等经典游戏IP。本届ChinaJoy，智冠进驻BTOB商务展区，以“AI赋能一站式解决方案”为参展主题，呼应大会“与AI同游”主旨，展区同步陈列《吞食天地》《飘流幻境》IP内容，同时开放IP授权洽谈。
-飞书深诺在W4馆设立的科幻双层展台推出出海营销智能系统Marvy2.0。据悉，当前游戏出海增长遇阻：2025年全球手游规模823亿美元，下载量连续下滑，获客成本上涨三成，国内厂商投放支出占全球35%，传统粗放投放模式难以为继。Marvy2.0是覆盖市场洞察、创意制作、广告投放、用户运营、合规审核的全链路AI系统，依托海量行业数据，显著压缩市场调研、素材生产、达人对接周期；配套AIWhatsApp运营工具，实现玩家全生命周期精细化运营。现场多家海外流量平台开展分享，品牌透露2026年四季度将上线轻量化MarvyLite，降低中小厂商使用门槛。
-值得一提的是，继2025年首次设立香港展区并取得热烈反响后，今年香港展区再度亮相ChinaJoy。在香港特别行政区政府文化体育及旅游局辖下文创产业发展处的资助下，香港游戏开发联盟（GameDEVA）将带领18家香港游戏企业参展，集中展示了《凉茶王》等18个潜力十足的原创游戏IP。据悉，展会期间，联盟还组织考察团拜访上海头部游戏企业，推动香港与内地游戏产业的深度交流与合作。
-实际上，开展第二日展会产业分层明显。C区这边面向普通玩家，主打国风、沉浸式线下体验，还有多设备云游戏，说白了就是怎么让玩家更容易上手、玩得更爽。B区那边完全是另一个画风，基本围着AI转——游戏出海怎么增收、工业化制作怎么落地、版权风险怎么管控，都给出一整套方案，帮行业在存量市场里省成本、提效率。
-连续逛了两天下来，不管是游戏主机大力扶持国产单机，老牌厂商把IP做成线下实景，云游戏不再被硬件卡脖子，还是B端用AI重新优化出海和整套研发流程——都能看出一个明显的变化：游戏行业不再只想着把盘子做大了。一边用国风、非遗这些传统文化给游戏内容加料，另一边把AI塞进制宣运全流程，省钱又提效。
-今年的ChinaJoy还有两天，后面还有不少行业交流会、新品签约仪式，更多新技术和跨界合作的消息也会陆续放出来。
-采写：南都N视频记者 石力</t>
+          <t>&lt;p&gt;　　8月10日，游戏科学联合创始人、《黑神话》系列美术总监杨奇在社交平台回应网友提问，明确新作《黑神话：钟馗》在设计、游戏资产制作阶段将全面避开AIGC工具，团队选择纯人工“手搓”创作，拒绝依靠AI压缩开发周期。&lt;/p&gt;
+&lt;p&gt;　　此次对话源于杨奇分享观影感悟，他发文盛赞诺兰新片《奥德赛》，称其为史诗电影创作标杆，从中收获大量创作启发。有网友在评论区提问，当下成熟的生成式AI能否大幅加快《黑神话：钟馗》研发进度、缩短上线等待时间。对此杨奇作出回应，称并非抵触AI技术，而是现阶段核心创作环节选择远离AIGC。&lt;/p&gt;
+&lt;p&gt;　　杨奇以诺兰的创作逻辑佐证自身理念：如今数字影视、3D后期技术迭代飞速，不少从业者追逐新式工具，诺兰却反向选用传统胶片技术，依旧打造出口碑顶尖的史诗作品。在他看来，技术风口不存在必须追赶的“末班车”，团队不必急于拥抱AI提速，新技术未来有充足时间尝试，新作开发不必仓促赶工。&lt;/p&gt;
+&lt;p&gt;　　这一选择依托《黑神话：悟空》数千万份的累计销量、海外占比超50%的市场底气。该系列主打东方神话与写实国风美术，手绘、手工建模是把控作品气质、传递东方美学的核心。而AIGC素材普遍存在细节粗糙、风格同质化、缺少人文情绪等问题，与黑神话的精品创作定位相悖。&lt;/p&gt;
+&lt;p&gt;　　这也是精品厂商的普遍选择。本届ChinaJoy上，多家开发商表示，AI仅用于研发原型的快速方案验证，最终上线的核心美术资产均以人工打磨为主。&lt;/p&gt;
+&lt;p&gt;　　8月1日，盛趣游戏副总裁谭雁峰在《永恒之塔2》国服官宣后的采访活动中介绍，公司三年前搭建完整AI研发体系，设立专项部门、自研全岗位AI工具平台，覆盖游戏研发运营全链路。数据显示，AI将美术生产效率提升80%以上，代码检测与漏洞排查周期从数月压缩至单日，同时企业通过产业投资、算力共建持续夯实AI落地能力。&lt;/p&gt;
+&lt;p&gt;　　谭雁峰表示，AI的核心价值是压缩研发试错成本、缩短迭代周期。以往新玩法验证流程繁琐、周期漫长，如今AI可快速生成多套差异化方案，团队仅需筛选优质方案落地测试，研发效率大幅提升。但他明确否定“AI速成3A游戏”的误区，指出AI仅能产出标准化素材，无法完成世界观搭建、剧情打磨、核心玩法设计等核心创作工作。&lt;/p&gt;
+&lt;p&gt;　　在谭雁峰看来，国风游戏的独特风格与人文内核，依托创作者的审美积淀与思想表达，无法靠堆砌传统元素、AI批量生成实现。据他介绍，盛趣积极探索AI原生玩法，通过AI-NPC、轻量化UGC编辑器降低玩家创作门槛，但这类应用仅用于激活玩家共创生态，绝不替代官方核心内容创作。&lt;/p&gt;
+&lt;p&gt;　　另据了解，人才培养层面，盛趣的核心观点在于——AI将替代重复性流水线岗位，但无法取代从业者的内容判断力与原创思维。谭雁峰认为，未来游戏行业核心人才，将聚焦“兼具原创能力与AI使用能力”的复合型从业者。&lt;/p&gt;
+&lt;p&gt;　　相较于游戏科学的“主动避退”，3D引擎供应商Unity中国选择“深度拥抱、理性约束”的中间路线。7月28日，Unity中国总裁张俊波在团结引擎2.0发布会后表示，新版引擎核心升级为全维度适配AI生态，同时上线自研两年的AIAgent工具Codely，现已面向开发者开放，成为团队核心迭代产品。&lt;/p&gt;
+&lt;p&gt;　　尽管深耕AI落地，张俊波坚决反对“一句话生成游戏”的行业噱头。他认为，该模式的核心创意归属AI，无法赋能开发者创作。AI编码适配轻量化休闲游戏，但长线运营的重度游戏若完全依赖AI编码，将产生极高的后续维护成本。&lt;/p&gt;
+&lt;p&gt;　　张俊波还披露了内部AI应用痛点，为行业敲响警钟：半数员工依托命令行生成AI代码，无人熟知代码细节，出现漏洞后难以溯源排查。他坦言，AI编码效率虽高，但漏洞修复、堆栈调试成本远高于人工开发，甚至要求员工将AI生成代码手动重写后再提交，规避技术风险。&lt;/p&gt;
+&lt;p&gt;　　据张俊波介绍，在技术布局层面，Unity中国优先落地游戏垂类专用模型，摒弃通用大模型的冗余弊端。通用大模型数据繁杂、知识滞后重复，而其与清华合作研发的垂类Agent，可凭借小参数实现通用超大模型的引擎适配效果，可控性与专业性更强。&lt;/p&gt;
+&lt;p&gt;　　针对“AI颠覆引擎行业”的言论，张俊波认为引擎市场体量有限，AI的核心目标是革新游戏创作模式，反而会拓宽引擎的行业应用边界。&lt;/p&gt;
+&lt;p&gt;　　采写：南都N视频记者 石力&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -651,7 +644,7 @@
       <c r="A7" s="2" t="inlineStr"/>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>2026年上半年亚马逊广告服务出海游戏客户数较2024年同期增长近90%；2026年上半年中国电竞产业收入增长2.78%丨游戏早参</t>
+          <t>7月共38 家中国游戏厂商占全球百强近四成收入</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -661,19 +654,13 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>每经记者：张梓桐    每经编辑：陈旭
-丨2026年8月4日 星期二丨
-NO.1 2026年上半年亚马逊广告服务出海游戏客户数较2024年同期增长近90%
-8月3日，ChinaJoy期间，亚马逊中国副总裁，亚马逊广告中国及韩国大客户拓展负责人杨彤透露，今年上半年，亚马逊广告服务的出海游戏客户数量较2024年同期增长了近90%，涵盖了腾讯、网易、米哈游等国内手游大厂以及鹰角网络、西山居等原生PC/主机精品游戏厂商。
-点评：全球PC/主机核心玩家以18~34岁的Z世代年轻群体为主，他们越来越依赖直播内容、主播试玩与社区口碑来发现和决策游戏，而非传统买量广告或商店榜单。因此，越来越多出海游戏品牌正从“单纯买量”转向社区营销，并更注重核心玩家的真实参与和互动，以建立良好口碑。
-NO.2 2026年上半年中国电竞产业收入同比增长2.78%
-根据《2026年1~6月中国电子竞技产业报告》，2026年上半年，我国电子竞技产业收入131.15亿元，同比增长2.78%。直播收入依然占比最高，达80.43%。截至2026年6月，我国电子竞技用户规模4.95亿，同比增长0.55%。
-点评：增速降温缓解市场对行业过热、政策收紧的担忧，估值泡沫持续出清，板块定价更趋理性。同时行业收入结构持续优化，摆脱单一流量依赖，产业链盈利韧性显著增强。
-NO.3 《闪耀暖暖》7周年内容迭代出圈
-作为国内3D换装细分赛道标杆产品，叠纸游戏旗下《闪耀暖暖》上线7周年持续通过高规格内容迭代激活用户活力。本次7周年前瞻直播推出“荒芜恩典”“虹色诗”两套全新闪耀套装，相关内容在玩家社区引发高热度讨论。
-点评：从资本市场来看，本次迭代印证女性向、细分长线游戏的抗周期属性。在行业新品不确定性加剧、买量成本走高背景下，头部长青精品通过版本迭代、内容创新即可实现用户回流与口碑发酵，具备稳定现金流优势。
-免责声明：本文内容与数据仅供参考，不构成投资建议，使用前请核实。据此操作，风险自担。
-每日经济新闻</t>
+          <t>&lt;p&gt;　　北京商报讯（记者 卢扬 实习记者 张继文）8月13日，Sensor Tower 商店情报平台显示，2026年7月共38个中国厂商入围全球手游发行商收入榜 TOP 100，合计吸金23亿美元，占本期全球 TOP 100手游发行商收入42.6%。&lt;/p&gt;
+&lt;p&gt;　　7月中国手游 Top 5发行商收入均过亿（美元），腾讯、网易、米哈游实现两位数增长，其中米哈游收入环比大增71%，增幅位居 Top 30发行商前列；沐瞳科技、心动网络、Modo Global等多家发行商在暑期内容与活动推动下实现收入显著增长。&lt;/p&gt;
+&lt;p&gt;　　腾讯持续蝉联7月全球手游发行商收入榜冠军。稳健表现主要得益于《王者荣耀》、《和平精英》及《PUBG MOBILE（绝地求生）》等头部主力的全线增长。其中，《王者荣耀》7月收入环比大涨35%，全球吸金约2亿美元。&lt;/p&gt;
+&lt;p&gt;　　而网易位于中国手游发行商排行榜第4名。旗下《蛋仔派对》7月收入表现突出，成为网易旗下手游收入冠军。Sensor Tower 数据显示，截至7月31日，该作全球累计收入已超过7.7亿美元。&lt;/p&gt;
+&lt;p&gt;　　值得注意的是，《我的花园世界》成为 Modo Global 7月收入增长的核心驱动力，Sensor Tower 数据显示，游戏全球单月收入创新高，突破1600万美元。此外，7月下旬国际服开始覆盖欧洲更多市场，德国、英国、法国、奥地利等地区陆续上线，为海外业务带来新的市场增量。&lt;/p&gt;
+&lt;p&gt;　　榜单之外，入围全球收入 TOP 100的中国手游发行商依次是：游卡网络、鹰角网络、SparkGame、露珠游戏、Tap4Fun、益世界、游酷盛世和 BeHeFun Games 共38家厂商。&lt;/p&gt;
+&lt;p&gt;　　同时，受暑期档拉动，本期中国App Store手游收入榜呈现出明显的普涨趋势，TOP 20中多达16款产品实现了月度收入环比增长。头部格局依然稳固，腾讯旗下《王者荣耀》、《和平精英》、《三角洲行动》和点点互动《无尽冬日》继续包揽榜单前四。整体来看，腾讯系产品共占据了10个席位，占据半壁江山。榜单中腰部的交替更为活跃，米哈游旗下《绝区零》和《崩坏：星穹铁道》，以及《英雄联盟手游》、《第五人格》、《FC足球世界-杯赛》等多款不同品类的产品凭借暑期活动节点重返 TOP 20，进一步丰富了当月榜单结构。&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -681,7 +668,7 @@
       <c r="A8" s="2" t="inlineStr"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>巴黎电竞世界杯数据连创新高，欧洲手游电竞迎来增长窗口期</t>
+          <t>预约超200万、首日登顶免费榜！《赘婿》开门红引爆阅文下半年IP游戏生态</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -691,25 +678,18 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>扬子晚报网8月1日讯（记者 姜天圣）8月1日，2026年电竞世界杯决胜巅峰项目在法国巴黎落下帷幕。本次赛事中，中国俱乐部在男子赛道和女子赛道中均有亮眼的发挥。作为沐瞳科技研发的多人在线战术竞技手游，决胜巅峰是全球受众规模最大的移动电竞产品之一，已形成覆盖全球多赛区的成熟赛事体系。赛事期间，沐瞳科技赛事生态负责人吴健荣接受采访时表示，随着当地从小接触手游的新生代创造，欧洲移动电竞规模正在稳健增长。
-本届电竞世俱杯由原定举办地沙特利雅得临时迁至巴黎，相关决策在赛事启动前2月才最终敲定。吴健荣认为，欧洲市场对提升电竞世俱杯的国际影响力具有正向价值；本次赛事能顺利举办也得益于法国完善的电竞产业基础与政策支持。
-吴健荣表示，当前欧洲移动端游戏用户规模正以每年10%左右的速度自然增长，其中东欧地区增长势头尤为突出。随着原生接触手游的新生代用户成长，欧洲电竞市场长期以来以主机、PC端为主的格局正在逐步改变，移动端竞技赛事的受众基础持续扩大。据介绍，沐瞳科技当前将土耳其作为布局欧亚市场的核心踏板，依托当地成熟的电竞生态与战队竞技实力，逐步辐射欧洲全域。2025年以来，沐瞳通过落地世界赛、开展当地特色主题运营等动作完成用户拉新，土耳其本土战队已稳居MLBB国际赛八强行列，成为区域市场的核心增长点。
-电竞世俱杯决胜巅峰女子项目是本届赛事体系中唯一设置的独立女子电竞赛事。吴健荣介绍，该赛事始于五年前针对东南亚女性用户群体的一次探索。彼时团队发现东南亚女性玩家基数庞大，但缺乏专属竞技舞台，遂以12国线上邀请赛的形式试水，赛事关注度与商业反馈均超出预期。随后赛事逐步升级为线下赛并纳入电竞世界杯体系，今年正式完成从“邀请制”到“选拔制”的品牌升级，全球各赛区均已建立预选赛晋级通道，女子电竞生态从区域探索走向全球规范化发展。
-吴健荣直言“长期稳定投入是俱乐部稳定的核心”。随着全球各赛区对决胜巅峰女子项目持续加码，强弱差距正在快速缩小：本届赛事埃及战队首次闯入八强，中国女子战队成功晋级淘汰赛，均创下历史最佳战绩。他坦言，当前仍有部分俱乐部持短期试水心态，但长期深耕的战队数量已从三年前的不足5支增长至7至8支，生态正向好发展。
-他同时提到，近年来多家国际知名俱乐部相继入局决胜巅峰女子赛道，正是行业对女子电竞商业价值认可度提升的信号。目前头部女子战队已探索出赛事奖金、主播运营、品牌代言相结合的多元营收模式，女子电竞的商业化路径正逐步清晰。
-Esports Charts数据显示，2026电竞世俱杯决胜巅峰男子项目全球季中杯峰值在线观看人数（PCV）突破201万，创造历史。电竞世俱杯决胜巅峰女子项目同样刷新赛事纪录，PCV突破56万，成为该赛事史上收视最高的一届。</t>
+          <t>&lt;p&gt;　　在近日召开的业绩发布会上，阅文集团对外披露了下半年游戏业务的重磅排期与战略布局。随着旗下优质网文IP深度融入游戏生态，多款覆盖不同赛道、由行业头部厂商精细打造的重磅游戏正加速落地，展现出极强的IP变现能力与商业延展性。&lt;/p&gt;
+&lt;p&gt;　　阅文集团透露下半年的代表性项目包括：1）由三七互娱发行的MMO《斗破苍穹：斗帝之路》已于2026年7月29日进行公测；2）《赘婿》模拟经营手游，已于8月12日进行全平台公测；3）由快手研发的UE5旗舰MMO《诡秘之主》，定于2026年8月21日全平台公测，目前预约已全面开放。&lt;/p&gt;
+&lt;p&gt;　　据悉，《赘婿》手游预约量轻松突破200万大关。上线首日即展现出爆款潜质，一举登顶 App Store免费榜及各大主流安卓渠道免费榜榜首，留存与玩家口碑表现亮眼。&lt;/p&gt;
+&lt;p&gt;　　行业分析人士指出，《赘婿》手游的开门红不仅为阅文集团下半年的业绩表现打下了坚实基础，更验证了阅文从“文字IP”向“高品质游戏”跨界赋能的成熟链路。随着后续《诡秘之主》等超级IP游戏的陆续上线，阅文在“IP+游戏”生态领域的收益有望迎来新一轮爆发。&lt;/p&gt;</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>https://inews.gtimg.com/om_bt/OEiGinXlfEnKvJ7HUMzLqCh04RgrAa3FEYsLPC6wxFKqcAA/641</t>
-        </is>
-      </c>
+      <c r="A9" s="2" t="inlineStr"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>决胜毫秒间，AI构未来：骁龙持续推动移动电竞与游戏创作创新</t>
+          <t>自费675元只为博君一笑，5个高中生做出了98%好评的免费游戏</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -719,44 +699,47 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7月30日，2026骁龙游戏技术赏在上海启幕。高通技术公司高级副总裁兼手机业务总经理Chris Patrick与高通公司全球副总裁侯明娟携手iQOO、和平精英、一加、完美世界、红魔、机核、TapTap和独立游戏制作人等生态伙伴，全方位展现骁龙凭借移动技术创新、生态协同合作以及对AI能力的深度探索，持续重塑从职业移动电竞赛场到大众日常游玩的游戏体验，同时不断开辟游戏创作的全新可能。
-移动游戏已成为中国最主流的娱乐方式之一。侯明娟在开场致辞中特别提到：“移动电竞赛场是对骁龙游戏技术能力要求最严苛的试练场。骁龙的技术优势，从来不只是体现在硬核参数上，而是体现在那些真正决定胜负的瞬间——每一波关键团战，每一场绝地翻盘。”
-高通公司全球副总裁侯明娟
-制胜时刻：第五代骁龙8至尊版为巅峰而生
-凭借全球最快的移动CPU、行业领先的GPU架构和超低时延连接能力，第五代骁龙8至尊版成为了王者荣耀职业联赛、和平精英职业联赛、穿越火线枪战王者职业联赛、QQ飞车手游S联赛以及英雄联盟手游超级联赛——五大热门移动电竞赛事的官方指定芯片，持续为顶级移动电竞赛事提供平台支持。
-高通技术公司高级副总裁兼手机业务总经理Chris Patrick表示：“从顶级电竞赛事，到全球性能要求最高的移动游戏，骁龙始终在幕后为每一个决定胜负的瞬间提供支持。骁龙不仅提供行业领先的性能表现，也在不断拓展整个移动游戏生态的可能性。”
-高通技术公司高级副总裁兼手机业务总经理Chris Patrick
-以iQOO 15王者荣耀职业联赛官方比赛用机认证测试为例，通过总时长9020分钟的局内累计测试，从持久稳定性能、触控时延和连接三大重要性能维度，对搭载第五代骁龙8至尊版的iQOO 15进行评估，其在帧率稳定性、触控延时、网络平均延时、平均FPS、平均每分钟耗电量、平均每分钟温度差、BO7最高温度等七大细分项目中，全面领先比赛用机通过标准。
-满足顶级赛事高标准体验的背后，是高通与iQOO长达八年的深度携手。正如iQOO产品副总裁罗锋所言，从旗舰性能的探索，到专业电竞赛事的联合打磨，再到用户体验的持续突破，双方的合作关系已经深入到产品定义的每一个细节。
-从赛场到玩家：骁龙以技术创新定义顶级游戏体验
-依托第五代骁龙8至尊版强劲的硬件实力，游戏体验优化技术套件——骁龙至尊游戏（Snapdragon Elite Gaming）同步迭代升级。软硬结合，带来一系列特性，有效提升高帧稳定性、高清画质表现等。再联合手机厂商、游戏工作室进行优化落地，让广大手游玩家无论在竞技、亦或非竞技类游戏中，都能畅享顶级游戏体验。
-超高帧游戏
-流畅帧率是构筑沉浸式移动游戏体验的重要创新方向。长期以来，骁龙持续推动移动游戏平台向更高帧率演进。行业每一次向更高帧率演进突破的关键节点，骁龙始终先行一步，率先完成技术落地。以165fps为例，骁龙领先行业9个月支持超高帧游戏。
-以《和平精英》为例，这款游戏本质上是一场关于“极限”的较量。上百名玩家的实时博弈、载具的高速追逐、枪战中毫秒级的判定精度，对移动设备的算力、图形渲染能力以及功耗控制，提出了近乎苛刻的要求。和平精英策划总监、电竞中心总监黄鑫龙特别强调，正因如此，《和平精英》与骁龙始终保持紧密合作，从帧率表现到图形渲染，一起推高玩家游戏体验的上限。
-芯片层的技术支持、游戏内的专项调校缺一不可；而作为游戏载体的手机，也必须拥有与之匹配的综合实力，才能将流畅超高帧体验送达每位玩家手中。搭载第五代骁龙8至尊版的一加15首发165fps超高帧技术，引领行业进入超高帧游戏新时代。一加中国区品牌总经理刘宝有表示：“正因为对高帧率体验和触控体验的极致追求，‘射击游戏用一加’越来越成为共识。能够取得这样的成绩，得益于我们和骁龙的深度合作，释放出骁龙移动平台的性能上限，实现了更强的满帧表现。”
-Adreno独立高速显存
-随着更多主机级游戏登陆移动端，图形保真度和世界复杂度实现突破的同时，新的瓶颈随之产生。正是基于这一洞察，高通在第五代骁龙8至尊版上推出Adreno独立高速显存，通过面向图形工作负载优化内存路径，能够有效降低时延并提高内存效率。这一架构使Adreno GPU能够以更低功耗处理更大的数据集、纹理和几何体，让开发者可以在玩家喜爱的游戏中进一步提升视觉保真度，同时保持流畅的游戏体验。
-Adreno图像运动引擎和骁龙游戏超分
-Adreno图像运动引擎与骁龙游戏超分是骁龙至尊游戏中，对视觉渲染与动态响应优化显著的两大特性。作为一款采用虚幻5开发的游戏，《异环》高密度的城市建筑、高速移动的载具，以及激烈战斗，给移动终端带来了前所未有的压力。上述两项骁龙至尊游戏特性的落地，助力《异环》解决了移动端带宽、渲染压力以及功耗之间的矛盾。完美世界技术中台负责人药师表示：“骁龙提供的不只是单纯的硬件芯片性能，更包含了图形优化技术、性能分析工具以及全方位的平台级专家支持。正是在这种深厚的技术积淀和深度的合作下，我们才有底气发起下一场跨时代的技术挑战——去攻克《异环》这款次世代二次元都市开放游戏移动端性能问题。”
-此外，第五代骁龙8至尊版不仅赋能手机，还发力游戏平板等丰富多样的高性能游戏终端品类。其中，红魔长期深耕电竞设备领域，在手机、平板、音频外设等领域携手骁龙，不断将极致的电竞体验延伸到用户的生活方式当中。努比亚技术有限公司常务副总裁余航表示：“红魔和骁龙强强联手，就是强悍性能的代名词。骁龙为红魔在游戏体验上提供了更大的发挥空间，从而让红魔能够不断为用户带来更加极致的游戏体验。”
-AI技术开辟游戏体验与创作全新可能
-AI是当前游戏时代的标志性技术之一。骁龙已开始借助AI实现游戏体验的进一步跃升。本次骁龙游戏技术赏期间，Chris Patrick预告了下一代骁龙8系旗舰移动平台的全新游戏特性——Qualcomm Adreno Neural Fusion，这一AI驱动的解决方案融合神经网络处理、超级分辨率和帧生成等技术，旨在变革游戏场景渲染和融合方式，帮助开发者在移动终端上实现更高品质、更具沉浸感的视觉体验。预计将在今年9月举行的骁龙峰会上正式发布。
-不仅是硬核游戏技术的迭代焕新，AI对游戏的影响也反映在游戏创作方式的深刻变革中。在以“21天，看见游戏如何被创造”为主题的圆桌对话中，侯明娟坦言：“AI正在改变游戏产业。它让创意能够更快变成产品，让个人开发者拥有过去只有大型团队才具备的生产力，也让游戏开始从预设内容走向动态生成、实时交互。对于骁龙而言，我们相信技术最大的价值，不是替代创造力，而是释放创造力。我们希望通过先进的AI和计算能力，让开发者能够更专注于创意本身。”
-从左到右依次为：高通公司全球副总裁侯明娟、机核网主编白广大、TapTap制造产品负责人天一、《积案拂尘》开发者简律纯
-骁龙在移动游戏领域的合作伙伴生态，已覆盖产业链的每一个环节。背后贯穿的是同一条逻辑：以骁龙平台为纽带，让创新技术和AI能力触达每一个需要它的人。这不仅是骁龙对游戏行业的长期承诺，也是其持续投入的方向。
-ChinaJoy期间，骁龙将继续携手广大生态合作伙伴，在骁龙主题馆以“集你所爱”为主题，从最丰富的硬件展示，到最沉浸的互动科技，把AI真正带进了游戏娱乐和创作体验中，让每一种热爱，被看见、被放大、被实现。届时，骁龙京东超级品类日也将再度来袭，搭载骁龙平台的手机、AI PC、平板电脑、XR设备、智能手表、耳机等全品类终端将集中亮相。（心月）</t>
+          <t>&lt;p&gt;　　这大概是2026年8月初中文互联网上最离奇的一幕。&lt;/p&gt;
+&lt;p&gt;　　8月1日，一款名字长得像开玩笑的游戏悄悄出现在Steam新品列表里。《完蛋！我被男同学包围了》。看到这标题的第一反应，估计和大部分人一样：又来？自从2023年《完蛋！我被美女包围了》爆火之后，各种&amp;quot;完蛋体&amp;quot;跟风作就没消停过。一个蹭热度的低成本山寨货，名字都懒得原创，能有什么花头？&lt;/p&gt;
+&lt;p&gt;　　但事情的发展出乎所有人意料。&lt;/p&gt;
+&lt;p&gt;　　上线不到一周，游戏收获超过2000条Steam玩家评价，好评率稳定在98%，稳稳站上&amp;quot;好评如潮&amp;quot;的档位。粗略估计有差不多10万玩家下载了这款游戏。B站知名UP主的二创视频播放量短短两天突破550万（目前已涨到800万），抖音相关话题播放量超过5500万，甚至一度冲上热搜。&lt;/p&gt;
+&lt;p&gt;　　更颠覆认知的是开发团队的身份，不是什么独立工作室，也不是手握资源的中小厂商，而是一群还在江西省南昌市读高中的少年。&lt;/p&gt;
+&lt;p&gt;　　675块启动的“草台班子”&lt;/p&gt;
+&lt;p&gt;　　这群高中生给自己起了个名字叫“游戏学社”。顺着游戏画面边角处一闪而过的&amp;quot;赣A&amp;quot;车牌，以及校服胸口印着的&amp;quot;LS&amp;quot;缩写，线索最终指向了南昌雷式中学。游戏里的教室、操场、食堂，全都是这所学校里再真实不过的场景。&lt;/p&gt;
+&lt;p&gt;　　五个人的分工意外的清晰：编程与开发由团队中的一位伙伴负责，剧情架构与编剧主要由&amp;quot;坦克&amp;quot;主导，而主创&amp;quot;唐王&amp;quot;本人承担了演员和角色的本色演出。&lt;/p&gt;
+&lt;p&gt;　　这群高中生为了把游戏送上Steam，自掏腰包凑了675元人民币的&amp;quot;发行费&amp;quot;。游戏全程免费下载、不含任何内购。不为钱、不图利，纯粹就想让更多人&amp;quot;品尝&amp;quot;他们的作品。&lt;/p&gt;
+&lt;p&gt;　　更让人意外的是，他们早在2025年10月就在B站公布过一款游戏。做一款整活儿游戏，这群少年是认真筹谋许久的。&lt;/p&gt;
+&lt;p&gt;　　抽象到极致，反而成了核心竞争力&lt;/p&gt;
+&lt;p&gt;　　点开游戏，最直接的第一印象就是一个字：糙。&lt;/p&gt;
+&lt;p&gt;　　从UI到成片画面，离&amp;quot;精良&amp;quot;还有老大一段距离。UI风格甚至都不统一，部分地方文字&amp;quot;怼穿&amp;quot;了文本框都没有做适配。画面基本就是PPT加上少量视频，大部分场景都&amp;quot;假&amp;quot;得离谱，现实中大概率找不到会做那种表情、摆那种姿势、说那种对白的人。&lt;/p&gt;
+&lt;p&gt;　　剧情也谈不上什么精细打磨。玩家扮演一个高中小透明，突然被五个性格各异的男同学包围：唐王，班上最活泼的；白子，最好相处的前桌；钩哥，体育健将；坦克，乐于助人的热心男孩；还有一个叫&amp;quot;**&amp;quot;的邪恶校霸。靠选项推进剧情，每个角色都有专属支线，能触发多个不同结局。后来的&amp;quot;研学篇&amp;quot;更是彻底放飞，加入了核爆60秒、找伪人、躲猫猫等玩法。&lt;/p&gt;
+&lt;p&gt;　　制作组像是在&amp;quot;明着演&amp;quot;，甚至有点&amp;quot;用力过猛&amp;quot;的嫌疑。但偏偏是这种粗糙，成了它的核心竞争力。&lt;/p&gt;
+&lt;p&gt;　　对比一下就有意思了。2024年有款叫《糟糕！他们太爱我了怎么办？》的真人乙游，想做女性向恋爱互动，结果因为颜值、演技、剧本都没撑起来，好评率只有59%左右。同样是&amp;quot;性转版&amp;quot;，《糟糕》想认真谈恋爱，翻车了。而《完蛋！我被男同学包围了》走了完全相反的路，压根没想认真，靠&amp;quot;抽象&amp;quot;杀疯了。&lt;/p&gt;
+&lt;p&gt;　　游戏简介里写得明明白白：&amp;quot;本游戏所有剧情内容都为开心和搞笑服务！！！一定要玩的开心呀！&amp;quot;&lt;/p&gt;
+&lt;p&gt;　　一条高赞Steam评论精准概括了它的定位：&amp;quot;神作，这游戏已经抽象到了好玩的地步，别的游戏我都希望打折减价，但是这游戏我反而希望卖点钱，哪怕一块钱也好，这样我就可以送好友了。&amp;quot;&lt;/p&gt;
+&lt;p&gt;　　一群少年宴请了离青春越来越远的我们&lt;/p&gt;
+&lt;p&gt;　　但笑完之后，评论区出现了另一种声音。&lt;/p&gt;
+&lt;p&gt;　　五个高中生，凑了675块钱，做了一个免费游戏，拿下了98%的好评率。&lt;/p&gt;
+&lt;p&gt;　　这件事本身已经足够荒诞。但更荒诞的是，那些在评论区打出“笑着笑着就哭了”的成年玩家，他们哭的不是游戏，而是从游戏里看到了自己。&lt;/p&gt;
+&lt;p&gt;　　他们怀念的，从来不只是学生时代本身。他们怀念的是那个还没学会用“有没有用”来丈量一切事物的自己——那个还能为一件毫无实际收益的事情废寝忘食、为一次完全没有理由的快乐全力以赴的自己。&lt;/p&gt;
+&lt;p&gt;　　加缪在《西西弗神话》里写，西西弗被诸神惩罚，永无止境地把巨石推上山顶，而石头每次都在抵达山顶前滚落。诸神认为没有比徒劳无功且没有希望的劳动更可怕的惩罚了。而加缪说：我们必须想象西西弗是幸福的。因为西西弗在推石头的过程中，已经为自己创造了一种意义——即使在荒诞的命运面前，人依然可以通过自己的选择和行动，找到属于自己的幸福。&lt;/p&gt;
+&lt;p&gt;　　成年人每天推的石头，比西西弗的还重。房贷、KPI、人际关系、社会期待，每一块都刻着“必须”和“应该”几个字。而五个高中生，在一间不知名的教室里，做了一个免费游戏，然后把它扔进了这个巨大的、充满算计的世界里。他们没有改变这个世界，但他们至少证明了一件事：在这个被效率和目的统治的时代，还有人愿意为了“好玩”本身去浪费时间。&lt;/p&gt;
+&lt;p&gt;　　这种“浪费时间的能力”，在成年人的世界里几乎失传了。它被遗忘在某个课间的走廊里，被遗落在某个暑假的操场上，被封存在某次毕业的合影中。直到有人用一款粗糙的游戏把它重新挖出来，埋得不深，也就隔着一整个青春期那么远。&lt;/p&gt;
+&lt;p&gt;　　当然，这种状态注定无法持续。开学之后，他们照样要面对作业、考试、升学。那些在评论区感动过的成年人，第二天照样要挤地铁、赶deadline、应付生活里的一地鸡毛。这款游戏不会改变任何人的命运，五个高中生也不会永远停留在那个可以为了“好玩”凑出675块钱的夏天。&lt;/p&gt;
+&lt;p&gt;　　但恰恰是因为它短暂、脆弱、不可持续，才显得珍贵。成年人之所以会被它打动，正是因为所有人都清楚——那样的日子已经回不去了，而他们用一款游戏替所有人保存了一点残片。一个尚未被彻底规训的少年时代，替早已学会顺从的成年人，重新证明了一次纯粹的快乐是可能的。&lt;/p&gt;
+&lt;p&gt;　　哪怕只有几个小时，哪怕只是一场游戏。&lt;/p&gt;</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>https://inews.gtimg.com/om_bt/Os_5AhM4QxRRLk2hKyzEgH67RvG-WSKfPFDALYoQPJdnAAA/641</t>
+          <t>https://inews.gtimg.com/om_bt/OS8nCUGt1hzKPij1sZPKYtrdL-5cmPvyRpcDpvLef6Y-IAA/1000</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>高通第七次打造 ChinaJoy 骁龙主题馆，“集你所爱”呈现前沿数字娱乐盛宴</t>
+          <t>甄子丹加盟！国产3A游戏《影之刃零》公开11分钟实机预告</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -766,20 +749,28 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>7 月 31 日，2026 年中国国际数码互动娱乐展览会（ChinaJoy）在上海新国际博览中心正式开幕。高通（中国）围绕 “集你所爱” 主题，第七次打造 “骁龙主题馆”。展会首日，高通公司中国区董事长孟樸和全球副总裁侯明娟携手中国电信、中国移动、小米、iQOO、荣耀、联想、京东、完美世界等超 140 家行业合作伙伴代表出席了开馆仪式，共同呈现涵盖 AI 创新、顶级游戏、沉浸式 XR 与多终端生态融合的数字娱乐盛宴。
-在面积超过 1000 平米的骁龙展台内，高通集中展示了 300 多款设备、200 多项技术演示以及 40 余款移动端及 PC 游戏。在第五代骁龙 8 至尊版移动平台的卓越性能、能效和端侧 AI 处理能力赋能下，骁龙至尊游戏区集结了来自腾讯、网易、鹰角、库洛及完美世界等厂商的 14 款头部游戏大作。
-其中，《王者荣耀》通过骁龙自适应游戏画质技术保障了复杂团战的稳帧表现，并依托 Hexagon NPU 打造了端侧离线语音识别方案；《和平精英》实现了 165fps 超高帧满帧体验；《崩坏：星穹铁道》通过 Adreno 独立高速显存技术大幅优化了功耗；基于虚幻引擎 5 的《异环》则通过骁龙超级分辨率 2.0 等多项特性提升了画质与帧率。同时，《遗忘之海》、《怪物猎人：旅人》及《王者万象棋》等新作也在现场开放体验。
-在 XR 体验方面，“骁龙 XR 奇幻之旅” 联动国创 IP《凡人修仙传》，借助 5G-A 万兆级网络、双目 16K 超高清视效渲染及定制动感座舱，为玩家重现原作关键战役。此外，基于第二代骁龙 XR2 平台赋能的 PICO 4 Ultra，玩家可沉浸式体验与《和平精英》光子鸡 IP 深度定制的雪地大作战。现场还汇集了来自雷鸟创新、千问、Rokid、vivo、小米等品牌的十余款 XR 设备。
-今年的展馆特别增设了 “骁龙 AI 造梦场” 展区，玩家可在搭载第五代骁龙 8 至尊版的设备上实时生成专属 3D 赛博城市数字分身，并利用 TapTap 制造等创作工具感受跨端游戏创作体验。同时，由 Rokid AR Studio、国内首秀的第二代智能戒指与骁龙 PC 组成的跨终端系统，支持玩家通过手势和语音与 AI 萌宠进行实时互动。现场还展示了端侧 AI 游戏助手及 3 款由 AI 大语言模型驱动的游戏作品。
-在终端生态展示上，“骁友装备库” 集结了覆盖十大品类的超 100 款最新设备，其中包括荣耀 Robot Phone、千问 AI 眼镜、第二代智能戒指等创新 AI 终端。作为五大头部移动电竞赛事的官方指定芯片，骁龙还在现场设置了 “骁龙冠军时刻” 打卡区供玩家体验。此外，高通联合京东开启了 “骁龙京东超级品类日”，打通线上线下联动福利，全面推动下一代数字娱乐体验的加速普及。</t>
+          <t>&lt;p&gt;　　新京报讯（记者刘臻）8月12日早上10:00，国产武侠3A游戏《影之刃零》正式开启全平台预售，11分钟实机预告公开。预告中介绍，甄子丹自2023年起担任《影之刃零》监制，并为“暗魔天堡之主：魔渊”进行面捕及动捕，该形象也首次在视频的结尾亮相。&lt;/p&gt;
+&lt;p&gt;　　目前，该游戏已在Steam等各大平台开启预购，各平台国区统一售价：购买268元数字标准版，即可获得以下内容：提前获得饰品 — 聚宝盆（意识尘埃掉落率 +10%）；提前获得外观 — 传承（提前获得的内容也可通过游戏进程在游戏内获得）。&lt;/p&gt;
+&lt;img src="https://inews.gtimg.com/om_bt/OS8nCUGt1hzKPij1sZPKYtrdL-5cmPvyRpcDpvLef6Y-IAA/1000" alt="https://inews.gtimg.com/om_bt/OS8nCUGt1hzKPij1sZPKYtrdL-5cmPvyRpcDpvLef6Y-IAA/1000" /&gt;
+&lt;p&gt;　　甄子丹自2023年起担任《影之刃零》监制。&lt;/p&gt;
+&lt;p&gt;　　购买328元数字豪华版，即可获得以下内容：提前获得饰品 — 聚宝盆（意识尘埃掉落率 +10%）；提前获得外观 — 传承；专属豪华版外观 — 武林传说；专属豪华版外观 — 机械魔躯；游戏内美术设定特典；游戏内原声音乐特典。&lt;/p&gt;
+&lt;img src="https://inews.gtimg.com/om_bt/OchSCzdIvOPONV7l_Zpc1kPsBtyBP7YAacOD0BcQVVbIcAA/1000" alt="https://inews.gtimg.com/om_bt/OchSCzdIvOPONV7l_Zpc1kPsBtyBP7YAacOD0BcQVVbIcAA/1000" /&gt;
+&lt;p&gt;　　预购信息。&lt;/p&gt;
+&lt;p&gt;　　据悉，该作将于10月29日正式发售。&lt;/p&gt;
+&lt;p&gt;　　编辑 徐美琳&lt;/p&gt;
+&lt;p&gt;　　校对 陈荻雁&lt;/p&gt;</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr"/>
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>https://inews.gtimg.com/news_bt/OOqRM-wD84505abyWWvzPxAsG2GZlTiM09nvN-Xjcta4UAA/641</t>
+        </is>
+      </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>秒懂产业局丨从科韵路到洛杉矶，粤产游戏不卖皮肤卖文化</t>
+          <t>实力为王！“白鲨战队”加冕2026 CFPL夏季赛总冠军</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -789,38 +780,56 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>当一本创刊18年的生活月刊，选择在8月8日这天彻底撕掉旧标签，将全部版面献给游戏与二次元，这本身就是一则比演唱会更值得细品的“产业信号弹”。
-由羊城晚报报业集团主管主办的《优悦生活》杂志，在8月8日正式宣布全面改版，从传统生活消费杂志转型为游戏电竞主题刊物，成为粤港澳大湾区首份由主流媒体打造的游戏电竞主题杂志。首期《鸣潮·玄方地界版本特辑》于8月10日正式上线发售，开售后24小时全渠道销量即突破4000本。
-这本杂志的转身，恰逢《鸣潮》全球巡回演唱会上海站刚落下帷幕不久。不久前，库洛游戏在上海东方体育中心连唱三天，累计吸引约三万人次到场。唢呐、古筝、琵琶与交响乐团同台共振，威亚剑客踏竹对打，虚实融合的舞美将游戏世界完整复刻于舞台之上。
-演唱会上海站落幕，属于“致予新世界”的旅程才刚刚开始。按规划，这场全球巡演将在2026年内覆盖台北、东京、首尔、新加坡等亚洲城市。截至目前，亚洲各站门票均已售罄。10月17日，巡演将登陆美国洛杉矶孔雀剧院，完成北美首秀。从上海东方体育中心到洛杉矶孔雀剧院，一场横跨太平洋的文化远征已然启程。
-你以为这只是一场演唱会？格局小了。这背后是广东游戏产业正在上演的“换挡提速”。
-数据显示，2025年广东游戏产业总营收达2836.13亿元，同比增长8.9%，占全国市场规模高达80.85%，连续多年稳居全国首位。从企业数量来看，广东拥有27家上市游戏企业，高居全国首位。
-出海方面，2025年广东游戏出海营收达464.27亿元，同比增长9.60%；其中广州一城便贡献264亿元，占广东半壁江山以上，增速高达38.52%，领跑全国重点城市。广州全市约3200家游戏企业、超10万从业人员，形成了覆盖研发、发行、运营、出海服务等环节的完整产业链。
-坐拥如此庞大的产业体量，却长期缺少一本系统覆盖游戏创作、电竞赛事、产业深度观察的专业纸质期刊。《优悦生活》的转型，正是对这一短板的直接回应。
-在广东，过去拼买量、卷换皮的时代正在翻篇。今年5月20日，广东省印发《广东省服务贸易高质量发展三年行动计划（2026—2028年）》，明确提出到2028年全省服务贸易进出口总额超过3100亿美元。网络游戏与游戏出海被作为核心发展力量着重提及。
-文件明确支持广州、深圳建设省网络游戏出海服务中心，提供境外市场研究、运营发行等一站式服务，打造“粤产游戏出海矩阵”和“游戏企业出海联盟”，扩大广东游戏海外影响力。政策同时强调对虚拟引擎研发、游戏大模型训练、算力效率提升等底层技术的支持——着眼的不只是产品“走出去”，更是产业核心竞争力的整体提升。
-广州各区也纷纷亮出实招。黄埔区正加快布局小游戏产业基地，力争三年建成大湾区小游戏产业新高地。南方智媒大厦已入驻相关企业40余家，未来预计集聚150家，年产值有望突破50亿元。政策扶持更是真金白银：精品小游戏项目最高奖励500万元，版号获批每款最高50万元，爆款最高1000万元。初创团队最高奖励10万元，入孵团队前6个月免租金。
-广东游戏，不再满足于当“世界代工厂”，而是要把自己的IP做成全球爆款。
-从科韵路到国际舞台，从“卖皮肤”到“卖文化”，这波转型稳准狠。当《星炬不熄》的合唱响彻东方体育中心，当洛杉矶孔雀剧院的灯光即将为粤产游戏点亮，所有人都该听懂了，粤产游戏的“新世界”，不再是画饼，是正在发生的未来。
-策划丨吴江
-统筹丨刘佳宁
-文字丨杭莹
-拍摄丨刘佳宁
-剪辑丨沈钊
-主持丨汪海晏
-设计丨范英兰</t>
+          <t>&lt;p&gt;　　8月8日，2026穿越火线IP嘉年华暨穿越火线职业联赛（CFPL）夏季赛总决赛，在济南融创国际体育中心举行。活动以“品牌展演+职业赛事”两条主线展开，将怀旧情怀、音乐演出、明星互动与顶级电竞对抗融为一体，吸引众多玩家与市民到场参与。当晚，CNCF赛区五支战队出征巴黎的仪式，与CFPL夏季赛总冠军的诞生，成为整场活动的两个高潮。&lt;/p&gt;
+&lt;img src="https://inews.gtimg.com/news_bt/OOqRM-wD84505abyWWvzPxAsG2GZlTiM09nvN-Xjcta4UAA/641" alt="https://inews.gtimg.com/news_bt/OOqRM-wD84505abyWWvzPxAsG2GZlTiM09nvN-Xjcta4UAA/641" /&gt;
+&lt;p&gt;　　经过四局较量，“白鲨战队”以“3:1”的总比分战胜“KZ战队”，捧起2026 CFPL夏季赛总冠军奖杯；队内核心选手“Xxiao.白鲨”当选总决赛FMVP。接下来，CFML（穿越火线枪战王者职业联赛）的“巅峰对决”将继续在泉城上演，KZ与白鲨的较量从端游延续到移动端，让这份热度得以延续。&lt;/p&gt;
+&lt;img src="https://inews.gtimg.com/news_bt/O774xxY8qgqvYlrN67uHfnhS_EvpEUFv1hV-lyvgi6Zx8AA/641" alt="https://inews.gtimg.com/news_bt/O774xxY8qgqvYlrN67uHfnhS_EvpEUFv1hV-lyvgi6Zx8AA/641" /&gt;
+&lt;img src="https://inews.gtimg.com/news_bt/OnsuDcLaXbdp8CQnUgtVma-vP5EOUtItMc4Xq54FRobC0AA/641" alt="https://inews.gtimg.com/news_bt/OnsuDcLaXbdp8CQnUgtVma-vP5EOUtItMc4Xq54FRobC0AA/641" /&gt;
+&lt;p&gt;　　品牌盛典：唤醒十八年热血记忆为热爱正名&lt;/p&gt;
+&lt;p&gt;　　当天下午，“开幕式礼盒解锁仪式”率先拉开活动序幕。随后的“情怀模块”环节，18位穿越火线传奇选手与主播分三组登台，白鲨AyoM、马哲、年鹏Enpi，以及秋宇、Vtop川、飞段等悉数亮相，唤起了不少老玩家的回忆。腾讯互娱K1合作部总经理许光在现场作年度发布，介绍产品与生态的新规划。&lt;/p&gt;
+&lt;img src="https://inews.gtimg.com/news_bt/OzinM6LZ3XLxb0--aiy0ktk0bMrFlYOFPERaFFtnmwpuAAA/641" alt="https://inews.gtimg.com/news_bt/OzinM6LZ3XLxb0--aiy0ktk0bMrFlYOFPERaFFtnmwpuAAA/641" /&gt;
+&lt;p&gt;　　说唱歌手王以太献唱《目不转睛》《危险派对》，将现场气氛带到顶点。AK明星表演赛中，由张国伟、马哲、Enpi等组成的“一发入魂队”进行新沙漠TD 5V5表演赛，明星与职业选手同场竞技。金火线杯颁奖环节，CF喷漆老六、饱饱、无敌老墨言等获得年度最具人气作者，体现出穿越火线活跃的内容创作生态。&lt;/p&gt;
+&lt;img src="https://inews.gtimg.com/news_bt/OL9qEKaA7HIrE5f_L-PjzyUFFChSD34YIeCH09xHh_cS0AA/641" alt="https://inews.gtimg.com/news_bt/OL9qEKaA7HIrE5f_L-PjzyUFFChSD34YIeCH09xHh_cS0AA/641" /&gt;
+&lt;img src="https://inews.gtimg.com/news_bt/OOEqpNhgJSmaAug3dIa01MbdoYwn4bN0zuGpNNiBX70NkAA/641" alt="https://inews.gtimg.com/news_bt/OOEqpNhgJSmaAug3dIa01MbdoYwn4bN0zuGpNNiBX70NkAA/641" /&gt;
+&lt;img src="https://inews.gtimg.com/news_bt/OuUe3zmbHq2rSRXc_gySATMPt8GPH7cTtNMndsFKi-RacAA/641" alt="https://inews.gtimg.com/news_bt/OuUe3zmbHq2rSRXc_gySATMPt8GPH7cTtNMndsFKi-RacAA/641" /&gt;
+&lt;img src="https://inews.gtimg.com/news_bt/OnD1JgPSPG6ReoxyNtCtZaTNjoArQvaEYg3ZNKDmrRXqkAA/641" alt="https://inews.gtimg.com/news_bt/OnD1JgPSPG6ReoxyNtCtZaTNjoArQvaEYg3ZNKDmrRXqkAA/641" /&gt;
+&lt;p&gt;　　EWC出征仪式：CNCF集体奔赴，从泉城走向世界&lt;/p&gt;
+&lt;p&gt;　　仪式现场，来自成都AG、白鲨、KZ、EP、Q9五支俱乐部的玩家代表，依次将象征荣耀的“徽章”、“钥匙”与“战旗”传递到舞台，让普通用户成为CNCF出征的核心组成部分。&lt;/p&gt;
+&lt;img src="https://inews.gtimg.com/news_bt/O5Dr386raveg9n79ZSbQuvtrI-PXCkTChbbCJv3SSWtCUAA/641" alt="https://inews.gtimg.com/news_bt/O5Dr386raveg9n79ZSbQuvtrI-PXCkTChbbCJv3SSWtCUAA/641" /&gt;
+&lt;img src="https://inews.gtimg.com/news_bt/OfpYu72CNn9Sap_Xpp0BzKL8lUV4rm6fB3l11PJmqWJ2MAA/641" alt="https://inews.gtimg.com/news_bt/OfpYu72CNn9Sap_Xpp0BzKL8lUV4rm6fB3l11PJmqWJ2MAA/641" /&gt;
+&lt;p&gt;　　随后，济南市历城区政府党组成员、副区长侯莉将“徽章”授予出征战队，济南市体育局党组成员、副局长张居忠完成“钥匙”与“战旗”的授予。两位嘉宾与选手共同启动仪式，正式拉开穿越火线2026 EWC出征序幕，也进一步凝聚了CNCF赛区的荣誉感。&lt;/p&gt;
+&lt;img src="https://inews.gtimg.com/news_bt/OzgZeJ-L3WX2RcMYosIun8fuzlwUTNGn8u-kUX0ginoQYAA/641" alt="https://inews.gtimg.com/news_bt/OzgZeJ-L3WX2RcMYosIun8fuzlwUTNGn8u-kUX0ginoQYAA/641" /&gt;
+&lt;p&gt;　　这场出征不只在舞台上。借助玩家故事、梦想信物与赛区战旗传递，配合线上话题运营、游戏内活动及全国10城观赛联动，穿越火线把众多玩家的期待带向巴黎。以法国文化元素为灵感设计的法式徽章、EWC钥匙、出征旗帜与限定出征服等实体信物，将在巴黎线下完成徽章交换，搭建起国内外玩家的文化连接。&lt;/p&gt;
+&lt;img src="https://inews.gtimg.com/news_bt/O-pZHUa-SqoGkZM3CFwjJhPEX_wiKehLNCECOP2Y6GP5QAA/641" alt="https://inews.gtimg.com/news_bt/O-pZHUa-SqoGkZM3CFwjJhPEX_wiKehLNCECOP2Y6GP5QAA/641" /&gt;
+&lt;p&gt;　　巅峰对决：枪响正当燃，实力见真章&lt;/p&gt;
+&lt;p&gt;　　总决赛以“枪响正当燃”为主题，回归穿越火线最本真的竞技精神。CFPL S28总决赛在KZ与白鲨之间展开，五局三胜的赛制下，每一局的地图BP、解说席的战术拆解与赛后评论席的复盘都牵动人心，场间抽奖与选手互动则让现场热度持续在线。&lt;/p&gt;
+&lt;img src="https://inews.gtimg.com/news_bt/OK6BeyKM4JdE24t9XPDr-gbTNS9vJkKzglPTlz3IKTSdcAA/641" alt="https://inews.gtimg.com/news_bt/OK6BeyKM4JdE24t9XPDr-gbTNS9vJkKzglPTlz3IKTSdcAA/641" /&gt;
+&lt;img src="https://inews.gtimg.com/news_bt/OdaYj5SS4o5buE8_xAq0SQwsoawdYEtvSyO5pLS-BhiLsAA/641" alt="https://inews.gtimg.com/news_bt/OdaYj5SS4o5buE8_xAq0SQwsoawdYEtvSyO5pLS-BhiLsAA/641" /&gt;
+&lt;img src="https://inews.gtimg.com/news_bt/O-OeqJeFxgSEod_6KhuvRd8eKMsxfPcwX8xFpgEKNctNgAA/641" alt="https://inews.gtimg.com/news_bt/O-OeqJeFxgSEod_6KhuvRd8eKMsxfPcwX8xFpgEKNctNgAA/641" /&gt;
+&lt;img src="https://inews.gtimg.com/news_bt/Opu2OhDS0dfNKpaYb0kEufNF4WSPVbe-a84PioCZnG1tsAA/641" alt="https://inews.gtimg.com/news_bt/Opu2OhDS0dfNKpaYb0kEufNF4WSPVbe-a84PioCZnG1tsAA/641" /&gt;
+&lt;p&gt;　　双线辉映，电竞与泉城的双向奔赴&lt;/p&gt;
+&lt;p&gt;　　会场之外，济南城市嘉年华在外场同步展开。沉浸式IP打卡装置、玩家共创工坊、俱乐部主题展位与限定周边市集，把线上的热情延伸到泉城街头。不少市民与玩家在商圈、广场和电竞馆之间穿梭，电竞由此走出赛场，融入这座城市的夏日生活，也为济南推进“电竞+文旅+消费”提供了鲜活场景。&lt;/p&gt;
+&lt;img src="https://inews.gtimg.com/news_bt/OBmisICWH7ITAweI9QCfn7yj6VX8LxyrQma8E-ZCxFmvUAA/641" alt="https://inews.gtimg.com/news_bt/OBmisICWH7ITAweI9QCfn7yj6VX8LxyrQma8E-ZCxFmvUAA/641" /&gt;
+&lt;img src="https://inews.gtimg.com/news_bt/O874798L_E4cRLKXqSt-DjfzVjP5xvtGTPs0DVdix_f6UAA/641" alt="https://inews.gtimg.com/news_bt/O874798L_E4cRLKXqSt-DjfzVjP5xvtGTPs0DVdix_f6UAA/641" /&gt;
+&lt;img src="https://inews.gtimg.com/news_bt/OCSbWQ77AVnwf9Gp6scU1KGEzjUIjdKlbxk_7yIJEBId8AA/641" alt="https://inews.gtimg.com/news_bt/OCSbWQ77AVnwf9Gp6scU1KGEzjUIjdKlbxk_7yIJEBId8AA/641" /&gt;
+&lt;p&gt;　　这是穿越火线IP与济南的又一次结缘。2024年，济南曾承办穿越火线职业联赛（CFPL）春季赛总决赛，办赛组织获得业内认可。目前，全市已集聚电竞企业335家，具备办赛条件的综合性场馆104处，形成4大电竞产业集聚区，并出台《济南市电竞游戏产业发展行动计划（2024—2026年）》。从承接单项赛事到引入综合性IP活动，济南正借力“电竞+文旅+消费”的融合路径，为本地电竞人才和内容生态搭建展示平台。&lt;/p&gt;
+&lt;img src="https://inews.gtimg.com/news_bt/O_MoeAtifwZIu73kwe2MFy3X63YrNibrXKRoPL119d70MAA/641" alt="https://inews.gtimg.com/news_bt/O_MoeAtifwZIu73kwe2MFy3X63YrNibrXKRoPL119d70MAA/641" /&gt;
+&lt;img src="https://inews.gtimg.com/news_bt/OQ1TQmnuVoszoJyEeME7JMSOq5U1w5Txvzdaesosa1Pb4AA/641" alt="https://inews.gtimg.com/news_bt/OQ1TQmnuVoszoJyEeME7JMSOq5U1w5Txvzdaesosa1Pb4AA/641" /&gt;
+&lt;p&gt;　　随着2026穿越火线IP嘉年华端游盛典落幕，一座奖杯有了归属，CNCF赛区也由此迈向更大的国际舞台。从现场看，嘉年华互动、玩家共创、俱乐部生态与商业权益的联动，让赛事影响力、用户活跃度与联盟商业价值都得到了同步提升。&lt;/p&gt;
+&lt;p&gt;　　从济南点亮的“CNCF”旗帜，到将在巴黎完成交换的出征信物，穿越火线正以IP为纽带，把竞技、玩家与城市连接在一起，也为济南发展电竞产业写下新的注脚。&lt;/p&gt;
+&lt;p&gt;　　编辑：罗宁&lt;/p&gt;</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>https://inews.gtimg.com/om_bt/OjNqpckxKYQF4ZfuZVsPad8H1QLevJ23yXfphpFZxU42IAA/641</t>
+          <t>https://inews.gtimg.com/om_bt/O8g8quxxy3xtIhxdFpLoPgcXTjneQ9U-ury0EGnZVIfPcAA/641</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>世纪华通总裁谈“AI改写游戏”：业务链每一环节都能实现创收</t>
+          <t>图集｜在济南见证冠军诞生！白鲨战队斩获CFPLS28夏季赛总冠军</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -830,32 +839,63 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>“AI对游戏产业最深刻的改变，不会只停留在某一个环节，它会从底层重新定义游戏从创意到体验的整个价值链。”
-AI究竟如何改写游戏行业？8月4日，世纪华通总裁谢斐在接受澎湃新闻记者采访时坦言，过去一年，AI美术、AI代码、AI测试工具在游戏公司内部快速铺开，研发流程被压缩，“在研发、美术、测试、投放、运营整条业务链，每一环都能实现创收。”
-据谢斐介绍，世纪华通的AI投入分两层：业务应用层落地，以及智算力底座建设。后者包括在长三角、大湾区布局的算力基础设施。此外，公司通过产业基金投资了摩尔线程，并在物理AI、脑机接口方向有布局。
-她介绍，AI对游戏产业最深刻的改变，不会只停留在某一个环节，它会从底层重新定义游戏从创意到体验的整个价值链。当前最为大家熟知的就是研发流程的重构，AI正在把它变成一种“协作文档式”的生产：策划可以用自然语言生成原型，美术可以用AI批量生成素材并实时迭代，测试可以交给AI自动化完成；代码开发可以由AI辅助生成。当AI从帮人干活进化到自己能干活，真正的变化是人的角色从执行者变成了定义者：定义什么值得做、什么流程值得跑，剩下的交给AI去执行。
-在谢斐看来，世纪华通正在用AI重新定义内容的创作方式、交互方式和商业模式，希望世纪华通不再仅仅被定义为一家“游戏公司”，而是一家以AI为引擎的全球化数字内容公司。
-根据世纪华通最新发布的业绩预告，2026年上半年合并营业收入约220亿元，同比增长约28%；归母净利润43亿元至47.7亿元，同比增长61.87%至79.57%。
-谈到业绩增长背后的原因，谢斐向记者透露，今年上半年，世纪华通营收、利润均刷新历史纪录，不过在人员扩充、赛道拓展上依旧保持谨慎，不盲目扩张，“我们更愿意把资源投向长期价值领域，即便部分投入短期难以见效，也持续加码。企业长期发展需要成熟架构与制度保驾护航，我们搭建完善的容错机制，在创新遇到阶段性难题时，由公司为团队托底，鼓励大胆探索。”
-世纪华通在出海方面的探索，也格外受到业内关注，CenturyGames稳居中国发行商全球收入第二。旗下《WhiteoutSurvival》上线超过3年，累计下载量突破3亿，2026年6月再次拿下全球手游收入冠军。更年轻的《Kingshot》在2026年4月反超《WhiteoutSurvival》，成为公司海外收入第一的产品，增速超过前者同期。
-这两款产品构成了世纪华通当前业绩的核心支撑。谢斐将出海的难点归结为三道坎：思维方式从“我做什么卖什么”转向“用户要什么做什么”；本地化运营深入文化语境和合规体系；以及长线运营的耐心。
-“最难的从来不是语言翻译，也不是买量投放，而是文化的深度共鸣和本土化的组织能力。”她向澎湃新闻记者表示。
-谢斐介绍，游戏本地化运营的深水区是真正扎进当地的文化语境里。比如欧美玩家非常看重社区氛围，就在核心市场建本土运营团队，跟着他们的节日做定制活动，认真听社区反馈迭代内容，甚至让玩家参与到内容共创里。还有合规，海外各国的数据隐私规则、内容分级标准、税务劳动法规都不一样，这是生命线，必须建本土化的合规团队。
-在长线运营的耐心方面，她表示，出海并非只是赚快钱，而是多年积累的长线运营经验磨砺出来的，厂商需要持续更新内容和玩家建立情感连接。
-在生态构建方面，过去几年世纪华通接连投资摩尔线程、无问芯穹等多家硬科技企业，对此，谢斐认为，游戏行业一直是前沿技术最早的试验场和落地场景。从早年的3D显卡，到云计算，再到今天的AI，每一次硬件和底层技术的突破，最先商业化、最先规模化落地的场景一定是游戏。今天的硬科技，可能就是三五年后游戏行业的基础设施。提前布局，不是为了赚短期的股价红利，是为了在下一轮技术变革到来的时候有底气站在前面，而不是跟着别人跑。
-对于AI产业终局，谢斐提到，随着算力、大模型、AIGC等技术快速普及迭代，AI正褪去高端技术的稀缺属性，如同早年的水电、网络、交通基础设施一般，成为数字产业普惠化、通用化、必备化的基础能力。</t>
+          <t>&lt;p&gt;　　8月8日，备受瞩目的2026穿越火线IP嘉年华暨穿越火线双端职业联赛夏季总决赛，在济南融创国际体育中心盛大启幕。当日下午，CFPLS28端游夏季赛总决赛率先开战，KZ、白鲨两大老牌豪门战队巅峰会师。经过一番激战，白鲨战队在泉城捧起CFPLS28夏季赛冠军奖杯。赛场之上，队员相拥庆祝，属于胜利者的荣光在济南融创国际体育中心的聚光灯下熠熠生辉。&lt;/p&gt;
+&lt;img src="https://inews.gtimg.com/om_bt/O8g8quxxy3xtIhxdFpLoPgcXTjneQ9U-ury0EGnZVIfPcAA/641" alt="https://inews.gtimg.com/om_bt/O8g8quxxy3xtIhxdFpLoPgcXTjneQ9U-ury0EGnZVIfPcAA/641" /&gt;
+&lt;img src="https://inews.gtimg.com/om_bt/OOaocPeASJkSAk0Yre7ez-USmuTJSpM85zf1AqSVYBj_AAA/641" alt="https://inews.gtimg.com/om_bt/OOaocPeASJkSAk0Yre7ez-USmuTJSpM85zf1AqSVYBj_AAA/641" /&gt;
+&lt;img src="https://inews.gtimg.com/om_bt/OyDjc9SKcgAQx_m4JFvUztDYYAjJwzXNlFqC5N5jnXgQYAA/641" alt="https://inews.gtimg.com/om_bt/OyDjc9SKcgAQx_m4JFvUztDYYAjJwzXNlFqC5N5jnXgQYAA/641" /&gt;
+&lt;img src="https://inews.gtimg.com/om_bt/OF4psFWeieDdXuZ87coYFEpSTkBFv5S6rMRt4hMyAkRFMAA/641" alt="https://inews.gtimg.com/om_bt/OF4psFWeieDdXuZ87coYFEpSTkBFv5S6rMRt4hMyAkRFMAA/641" /&gt;
+&lt;img src="https://inews.gtimg.com/om_bt/O0-6Go9C_Bs6SNoiPjuEZtAsziDpmtS2Zn1iUE7uWFEbUAA/641" alt="https://inews.gtimg.com/om_bt/O0-6Go9C_Bs6SNoiPjuEZtAsziDpmtS2Zn1iUE7uWFEbUAA/641" /&gt;
+&lt;img src="https://inews.gtimg.com/om_bt/O1zEZaKNwznQS7Fm6abrLgnnPWl9elxKb5LPlrxCH2MnEAA/641" alt="https://inews.gtimg.com/om_bt/O1zEZaKNwznQS7Fm6abrLgnnPWl9elxKb5LPlrxCH2MnEAA/641" /&gt;
+&lt;img src="https://inews.gtimg.com/om_bt/OTXCtAxTay4bCnDArk6i6_TFlAHEWoM4MmGJDzbenAbcoAA/641" alt="https://inews.gtimg.com/om_bt/OTXCtAxTay4bCnDArk6i6_TFlAHEWoM4MmGJDzbenAbcoAA/641" /&gt;
+&lt;img src="https://inews.gtimg.com/om_bt/O3Jz6nG7qVHHliEz-N0vQ6I10AuXsCFgZWe6ttk_nmqnwAA/641" alt="https://inews.gtimg.com/om_bt/O3Jz6nG7qVHHliEz-N0vQ6I10AuXsCFgZWe6ttk_nmqnwAA/641" /&gt;
+&lt;img src="https://inews.gtimg.com/om_bt/ONafaXXXKPwTZFvSz1IpTrtOnX_kiQ3bdmNcpxfGyzFgIAA/641" alt="https://inews.gtimg.com/om_bt/ONafaXXXKPwTZFvSz1IpTrtOnX_kiQ3bdmNcpxfGyzFgIAA/641" /&gt;
+&lt;img src="https://inews.gtimg.com/om_bt/OqVTMGfrITveXMZvIsl6RK-AEEAhqXb5FEQEmn0MCom5kAA/641" alt="https://inews.gtimg.com/om_bt/OqVTMGfrITveXMZvIsl6RK-AEEAhqXb5FEQEmn0MCom5kAA/641" /&gt;
+&lt;img src="https://inews.gtimg.com/om_bt/OYw8OQeRLTm-23grNbSw1znR4OchbX1Ra_zVsiCJ_oVGsAA/641" alt="https://inews.gtimg.com/om_bt/OYw8OQeRLTm-23grNbSw1znR4OchbX1Ra_zVsiCJ_oVGsAA/641" /&gt;
+&lt;img src="https://inews.gtimg.com/om_bt/OAYAppPy0UYjk4vw9jm_EnXlIj9AX9ObOBVQf8Ioy_DOgAA/641" alt="https://inews.gtimg.com/om_bt/OAYAppPy0UYjk4vw9jm_EnXlIj9AX9ObOBVQf8Ioy_DOgAA/641" /&gt;
+&lt;img src="https://inews.gtimg.com/om_bt/OuOvMiCy8nus-1qUPy1WDGxuzhwRN0AeGF4UmPobUItHoAA/641" alt="https://inews.gtimg.com/om_bt/OuOvMiCy8nus-1qUPy1WDGxuzhwRN0AeGF4UmPobUItHoAA/641" /&gt;
+&lt;img src="https://inews.gtimg.com/om_bt/OHqT2dbFH3MEh-5VUjs8m7fTjPJnrpRNY30fsUOyMChdAAA/641" alt="https://inews.gtimg.com/om_bt/OHqT2dbFH3MEh-5VUjs8m7fTjPJnrpRNY30fsUOyMChdAAA/641" /&gt;
+&lt;img src="https://inews.gtimg.com/om_bt/OBnLXfJO4YrkhBarx8uxvcYhhaRATbb2iUbe4Z4xj5DvEAA/641" alt="https://inews.gtimg.com/om_bt/OBnLXfJO4YrkhBarx8uxvcYhhaRATbb2iUbe4Z4xj5DvEAA/641" /&gt;
+&lt;img src="https://inews.gtimg.com/om_bt/OHCODiqMFaTg42MBU4FNzUtKBGR-V3neEm8n0WHpeM36gAA/641" alt="https://inews.gtimg.com/om_bt/OHCODiqMFaTg42MBU4FNzUtKBGR-V3neEm8n0WHpeM36gAA/641" /&gt;
+&lt;img src="https://inews.gtimg.com/om_bt/OHCODiqMFaTg42MBU4FNzUtKBGR-V3neEm8n0WHpeM36gAA/641" alt="https://inews.gtimg.com/om_bt/OHCODiqMFaTg42MBU4FNzUtKBGR-V3neEm8n0WHpeM36gAA/641" /&gt;
+&lt;img src="https://inews.gtimg.com/om_bt/OefuxZMS7s_p1giKHlxRpzOmqJTVWi56VuEt0JpJuBtmsAA/641" alt="https://inews.gtimg.com/om_bt/OefuxZMS7s_p1giKHlxRpzOmqJTVWi56VuEt0JpJuBtmsAA/641" /&gt;
+&lt;img src="https://inews.gtimg.com/om_bt/OSE6nM5EUFZk2bTLoF8GCybaqm62BCHmCcbcQglsTHymgAA/641" alt="https://inews.gtimg.com/om_bt/OSE6nM5EUFZk2bTLoF8GCybaqm62BCHmCcbcQglsTHymgAA/641" /&gt;
+&lt;img src="https://inews.gtimg.com/om_bt/O9PitEZFa9Oic9kxi7MwD9fNKcHPAysFfJ3YZKYNgsI2AAA/641" alt="https://inews.gtimg.com/om_bt/O9PitEZFa9Oic9kxi7MwD9fNKcHPAysFfJ3YZKYNgsI2AAA/641" /&gt;
+&lt;img src="https://inews.gtimg.com/om_bt/OV4XLnlfriiDDGCTMzR8WeMZOg5skybfMnWpx63S5UXjQAA/641" alt="https://inews.gtimg.com/om_bt/OV4XLnlfriiDDGCTMzR8WeMZOg5skybfMnWpx63S5UXjQAA/641" /&gt;
+&lt;img src="https://inews.gtimg.com/om_bt/OzqBhbNwzVF6veuJiCmvyqgasl_CVaS3DOTEKNjdr7WFAAA/641" alt="https://inews.gtimg.com/om_bt/OzqBhbNwzVF6veuJiCmvyqgasl_CVaS3DOTEKNjdr7WFAAA/641" /&gt;
+&lt;img src="https://inews.gtimg.com/om_bt/ODRCk1InNZZ-wVueN-BRlEpaL0gHOy1e4GQMMxAMfQhmUAA/641" alt="https://inews.gtimg.com/om_bt/ODRCk1InNZZ-wVueN-BRlEpaL0gHOy1e4GQMMxAMfQhmUAA/641" /&gt;
+&lt;img src="https://inews.gtimg.com/om_bt/OSWXbkdkf-ntvaOguwMB-IckAQPSFiGO35Sp6GjVpvfmgAA/641" alt="https://inews.gtimg.com/om_bt/OSWXbkdkf-ntvaOguwMB-IckAQPSFiGO35Sp6GjVpvfmgAA/641" /&gt;
+&lt;img src="https://inews.gtimg.com/om_bt/OJ64lF_8U-NyrPOp2nonJGoQG-Ozm1fzzH3SzS0P20mCUAA/641" alt="https://inews.gtimg.com/om_bt/OJ64lF_8U-NyrPOp2nonJGoQG-Ozm1fzzH3SzS0P20mCUAA/641" /&gt;
+&lt;img src="https://inews.gtimg.com/om_bt/ORLtJNpOHLgJs0Nn9nxbI9BpkG3hnCtMnOmQNO2RVgSD0AA/641" alt="https://inews.gtimg.com/om_bt/ORLtJNpOHLgJs0Nn9nxbI9BpkG3hnCtMnOmQNO2RVgSD0AA/641" /&gt;
+&lt;img src="https://inews.gtimg.com/om_bt/Oc1tzYR4lr7O_E5fhU9m_YmzQGjXAmxdrJXTFGswHF6_4AA/641" alt="https://inews.gtimg.com/om_bt/Oc1tzYR4lr7O_E5fhU9m_YmzQGjXAmxdrJXTFGswHF6_4AA/641" /&gt;
+&lt;img src="https://inews.gtimg.com/om_bt/Ouzik6XZftcgHoJKfePENQxjycR8CoCVwmFXrVry4QJ2EAA/641" alt="https://inews.gtimg.com/om_bt/Ouzik6XZftcgHoJKfePENQxjycR8CoCVwmFXrVry4QJ2EAA/641" /&gt;
+&lt;img src="https://inews.gtimg.com/om_bt/OA8gMJv5GWEQxE263qFHJStPpCpwvbeiZJ9Lzfg9tRgTwAA/641" alt="https://inews.gtimg.com/om_bt/OA8gMJv5GWEQxE263qFHJStPpCpwvbeiZJ9Lzfg9tRgTwAA/641" /&gt;
+&lt;img src="https://inews.gtimg.com/om_bt/OJ5Gq3qLCCCOi_S2Dzr7xhgMNuGfvs-IftpvnYHBThZwwAA/641" alt="https://inews.gtimg.com/om_bt/OJ5Gq3qLCCCOi_S2Dzr7xhgMNuGfvs-IftpvnYHBThZwwAA/641" /&gt;
+&lt;img src="https://inews.gtimg.com/om_bt/OlANlHiRQgXg_7FLOCiKyOzkWxX3moH5SkQltuv5ZD_qkAA/641" alt="https://inews.gtimg.com/om_bt/OlANlHiRQgXg_7FLOCiKyOzkWxX3moH5SkQltuv5ZD_qkAA/641" /&gt;
+&lt;img src="https://inews.gtimg.com/om_bt/OFCqNEpm28Sv1X11DYskzTGD-SAGmcS2sDwsqSnSAQJscAA/641" alt="https://inews.gtimg.com/om_bt/OFCqNEpm28Sv1X11DYskzTGD-SAGmcS2sDwsqSnSAQJscAA/641" /&gt;
+&lt;img src="https://inews.gtimg.com/om_bt/Oswhy5awzGJMKsQQhlPDCM5o5ysACidvBQsgwXt5PBJqkAA/641" alt="https://inews.gtimg.com/om_bt/Oswhy5awzGJMKsQQhlPDCM5o5ysACidvBQsgwXt5PBJqkAA/641" /&gt;
+&lt;img src="https://inews.gtimg.com/om_bt/OSEL67wp-P4_Ub5wPmKVCEB5VkbFNrz439pYK_sLEdV5AAA/641" alt="https://inews.gtimg.com/om_bt/OSEL67wp-P4_Ub5wPmKVCEB5VkbFNrz439pYK_sLEdV5AAA/641" /&gt;
+&lt;img src="https://inews.gtimg.com/om_bt/OxStPncn_6CWr2bc3LjSirfLadWViE2kKXbhkyspud7TcAA/641" alt="https://inews.gtimg.com/om_bt/OxStPncn_6CWr2bc3LjSirfLadWViE2kKXbhkyspud7TcAA/641" /&gt;
+&lt;img src="https://inews.gtimg.com/om_bt/OaKxaSFs9gujZxBQrBYNLhCYqN2IrlzXQC01dSE2QvwHgAA/641" alt="https://inews.gtimg.com/om_bt/OaKxaSFs9gujZxBQrBYNLhCYqN2IrlzXQC01dSE2QvwHgAA/641" /&gt;
+&lt;img src="https://inews.gtimg.com/om_bt/O3ZoD99CCpDX_i4VhT07PnGJMNMrWopzM8w3yL1ISv9WAAA/641" alt="https://inews.gtimg.com/om_bt/O3ZoD99CCpDX_i4VhT07PnGJMNMrWopzM8w3yL1ISv9WAAA/641" /&gt;
+&lt;img src="https://inews.gtimg.com/om_bt/OWSpwWDJGzrL568mnBYvVlpQSyajSBhTq9fvqLIQyxz40AA/641" alt="https://inews.gtimg.com/om_bt/OWSpwWDJGzrL568mnBYvVlpQSyajSBhTq9fvqLIQyxz40AA/641" /&gt;
+&lt;img src="https://inews.gtimg.com/om_bt/OqBIHR74yY66TxL0lO-WKIUfJa3SR5KMVly0Ctzt5OI54AA/641" alt="https://inews.gtimg.com/om_bt/OqBIHR74yY66TxL0lO-WKIUfJa3SR5KMVly0Ctzt5OI54AA/641" /&gt;
+&lt;img src="https://inews.gtimg.com/om_bt/OyFs9pBsGgc4M-eZsWezuRanJSmX8pBrxbrEu8CP_tQIoAA/641" alt="https://inews.gtimg.com/om_bt/OyFs9pBsGgc4M-eZsWezuRanJSmX8pBrxbrEu8CP_tQIoAA/641" /&gt;
+&lt;img src="https://inews.gtimg.com/om_bt/OULsQRmkywBAttstgdXQiICvu7cyjpMXC_KgsG5ivjBPEAA/641" alt="https://inews.gtimg.com/om_bt/OULsQRmkywBAttstgdXQiICvu7cyjpMXC_KgsG5ivjBPEAA/641" /&gt;
+&lt;img src="https://inews.gtimg.com/om_bt/OVG1dU3Wjlw2Sg9GfPF-BF5HqnqpIMN17BlcMSTtHQRW0AA/641" alt="https://inews.gtimg.com/om_bt/OVG1dU3Wjlw2Sg9GfPF-BF5HqnqpIMN17BlcMSTtHQRW0AA/641" /&gt;
+&lt;img src="https://inews.gtimg.com/om_bt/OEQI-lQ5INblbj8OeYY5gnal3g60AnkQUpbn6HgIji_yoAA/641" alt="https://inews.gtimg.com/om_bt/OEQI-lQ5INblbj8OeYY5gnal3g60AnkQUpbn6HgIji_yoAA/641" /&gt;
+&lt;p&gt;　　（济南日报·爱济南 记者：宋嘉祎 摄影：刚永超）&lt;/p&gt;</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>https://inews.gtimg.com/om_bt/Ovnp0p0Yo9FCawy8DQoNy5jnrhR6mdF_2otszy75utjksAA/1000</t>
+          <t>https://inews.gtimg.com/om_bt/ORnQmqCZsSsca2uiD1sM3JdZnUPQrPqZ4K5z1Unlf7Ln0AA/641</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>世纪华通邓琪：从降本增效到价值创造 AI重构游戏业态</t>
+          <t>全民健身日，与现代电竞“双向奔赴”！穿越火线IP嘉年华在泉城济南开启线下狂欢</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -865,29 +905,29 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>中经记者 董曙光 北京报道
-8月5日，由中国经营报社主办的“2026中国数字产业生态大会”在北京中关村国际技术交易中心举行。
-在“AI驱动产业变革与价值重构”圆桌对话环节，世纪华通（002602.SZ）旗下盛趣资本执行董事邓琪表示，本轮AI技术已从早期的试验阶段全面进入游戏产业各环节的深度整合期，覆盖了从研发、发行到精细化用户运营的全链条，AI本身亦开始渗透至游戏玩法层面。她表示，AI的发展将对公司和整个行业带来深刻变革。
-世纪华通旗下盛趣资本执行董事邓琪
-邓琪认为，两三年前AI技术兴起之初，游戏因其较高的容错性被视为理想的试验场景。她解释称，相较于医疗、无人驾驶等领域，游戏对生成式内容出现偏差的容忍度更高，用户有时甚至会将这些偏差视为设计上的意外惊喜。但她同时强调，游戏作为面向市场的产品，其本质依然是严肃的。
-在早期阶段，AI对游戏产业的影响更多集中在生产和内容生成环节，如辅助编程和3D资产生成，主要价值体现在为研发端降本增效。
-邓琪表示，随着视频生成技术的持续迭代，世纪华通目前用于产品宣传的演示Demo以及15秒量级的互动玩法视频，已基本实现AI全流程生成。这些应用不仅提升了效率，也为验证新产品能否获得用户认可争取了更充裕的试错时间。
-邓琪透露，目前公司从顶层战略规划、核心技术研发、全场景落地应用、产业生态拓展等维度，构建了完整的AI技术布局体系，该体系不仅提高了个人产出效率，更通过将各岗位员工的产出纳入统一管线和产出体系，带动了整体研发效率的提升。她举例称，过去研发一款可供测试的产品Demo大约需要六个月，如今这一周期已缩短至三个月左右，释放出的时间和资源可用于探索更多元的创意方向。
-在发行环节，邓琪介绍，以往世纪华通需根据不同渠道的游戏属性进行买量投放，如今借助AI可批量生成多样化素材和投放点位，以更精准地触达潜在用户。同时，大语言模型的应用显著加快了本地化翻译速度，为公司拓展海外发行区域提供了支撑。在用户运营层面，AI提供的数据分析能力可将用户反馈数字化并形成表格化呈现，帮助运营团队更准确地判断用户偏好，进而作出针对性的功能调整与反馈。
-邓琪将AI对游戏行业的影响概括为“从降本到增效”，并最终指向为用户创造更多价值。她表示，上述应用已进入成熟使用阶段。公司更期待未来在创意层面取得突破，即如何运用现有AI技术探索和研发出市场上尚未出现的原生玩法，为用户带来前所未有的体验。
-针对市场关于AI技术是否存在泡沫的讨论，邓琪回应称，泡沫的存在有其积极意义。她认为，泡沫能够吸引更多社会资本进入，资金的聚集是吸引创意人才的前提，而人才的汇聚才能催生具有突破性的可应用技术。
-邓琪坦承，本轮AI热潮在现阶段确实存在一定程度的价值高估，但这也是任何新技术发展初期的普遍现象。
-从投资视角出发，邓琪认为核心在于如何在泡沫中甄别具备长期价值的实质资产。她指出，本轮AI已在技术层和产业应用层产生具体产出。“说明这并非炒作出来的风口，而是具备落地能力、能切实推动企业变革的技术。”与此同时，她表示不希望市场上出现过多唱空声音，认为这将阻碍社会与技术进步。
-邓琪表示，投资者在泡沫中应保持冷静反思，深入理解底层需求，从中提炼真正值得布局的方向。“什么时候该布局硬件，什么时候该布局软件，什么时候软件又会对硬件形成反向的推动，这些都需要在泡沫中沉下心来认真思考。”她说。
-（编辑：董曙光 审核：吴可仲 校对：颜京宁）</t>
+          <t>&lt;p&gt;　　“推动电竞成为体育产业的新引擎。”&lt;/p&gt;
+&lt;p&gt;　　值全民健身日到来之际，2026穿越火线IP嘉年华活动首度在泉城济南开启线下狂欢。&lt;/p&gt;
+&lt;img src="https://inews.gtimg.com/om_bt/ORnQmqCZsSsca2uiD1sM3JdZnUPQrPqZ4K5z1Unlf7Ln0AA/641" alt="https://inews.gtimg.com/om_bt/ORnQmqCZsSsca2uiD1sM3JdZnUPQrPqZ4K5z1Unlf7Ln0AA/641" /&gt;
+&lt;p&gt;　　8月8日到8月9日两天，2026穿越火线IP嘉年华暨穿越火线双端职业联赛夏季总决赛在济南融创国际体育中心举行。活动以“品牌展演+职业赛事”两条主线展开，将怀旧情怀、音乐演出、明星互动与顶级电竞对抗融为一体，吸引众多玩家与市民到场参与。&lt;/p&gt;
+&lt;p&gt;　　总决赛以“枪响正当燃”为主题，回归穿越火线最本真的竞技精神。8月8日晚，CNCF赛区五支战队出征巴黎的仪式，与CFPL夏季赛总冠军的诞生，成为整场活动的两个高潮。经过四局较量，“白鲨战队”以“3:1”的总比分战胜“KZ战队”，捧起2026 CFPL夏季赛总冠军奖杯。在8月9日进行的CFMS19总决赛中，“白鲨战队”实现双端夺冠，于济南再度捧杯。&lt;/p&gt;
+&lt;img src="https://inews.gtimg.com/om_bt/OPfpEPekpNMIYJUknLP8Kg5wDzVfwr8TuFrB90OBUc7zUAA/641" alt="https://inews.gtimg.com/om_bt/OPfpEPekpNMIYJUknLP8Kg5wDzVfwr8TuFrB90OBUc7zUAA/641" /&gt;
+&lt;p&gt;　　值得一提的是，这是穿越火线IP与济南的又一次结缘。2024年，济南曾承办穿越火线职业联赛（CFPL）春季赛总决赛，办赛组织获得业内认可。缘何三次选择泉城？目前，济南市已集聚电竞企业335家，具备办赛条件的综合性场馆104处，形成4大电竞产业集聚区，并出台《济南市电竞游戏产业发展行动计划（2024—2026年）》。从承接单项赛事到引入综合性IP活动，济南正借力“电竞+文旅+消费”的融合路径，为本地电竞人才和内容生态搭建展示平台。&lt;/p&gt;
+&lt;p&gt;　　穿越火线系列电竞业务负责人表示，本次赛事带来票务经济超600万元，赛事经济方面，吃住行游购等超3000万元，秉持以赛创牌、以赛促产、以产为基、以产促融的理念，希望携手济南推进电竞产业成为体育产业的一个增长的新引擎。&lt;/p&gt;
+&lt;img src="https://inews.gtimg.com/om_bt/OfAv2ZIkexhuNBQ8B-sUDBTAPAm42eEmSYP-_TiB4BdlEAA/641" alt="https://inews.gtimg.com/om_bt/OfAv2ZIkexhuNBQ8B-sUDBTAPAm42eEmSYP-_TiB4BdlEAA/641" /&gt;
+&lt;p&gt;　　此次穿越火线嘉年华正以IP为纽带，把竞技、玩家与城市连接在一起，以“电竞+文旅”的形式，让“跟着赛事去旅行”成为城市新常态。&lt;/p&gt;
+&lt;p&gt;　　（大众新闻记者 李伟 济南报道）&lt;/p&gt;</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr"/>
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>https://inews.gtimg.com/om_bt/OtE2ulehfw7GVzYGtSYicQsE88kYwemDR1_emHn8ldzkEAA/641</t>
+        </is>
+      </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>腾讯游戏Q2营收659亿：本土市场双位数增长 海外休闲赛道突围|财报解读</t>
+          <t>电竞世俱杯欧洲战队MSC首冠！决胜巅峰包揽2026全球电竞收视榜前三</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -897,24 +937,23 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>财联社8月12日讯 （记者 王彦琳）腾讯控股（00700.HK）今日晚间发布的2026年第二季度财报显示，其核心业务之一的网络游戏总收入659亿元，同比增长11%，整体重回双位数增长态势，增长动力主要来自《三角洲行动》《无畏契约》《无畏契约：源能行动》及《洛克王国：世界》等多款核心产品。
-分市场来看，本土市场方面，腾讯游戏第二季度实现收入473亿元，同比增长17%，在射击品类与竞技赛道上，持续保持领先位置。《王者荣耀》《三角洲行动》等多款新老产品表现优异。财报显示，《三角洲行动》与《无畏契约》的平均日活跃账户数在二季度创下新高，《洛克王国：世界》今年3月上线后，在中国市场发布的所有新手游中，按平均日活跃账户数和按流水计算均排名第一。
-此外，腾讯今年7月宣布上线的开放世界生存搜打撤游戏《失控进化》，上线后迅速登顶iOS免费榜总榜。该产品虽不计入二季度收入，但作为下半年新品储备，与现有长青产品及成熟产品形成梯队，为后续业务增长提供新的支撑。
-国际市场方面，受汇率波动影响二季度游戏收入同比下降0.8%，但按固定汇率计算同比增长4%至186亿元，主要受《鸣潮》《VALORANT》驱动。此外，腾讯2015年收购的欧洲休闲游戏厂商Miniclip在国际市场取得突破，推出的休闲游戏《Arrows – Puzzle Escape》在二季度成为全球下载量最高的手游，带来强劲的应用内广告收入。
-当前，AI正成为推动腾讯游戏业务增长的引擎，深入覆盖玩家体验、研发生产、运营服务等在内的全链路环节，比如，《三角洲行动》利用Agent实现运营效能提升，并通过Hy3D能力进行场景端手一体化生产管线的提效。
-同时，AI与玩法的融合探索持续推进。据悉，《和平精英》AI NPC玩法累计体验用户数增加至1.67亿、最高日活跃用户数达1770万。《洛克王国：世界》推出面向复杂玩法决策的游戏原生Coach Agent“斯嘉丽”，区别于通用大模型“百科全书式”的回答，“斯嘉丽”能够理解玩家的背包、阵容、对局环境，为玩家生成个性化、可执行的阵容与打法建议。自上线以来，“斯嘉丽”有效促进PVP破冰及活跃，期间PVP激活率增幅20%，破冰用户使用功能后胜率也获得实质改善。</t>
+          <t>&lt;p&gt;　　扬子晚报网8月2日讯（记者 姜天圣）当地时间8月1日，2026电竞世俱杯（EWC）决胜巅峰全球季中杯（MSC）在法国巴黎凡尔赛门展览中心落幕。决赛中，来自东欧中亚赛区的Team Spirit以4:3战胜来自缅甸的Yangon Galacticos，成为该项全球赛事中首个来自欧洲的冠军战队。&lt;/p&gt;
+&lt;img src="https://inews.gtimg.com/om_bt/OtE2ulehfw7GVzYGtSYicQsE88kYwemDR1_emHn8ldzkEAA/641" alt="https://inews.gtimg.com/om_bt/OtE2ulehfw7GVzYGtSYicQsE88kYwemDR1_emHn8ldzkEAA/641" /&gt;
+&lt;p&gt;　　现场&lt;/p&gt;
+&lt;p&gt;　　电竞权威数据平台Esports Charts显示，本届赛事最高峰值在线观看人数（PCV）达到288万，成为2026电竞世俱杯截至目前收视最高项目，与M7世界总决赛、印尼MPL一起，包揽2026年全球电竞赛事收视前三，再次印证了决胜巅峰（MLBB）赛事体系的全球影响力。&lt;/p&gt;
+&lt;img src="https://inews.gtimg.com/om_bt/OSiSHpvz8BFsmbB8zjKuiXnjIOlh8G19AoqxYPSJMBuKgAA/641" alt="https://inews.gtimg.com/om_bt/OSiSHpvz8BFsmbB8zjKuiXnjIOlh8G19AoqxYPSJMBuKgAA/641" /&gt;
+&lt;p&gt;　　数据&lt;/p&gt;
+&lt;p&gt;　　作为迄今规模最大的一届MSC，本届赛事首次落地欧洲，汇聚了来自五大赛区的25支战队，覆盖亚洲、欧洲、美洲和非洲，并首次为印度、泰国、韩国和西欧区域开辟独立晋级路径，Team Spirit夺冠不仅意味着MSC诞生了一支来自新区域的冠军战队，也表明MLBB全球电竞版图正在从传统强区主导，走向更多赛区共同竞争的新阶段。&lt;/p&gt;
+&lt;p&gt;　　根据沐瞳科技官方2026赛程，MLBB后续还将继续拓展国际赛事布局，包括作为首批确认项目亮相的Esports Nations Cup（ENC 2026），以及在土耳其举办的M8世界总决赛等。MLBB正逐步形成从季中顶级赛事到国家队赛事、再到年度世界赛的完整国际赛事链路，随着更多区域、战队获得通往世界舞台的清晰路径，MLBB全球电竞生态的国际连接能力与长期增长空间正持续释放。&lt;/p&gt;
+&lt;p&gt;　　沐瞳国际化赛事负责人Tiger Xu表示：“MSC在巴黎电竞世俱杯顺利收官，不仅意味着又一支世界级冠军战队的诞生，也让我们看到MLBB全球电竞正在进入一个新的时代。我们看到MSC不再只是少数传统强区主导的舞台，而是在吸引更多赛区、更多选手不断突破。未来，我们也将继续通过更开放的全球赛事结构、更高水平的竞技内容和更广泛的生态合作，持续推动MLBB国际影响力的提升。”&lt;/p&gt;</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0812%2F7cd9b7b7j00tjn7qt006ed000fc008mg.jpg&amp;thumbnail=660x2147483647&amp;quality=80&amp;type=jpg</t>
-        </is>
-      </c>
+      <c r="A15" s="2" t="inlineStr"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>《逃离塔科夫》前首席游戏设计师加盟Nomion Games，出任创意总监</t>
+          <t>Flandre出师不利，BLG 1-2遭JDG逆转吃到赛段第二败</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -924,31 +963,44 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>8月7日，Nomion Games宣布，曾任《逃离塔科夫》首席游戏设计师的让·秋列格诺夫(Jean Tyulegenov)已加入工作室并出任创意总监，负责《Rush is Real》的创意方向和开发工作。
-《Rush is Real》于2026年2月底首次公开，当时团队将其定位为一款“高风险射击游戏”，项目仍处于实验和原型开发阶段。Nomion Games本次进一步介绍了秋列格诺夫在新作中的职责及设计思路。
-曾参与《逃离塔科夫》多项核心系统
-秋列格诺夫于2017年加入《逃离塔科夫》开发商Battlestate Games，并于2026年5月公开确认离职，在该工作室任职约九年。
-秋列格诺夫在书面采访中回顾称，他入职时主要负责任务设计，约半年后开始组建并领导游戏设计团队，此后长期担任首席游戏设计师。他表示，自己曾参与武器和护甲数值设定、跳蚤市场经济平衡、任务及部分地图区域设计，以及Boss、AI和游戏内活动等内容，同时负责团队管理、危机处理，并参与产品决策、展会和社区沟通等工作。
-他尤其提到AI开发的复杂性：大量遗留代码、Unity的NavMesh寻路、实时PvP及可开关或上锁的门相互叠加，AI还依赖动画、墙体弹道判定和服务器端等系统，很难穷尽游戏中可能出现的所有情况。
-谈及离职原因，他的回答是“想创造新的东西”。《逃离塔科夫》1.0于2025年11月15日正式推出并登陆Steam。他认为，经过多年开发，游戏框架已经趋于成熟，而自己希望把精力投入新的游戏构想。
-《Rush is Real》主打高风险对局，观众机制仍在构思
-Nomion Games将《Rush is Real》称为一款“高风险射击游戏”。团队此前表示，本作并非传统撤离射击或大逃杀，而是介于两者之间的实验性项目。据目前介绍，玩家、观众和场上环境都可能影响战局，玩家必须不断行动，一味等待将难以取胜。
-秋列格诺夫表示，《Rush is Real》的核心构想早在他参与《逃离塔科夫》开发期间便已出现，如今团队希望在这款新作中实现这一构想。
-按照这一思路，团队计划先围绕一项原创机制搭建游戏，再加入射击、成长等玩家熟悉的系统。新作还将探索更多样的获胜条件，不过这也增加了关卡设计的复杂度，团队希望避免相关设计过度堆叠。
-团队还在构思观众介入对局的方式。按照秋列格诺夫的设想，无论通过游戏内观战还是直播平台观看，观众未来都可能像体育赛事观众一样，间接影响战局。不过，这项机制目前仍处于构思阶段，具体实现方式尚未确定。
-目前，《Rush is Real》尚未公布发售平台和发售时间，更多玩法细节及公开测试安排有待后续披露。</t>
+          <t>&lt;p&gt;　　北京时间8月12日，BLG 1-2被JDG逆转，遭遇赛段第二败。&lt;/p&gt;
+&lt;p&gt;　　JDG选用：兰博 皇子 维克托 烬 泰坦&lt;/p&gt;
+&lt;p&gt;　　BLG选用：狼母 赵信 辛德拉 EZ 卡尔玛&lt;/p&gt;
+&lt;p&gt;　　第8分钟，Vampire泰坦控住卡尔玛，随后HongQ维克托将其击杀；&lt;/p&gt;
+&lt;p&gt;　　第22分钟，Xun赵信控住维克托并将其击败，随后配合队友击杀泰坦，BLG打出2换4；&lt;/p&gt;
+&lt;p&gt;　　第30分钟，小龙处，Flandre狼母开到泰坦，随后Knight辛德拉打出高额伤害击杀JDG四人，BLG打出1换5并推平基地赢下比赛。&lt;/p&gt;
+&lt;p&gt;　　本局MVP给到输出拉满的Knight！&lt;/p&gt;
+&lt;p&gt;　　BLG选用：纳尔 盲僧 阿卡丽 卢锡安 米利欧&lt;/p&gt;
+&lt;p&gt;　　JDG选用：鳄鱼 蝎子 蛇女 霞 洛&lt;/p&gt;
+&lt;p&gt;　　第2分钟，Junjia蝎子来到下路，抓到Viper卢锡安拿下一血；&lt;/p&gt;
+&lt;p&gt;　　第10分钟，Knight阿卡丽在中路完成对HongQ蛇女的单杀；&lt;/p&gt;
+&lt;p&gt;　　第15分钟，JDG将所有技能都交给了ON米利欧，BLG找到机会秒掉Gala霞，后续卢锡安完全没人能限制，BLG打出2换4；&lt;/p&gt;
+&lt;p&gt;　　第20分钟，Flandre纳尔从先锋上下来后怒气不好，和Knight阿卡丽被分别击杀，JDG打出0换2并收下听牌龙；&lt;/p&gt;
+&lt;p&gt;　　第25分钟，JunJia蝎子控住纳尔，随后GALA霞打出高额伤害砍下三杀，JDG打出零换五并推平基地扳回一局。&lt;/p&gt;
+&lt;p&gt;　　本局MVP给到Junjia！&lt;/p&gt;
+&lt;p&gt;　　JDG选用：武器 梦魇 兔子 寒冰 萨勒芬妮&lt;/p&gt;
+&lt;p&gt;　　BLG选用：慎 纳亚菲利 狐狸 爆弹 牛头&lt;/p&gt;
+&lt;p&gt;　　第3分钟，Junjia梦魇来到中路抓到Knight狐狸拿下一血，Xun赶来收掉HongQ；&lt;/p&gt;
+&lt;p&gt;　　第8分钟，Gala寒冰大招命中中路Knight狐狸，HongQ兔子补上伤害将其击杀；&lt;/p&gt;
+&lt;p&gt;　　第16分钟，BLG虽然抢下先锋，但是上野都被击杀，JDG领先达到5k；&lt;/p&gt;
+&lt;p&gt;　　第23分钟，BLG阵型太差，Xiaoxu武器进场没人可以阻止，JDG打出2换4收下大龙；&lt;/p&gt;
+&lt;p&gt;　　第25分钟，Knight狐狸连续两波亲到，BLG拿下两颗赏金人头；&lt;/p&gt;
+&lt;p&gt;　　第27分钟，Xiaoxu武器拖了太久的时间且换掉一个，JDG其他人赶来后击杀BLG其他四人；&lt;/p&gt;
+&lt;p&gt;　　第28分钟，JDG推高地时遭到反打，BLG打出1换5团灭JDG；&lt;/p&gt;
+&lt;p&gt;　　第31分钟，Vampire萨勒芬妮开到两人，Junjia梦魇进场击杀爆弹，虽然Knight狐狸尽力收到两人，但Xiaoxu武器接管了残局；&lt;/p&gt;
+&lt;p&gt;　　第34分钟，JDG打出团灭上路一波结束比赛！&lt;/p&gt;</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0812%2Fad44e948j00tjmwoa00ind000j300ayg.jpg&amp;thumbnail=660x2147483647&amp;quality=80&amp;type=jpg</t>
+          <t>https://inews.gtimg.com/om_bt/ObNTexbhNV-gNXcABYBEyK7c71x4XUYL7dpy66Ksfq6kAAA/641</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Pearl Abyss二季度利润暴涨7411%，《红色沙漠》首个DLC年内推出</t>
+          <t>米哈游《未定事件簿》音乐会首秀即出圈，六周年“回忆杀”让玩家泪洒现场</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
@@ -958,29 +1010,43 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>IT之家 8 月 12 日消息，凭借《红色沙漠》的成功，Pearl Abyss 已经成为游戏行业最具影响力的开发商之一。这款游戏上市后销量迅猛，不仅取得了亮眼的商业成绩，也为开放世界游戏树立了新的标杆。如今，这些成绩已经开始反映在公司的季度业绩中。
-Pearl Abyss 公布了 2026 年第二季度财报，创下公司历史最佳季度业绩。报告显示，公司第二季度销售额达到 1,962 亿韩元（IT之家注：现汇率约合 9.36 亿元人民币），营业利润达到 676 亿韩元（现汇率约合 3.23 亿元人民币），均创下二季度业绩历史新高。
-其中，销售额同比大增 247.7%，营业利润更是同比暴涨 7411%。Pearl Abyss 表示，这一成绩主要得益于《红色沙漠》的巨大成功。
-随着游戏后续内容陆续推出，预计其未来几个月仍将为公司带来可观收益。
-Pearl Abyss 的 2026 年第二季度财报还显示，公司净利润从 2025 年第二季度的 227 亿韩元（现汇率约合 1.08 亿元人民币）亏损，扭转为本季度 995 亿韩元（现汇率约合 4.75 亿元人民币）的净利润。
-不过，与第一季度相比，公司第二季度的销售额和营业利润均有所下降。第二季度销售额环比下降 41.4%，营业利润环比下降 68.1%。这主要是因为《红色沙漠》带来的业绩增长在上一季度更加明显。
-尽管如此，《红色沙漠》依然贡献了 Pearl Abyss 第二季度约 70% 的营收，同时占公司海外销售收入的 91%。
-换句话说，《红色沙漠》已经成为一款真正意义上的全球爆款游戏。Pearl Abyss 此前还确认，该游戏仅用 26 天就卖出了超过 500 万份。
-对于《红色沙漠》的未来，Pearl Abyss 也已经制定了雄心勃勃的计划。公司表示，游戏首个 DLC 将在 2026 年年底前推出，具体内容预计会在第三季度公布。此外，《红色沙漠》预计将于 2027 年上半年登陆任天堂 Switch 2。
-Pearl Abyss 表示：“我们目前正在开发首个 DLC，目标是带来全新的游戏体验，并计划在今年内推出。”
-如果首个 DLC 取得良好成绩，并获得玩家积极反馈，Pearl Abyss 还计划继续为《红色沙漠》开发更多 DLC 内容。</t>
+          <t>&lt;img src="https://inews.gtimg.com/om_bt/ObNTexbhNV-gNXcABYBEyK7c71x4XUYL7dpy66Ksfq6kAAA/641" alt="https://inews.gtimg.com/om_bt/ObNTexbhNV-gNXcABYBEyK7c71x4XUYL7dpy66Ksfq6kAAA/641" /&gt;
+&lt;img src="https://inews.gtimg.com/om_bt/O6JQyZa43-gs8_i5reZ4rQVz5ALDPGgOLrXIhdcnKpNWwAA/641" alt="https://inews.gtimg.com/om_bt/O6JQyZa43-gs8_i5reZ4rQVz5ALDPGgOLrXIhdcnKpNWwAA/641" /&gt;
+&lt;p&gt;　　有人改签机票，有人盛装打扮，有人蹲点抢票，都为奔赴一场8月的音乐之约。&lt;/p&gt;
+&lt;p&gt;　　为庆祝开服六周年，2026年8月7日至9日，米哈游旗下现象级游戏《未定事件簿》“心乐未名”音乐会（英文：Stellis Serenade）在上海前滩31演艺中心大剧场连续三晚上演，每场演出时长不低于100分钟。这是《未定事件簿》自2020年7月30日上线以来举办的首届线下音乐会，也是继《原神》交响音乐会全球巡演、《崩坏：星穹铁道》“星铁LIVE”演唱会之后，米哈游在拓宽音乐会内容量级上的又一重要实践。&lt;/p&gt;
+&lt;p&gt;　　当第一声旋律响起，已有人悄然落泪&lt;/p&gt;
+&lt;p&gt;　　7月22日12时，“心乐未名”音乐会门票通过猫眼演出平台独家发售，开票后迅速售罄。这一场景，是六年深厚情感积累的集中释放。此外，官方专门开发了游戏等级核验功能——玩家需完成账号认证绑定方可购票。这一设计既保障了核心用户群体的参与权益，也为演艺行业探索“数字账号与实体票务打通”提供了新样本。&lt;/p&gt;
+&lt;img src="https://inews.gtimg.com/om_bt/O-xdAKDO8Vpc-clHkPQBp3Y-V89mW8gZL2QVpPP42Gl8IAA/641" alt="https://inews.gtimg.com/om_bt/O-xdAKDO8Vpc-clHkPQBp3Y-V89mW8gZL2QVpPP42Gl8IAA/641" /&gt;
+&lt;p&gt;　　演艺中心外的楼梯与商场内部均已装扮一新，巨幅海报格外醒目。不少“律师小姐”（游戏对玩家的称呼）上午10点便前来拍照打卡。9日受台风影响，立牌、花篮等装饰物被移至室内，在确保安全的同时，也不让玩家留下遗憾。&lt;/p&gt;
+&lt;p&gt;　　晚间7点半，演艺大厅几乎座无虚席。暗红帷幕缓缓升起，第一个音符流出，记者耳边已传来小声啜泣。《未定事件簿》为何如此触动人心？这款市面上鲜见的现实题材游戏，已陪伴玩家走过六年光阴。它不以奇幻异世界的毁天灭地、生死诀别取胜，而是用细腻笔触勾勒身边故事，刻画情与法的冲突。&lt;/p&gt;
+&lt;img src="https://inews.gtimg.com/om_bt/Ohmp2biZJ73YkEdhr5rXRcZmZPzySweGDOfD01CyJEsDgAA/641" alt="https://inews.gtimg.com/om_bt/Ohmp2biZJ73YkEdhr5rXRcZmZPzySweGDOfD01CyJEsDgAA/641" /&gt;
+&lt;p&gt;　　曲目编排从游戏一周年一路延展至六周年，串联起大量玩家熟悉的角色个人曲、活动主题曲及联动曲目。坚持调查真相而被害的记者孔茉莉，身在黑暗心向光明的艺人梨奈，因屡受伤害而一步步滑入深渊的杭嘉和……这些“剧中人”仿佛就在我们身边，令人深深共情。&lt;/p&gt;
+&lt;img src="https://inews.gtimg.com/om_bt/Oj5Zczw2Vof7XZOPozxTjOfc85NaUdv9ZQwRzZ7mQ6amUAA/641" alt="https://inews.gtimg.com/om_bt/Oj5Zczw2Vof7XZOPozxTjOfc85NaUdv9ZQwRzZ7mQ6amUAA/641" /&gt;
+&lt;p&gt;　　演出特别设计了充满记忆点的互动环节：四位男主角的标志性人偶相继登台，夏彦展示戒指，左然挥手致意，莫弈悠然品茶。不少玩家在现场感动落泪，社交平台上的自发传播迅速形成现象级讨论。剧院外广场设有主题氛围打卡点与集章活动，完成集章可兑换限量扇子周边，将游戏视觉符号与现实文化消费深度绑定，进一步强化了玩家在剧场内外的沉浸式体验。&lt;/p&gt;
+&lt;p&gt;　　8月9日，音乐会同步在官方微博、B站、微信视频号、小红书、抖音等主流平台进行线上放映，将现场的感染力延伸至更广泛的数字空间，引发玩家热烈反响。&lt;/p&gt;
+&lt;p&gt;　　9城联动，一次有纵深的跨界联动协作&lt;/p&gt;
+&lt;p&gt;　　为了赶赴这场六年之约，不少“律师小姐”各显神通。“幸好赶上了。”小洛刚下高铁，便拎着行李箱直奔演艺中心。她原本预订的北京飞往上海航班受台风影响停飞，9日一早果断改乘高铁，才得以准时抵达。&lt;/p&gt;
+&lt;img src="https://inews.gtimg.com/om_bt/O7gWjUx-zbhaVbBCBp3dUnKiToMAyxKkYloC36xHFdC1AAA/641" alt="https://inews.gtimg.com/om_bt/O7gWjUx-zbhaVbBCBp3dUnKiToMAyxKkYloC36xHFdC1AAA/641" /&gt;
+&lt;p&gt;　　“依维可”是今年刚参加工作的职场新人，接触《未定事件簿》已有五年。这次她购买了最前排的座位，热衷于参加各类游戏线下活动，今年已去过BilibiliWorld（BW）等展会，抢票经验颇为丰富。为保持观演的新鲜感，她这段时间特意屏蔽了音乐会的宣传，希望收获最完整的现场体验。&lt;/p&gt;
+&lt;p&gt;　　上海首演之外，“心乐未名”的辐射半径远不止于此。8月9日，米哈游联动QQ音乐，在广州、深圳、杭州、天津、成都、重庆、武汉、郑州8座城市同步开启线下观影活动。活动于当晚20时开场，预计时长约100分钟。观影套餐涵盖QQ音乐超级会员双月卡、观影票及周边伴手礼，通过QQ音乐APP独家购买，实现了演艺内容从剧场向全国影院场景的有效延伸。&lt;/p&gt;
+&lt;img src="https://inews.gtimg.com/om_bt/OI6qBH3Wyh3slZsoYImA7y2Yx28v7mfyILFDiR6UmzZnwAA/641" alt="https://inews.gtimg.com/om_bt/OI6qBH3Wyh3slZsoYImA7y2Yx28v7mfyILFDiR6UmzZnwAA/641" /&gt;
+&lt;p&gt;　　城市推广层面，活动联动猫眼演出、淘宝88VIP，在上海及全国9座城市的核心地段投放大屏广告，上海全市楼宇广告更从8月3日起覆盖整个演出周期，以城市级传播声量托举现场热度。8座联动城市的指定影院检票口外，专属合影立牌同步设置，供观众打卡留念，构建起一套涵盖剧场、影院、城市公共空间的立体触达网络。&lt;/p&gt;
+&lt;p&gt;　　值得关注的是，此次活动中，米哈游与QQ音乐、酷狗音乐、猫眼演出、淘宝88VIP等多个头部平台实现了深度联动。其中，米哈游与QQ音乐、酷狗音乐的联名装扮套装亦将于不久后上线，将音乐会的文化热度进一步向数字音乐消费场景延伸。&lt;/p&gt;
+&lt;p&gt;　　这一跨界协作模式，折射出国产游戏产业内容生态日趋成熟的现实——游戏企业不再满足于单一的线上流量运营，而是主动与演艺、音乐、票务、广告等行业深度融合，以IP内容为核心资产，构建起覆盖线上线下、横跨多个消费场景的文化产业链条。&lt;/p&gt;
+&lt;p&gt;　　助力“文商旅体展”，彰显国产游戏企业的文化担当&lt;/p&gt;
+&lt;p&gt;　　本次音乐会落地前滩，是上海推进“文商旅体展”联动发展的一次生动实践。演出期间，周边商圈客流与消费显著提振，文旅体验、文创产品销售同步拉升，持续放大上海在文化创意产业中的溢出效应，为城市文化经济的高质量发展注入新动能。&lt;/p&gt;
+&lt;img src="https://inews.gtimg.com/om_bt/OHxcZUf8ZrikBZu09sL0ZpACmRgl5rEPjnoi0l9KeK680AA/641" alt="https://inews.gtimg.com/om_bt/OHxcZUf8ZrikBZu09sL0ZpACmRgl5rEPjnoi0l9KeK680AA/641" /&gt;
+&lt;p&gt;　　小奈是一位从江苏来上海听音乐会的“妆娘”（化妆师），一袭红裙的她在打卡队伍中格外活跃，不断与人交流。她说，来听音乐会之前，已为四位女生完成化妆造型。近年来，国内二次元产业迅速发展，对妆造的需求急剧攀升，她的预约档期排得非常满。小奈自述，在《未定事件簿》四周年时成为玩家，想要快速接近自己喜欢的内容，参加线下活动是最直接的方式。“我对这次音乐会非常期待，7号就到上海了，除了打卡未定相关内容，还去了新天地等多个动漫快闪店。”她说。&lt;/p&gt;
+&lt;p&gt;　　游戏音乐会的兴起，是近年来中国文化产业深层融合的缩影。随着国产游戏在音乐、美术、叙事等维度积累日益深厚，将原创游戏音乐搬上专业舞台，已从小众尝试逐步成长为可复制、可规模化的文化路径。它模糊了“玩游戏”与“看演出”的边界，也为演艺行业引入了一大批原本游离于剧场之外的年轻受众。这种双向赋能，正在重塑中国年轻一代的文化消费图景。&lt;/p&gt;
+&lt;p&gt;　　米哈游以“心乐未名”音乐会为载体，将虚拟世界的音乐情感转化为现实舞台上的共鸣，既是对游戏IP价值的深度挖掘，也是国产文化企业主动承担文化传播责任、服务人民精神文化需求的生动实践。这场音乐会作为上海“文商旅体展”联动发展的创新样本，带动了周边商圈消费、文旅体验及文创产品销售，持续放大着上海文化创意产业的溢出效应。&lt;/p&gt;</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0812%2F7f71d484j00tjnicx0027d200m900cjg00m900cj.jpg&amp;thumbnail=660x2147483647&amp;quality=80&amp;type=jpg</t>
-        </is>
-      </c>
+      <c r="A17" s="2" t="inlineStr"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>腾讯财报：上半年游戏收入超1300亿，三角洲和无畏契约日活破新高</t>
+          <t>“终止合作，永久列入黑名单”</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
@@ -990,36 +1056,25 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>成为全球游戏行业最具影响力的价值连接者
-刚刚，腾讯发布了2026上半年财报。财报数据显示，腾讯上半年收入4012.43亿元，同比10%，公司权益持有人应占盈利增长1141.15亿元，同比增长10%。
-聚焦游戏业务来看，腾讯上半年国内游戏收入927亿元，海外市场收入374亿元，合计1301亿元。仅看第二季度，国内游戏市场收入473亿元，同比增长17%；国际游戏市场收入186亿元，剔除汇率影响同比增长4%，仍保持增长。
-在财报中出现的重点产品包括《三角洲行动》与《无畏契约》，被提及“平均日活用户数在第二季度创下新高”；《洛克王国：世界》，被提及为今年中国市场所有新上线手游中平均日活用户数和流水总数排名第一；《Arrows – Puzzle Escape》（腾讯子公司Miniclip旗下产品），被提及为2026年第二季度全球下载量最高的手游。
-除了以上游戏，明确带来了增长的还有《无畏契约手游》《鸣潮》《VALORANT》（无畏契约国际版）《PUBG MOBILE》以及《王者荣耀》。
-简单聊下2026年我们看到的腾讯游戏变化。
-在腾讯游戏业务的增长逻辑中，长青产品是核心焦点。尽管较少公布新数据，但游戏日报观察到，2026年腾讯头部长青都有了比往年更积极的运营动作。
-比如“无畏巡回”已经跑完了广州杭州北京长沙4所城市，，每一站热度都在明显拔高；《和平精英》在、、主题玩法、上多点开花，据了解，上周刚结束刺激之夜已经拿下了360多个热搜；
-《王者荣耀》也进一步走了出来，包括第一次参展BW，，让更多玩家得以线下相聚；还有《三角洲行动》，今年在各个城市落地线下活动的频次极高，成了，也摸索出了.....
-这些举动在为腾讯游戏拓盘争夺更多用户注意力。
-另外值得注意的是，即将上线满1年的“手瓦”（《无畏契约手游》）基本已锁定腾讯“长青产品”（季度平均日活500万以上，年收入40亿元以上）的新席位——今年手瓦先后公布了破1000万DAU，等数据，其在iOS畅销榜上也常稳居TOP5。
-再说新品。
-今年上半年，腾讯总计上线了6款新游，分别是三款自研产品-王者IP大世界《王者荣耀世界》、捉宠开放世界《洛克王国：世界》以及PVE射击《逆战：未来》；三款代理产品-卡牌格斗《全明星觉醒》、回合制RPG《三国志异闻录》以及二次元卡牌《卡厄斯梦境》。
-这其中有部分产品给腾讯带来了可见的增长，例如《洛克王国：世界》《逆战：未来》都曾登顶iOS畅销榜，前者首月冲至日均1300万DAU，，后者则填补了移动PVE射击的空白，且。
-另外一款备受关注的新品《王者荣耀世界》最高排名16位，虽然成绩难说理想，但也是，打开了IP再成长的更多可能性。
-顺带谈谈下半年可以重点关注的新品。目前已知的大产品有，相比于开放世界的极度内卷，万象棋涉足的赛道仍旧相对蓝海；另外包括《命运扳机》《彩虹六号》《战术小队》在内的射击新品，也会再探腾讯射击品类大盘增长的新可能性，其中部分产品有在2026年公测的可能性。
-至于更多腾讯储备产品，我们报道过较多次，
-总结来说，我们认为腾讯在2026下半年仍旧有稳定增长的趋势。</t>
+          <t>&lt;p&gt;　　米哈游人气产品《原神》。&lt;/p&gt;
+&lt;p&gt;　　此前，米哈游在官方账号“派蒙的工作笔记”发文回应创作者被合作方拖欠酬劳的情况。声明表示，米哈游陆续收到部分创作者反映，其通过云南昊曦文化传媒有限公司承接的合作款项未能按约收到。“我们非常理解创作者面临的困难并高度重视，于第一时间建立起专项沟通渠道，目前已和百余位受影响的创作者取得联系，持续跟进后续诉求。”&lt;/p&gt;
+&lt;p&gt;　　经核查，米哈游与云南昊曦的合作款项，已按合同约定及履约进度进行结算。米哈游已在上周致函云南昊曦，要求其尽快妥善处理与创作者之间的报酬纠纷。然而，云南昊曦在收到律师函后不仅未采取任何解决措施，也无积极沟通的表态。“上述行为已严重损害创作者合法权益，也对米哈游与创作者之间的信任关系造成了极大伤害。”&lt;/p&gt;
+&lt;p&gt;　　米哈游方面表示，目前已终止与云南昊曦的合作，将其永久列入《米哈游黑名单合作方清单》。米哈游还将继续支持创作者依法维权，并积极配合司法机关，提供必要的材料与协助。&lt;/p&gt;
+&lt;p&gt;　　米哈游方面提醒，本次事件中尚未与米哈游取得联系的受影响创作者，可通过米游社或游戏内联系官方客服，公司将于5个工作日内安排专人对接。&lt;/p&gt;
+&lt;p&gt;　　8月3日，米哈游品牌相关负责人向南都记者表示，米哈游始终将创作者权益置于重要位置，将持续与相关创作者保持沟通，后续进展将第一时间对外公开。&lt;/p&gt;
+&lt;p&gt;　　公开信息显示，米哈游成立于2011年，公司陆续推出了多款高品质人气产品，包括《崩坏学园2》《崩坏3》《未定事件簿》《原神》《崩坏：星穹铁道》《绝区零》及已曝光项目《崩坏：因缘精灵》《星布谷地》，并围绕原创IP打造了动画、音乐及周边等多元产品。&lt;/p&gt;</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0811%2F5049bf7ej00tjluov0027d001hc00u0g.jpg&amp;thumbnail=660x2147483647&amp;quality=80&amp;type=jpg</t>
+          <t>https://inews.gtimg.com/om_bt/OJnJkpNtFI9m43XG15yepdVf5pLtxBmzYLbaAjPgwCEJ8AA/641</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Remedy确认《马克思·佩恩1&amp;2》重制版仍在制作，R星负责发行</t>
+          <t>BW2026热度爆表，参展商突破170家创新高</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
@@ -1029,23 +1084,34 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>IT之家 8 月 11 日消息，据外媒 Inside Gaming 今天（11 日）报道，初代《马克思 · 佩恩》至今仍拥有数量可观的忠实玩家，玩家期待重制版已有多年。Remedy Entertainment 近期发布的报告再次确认，与 Rockstar Games 合作开发的《马克思 · 佩恩 1&amp;2》重制版仍在制作，只是目前还没有太多内容可以公开。
-Remedy 最新财报除了公布财务数据和愿望单数量，也回应了外界提出的问题，其中就包括《马克思 · 佩恩 1&amp;2》重制版的最新进展。
-此前在 2025 年 8 月，有消息确认 R 星正与 Remedy 合作开发《马克思 · 佩恩 1&amp;2》重制版。此次公布的 2026 年半年度报告则显示，项目仍在全面制作状态，但由于发行权掌握在 R 星手中，Remedy 目前无法公开更多信息。“很多问题都与《马克思 · 佩恩》有关，但 R 星负责该项目的发行，因此我们无法回答这些问题。”
-IT之家注：Remedy 旗下最具代表性的 IP 包括《心灵杀手》《控制》和《马克思 · 佩恩 1&amp;2》。
-R 星眼下还忙于《GTA 6》，重制版可能暂时不会成为公布消息的重点。不过，未来仍有望看到 R 星带来更多消息。</t>
+          <t>&lt;p&gt;　　7月10日，2026年哔哩哔哩世界数字娱乐动漫文化博览会（简称BW2026）在上海国家会展中心开幕。本届展会热度空前高涨，参展商超过170家，创历届新高。展会将持续至12日，日均观展客流规模预计达9万余人。&lt;/p&gt;
+&lt;p&gt;　　BW是国内动漫和游戏爱好者的一场盛会，早在上个月的售票阶段，今年的展会热度就已爆表，大会员票17秒售罄、普通票33秒抢空，展现出超高人气和吸引力。&lt;/p&gt;
+&lt;p&gt;　　展会首日，国家会展中心已是人潮涌动，观展市民在现场工作人员的引导下有序入场，完成随身物品安检并刷身份证验证后，顺利进入展馆。为满足参展观众的Cosplay需求，展会也特别为Cosplay观众设置通道，并在现场提供更衣间服务。&lt;/p&gt;
+&lt;img src="https://inews.gtimg.com/om_bt/OJnJkpNtFI9m43XG15yepdVf5pLtxBmzYLbaAjPgwCEJ8AA/641" alt="https://inews.gtimg.com/om_bt/OJnJkpNtFI9m43XG15yepdVf5pLtxBmzYLbaAjPgwCEJ8AA/641" /&gt;
+&lt;p&gt;　　IC photo&lt;/p&gt;
+&lt;p&gt;　　展馆内，170多家参展商设置了700多个展位，其中130家全球游戏厂商带来海量新作。展会9大主题展区涵盖游戏、动画、模玩、桌游、同人创作、虚拟主播等多个领域。&lt;/p&gt;
+&lt;p&gt;　　米哈游《崩坏：星穹铁道》携12米机甲亮相，《原神》今年再次回归BW；库洛游戏《鸣潮》打造以“玄鸟衔乐，风起梦州”为主题的展位；鹰角网络《明日方舟：终末地》展台则融入青瓦白墙国风建筑与高科技工业设备的设计。&lt;/p&gt;
+&lt;img src="https://inews.gtimg.com/om_bt/Op2uYe6yh-dxwosqnv_-rslbqEV_110VlbNLvGfQ3csrAAA/641" alt="https://inews.gtimg.com/om_bt/Op2uYe6yh-dxwosqnv_-rslbqEV_110VlbNLvGfQ3csrAAA/641" /&gt;
+&lt;p&gt;　　IC photo&lt;/p&gt;
+&lt;p&gt;　　《一盏秋声：锦衣卫》《猿公剑》等国产单机游戏在BW公开全新试玩，《黎明行者之血》《女神异闻录4 Revival》《刺客信条：黑旗 记忆重置》等多款海外游戏也在本届展会上亮相。&lt;/p&gt;
+&lt;img src="https://inews.gtimg.com/om_bt/OqlL_OrVhPebeV6gxYCeyTnIQE597-NHMz0Wnch5dTcscAA/641" alt="https://inews.gtimg.com/om_bt/OqlL_OrVhPebeV6gxYCeyTnIQE597-NHMz0Wnch5dTcscAA/641" /&gt;
+&lt;img src="https://inews.gtimg.com/om_bt/OUfQytFBizGQfBgBE4mPDqPuU6i_8_B5C-Riwtymd4tAgAA/641" alt="https://inews.gtimg.com/om_bt/OUfQytFBizGQfBgBE4mPDqPuU6i_8_B5C-Riwtymd4tAgAA/641" /&gt;
+&lt;p&gt;　　本届展会海外嘉宾阵容创下新高，超过30位国际行业重磅嘉宾空降现场，带来大量独家内容。例如，漫威影业总裁、首席创意官凯文·费奇时隔七年重返中国，在BW2026带来他的漫展首秀。&lt;/p&gt;
+&lt;p&gt;　　值得一提的是，今年是BW自2017年举办以来首次面向全球超过190个国家及地区同步售票，使得BW2026成为全国首个面向海外观众售票的综合性ACGN展会。&lt;/p&gt;
+&lt;p&gt;　　作为6月29日启幕的第二届上海国际游戏动漫月的重要组成部分，CCG EXPO、BilibiliWorld和Chinajoy三大展会于7月集中亮相，为动漫、游戏爱好者带来一场场盛会。动漫月将以8月24日完美世界DOTA2 2026全球邀请赛决赛作为收官，覆盖暑期消费黄金窗口期。&lt;/p&gt;
+&lt;p&gt;　　本文系观察者网独家稿件，未经授权，不得转载。&lt;/p&gt;</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0812%2F1e35f60cj00tjmr1y0024d000j300jng.jpg&amp;thumbnail=660x2147483647&amp;quality=80&amp;type=jpg</t>
+          <t>https://inews.gtimg.com/news_bt/OftE4KSPUQrrpQOebdg1Uy2Dt-r4d0kIGNaCJrbH1QY8EAA/641</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>《心灵杀手2》游戏全球销量超300万份</t>
+          <t>左手重锤，右手道歉：米哈游陷入彷徨</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -1055,23 +1121,66 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>IT之家 8 月 12 日消息，Remedy Entertainment 昨日（8 月 11 日）发布了 2026 年上半年（1~6 月）财报，总营收为 2,330 万欧元（IT之家注：现汇率约合 1.82 亿元人民币），同比下降 23.1%；营业利润亏损 290 万欧元（现汇率约合 2,260.8 万元人民币），而去年同期为盈利 80 万欧元（现汇率约合 623.7 万元人民币）。
-在 2026 年第 2 季度，该公司营收为 10.20 万欧元（现汇率约合 79.5 万元人民币），同比下降 40.0%；EBITDA（息税折旧摊销前利润）为 -240 万欧元（现汇率约合 -1,871 万元人民币）；营业利润（EBIT）为 -390 万欧元（现汇率约合 -3,040.3 万元人民币）。
-至于亏损原因，财报指出营收下降和亏损扩大主要是由于公司在 Q2 阶段为迎接秋季大作的发售，显著加大了市场推广和宣发支出。现金流状况整体保持稳健，期末现金及流动投资为 2,960 万欧元（现汇率约合 2.31 亿元人民币）。
-IT之家注：游戏方面，《控制：共振》（CONTROL Resonant）确认将于 2026 年 9 月 24 日全球同步发售，登陆 PC、PlayStation 5 和 Xbox Series X|S。截至 8 月中旬，该作的全平台愿望单（Wishlist）已突破 150 万，预购表现强劲。
-《心灵杀手 2》（Alan Wake 2）游戏全球累计销量已正式突破 300 万份，在发售后持续为公司带来稳定的长尾消费级收入和版税。</t>
+          <t>&lt;img src="https://inews.gtimg.com/news_bt/OftE4KSPUQrrpQOebdg1Uy2Dt-r4d0kIGNaCJrbH1QY8EAA/641" alt="https://inews.gtimg.com/news_bt/OftE4KSPUQrrpQOebdg1Uy2Dt-r4d0kIGNaCJrbH1QY8EAA/641" /&gt;
+&lt;p&gt;　　‍‍‍‍‍‍‍‍‍‍‍‍‍‍‍‍‍‍‍2026年8月的上海，酷暑未消。米哈游总部大楼里，两则几乎同时爆发的新闻，像两枚投向湖面的石子，在游戏行业激起层层涟漪。&lt;/p&gt;
+&lt;p&gt;　　一边是法务部的“胜利宣言”：两名B站UP主因提前泄露《原神》《崩坏：星穹铁道》《绝区零》的未公开版本视频，被法院以侵犯著作权罪分别判处有期徒刑一年二个月和一年，均适用缓刑。米哈游称之为“适用两高新司法解释后首例游戏泄密刑事案件”，措辞严厉，态度鲜明。&lt;/p&gt;
+&lt;p&gt;　　另一边是创作者们的“集体控诉”：上百名内容创作者通过云南昊曦文化传媒有限公司承接米哈游的合作项目，却迟迟收不到应得的酬劳。虽然米哈游迅速切割，将合作方永久拉黑，但“中间商赚差价、创作者喝西北风”的剧本，还是在社交媒体上引发了轩然大波。&lt;/p&gt;
+&lt;p&gt;　　一攻一守，一刚一柔，米哈游在这个夏天同时扮演着“维权斗士”和“被追责对象”的双重角色。这种戏剧性反差，恰恰折射出当下中国游戏行业最深刻的矛盾：当原创能力成为稀缺资产，当内容生态成为竞争核心，一家以“技术宅拯救世界”为slogan的公司，究竟该如何在平台巨头的阴影下，守住自己的星辰大海？&lt;/p&gt;
+&lt;p&gt;　　让我们先回到那起泄密案。&lt;/p&gt;
+&lt;p&gt;　　两名B站UP主，一个账号叫“真不想涩涩”，一个叫“风堇lover-兜兜”。他们在2025年7月开始，持续发布米哈游旗下多款游戏的未公开版本实机视频。苏某的视频点击量超过60万次，吴某超过30万次。最终，两人双双入狱。虽然是缓刑，但刑事案底的烙印，足以让任何年轻人的人生轨迹发生偏转。&lt;/p&gt;
+&lt;p&gt;　　米哈游在声明中说得情真意切：“每一帧还未公开的游戏内容，背后是创作团队的设计与打磨，也承载着每一位玩家对新版本的期待。”这话不假。对于《原神》这样采用“版本更新+角色卡池”商业模式的游戏来说，未公开内容就是最核心的商业机密。一次大规模泄密，可能直接摧毁一个版本周期的营销节奏，让精心策划的“惊喜”变成“旧闻”。&lt;/p&gt;
+&lt;p&gt;　　但如果我们把视野拉远，这次判决的意义远不止于米哈游一家。它标志着中国游戏行业对知识产权的保护，已经从民事索赔升级到了刑事追责。两高新的司法解释降低了入罪门槛，60万和30万的点击量，在短视频时代不过是中等体量的传播数据，却足以让发布者面临牢狱之灾。&lt;/p&gt;
+&lt;p&gt;　　这是一种“杀鸡儆猴”式的威慑，但也透露出一股被逼无奈的焦虑。&lt;/p&gt;
+&lt;p&gt;　　在游戏行业，泄密早已不是新鲜事。从早期的游戏杂志“偷跑”，到后来的内部测试泄露，再到如今的数据挖掘（datamining）和测试服解包，技术越进步，泄密的门槛越低。对于米哈游这样以“内容更新迭代”为核心卖点的公司来说，泄密是致命的——它摧毁的不是代码，而是“期待感”这种最脆弱也最昂贵的用户情感。&lt;/p&gt;
+&lt;p&gt;　　但刑事化的维权路径也引发了一个微妙的行业问题：当保护原创的拳头越来越硬，创作者生态的温情是否也在同步流失？米哈游在法庭上的强硬姿态，与几天后面对创作者讨薪时的被动局面，形成了一种颇具讽刺意味的对照。&lt;/p&gt;
+&lt;p&gt;　　如果说泄密案展现了米哈游作为“权利方”的锋利，那么创作者酬劳拖欠事件则暴露了它作为“平台方”的脆弱管理结构。&lt;/p&gt;
+&lt;p&gt;　　事情的脉络并不复杂：米哈游将部分创作者合作项目外包给云南昊曦文化传媒有限公司，后者作为中间商承接业务、分包给创作者。然而，当米哈游按约向昊曦结算了款项后，昊曦却没有把钱给到创作者手里。上百名创作者陷入“活干了、钱没拿到”的困境，最终只能将矛头指向米哈游。&lt;/p&gt;
+&lt;p&gt;　　米哈游的应对堪称教科书式的危机公关：第一时间建立专项沟通渠道，宣称已联系上百位创作者；致函昊曦要求解决，未果后迅速切割，将其永久列入黑名单；承诺配合司法机关，支持创作者依法维权。&lt;/p&gt;
+&lt;p&gt;　　但漂亮的公关，掩盖不了管理的缺位。&lt;/p&gt;
+&lt;p&gt;　　在游戏行业，UGC（用户生成内容）和PGC（专业生产内容）生态早已成为标配。腾讯有企鹅号、网易有网易号、米哈游有米游社和遍布B站、抖音的创作者矩阵。这些创作者不是员工，却承担着比员工更关键的市场职能——他们是游戏的“传教士”，是社区的“粘合剂”，是版本空窗期的“内容供应商”。&lt;/p&gt;
+&lt;p&gt;　　米哈游的问题在于，它既想享受创作者生态带来的流量红利，又不愿意直接承担管理这些“编外人员”的成本。通过第三方公司外包，看似降低了人力和管理负担，实则将品牌声誉置于不可控的风险之中。当创作者们发现自己被“层层转包”后成了最弱势的一环，他们对米哈游的信任崩塌，远比对一家名不见经传的文化传媒公司的愤怒来得猛烈。&lt;/p&gt;
+&lt;p&gt;　　这让人想起互联网行业的经典困境：平台型企业总是在“轻资产运营”和“重责任承担”之间摇摆。腾讯早年也经历过类似的创作者纠纷，最终选择逐步收紧外包、加强直签；字节跳动则通过巨量星图等工具，试图用技术手段规范交易流程。米哈游这次的教训是，当你把生态的毛细血管交给别人打理，一旦出血，公众只会看到衣服上的污渍，而不会去追究洗衣工的责任。&lt;/p&gt;
+&lt;p&gt;　　米哈游的这两件事，看似是彼此孤立的个案，但放在2026年的游戏行业大背景下，二者的接连发生串联起一个残酷的现实：中国游戏行业已经进入了“存量绞杀”时代，原创公司的生存空间正在被急剧压缩。&lt;/p&gt;
+&lt;p&gt;　　让我们看看数据。2024年，中国游戏市场实际销售收入增速已经降至个位数；2025年，版号发放虽然常态化，但用户时长和付费意愿的增长几乎停滞。更关键的是，玩家的口味被《原神》这样的产品“养刁了”，他们对画面品质、剧情深度、玩法创新的要求，已经逼近甚至超过了3A大作的标准。&lt;/p&gt;
+&lt;p&gt;　　这意味着什么？意味着游戏开发的成本在指数级上升，而回报却在边际递减。&lt;/p&gt;
+&lt;p&gt;　　米哈游是这场“军备竞赛”的发起者之一。《原神》上线时，业界惊叹于其开放世界的设计和跨平台的野心，但很少有人意识到，这种级别的投入正在重新定义行业的准入门槛。当米哈游用数亿美金和数百人的团队打磨一款游戏时，中小厂商根本没有能力跟进；而当腾讯、网易这样的巨头也开始all in开放世界和二次元赛道时，米哈游的先发优势正在快速被稀释。&lt;/p&gt;
+&lt;p&gt;　　这就是内卷的本质：不是大家都在做同样的事，而是标准越来越高，用户却不再增长。&lt;/p&gt;
+&lt;p&gt;　　腾讯的应对策略是“平台+投资”的双轮驱动。它不需要每一款游戏都自己研发，它只需要确保最好的游戏都在微信、QQ、应用宝上分发，同时通过投资库洛游戏、灵游坊等公司，卡住关键赛道。2025年，腾讯游戏业务收入依然稳健，靠的不是某一款爆款，而是整个生态系统的“蓄水池效应”。&lt;/p&gt;
+&lt;p&gt;　　网易则走了一条“精品化+全球化”的路子。《蛋仔派对》证明了它在社交游戏上的嗅觉，《逆水寒》手游展示了它用AI技术降本增效的能力。丁磊的哲学是：不做第一个吃螃蟹的，但要做把螃蟹做得最好吃的。&lt;/p&gt;
+&lt;p&gt;　　而米哈游呢？它依然是一家“单核驱动”的公司。《原神》之后，《崩坏：星穹铁道》表现不俗，《绝区零》也收获了核心玩家的认可，但客观来说，还没有一款产品能达到《原神》的现象级高度。更关键的是，米哈游的商业模式高度依赖“新鲜感”——玩家通关了剧情、抽齐了角色，就会进入长草期。为了维持日活，公司必须保持高强度的版本更新，这意味着研发团队永远在“赶工期”，创作者生态永远在“填内容”，而泄密的风险，也永远悬在头顶。&lt;/p&gt;
+&lt;p&gt;　　米哈游与腾讯、网易的根本差异，不在于产品类型，而在于商业哲学的分野。&lt;/p&gt;
+&lt;p&gt;　　腾讯是“平台逻辑”的代表。它的核心资产不是某一款游戏，而是连接10亿用户的社交网络。游戏对腾讯来说，是流量的变现工具，是社交关系的润滑剂。因此，腾讯可以容忍游戏的失败，只要平台还在，下一款游戏总能找到用户。这种逻辑的优势是抗风险能力强，劣势是创新动力不足——毕竟，为什么要冒险做一款颠覆性的产品，去动摇自己现有的现金牛呢？&lt;/p&gt;
+&lt;p&gt;　　网易是“运营逻辑”的集大成者。它擅长把一款游戏的长线运营做到极致，通过精细化的活动策划、社交系统设计和付费点挖掘，让产品的生命周期远超行业平均。网易的游戏往往“慢热”但“长寿”，这背后是强大的运营中台和数据分析能力。&lt;/p&gt;
+&lt;p&gt;　　米哈游则是“内容逻辑”的信徒。它相信好内容自带传播力，相信“技术宅”的审美可以征服世界，相信IP的力量可以跨越国界。从《崩坏学园2》到《原神》，米哈游的成长史就是一部“内容逆袭平台”的励志剧。它证明了，在没有腾讯流量加持的情况下，一家纯靠产品力的公司也能做到全球月活过亿、年营收数百亿。&lt;/p&gt;
+&lt;p&gt;　　但“内容逻辑”有一个致命的弱点：它极度依赖创始团队的审美和执行力，且难以规模化复制。&lt;/p&gt;
+&lt;p&gt;　　蔡浩宇、刘伟、罗宇皓三位创始人，是米哈游的灵魂。他们对二次元的理解、对技术美术的追求、对玩家社区的共情，构成了米哈游的核心竞争力。但这种竞争力是“人治”的，而非“制度”的。当公司从几百人扩张到数千人，当创始人逐渐退居幕后，当新一代产品经理需要在“延续经典”和“大胆创新”之间做选择时，米哈游是否还能保持那份“技术宅”的纯粹？&lt;/p&gt;
+&lt;p&gt;　　更重要的是，“内容逻辑”在面对“平台逻辑”时，天然处于弱势。腾讯可以投资你的竞争对手，可以在微信里给你的游戏限流，可以用《王者荣耀世界》正面硬刚《原神》。平台掌握的是“基础设施”，内容掌握的是“上层建筑”——在历史的大多数时间里，基础设施的拥有者总是更强势的一方。&lt;/p&gt;
+&lt;p&gt;　　2011年，三个上海交大的学生在宿舍创办了米哈游。没人会想到，这个曾经差点因为融不到资而夭折的小团队，会在十几年后成为中国游戏行业的“第三极”。&lt;/p&gt;
+&lt;p&gt;　　但“新星”的光芒总是短暂的。要成为“恒星”，米哈游必须跨越三道鸿沟。&lt;/p&gt;
+&lt;p&gt;　　第一道鸿沟：从“单一爆款”到“产品矩阵”。&lt;/p&gt;
+&lt;p&gt;　　《原神》太成功了，成功到它既是米哈游的皇冠，也是它的枷锁。资本市场和玩家都在问：下一款《原神》在哪里？米哈游正在用《崩坏：星穹铁道》和《绝区零》回答这个问题，但似乎还不够响亮。真正的游戏巨头，需要的是一个能够持续产出高质量产品的“pipeline”，而不是押注于某一款神作的降临。&lt;/p&gt;
+&lt;p&gt;　　第二道鸿沟：从“创作者生态”到“平台治理能力”。&lt;/p&gt;
+&lt;p&gt;　　这次创作者酬劳风波给米哈游敲响了警钟。当你拥有数百万的社区创作者、数千万的UGC内容时，你已经不再是一家单纯的游戏公司，而是一个“准平台”。平台需要规则、需要治理、需要承担社会责任。米哈游必须建立更完善的创作者权益保障机制，而不是在出事后才被动切割。&lt;/p&gt;
+&lt;p&gt;　　第三道鸿沟：从“内容信仰”到“商业韧性”。&lt;/p&gt;
+&lt;p&gt;　　米哈游的文化里有一种理想主义的底色，这让它在创业阶段能够吸引顶尖人才、作出突破性产品。但在存量竞争时代，理想主义需要与商业理性握手言和。这意味着更精细化的成本控制、更多元化的收入来源、更灵活的全球化策略。米哈游已经开始布局AI、云游戏、动画电影等领域，但这些探索能否转化为真正的第二曲线，还有待时间检验。&lt;/p&gt;
+&lt;p&gt;　　2026年的夏天，米哈游站在一个微妙的十字路口。&lt;/p&gt;
+&lt;p&gt;　　它的左边，是知识产权的坚固城墙——泄密者被判刑，彰显了原创的尊严；它的右边，是创作者生态的裂缝——外包管理的失控，暴露了平台的稚嫩。它的前方，是腾讯、网易等巨头的步步紧逼，是行业增速放缓的凛冬将至；它的身后，是《原神》带来的辉煌记忆，是“技术宅拯救世界”的初心。&lt;/p&gt;
+&lt;p&gt;　　米哈游的故事，本质上是中国游戏行业从“渠道为王”向“内容为王”转型的一个缩影。它证明了原创的力量，也暴露了原创的脆弱。它让我们看到，在一个内卷到极致的市场里，即便是最有才华的创作者，也不得不在法律、商业、生态的重重铁幕下，艰难地寻找属于自己的星光。&lt;/p&gt;
+&lt;p&gt;　　也许，米哈游最终无法成为下一个腾讯或网易。但那未必是坏事。中国游戏行业需要的，不是第二个平台巨头，而是更多像米哈游这样，愿意为了“一帧未公开的游戏内容”不惜诉诸刑律、为了“技术宅的梦想”敢于 挑战行业格局的“偏执者”。&lt;/p&gt;
+&lt;p&gt;　　只是，偏执者要想走得更远，必须学会在理想与现实之间，找到那个最艰难的平衡点。&lt;/p&gt;
+&lt;p&gt;　　这，才是米哈游真正的“未定事件簿”。&lt;/p&gt;</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0811%2Fd9caef70j00tjlvl5006yd000u0017tg.jpg&amp;thumbnail=660x2147483647&amp;quality=80&amp;type=jpg</t>
+          <t>https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0813%2Faecb2bd0j00tjosqj000jd000fa008lg.jpg&amp;thumbnail=660x2147483647&amp;quality=80&amp;type=jpg</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>《剑星》开发商Shift Up 3A新作Spirits更多细节</t>
+          <t>《Big Walk》大火 开发商却想开摆？</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -1081,26 +1190,24 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>《剑星》开发商Shift Up正开发多个大作。除了续作《剑星：血雨》，该公司还在开发代号为Spirits的3A游戏，计划年内公布，将采用即时服务模式。
-Spirits：
-- 基于“东方幻想”宇宙打造的3A级游戏
-- Shift Up下一款旗舰作品及核心项目
-- 在高效且结构良好的开发流程下顺利推进
-- 目标为全球跨平台实时服务
-- 计划于2026年内揭晓
-- “我们专注于打造一款高度精致的游戏，将我们积累的开发能力和实时服务经验融为一体。”</t>
+          <t>&lt;p&gt;　　据gamesradar+报道，《Big Walk》成为2026年评价最高的游戏之一，但开发商House House表示目前没有后续内容计划，团队希望先好好休息。&lt;/p&gt;
+&lt;img src="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0813%2Faecb2bd0j00tjosqj000jd000fa008lg.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" alt="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0813%2Faecb2bd0j00tjosqj000jd000fa008lg.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" /&gt;
+&lt;p&gt;　　House House在论坛问答中谈到了《Big Walk》及工作室的未来。开发团队表示，游戏一路开发至今耗费了大量时间和精力，因此目前还没有确定作品下一步该怎么走，需要休息一段时间后再考虑未来计划。&lt;/p&gt;
+&lt;p&gt;　　House House确认，目前没有正在制作的《Big Walk》追加内容。不过，团队认为游戏本身拥有较为自由的互动设计，玩家仍可以尝试各种非预期玩法，甚至自行创造新的游戏方式。&lt;/p&gt;
+&lt;p&gt;　　开发者举例称，团队成员自己就经常在游戏里玩捉迷藏，并希望玩家也能利用游戏世界的互动性，“在游戏里创造属于自己的游戏”。&lt;/p&gt;
+&lt;img src="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0813%2Fdcc4c0bdj00tjosqj000qd000fa008lg.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" alt="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0813%2Fdcc4c0bdj00tjosqj000qd000fa008lg.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" /&gt;</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0808%2Fd09c5ed1j00tjfu1r003sd000fa008kg.jpg&amp;thumbnail=660x2147483647&amp;quality=80&amp;type=jpg</t>
+          <t>https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0811%2F5049bf7ej00tjluov0027d001hc00u0g.jpg&amp;thumbnail=660x2147483647&amp;quality=80&amp;type=jpg</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>R星母公司有29款新作！不止《GTA6》PS5大表哥2？</t>
+          <t>Remedy确认《马克思·佩恩1&amp;2》重制版仍在制作，R星负责发行</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
@@ -1110,23 +1217,25 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>据Insider Gaming报道，Take-Two Interactive近期公开了自家全新游戏储备阵容，目前旗下共有29款游戏处于开发阶段，新作覆盖多平台、多品类，阵容体量十分庞大。
-作为业内头部游戏厂商，Take-Two手握三大核心工作室，分别是打造《GTA》系列的Rockstar Games、主营主机/PC/移动端游戏的2K Games，以及专注手游领域的Zynga，此次29款新作均由三大工作室筹备开发。
-根据官方最新财报信息，这批开发中作品涵盖手游、体育游戏、全新原创IP、经典核心IP四大赛道，布局十分全面。其中手游品类共3款，包含Zynga已公布的《CSR 3》《Top Goal》两款作品；体育游戏阵容最为充足，共计8款，已官宣的有《NBA 2K27》《PGA 2K27》《WWE 2K27》，其中《NBA 2K27》已定档2026年9月4日发售。
-原创IP方面，目前有3款新作正在打磨，分别是Ghost Story Games打造的《Judas》以及31st Union开发的《ETHOS计划》，两款新作暂未公布发售时间。而玩家最关注的经典核心IP阵容最为豪华，足足有15款作品，包含8部正统续作与7款重制、复刻及平台移植作品。玩家心心念念的PS5版《荒野大镖客：救赎2》或许就在其中。
-在所有新作中，仅有《GTA6》敲定发售时间，定于2026年11月19日正式上线，也是目前Take-Two牌面最足、关注度最高的重磅大作。</t>
+          <t>&lt;p&gt;　　IT之家 8 月 11 日消息，据外媒 Inside Gaming 今天（11 日）报道，初代《马克思 · 佩恩》至今仍拥有数量可观的忠实玩家，玩家期待重制版已有多年。Remedy Entertainment 近期发布的报告再次确认，与 Rockstar Games 合作开发的《马克思 · 佩恩 1&amp;amp;2》重制版仍在制作，只是目前还没有太多内容可以公开。&lt;/p&gt;
+&lt;img src="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0811%2F5049bf7ej00tjluov0027d001hc00u0g.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" alt="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0811%2F5049bf7ej00tjluov0027d001hc00u0g.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" /&gt;
+&lt;p&gt;　　Remedy 最新财报除了公布财务数据和愿望单数量，也回应了外界提出的问题，其中就包括《马克思 · 佩恩 1&amp;amp;2》重制版的最新进展。&lt;/p&gt;
+&lt;p&gt;　　此前在 2025 年 8 月，有消息确认 R 星正与 Remedy 合作开发《马克思 · 佩恩 1&amp;amp;2》重制版。此次公布的 2026 年半年度报告则显示，项目仍在全面制作状态，但由于发行权掌握在 R 星手中，Remedy 目前无法公开更多信息。“很多问题都与《马克思 · 佩恩》有关，但 R 星负责该项目的发行，因此我们无法回答这些问题。”&lt;/p&gt;
+&lt;img src="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0811%2Fd64acd0ej00tjluov004vd0014000mig.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" alt="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0811%2Fd64acd0ej00tjluov004vd0014000mig.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" /&gt;
+&lt;p&gt;　　IT之家注：Remedy 旗下最具代表性的 IP 包括《心灵杀手》《控制》和《马克思 · 佩恩 1&amp;amp;2》。&lt;/p&gt;
+&lt;p&gt;　　R 星眼下还忙于《GTA 6》，重制版可能暂时不会成为公布消息的重点。不过，未来仍有望看到 R 星带来更多消息。&lt;/p&gt;</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0722%2Fa9c693bdj00tikoy00015d000hs00a0g.jpg&amp;thumbnail=660x2147483647&amp;quality=80&amp;type=jpg</t>
+          <t>https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0812%2F7f71d484j00tjnicx0027d200m900cjg00m900cj.jpg&amp;thumbnail=660x2147483647&amp;quality=80&amp;type=jpg</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>暑期档游戏行业火热：优质国产单机新作密集发力，ChinaJoy7月底开幕</t>
+          <t>腾讯财报：上半年游戏收入超1300亿，三角洲和无畏契约日活破新高</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
@@ -1136,35 +1245,34 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>2026年的夏天，游戏圈和外面的天气一样持续升温。从《刺客信条：黑旗 记忆重置》首日全球狂卖200万份，到优质国产单机新作密集释放信号，再到月底ChinaJoy以空前规模重装开幕——这个7月，中国游戏市场正在成为全球瞩目的焦点。
-国单赛道：从"古剑"到"抵抗者"，群雄并起
-7月18日，上海烛龙工作室为旗下虚幻5引擎新作《古剑》举办了首次大规模线下试玩会，对外展示了产品的阶段性成果，全球知名游戏媒体IGN同步发布了41分钟实机演示视频。玩家反馈显示，战斗手感、BOSS设计（彩衣侯·空空子、无头剑客、三尾猫妖“三命”等）与中式叙事均超出预期。该项目定位中式神话动作RPG，主线约20-25小时，计划全球同步登陆PS5、Xbox Series X|S与PC平台。
-与此同时，国产抗日题材FPS《抵抗者》确认参展月底的ChinaJoy并首次开放线下试玩。该作采用虚幻5引擎打造，背景设定在1940年代中国战场，融合谍战解谜与动作射击，场景涵盖林海雪原、上海石库门等标志性地点，被媒体评价为"中国版的《使命召唤》式线性叙事体验"。
-此外，成都日蚀边缘工作室的3A新作《湮灭之潮》也传来消息，女主角英文配音演员Jennifer English（《博德之门3》影心配音）因个人健康原因退出，全部英文配音需重录，新配音演员将于8月科隆游戏展试玩中首次亮相。
-Steam半年营收800亿，老游戏碾压新游
-数据分析机构Alinea Analytics估算，Steam平台在2026年上半年创下了111亿美元（约合人民币800亿元）的总收入，同比增长14.5%，为平台有史以来最高半年营收纪录。但其中新游戏仅贡献了21%的收入，剩余的79%来自老游戏的持续运营与内容更新。
-这组数据揭示了一个残酷现实：游戏行业的"马太效应"正在加剧，头部老游戏持续吞噬用户时间和消费，新游戏要突围的难度越来越大。
-ChinaJoy 2026重装开幕："与AI同游"引爆夏日上海
-如果说7月的游戏圈有一场"大考"，那答案必然是月底的ChinaJoy。第二十三届中国国际数码互动娱乐展览会将于7月31日至8月3日在上海新国际博览中心举办，主题定为"与AI同游"——AI不再是一个挂在嘴边的概念，而是本届展会贯穿始终的核心主线。
-本届展会总展览面积突破14万平方米，已有近900家企业确认参展，其中外资企业275家，覆盖美国、加拿大、英国、德国等39个国家和地区。其中BTOC互动娱乐馆汇聚超350家企业；BTOB商务洽谈馆超500家企业入驻，外资占比高达46.6%。海外专业观众预计将达万人次，ChinaJoy正加速成为联通全球的数字娱乐产业中枢。
-腾讯游戏、网易游戏、暴雪游戏、世纪华通、巨人网络、完美世界、金山世游、朝夕光年、PlayStation、360游戏、B站游戏、Pocketpair等500余家厂商将带来逾1000款游戏产品现场试玩。Steam线上盛典同步开启，报名游戏已超600款，实现"线下盛会、线上联动"的全球立体呈现。
-高通联合产业伙伴打造骁龙主题馆，以"AI驱动体验进化"为核心，呈现多终端融合的沉浸式娱乐体验。宇树科技、逐际动力、魔法原子、露米智能等企业携人形机器人与具身智能产品集中亮相，让科幻电影中的场景照进现实。展会还与傲鲨智能联合推出外骨骼机器人体验，观众可亲身感受"赛博逛展"。全新增设的Vision Future前沿科技展区集中展示智能机器人、AI大模型、智能穿戴等新技术；ChinaJoy Next Play创新游戏体验场提供AI NPC、互动叙事、生成式内容等前沿产品试玩。
-其他硬件、科技、潮玩、文化等方面的多家品牌方也将悉数亮相。
-本届ChinaJoy首设官方主舞台，英特尔大师挑战赛总决赛落地引爆赛事热情。抖音投入流量资源打造专属主题展区，快手投入亿级流量扶持，邀约cosplay、电竞等领域头部KOL打造大型直播。支付宝"碰一下"首发"碰一下组队"与"积分膨胀"玩法，推出内置NFT芯片的实物票根周边。同期还将举办AniSonic星尘十周年演唱会与玄歌国风演唱会，实现次元文化的深度共振。展会还围绕"上海之夏"国际消费季，联合浦东新区多个商圈推出专属票根权益，将展会影响延伸至全城消费场景。
-同期举办的6大行业峰会紧扣"AI驱动数字内容创作"脉搏，首设"数字娱乐消费场景峰会"与"短剧创新论坛"。第六届中国游戏创新大赛共征集204款作品，参赛主体覆盖全国19个省份及6个海外国家。ChinaJoy AGS学院游戏展区为高校创作提供公益性国际化展示平台，世纪华通发起的第二届数龙杯全球AI创新大赛也将在展会期间亮相。
-本届ChinaJoy传递的信号清晰而坚定：中国游戏产业正在从"规模扩张"转向"技术+内容+生态"的立体竞争，而AI正在成为这一转型中最具确定性的加速器。</t>
+          <t>&lt;p&gt;　　成为全球游戏行业最具影响力的价值连接者&lt;/p&gt;
+&lt;p&gt;　　刚刚，腾讯发布了2026上半年财报。财报数据显示，腾讯上半年收入4012.43亿元，同比10%，公司权益持有人应占盈利增长1141.15亿元，同比增长10%。&lt;/p&gt;
+&lt;img src="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0812%2F7f71d484j00tjnicx0027d200m900cjg00m900cj.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" alt="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0812%2F7f71d484j00tjnicx0027d200m900cjg00m900cj.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" /&gt;
+&lt;p&gt;　　聚焦游戏业务来看，腾讯上半年国内游戏收入927亿元，海外市场收入374亿元，合计1301亿元。仅看第二季度，国内游戏市场收入473亿元，同比增长17%；国际游戏市场收入186亿元，剔除汇率影响同比增长4%，仍保持增长。&lt;/p&gt;
+&lt;p&gt;　　在财报中出现的重点产品包括《三角洲行动》与《无畏契约》，被提及“平均日活用户数在第二季度创下新高”；《洛克王国：世界》，被提及为今年中国市场所有新上线手游中平均日活用户数和流水总数排名第一；《Arrows – Puzzle Escape》（腾讯子公司Miniclip旗下产品），被提及为2026年第二季度全球下载量最高的手游。&lt;/p&gt;
+&lt;p&gt;　　除了以上游戏，明确带来了增长的还有《无畏契约手游》《鸣潮》《VALORANT》（无畏契约国际版）《PUBG MOBILE》以及《王者荣耀》。&lt;/p&gt;
+&lt;img src="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0812%2Fb1493ab7j00tjnicy00c5d200mi00btg00mi00bt.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" alt="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0812%2Fb1493ab7j00tjnicy00c5d200mi00btg00mi00bt.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" /&gt;
+&lt;p&gt;　　简单聊下2026年我们看到的腾讯游戏变化。&lt;/p&gt;
+&lt;p&gt;　　在腾讯游戏业务的增长逻辑中，长青产品是核心焦点。尽管较少公布新数据，但游戏日报观察到，2026年腾讯头部长青都有了比往年更积极的运营动作。&lt;/p&gt;
+&lt;p&gt;　　比如“无畏巡回”已经跑完了广州杭州北京长沙4所城市，，每一站热度都在明显拔高；《和平精英》在、、主题玩法、上多点开花，据了解，上周刚结束刺激之夜已经拿下了360多个热搜；&lt;/p&gt;
+&lt;p&gt;　　《王者荣耀》也进一步走了出来，包括第一次参展BW，，让更多玩家得以线下相聚；还有《三角洲行动》，今年在各个城市落地线下活动的频次极高，成了，也摸索出了.....&lt;/p&gt;
+&lt;p&gt;　　这些举动在为腾讯游戏拓盘争夺更多用户注意力。&lt;/p&gt;
+&lt;p&gt;　　另外值得注意的是，即将上线满1年的“手瓦”（《无畏契约手游》）基本已锁定腾讯“长青产品”（季度平均日活500万以上，年收入40亿元以上）的新席位——今年手瓦先后公布了破1000万DAU，等数据，其在iOS畅销榜上也常稳居TOP5。&lt;/p&gt;
+&lt;p&gt;　　再说新品。&lt;/p&gt;
+&lt;p&gt;　　今年上半年，腾讯总计上线了6款新游，分别是三款自研产品-王者IP大世界《王者荣耀世界》、捉宠开放世界《洛克王国：世界》以及PVE射击《逆战：未来》；三款代理产品-卡牌格斗《全明星觉醒》、回合制RPG《三国志异闻录》以及二次元卡牌《卡厄斯梦境》。&lt;/p&gt;
+&lt;p&gt;　　这其中有部分产品给腾讯带来了可见的增长，例如《洛克王国：世界》《逆战：未来》都曾登顶iOS畅销榜，前者首月冲至日均1300万DAU，，后者则填补了移动PVE射击的空白，且。&lt;/p&gt;
+&lt;p&gt;　　另外一款备受关注的新品《王者荣耀世界》最高排名16位，虽然成绩难说理想，但也是，打开了IP再成长的更多可能性。&lt;/p&gt;
+&lt;p&gt;　　顺带谈谈下半年可以重点关注的新品。目前已知的大产品有，相比于开放世界的极度内卷，万象棋涉足的赛道仍旧相对蓝海；另外包括《命运扳机》《彩虹六号》《战术小队》在内的射击新品，也会再探腾讯射击品类大盘增长的新可能性，其中部分产品有在2026年公测的可能性。&lt;/p&gt;
+&lt;p&gt;　　至于更多腾讯储备产品，我们报道过较多次，&lt;/p&gt;
+&lt;p&gt;　　总结来说，我们认为腾讯在2026下半年仍旧有稳定增长的趋势。&lt;/p&gt;</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0808%2Ff9f227d9j00tjfpha001jd000q100fig.jpg&amp;thumbnail=660x2147483647&amp;quality=80&amp;type=jpg</t>
-        </is>
-      </c>
+      <c r="A23" s="2" t="inlineStr"/>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>《GTA 6》在列，Take-Two正研发29款游戏</t>
+          <t>恺英网络旗下游戏《盗墓笔记：启程》正式公测</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
@@ -1174,24 +1282,19 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>IT之家 8 月 8 日消息，在 2027 财年（2026 年 4 月 1 日至 2027 年 3 月 31 日）第 1 财季（2026 年 4 月 1 日 ~6 月 30 日）财报中，Take-Two Interactive 披露称目前正在开发 29 款游戏。
-本次披露的 29 款游戏主要由旗下 Rockstar Games、2K Games 和 Zynga 推进，前两家工作室覆盖主机、PC 和移动平台，Zynga 则专注移动游戏。
-在游戏类型方面，在 29 款在研作品中有 3 款手游，其中，Zynga 已公开《CSR 3》和《Top Goal》其中 2 款。
-体育游戏共有 8 款在研，已公布的项目包括 NBA 2K27、PGA 2K27 和 WWE 2K27。其中，《NBA 2K27》计划于 2026 年 9 月 4 日发售。
-核心新 IP 部分共有 3 款在研作品。已公布项目包括《Judas》，由 Ghost Story Games 开发，以及 Project ETHOS，由 31st Union 开发。
-既有核心 IP 方面，Take-Two 共列出 15 款在研作品，其中包括 8 款续作，以及 7 款重制版、复刻版和平台扩展内容。这 15 款作品中，只有《侠盗猎车手 6》（Grand Theft Auto 6，GTA6）拥有确认发售日期，定于 2026 年 11 月 19 日推出。IT之家附上相关截图如下：</t>
+          <t>&lt;p&gt;　　8月11日，恺英网络宣布，旗下寻宝盗墓探险游戏《盗墓笔记：启程》正式开启全平台公测。&lt;/p&gt;</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0623%2F18772d0bj00th2mnj008yd000fa008mg.jpg&amp;thumbnail=660x2147483647&amp;quality=80&amp;type=jpg</t>
+          <t>https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0811%2F3c9bc217j00tjm295001yd0015o00kug.jpg&amp;thumbnail=660x2147483647&amp;quality=80&amp;type=jpg</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>KRAFTON携五款新作亮相2026科隆国际游戏展</t>
+          <t>苹果Apple Arcade下月新增两款益智游戏</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
@@ -1201,26 +1304,19 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>KRAFTON宣布将参加于8月26日至30日在德国科隆举办的全球最大游戏展会——科隆国际游戏展(Gamescom 2026)。
-本届科隆国际游戏展期间，KRAFTON将带来共计五款全新作品。其中包括PUBG STUDIOS开发的新作，以及《NO LAW》《Project ZETA》《Age Twisters》《TARAE: The Unbound》等涵盖多种游戏类型的新作阵容。
-今年，除了KRAFTON旗下创意工作室开发的新作外，公司还将首次展出多款Second-Party Publishing(二方发行)作品。通过这一阵容，KRAFTON将全面展示其自主研发实力与持续扩张的发行产品组合。
-其中，PUBG STUDIOS尚未公开的新作将首次通过本届科隆国际游戏展亮相。该作品基于PUBG IP打造，将为玩家带来全新的世界观背景与游戏体验。
-《NO LAW》是由Neon Giant开发中的沉浸式开放世界FPS游戏，以高密度、无秩序的赛博黑色港口都市“Port Desire(欲望港)”为舞台。玩家将化身退役军人Grey Harker，在探索城市各处隐藏故事的过程中，踏上寻回被夺走之物的旅程。
-NIRVANANA开发的《Project ZETA》是一款“多队伍战术竞技场”类型新作，四支队伍将在同一战场展开激烈对抗。游戏计划于6月开启首次全球社区测试，并将在科隆国际游戏展期间与玩家见面。
-Piccolo Studio开发的《Age Twisters》是一款双人合作叙事冒险游戏;Boundary开发的《TARAE: The Unbound》则是一款以东方奇幻世界观为背景的俯视角黑暗幻想动作RPG。两款作品均将通过科隆国际游戏展2026首次向玩家公开。
-更多信息可通过KRAFTON科隆国际游戏展2026官方专题页面查看。</t>
+          <t>&lt;p&gt;　　IT之家 8 月 11 日消息，苹果公司今天宣布旗下 Apple Arcade 订阅服务将从 9 月 3 日起新增两款益智游戏，分别是《Cozy Puzzles+》和《舒适拼图 +》。&lt;/p&gt;
+&lt;img src="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0811%2F3c9bc217j00tjm295001yd0015o00kug.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" alt="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0811%2F3c9bc217j00tjm295001yd0015o00kug.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" /&gt;
+&lt;p&gt;　　IT之家了解到，《Cozy Puzzles+》是一款类似《俄罗斯方块》的游戏，玩家需要将不同的彩色方块拖入 8*8 网格中，通过填满横向、纵向的整行来获得更高分数，空间耗尽即代表游戏结束，考验玩家的布局策略。&lt;/p&gt;
+&lt;p&gt;　　而《舒适拼图 +》（Art of Fauna: Cozy Puzzles+）则是一款氛围轻松的拼图游戏，内含 18 和 19 世纪的复古野生动物插画与科学文献艺术作品，主打轻松、从容的解谜体验，本作曾获得 2025 年 Apple 设计大奖。&lt;/p&gt;
+&lt;p&gt;　　按照惯例，这两款 Apple Arcade 平台的新游戏都不会有广告，也不会有内购项目，主打完全沉浸的体验。&lt;/p&gt;</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0806%2F00465567j00tjc4zc00ktd000u000cum.jpg&amp;thumbnail=660x2147483647&amp;quality=80&amp;type=jpg</t>
-        </is>
-      </c>
+      <c r="A25" s="2" t="inlineStr"/>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>盗墓笔记、诡秘之主、怪物猎人领衔：8月定档手游扎堆，谁能成爆款？</t>
+          <t>腾讯Q2游戏收入重回双位数增长</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
@@ -1230,66 +1326,19 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>今年暑期档下半程，游戏圈战火延续。
-据陀螺君统计，8月超20款新游定档上线或明确公测节点，至少18款产品启动测试，数量与7月持平，热度不减。
-从排期看，8月上旬尤为密集，仅8月6日便有《魂坠深境》《航海王：集结》《群星征途2117》《丹墨三国：弈》等多款集中发力。
-品类上，卡牌RPG与策略仍是基本盘，“搜打撤”赛道迎来多款新品，二次元音游、中式志怪恐怖、派对社交等细分领域亦有重磅入局。腾讯、网易、B站、朝夕光年、恺英网络等厂商均在本月“上新”或进行关键新游测试。
-注：新游档期信息主要采集自官方、TapTap、好游快爆及App Store预订页面，标“*”者为App Store预定信息，官方尚未正式定档，实际上线时间请以厂商公告为准。
-本月，腾讯预计有4款产品进入关键测试节点，覆盖暗黑MMO、开放世界狩猎、休闲派对、经典移植四大品类，堪称全赛道出击。
-网易以中式志怪“搜打撤”新作《诡影藏锋》差异化入局。B站在二次元音游与经典MMO两端同时落子。朝夕光年携《航海王：集结》重启归来。恺英网络、快手、凉屋游戏等厂商同样颇具看点。
-具体来看，8月上线的重点产品介绍：
-凉屋游戏——《魂坠深境》（8月6日上线）
-《魂坠深境》是凉屋游戏推出的卡牌Roguelike新作，定档8月6日上线。
-游戏以策略构筑与序列式卡牌对战为核心玩法，辅以暗黑西幻风格的美术基调与克系诡异氛围，主打的是一套围绕“取舍”展开的深度博弈机制：战斗序列中，玩家每打出一张卡牌，需以牺牲其后若干张卡牌为代价，出牌顺序与牺牲决策共同构成策略内核。
-在内容体量上，游戏现已开放700余张特色卡牌、170余种祝福、50种印记及85种护符供玩家自由构筑，四大职业与十七位出战者各自拥有独立卡池和专属天赋树，彼此之间的搭配组合具备可观的策略纵深。
-恺英网络——《盗墓笔记：启程》（8月11日公测）
-《盗墓笔记：启程》由南派三叔正版授权，虚幻4研发的寻宝盗墓探险手游。
-玩家以“九门后人”身份随铁三角深入鲁王宫、西王母宫等原著古墓，箱庭式地宫中以星图推演、铭文比对等考古逻辑解谜，搭配六大职业与ARPG+策略+Roguelike战斗。
-游戏“地下探险+雨村闲居”双线并行，支持种田钓鱼送礼等休闲玩法。6月份官宣全平台预约破500万。
-延趣网络——《赘婿》（8月12日首发）
-《赘婿》获同名小说及剧版正版授权，三七互娱运营的游戏。
-玩家化身宁毅从苏家赘婿起步，以“拼刀刀砍价、直播带货”等现代商业思维经营古代商场，走“经营赚钱→养门客红颜→商战打脸→身份晋升”的模拟经营+放置养成闭环，复刻大婚、掌印争夺等名场面，穿插斗鸭、抓大鹅等轻量休闲玩法。
-快手弹指宇宙——《诡秘之主》（8月21日上线）
-《诡秘之主》是一款UE5研发的欧式古风神秘学MMORPG游戏，改编自同名网络小说。
-玩家从22条神之途径中选择，通过服用魔药与“扮演法”晋升（序列9至序列0），内置SAN值精神机制，理智归零将失控异变。包含原著向剧情线与个人主线双线叙事，支持千人同屏阵营混战。
-据悉该团队超过600人，项目研发时间超过四年，累计投入超10亿元。
-金山世游——《猫咪和汤：魔法与美食》（8月27日上线）
-《猫咪和汤：魔法与美食》（英文名：《Cats &amp; Soup》）是一款由Neowiz 运营，Hidea 开发的治愈系猫咪魔法合成装扮类手游，金山世游负责其国服代理。
-游戏的全球累计下载次数突破7000万，并持续保持高人气。简单的游戏方式与可爱的画风等疗愈要素是该游戏的主要特点，目前游戏在好游快爆平台评分达8.2分。
-已定档产品之外，8月预计有18款游戏进入测试阶段，其激烈程度不亚于正式上线潮。
-重点测试产品有：
-腾讯游戏——《天堂：血统》《怪物猎人：旅人》《奥星热浪》
-《天堂：血统》（8月5日限量计费删档测试）：天堂IP正版硬核MMO，高清还原亚丁大陆与血盟攻城，支持PC/手机双端互通与自由交易，主打经典打宝与挂机减负。
-《怪物猎人：旅人》（8月7日限量删档测试）：怪猎系列首款移动端开放世界狩猎手游，由天美研发、卡普空监修。以埃索岛无缝大地图、融光种独占怪物、四人共斗与太刀/大剑/弓等经典武器还原为核心，单局压缩至15-25分钟。
-《奥星热浪》（8月14日限量删档测试）：光子工作室出品，以“梗文化+轻量搜打撤+派对社交”拼装出哈基镇、来财行动与家园循环，法棍当武器，主打年轻玩家的抽象整活与解压。
-网易游戏——《诡影藏锋》（8月7日“藏锋测试”）
-这是雷火工作室用虚幻5打造的首款中式志怪第一人称“搜打撤”新作。
-玩家扮通玄院探客潜入荒村、废庙、古宅等禁地，15分钟内搜奇珍、破机关、斗纸人傀儡与缢死女鬼，赶在时限前找生门撤离。
-游戏战斗弃用枪械，以刀剑枪扇戟等冷兵近身格挡闪避，辅以结印咒术驱鬼，单排或三排（含PvPvE）并行，暗黑水墨写实美术搭配浓雾烛影，Steam页面已挂“免费开玩”。
-B站——《BanG Dream! Our Notes》《仙境传说3》
-《BanG Dream! Our Notes》（8月6日海外β测试）：B站代理海外发行，围绕五支乐队展开叙事，延续动画世界观，引入“电影叙事系统”强化角色表情与镜头语言。保留竖版下落式玩法，新增“辅助模式”降低门槛，新增“激奏演出”及最多五人同台的派对联机。
-《仙境传说3》（8月27日PC端不限量删档“重逢测试”）：B站独家代理，Gravity与欢乐互娱联合研发，RO正统续作。PC原生架构+多端互通，次世代2.5D俯视视角MMO，延续普隆德拉摆摊、转职BD、MVP与百人GVG攻城、自由交易等经典元素。
-朝夕光年——《航海王：集结》（8月6日限量删档“集结测试”）
-东映动画正版授权的3D动作冒险手游，原《代号：伙伴》重启。以多人协作PVE团本为核心，主打六人分两队兵分两路联动作战、三角色轮切与输出/特攻/辅助分工，将草帽团经典战役做成赛季制副本，以“猜拳式”攻防克制兼顾团战配合与PVP策略。
-此外，8月新品矩阵中还有《全职掌门》《鸡械绿洲》《三国将魂》《满庭芳·宋上繁华》《大侠闯天下》等值得关注的面孔。
-纵观8月产品阵容，三大趋势尤为突出：
-其一，“搜打撤”玩法从战术射击向国风恐怖、休闲派对快速外溢，《诡影藏锋》《奥星热浪》分别以东方惊悚和抽象整活切入细分赛道。
-其二，IP改编仍是重头戏，从《盗墓笔记》《诡秘之主》到《怪物猎人》《航海王》《天堂》《仙境传说》，文学、动漫、经典端游IP全面开花，移动端价值持续深挖。
-其三，头部厂商排兵布阵层次分明，腾讯三款产品覆盖三种截然不同的用户画像，B站兼顾二次元核心与经典MMO两端，网易以风格化单品寻求突破，多端互通已成为中大型产品标配。
-结语：
-8月竞争压力不仅来自新品扎堆，还有多款长青产品在暑期后半程的版本攻势。在大厂新品密集轰炸、经典IP集中变现与存量市场三方角力下，谁能在8月真正承接住暑期档后半段用户的注意力，成为今夏最后的赢家？拭目以待。</t>
+          <t>&lt;p&gt;　　每经AI快讯，8月12日，腾讯控股发布2026年第二季度财报。网络游戏业务总收入659亿元，同比增长11%，整体重回双位数增长态势。本土市场收入473亿元，同比增长17%。增长动力主要来自四款核心产品：《三角洲行动》、《无畏契约》、《无畏契约：能源行动》及《洛克王国：世界》。其中《三角洲行动》与《无畏契约》平均日活跃用户均在本季度创下历史新高。国际市场收入186亿元，按固定汇率计算同比增长4%，主要受《鸣潮》《VALORANT》驱动。&lt;/p&gt;</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0812%2Faf825c98j00tjnat6001hd000u000gum.jpg&amp;thumbnail=660x2147483647&amp;quality=80&amp;type=jpg</t>
+          <t>https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0808%2Fae1c43abj00tjg81q000dd200u0006pg00is0046.jpg&amp;thumbnail=660x2147483647&amp;quality=80&amp;type=jpg</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>18岁了，腾讯这款枪战启蒙游戏的长青密码才刚被读懂</t>
+          <t>《使命召唤手游》×《崩坏3》联动官宣！《王者万象棋》定档今年9月</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
@@ -1299,44 +1348,42 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>近日，2026年穿越火线IP嘉年华暨双端职业联赛夏季赛总决赛，在济南融创国际体育中心落下帷幕。无数CFer从各地赶来，奔赴这场“三亿鼠标的枪战梦想”的18周年之约。
-当玩家纪录片的画面一帧帧掠过，十八位老玩家登台讲述自己与CF的青春故事时，现场几乎没有质疑声：这款走过十八年的FPS网游，热度从未消退过。而在嘉年华的现场，3A叙事单机新作《穿越火线：潜伏》的首次亮相，让更多人意识到：18岁的CF不仅情怀犹在，还在试图重新定义射击赛道的边界。
-随着两日时间里面，CF全系作品开始亮出自己新的计划，关于这款18年的枪战启蒙游戏的长青密码才刚刚被人读懂。
-多产品矩阵打造出来的长青之路
-CF之所以能走过18年仍保持活力，最主要的原因还是在于产品策略的精准与克制。一个长青的IP，从来不是依靠单一产品的“一招鲜”就能够走下去的，而是让不同的爱好的玩家在不同时间和不同阶段都能找到与CF的连接方式。
-从端游到手游，再到CFHD，CF已经构建起覆盖多终端、多玩法的产品矩阵。端游有着最核心的竞技特性和玩家情怀，手游则满足了移动时代的碎片化需求，CFHD则是在画质与玩法深度上尝试突破。三者各有侧重，却又共享同一套IP资产与玩家认知。这种“多产品协同”的打法，让CF在面对用户代际更迭时，始终有着足够的缓冲与延展空间。
-而CF 18年的长青运营也了解到了不同时代不同玩家的游戏理解，这也帮助CF在产品形态上的进一步创新。
-本次嘉年华上，端游推出“全能纪元”大版本，全新玩法“生化潜能”模式的上线、经典模式的回归，手游与《环太平洋》的联动，CFHD全新PVE“秘境模式”的推出——每一处更新背后，都是对玩家需求的精准回应。CF没有因为时间的长度而固步自封，反而因为懂玩家的心而持续给玩家带去惊喜。
-更值得关注的是《穿越火线：潜伏》的战略意义。这款由That’s No Moon工作室开发、腾讯与Smilegate联合发行的买断制3A叙事单机新作，历时近五年打磨，采用UE5引擎，定位第三人称战术潜行射击，将登陆PC、PS、Xbox多端平台。它的目标不仅是填补CF IP在单人叙事领域的空白，更重要的是要以全球品质标准和全球玩家可理解的叙事表达，让CF在全球范围内获得更多玩家的认可和喜爱。
-简单来说，《穿越火线：潜伏》是CF要从“中国一代玩家的枪战启蒙”迈向“全球性射击IP”的关键落子。而在这一过程中，需要注意两个方面，一方面是要稳定现有的基本盘，于是需要先保证三端产品持续服务核心玩家，守住基本盘；另一方面则是用新的产品扩宽IP边界。
-FPS的黄埔军校
-如果说产品是的骨架，那么电竞生态就是它的灵魂。18年时间，CF的电竞体系经历了从草根到职业、从国内到世界的完整进化路径，被誉为“FPS的黄埔军校”绝非虚名，堪称全民电竞赛事的范本。
-这条路的起点始于2008年的百城联赛。从最初的网吧赛、城市赛，到如今覆盖全国数百座城市的基层赛事网络，百城联赛一直是CF电竞最坚实的土壤。它不仅为职业联赛输送了大量人才，更重要的是让电竞真正扎进了地方——每一个城市赛区都有自己的故事，每一支民间战队都有可能成为黑马。这种“接地气”的赛事生态，在国内FPS赛道里面几乎找不到第二个案例。
-然后依托百城联赛的底子，CFPL和CFML等职业联赛由此构建起专业的赛事体系，然后让整个CF的电竞生态形成活水效应。特别是在今年的下半年，百城联赛将首次开放直通CFS世界赛的晋级通道，这意味着民间选手也有机会站上国际舞台。大众竞技与职业电竞之间的通路被打通，CF电竞的人才储备池将进一步扩大。
-更值得关注的是CF在国际舞台上的突破。从早期的CFS世界赛，到如今出征EWC（电子竞技世界杯），穿越火线正在加速融入全球电竞体系。对于一款深耕中国市场的FPS产品来说，这既是品牌影响力的延伸，也是IP全球化战略的重要组成部分。
-可以说，CF电竞已经形成了一个从“百城→职业→世界”的完整闭环。它与产品相互赋能：赛事为产品提供持续的曝光与内容素材，产品则为赛事提供稳定的用户基础与玩法支撑。这种生态协同，正是CF能够长线运营的核心竞争力之一。
-18载的情感维系
-18年的时间，玩家和官方之间最深的维系并不只是一把武器或者一个版本，而是双方之间的情感维系，这是看不见也摸不着的，但是却是两者之间最深的羁绊。
-三亿鼠标的枪战梦想，这对于很多人来说，最初的这句话只是一句口号，然而18年过去，回过头再来看，这句诞生在CF之初的口号已经成为一代人真实的集体记忆。从网吧五连坐到宿舍开黑，从第一次爆头的兴奋到排位连败的不甘，CF承载的早已不只是游戏本身，而是一种社交方式、一种青春符号。
-18年走下来，CF从游戏房间里的暗语到电竞赛场上的名场面，再到玩家社区的自嘲黑话，已经积累了无数的梗和名场面，它们构成了一代FPS玩家的共同语言。而这些能够随时拨动CF玩家心弦的共同语言，恰恰构成了CF最坚固的护城河——玩家的"身份验证码"。
-也正是这种玩家文化的深厚沉淀，让CF这18年的漫长成长时，始终都有那么一群核心粉丝。他们可能不再有着灵活的身法，他们可能都已经成家立业，他们可能有着更重要的事情，他们可能不再高频登录，但只要CF有大事件、大更新的时候，这群人就可能会回来看看。这种“回得去的青春”，才是CF持续保持生命力的最重要支撑。
-他们总会为自己呐喊出发自心底的声音，为自己的青春再次燃烧起来。
-18岁，远未到巅峰
-18年，足够让一款网游从新兴走向成熟，也足够让一代玩家从少年步入成年。但CF没有在时间里变得陈旧，反而在18岁的节点上展现出愈发旺盛的生命力。
-产品端，三断产品协同作战，满足不同的玩家群体，3A单机大作即将叩响全球大门，给全球玩家带来全新的CF体验；电竞方面，从百城联赛到世界赛，赛事生态日益完善，草根玩家也可以通过赛事晋级走向巅峰；玩家的情感，不仅是18年沉淀下来的玩家文化，更是CF IP最坚实的基本盘。这三条线交织在一起，共同构成起了CF在历经18载后，依旧能够点燃玩家的底层逻辑。
-18岁的CF，远未到巅峰。它正带着三亿鼠标的枪战梦想，走向下一个更广阔的战场。</t>
+          <t>&lt;p&gt;　　游戏头条&lt;/p&gt;
+&lt;p&gt;　　中国首家顾问式新媒体，定制属于您的媒体内容&lt;/p&gt;
+&lt;img src="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0808%2Fae1c43abj00tjg81q000dd200u0006pg00is0046.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" alt="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0808%2Fae1c43abj00tjg81q000dd200u0006pg00is0046.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" /&gt;
+&lt;p&gt;　　▎《使命召唤手游》×《崩坏3》，腾讯与米哈游首次游戏联动官宣&lt;/p&gt;
+&lt;p&gt;　　8月7日，由腾讯天美工作室和动视暴雪联合开发的《使命召唤手游》宣布，将与米哈游旗下游戏《崩坏3》展开联动。相关宣传视频放出后，弹幕全是问号，甚至有网友感慨是否在做梦，并直呼起猛了。&lt;/p&gt;
+&lt;img src="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0808%2F49571ce6j00tjg81r00lkd200u000bwg00ls008m.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" alt="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0808%2F49571ce6j00tjg81r00lkd200u000bwg00ls008m.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" /&gt;
+&lt;p&gt;　　据腾讯《使命召唤手游》官方透露，联动活动将在9月启动。值得一提的是，这也是腾讯与米哈游在游戏上的首次联动。此前米哈游与腾讯的合作主要停留在平台层面，例如2023年5月《原神》曾与微信游戏圈展开社区合作，入驻后短时间成员数突破百万。&lt;/p&gt;
+&lt;p&gt;　　腾讯《使命召唤手游》官方还在评论区中分享了联动活动的海报，虽然并未直接给出联动角色正脸，但还是可以一眼认出这三位是《崩坏3》中的三位主角，分别是雷电芽衣（雷之律者）、琪亚娜（薪炎之律者）和布洛妮娅 · 扎伊切克（理之律者）。&lt;/p&gt;
+&lt;p&gt;　　▎腾讯《王者荣耀》IP自走棋游戏《王者万象棋》定档今年9月，全网预约人数突破5000万&lt;/p&gt;
+&lt;p&gt;　　8月7日，腾讯《王者荣耀》IP自走棋游戏《王者万象棋》宣布，本作定档 2026年9月，当前全网预约人数已突破5000万。&lt;/p&gt;
+&lt;img src="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0808%2Fe578aa75j00tjg81s00red200u000gwg00ls00c9.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" alt="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0808%2Fe578aa75j00tjg81s00red200u000gwg00ls00c9.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" /&gt;
+&lt;p&gt;　　据介绍，《王者荣耀》IP英雄策略对战自走棋衍生游戏《王者万象棋》由腾讯游戏天美工作室群研发，主打局内策略对战，公平竞技。游戏官方还宣布，《王者万象棋》体验服抢先开启，今日起通过好友资格分享或参与各平台放号活动，有机会获得体验服资格。&lt;/p&gt;
+&lt;p&gt;　　▎发售25年后，《重返德军总部》游戏终于在德国推出无删减完整版&lt;/p&gt;
+&lt;p&gt;　　8月7日消息，据德媒Golem今天报道，在发售25年后，《重返德军总部》游戏终于在德国推出无删减完整版。位于德国的玩家现在可以通过Steam、GOG和MS Store平台获取本作。&lt;/p&gt;
+&lt;p&gt;　　据报道，《重返德军总部》游戏最初在2001年发售，德国版经过大幅修改，删除了纳粹标志，并将与纳粹分子有关联的文本修改为“狼族”，USK（德国娱乐媒体检验局）分级为16岁以上。&lt;/p&gt;
+&lt;img src="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0808%2F89f39f97j00tjg81t00d7d200u000n5g00ls00gs.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" alt="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0808%2F89f39f97j00tjg81t00d7d200u000n5g00ls00gs.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" /&gt;
+&lt;p&gt;　　虽然经过了此番修改，但本作仍然于2002年4月，被德国联邦媒体儿童与青少年保护局（BzKJ）列入“危害青少年媒体”名单，禁止公开宣发，零售商不能将该作摆在货架上，Steam等数字平台也不能在德国显示该游戏。&lt;/p&gt;
+&lt;p&gt;　　当时监管机构认为，本作大量使用了纳粹元素，有美化纳粹、消遣极端主义符号之嫌。且删减版游戏与国际版并没有本质区别，玩法、任务和暴力内容并没有变化。&lt;/p&gt;
+&lt;p&gt;　　2018年，德国修改了电子游戏中纳粹符号的限制规则，允许游戏在符合艺术、历史表达的前提下使用相关符号。之后，BzKJ于今年初将《重返德军总部》从限制名单中删除。&lt;/p&gt;
+&lt;p&gt;　　▎SE确认《最终幻想7：启示录》将亮相科隆游戏展&lt;/p&gt;
+&lt;p&gt;　　8月8日，Square Enix现已确认，《最终幻想7：启示录》将亮相科隆游戏展开幕之夜直播活动。SE同时确认，本作导演滨口直树将参与开幕之夜活动，有望带来现场访谈等消息。&lt;/p&gt;
+&lt;img src="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0808%2F54ef4416j00tjg81u00n7d200u000gwg00ls00c9.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" alt="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0808%2F54ef4416j00tjg81u00n7d200u000gwg00ls00c9.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" /&gt;
+&lt;p&gt;　　据悉，今年的科隆游戏展开幕之夜活动由杰夫 · 基格利主持，并在美东时间8月25日下午2点举行（北京时间8月26日凌晨2点）。&lt;/p&gt;
+&lt;p&gt;　　《最终幻想7：启示录》计划于2027年推出，登陆PS5、Xbox Series X|S、Switch 2和PC平台，成为《最终幻想7》重制三部曲首部不再限时独占主机的作品。&lt;/p&gt;</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0807%2Fc4f2c590j00tje0oi0074d000fa008lg.jpg&amp;thumbnail=660x2147483647&amp;quality=80&amp;type=jpg</t>
+          <t>https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0812%2F8aa4a24aj00tjn04r0014d000u0009fm.jpg&amp;thumbnail=660x2147483647&amp;quality=80&amp;type=jpg</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>下周开始！一周一个大的:影之刃零黑钟馗GTA6三连发</t>
+          <t>魔兽：暴雪发布世界BOSS巢穴玩法新蓝贴！世界难度推荐装等273！</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
@@ -1346,24 +1393,107 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>进入 8 月中下旬，全球游戏市场即将进入重磅内容密集发布期。从下周起连续三周，每周都有重量级作品的核心动态落地，玩家们的好日子来了！
-8 月 12 日《影之刃零》预售 + 新实机公布、8 月 20 日游戏科学年度 820 活动、8 月 28 日《侠盗猎车手 6》全新实机前瞻，三大节点覆盖多元品类，被玩家调侃为 “每周一个大的” 的游戏狂欢月。
-率先登场的 8 月 12 日，灵游坊旗下《影之刃零》将正式开启全平台预售，同步公布游戏售价与 PC 配置要求，并放出 11 分钟全新实机演示，涵盖新剧情、角色与战斗系统。目前本作已完成全部内容研发，定于 10 月 29 日全球发售，Steam 愿望单已突破 162 万，创下国产单机海外热度纪录抖音。
-8 月 20 日的游戏科学年度 820 活动是国产游戏圈的固定重头戏。今年玩家的核心期待集中在《黑神话：钟馗》的最新开发进展上，尽管美术总监杨奇此前曾提前降温，称本次筹备时间紧张，更像是老朋友例行聚会，但并未打消观众热情，相关话题已提前登上各大社区热议榜。
-压轴的 8 月 28 日，Rockstar 将发布《GTA6》全新扩展实机前瞻 “分量十足的一瞥”，内容将于网飞抢先首播，后续登陆官方频道并推出中文字幕直播吧。本作定于 11 月 19 日登陆主机平台，每一次官方动态都会引发全网级别的讨论热度。
-连续三周的重磅内容覆盖国产与海外顶级 IP，让 8 月下旬成为玩家的重点关注期，游民星空届时将会为您带来第一时间的报道。</t>
+          <t>&lt;img src="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0812%2F8aa4a24aj00tjn04r0014d000u0009fm.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" alt="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0812%2F8aa4a24aj00tjn04r0014d000u0009fm.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" /&gt;
+&lt;p&gt;　　暴雪更新了“巢穴”介绍文章，调整了潮缚石窟的推荐装备等级。明天更新后，将开放世界难度，大家可以看下自己的装备是否满足。&lt;/p&gt;
+&lt;p&gt;　　此前公布的巢穴预览中，潮缚石窟各难度的推荐装等明显偏低：&lt;/p&gt;
+&lt;p&gt;　　世界：230&lt;/p&gt;
+&lt;p&gt;　　普通：243&lt;/p&gt;
+&lt;p&gt;　　英雄：259&lt;/p&gt;
+&lt;p&gt;　　神话：272&lt;/p&gt;
+&lt;p&gt;　　如今暴雪已经将推荐装等整体上调，新的数值更符合第2赛季的装备水平。&lt;/p&gt;
+&lt;p&gt;　　潮缚石窟推荐装等调整&lt;/p&gt;
+&lt;p&gt;　　暴雪表示，挑战的难度越高，获得的奖励也越丰厚。潮缚石窟共分为世界、普通、英雄和神话4种难度，每种难度都有对应的推荐装备等级。&lt;/p&gt;
+&lt;p&gt;　　难度&lt;/p&gt;
+&lt;p&gt;　　推荐装备等级&lt;/p&gt;
+&lt;p&gt;　　掉落装备等级&lt;/p&gt;
+&lt;p&gt;　　迷雾纹章&lt;/p&gt;
+&lt;p&gt;　　世界&lt;/p&gt;
+&lt;p&gt;　　273&lt;/p&gt;
+&lt;p&gt;　　279，勇士1/6&lt;/p&gt;
+&lt;p&gt;　　勇士迷雾纹章&lt;/p&gt;
+&lt;p&gt;　　普通&lt;/p&gt;
+&lt;p&gt;　　286&lt;/p&gt;
+&lt;p&gt;　　292，勇士1/6&lt;/p&gt;
+&lt;p&gt;　　勇士迷雾纹章&lt;/p&gt;
+&lt;p&gt;　　英雄&lt;/p&gt;
+&lt;p&gt;　　299&lt;/p&gt;
+&lt;p&gt;　　305，英雄1/6&lt;/p&gt;
+&lt;p&gt;　　英雄迷雾纹章&lt;/p&gt;
+&lt;p&gt;　　神话&lt;/p&gt;
+&lt;p&gt;　　312&lt;/p&gt;
+&lt;p&gt;　　318，神话1/6&lt;/p&gt;
+&lt;p&gt;　　神话迷雾纹章&lt;/p&gt;
+&lt;p&gt;　　从调整后的数据来看，世界难度推荐装等从230直接提高到273，神话难度则从272上调至312，整体提升幅度非常明显。&lt;/p&gt;
+&lt;p&gt;　　潮缚石窟的首领为纳迦女巫尼姆瑞莎·唤波者。世界难度可以通过随机组队进入，而普通及以上难度则需要玩家自行组建队伍。需要挑战该巢穴的玩家，建议根据新的推荐装等提前准备装备。&lt;/p&gt;
+&lt;p&gt;　　掉落装备如下：&lt;/p&gt;
+&lt;p&gt;　　难度&lt;/p&gt;
+&lt;p&gt;　　掉落装等&lt;/p&gt;
+&lt;p&gt;　　装备等级&lt;/p&gt;
+&lt;p&gt;　　世界&lt;/p&gt;
+&lt;p&gt;　　279&lt;/p&gt;
+&lt;p&gt;　　老兵1/6&lt;/p&gt;
+&lt;p&gt;　　普通&lt;/p&gt;
+&lt;p&gt;　　292&lt;/p&gt;
+&lt;p&gt;　　勇士1/6&lt;/p&gt;
+&lt;p&gt;　　英雄&lt;/p&gt;
+&lt;p&gt;　　305&lt;/p&gt;
+&lt;p&gt;　　英雄1/6&lt;/p&gt;
+&lt;p&gt;　　神话&lt;/p&gt;
+&lt;p&gt;　　318&lt;/p&gt;
+&lt;p&gt;　　神话1/6&lt;/p&gt;
+&lt;p&gt;　　掉落装备一览&lt;/p&gt;
+&lt;p&gt;　　纳迦女巫尼姆瑞莎·唤波者可掉落以下装备：&lt;/p&gt;
+&lt;p&gt;　　装备&lt;/p&gt;
+&lt;p&gt;　　类型&lt;/p&gt;
+&lt;p&gt;　　属性&lt;/p&gt;
+&lt;p&gt;　　潮缚女巫长袍&lt;/p&gt;
+&lt;p&gt;　　布甲胸部&lt;/p&gt;
+&lt;p&gt;　　暴击、精通&lt;/p&gt;
+&lt;p&gt;　　深渊石窟束带&lt;/p&gt;
+&lt;p&gt;　　布甲腰部&lt;/p&gt;
+&lt;p&gt;　　暴击、全能&lt;/p&gt;
+&lt;p&gt;　　破浪长靴&lt;/p&gt;
+&lt;p&gt;　　皮甲脚部&lt;/p&gt;
+&lt;p&gt;　　急速、全能&lt;/p&gt;
+&lt;p&gt;　　涨潮护腕&lt;/p&gt;
+&lt;p&gt;　　锁甲护腕&lt;/p&gt;
+&lt;p&gt;　　精通、暴击&lt;/p&gt;
+&lt;p&gt;　　涡流之怒护手&lt;/p&gt;
+&lt;p&gt;　　锁甲手部&lt;/p&gt;
+&lt;p&gt;　　暴击、急速&lt;/p&gt;
+&lt;p&gt;　　涌潮肩铠&lt;/p&gt;
+&lt;p&gt;　　板甲肩部&lt;/p&gt;
+&lt;p&gt;　　暴击、精通&lt;/p&gt;
+&lt;p&gt;　　遗忘石窟束腰&lt;/p&gt;
+&lt;p&gt;　　板甲腰部&lt;/p&gt;
+&lt;p&gt;　　急速、全能&lt;/p&gt;
+&lt;p&gt;　　破潮者的爆泡杖&lt;/p&gt;
+&lt;p&gt;　　敏捷法杖&lt;/p&gt;
+&lt;p&gt;　　暴击、全能&lt;/p&gt;
+&lt;p&gt;　　霜鳞的秘法叶片&lt;/p&gt;
+&lt;p&gt;　　智力副手&lt;/p&gt;
+&lt;p&gt;　　暴击、精通&lt;/p&gt;
+&lt;p&gt;　　泡鳍防溅盾&lt;/p&gt;
+&lt;p&gt;　　智力/力量盾牌&lt;/p&gt;
+&lt;p&gt;　　精通、急速&lt;/p&gt;
+&lt;p&gt;　　魅惑泡沫指环&lt;/p&gt;
+&lt;p&gt;　　戒指&lt;/p&gt;
+&lt;p&gt;　　急速、全能&lt;/p&gt;
+&lt;p&gt;　　唤波者的海石&lt;/p&gt;
+&lt;p&gt;　　饰品&lt;/p&gt;
+&lt;p&gt;　　急速，主属性被动触发&lt;/p&gt;</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0805%2F1361f2dfj00tja2e9003qd000p400p2g.jpg&amp;thumbnail=660x2147483647&amp;quality=80&amp;type=jpg</t>
+          <t>https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0812%2F7d083544j00tjmzzc001ad000u0009qm.jpg&amp;thumbnail=660x2147483647&amp;quality=80&amp;type=jpg</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>网易首款“吃打撤手游”《雾海之下》8月17日开启首测</t>
+          <t>魔兽：暴雪8月12日蓝贴！美服更新后大量BUG，暴雪发布问题清单！</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
@@ -1373,21 +1503,40 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>IT之家 8 月 5 日消息，网易宣布旗下雷火工作室推出的首款“吃打撤”玩法手游《雾海之下》将于 8 月 17 日开启首测“大狩猎测试”。
-据介绍，本作采用西幻魔物题材，核心玩法为“吃打撤”：开局前，玩家通过“吃下魔物料理”获得对应的魔物能力，以此替代传统装备系统；进入对局后与两名队友在迷雾中探索、狩猎、抢夺资源；最后必须在迷雾完全吞没区域前成功撤离。
-官方表示，本次测试时间从 2026 年 8 月 17 日至 8 月 23 日（共 7 天），测试平台包含安卓、iOS 双端，为限号、删档、不计费模式，测试资格从 8 月 14 日起陆续发放。</t>
+          <t>&lt;img src="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0812%2F7d083544j00tjmzzc001ad000u0009qm.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" alt="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0812%2F7d083544j00tjmzzc001ad000u0009qm.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" /&gt;
+&lt;p&gt;　　《至暗之夜：乌拉特克的诅咒》内容更新现已上线。以下是暴雪正在处理的12.1已知问题列表。&lt;/p&gt;
+&lt;img src="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0812%2F08519411j00tjmzzc001gd000u000hsm.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" alt="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0812%2F08519411j00tjmzzc001gd000u000hsm.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" /&gt;
+&lt;p&gt;　　12.1已知问题&lt;/p&gt;
+&lt;p&gt;　　更新于8月12日&lt;/p&gt;
+&lt;p&gt;　　住房&lt;/p&gt;
+&lt;p&gt;　　蓝图&lt;/p&gt;
+&lt;p&gt;　　从不同地块导入房屋外观时，可能出现朝向异常的问题。&lt;/p&gt;
+&lt;p&gt;　　装饰&lt;/p&gt;
+&lt;p&gt;　　螺旋木楼梯无法染色。&lt;/p&gt;
+&lt;p&gt;　　剃风屋顶工的木瓦染色后不会改变外观。&lt;/p&gt;
+&lt;p&gt;　　使用暴风城厨房时，相连房间的贴图可能穿过相邻墙壁。&lt;/p&gt;
+&lt;p&gt;　　“虚空精灵铁砧”图纸无法退款。&lt;/p&gt;
+&lt;p&gt;　　功能&lt;/p&gt;
+&lt;p&gt;　　房屋的入口房间无法移动至房屋内其他位置。&lt;/p&gt;
+&lt;p&gt;　　剃风海岸的来访居民可能生成在半空中。&lt;/p&gt;
+&lt;p&gt;　　用户界面&lt;/p&gt;
+&lt;p&gt;　　任务旁提示“可追踪”的帮助提示关闭后，仍可能再次出现。&lt;/p&gt;
+&lt;p&gt;　　训练场&lt;/p&gt;
+&lt;p&gt;　　进入队列后，“加入战斗”按钮仍可再次点击。&lt;/p&gt;
+&lt;p&gt;　　失败方可能错误收到“获胜方已投降”的提示。&lt;/p&gt;
+&lt;p&gt;　　记分板显示了一个多余的“获胜回合数”栏目。&lt;/p&gt;</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0811%2F88bbd74dj00tjlimd001fd000l400bwg.jpg&amp;thumbnail=660x2147483647&amp;quality=80&amp;type=jpg</t>
+          <t>https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0807%2F164d9162j00tjeag70013d000u000gvm.jpg&amp;thumbnail=660x2147483647&amp;quality=80&amp;type=jpg</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Epic喜加一：好评平台冒险游戏《蜘蛛狐》</t>
+          <t>魔兽：必看！暴雪发布完整12.1补丁说明！全职业改动定稿！</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
@@ -1397,21 +1546,606 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Epic游戏商城现已开始免费赠送动作冒险平台游戏《蜘蛛狐》。玩家可在8月13日前将该游戏永久入库。游戏支持简体中文，epic原价为25元。
-Epic商店页面：Spider Fox
-《蜘蛛狐》是一款单人游戏，讲述了一位疯狂科学家将世界各地不同动物的DNA进行融合的故事。主角是一只狐狸与蜘蛛的独特混合体，它需要拯救发生变异的野兽，并阻止反派的阴谋。该作获得了玩家的高度评价，在Steam上拥有96%的好评率。</t>
+          <t>&lt;p&gt;　　暴雪今天发布了12.1完整补丁说明，其中职业改动全部放出，意味着目前PTR的职业已经定型，后续只会通过热修的方式来修改了！马上也会为大家出一期定型的职业强度排名给大家参考！&lt;/p&gt;
+&lt;p&gt;　　随着“乌拉特克的诅咒”内容更新的开启，前往盘卷蛇岛的道路已然开启，继续推进“至暗之夜”剧情，凶恶的敌人、受诅咒的水域以及尘封已久的秘密正等待着你的探索。快来迎接全新的冒险吧，包括烈毒之渊团队副本、毒牙祭坛地下城、全新地下堡、第2赛季挑战、家宅系统更新等更多精彩内容。&lt;/p&gt;
+&lt;p&gt;　　探索全新野外区域——盘卷蛇岛&lt;/p&gt;
+&lt;img src="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0807%2F164d9162j00tjeag70013d000u000gvm.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" alt="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0807%2F164d9162j00tjeag70013d000u000gvm.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" /&gt;
+&lt;p&gt;　　随着祖阿曼东海岸外岛屿上的迷雾渐渐消散，你将继续见证祖尔加的故事。我们将与祖尔加拉并肩作战，和她一同追捕祖尔加，将被困的兄弟和其他人带回祖阿曼。我们将深入探寻盘卷蛇岛那段尘封的历史，揭开被锁藏的秘密，并寻觅那些被遗留在那里的身影。&lt;/p&gt;
+&lt;p&gt;　　深入群山，迎接全新冒险&lt;/p&gt;
+&lt;img src="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0807%2F59029edej00tjeag7001cd000u000ggm.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" alt="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0807%2F59029edej00tjeag7001cd000u000ggm.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" /&gt;
+&lt;p&gt;　　在盘卷蛇岛的山脉深处，这片腐化的生态系统中到处都是剧毒的水域与凶恶的敌人。在探索的过程中，你将体验到多种多样的全新活动。&lt;/p&gt;
+&lt;p&gt;　　潜入阿塔乌特克地窟，准备迎接充满挑战的团队内容与轮换的公共事件。积极参与这些公共事件，最终将引出一场震撼的首领战。&lt;/p&gt;
+&lt;p&gt;　　在此区域内，玩家还能解锁专属的区域天赋树，它能提供各种增强战斗力的增益效果，以及优化探索体验的便利性增益。例如，你可以选择某项特性来降低探索海岛时周围毒液的致命效力。&lt;/p&gt;
+&lt;img src="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0807%2F88c8aaf0j00tjeag7001fd000u000gum.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" alt="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0807%2F88c8aaf0j00tjeag7001fd000u000gum.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" /&gt;
+&lt;p&gt;　　遭遇诅咒狂潮，直面稀有精英&lt;/p&gt;
+&lt;img src="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0807%2Fa595975ej00tjeag70017d000u000glm.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" alt="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0807%2Fa595975ej00tjeag70017d000u000glm.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" /&gt;
+&lt;p&gt;　　当你在这片区域中冒险时，将会遭遇“诅咒狂潮”。它们会定期在海岛上的五个轮换位置生成稀有精英。&lt;/p&gt;
+&lt;img src="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0807%2Fcabb628aj00tjeag7001pd000u000gsm.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" alt="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0807%2Fcabb628aj00tjeag7001pd000u000gsm.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" /&gt;
+&lt;p&gt;　　击杀稀有精英即可解锁该地点的诅咒垂钓。你还会探索到一段关于始祖龟船长托卡的当地故事，你可以通过提升他船员的声望，学习如何在海岛周围更危险的诅咒水域中进行垂钓。&lt;/p&gt;
+&lt;p&gt;　　踏入巢穴，直面世界首领&lt;/p&gt;
+&lt;img src="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0807%2F3fa0560ej00tjeag7001ed000u000gtm.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" alt="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0807%2F3fa0560ej00tjeag7001ed000u000gtm.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" /&gt;
+&lt;p&gt;　　隆重介绍“巢穴”——世界首领战的全面进化之作。这些首领战将位于独立的副本环境中，并可根据15至25人的团队规模进行难度弹性缩放，最高可达史诗难度。你可以像寻找地下堡一样在特定地点发现巢穴，并且每个巢穴外都贴心地配备了集合石。&lt;/p&gt;
+&lt;img src="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0807%2F5e289559j00tjeag70012d000u000gum.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" alt="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0807%2F5e289559j00tjeag70012d000u000gum.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" /&gt;
+&lt;p&gt;　　在全新地下城“毒牙祭坛”中直面三位新首领&lt;/p&gt;
+&lt;img src="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0807%2F6c6addd1j00tjeag7001hd000u000gmm.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" alt="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0807%2F6c6addd1j00tjeag7001hd000u000gmm.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" /&gt;
+&lt;p&gt;　　这座包含三名首领的全新地下城将在内容更新上线时首发，并开放至史诗难度。在更新上线一周后，“至暗之夜”第2赛季正式开启时，它将加入史诗钥石地下城的轮换池。&lt;/p&gt;
+&lt;p&gt;　　深入烈毒之渊团队副本，直面乌拉特克&lt;/p&gt;
+&lt;img src="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0807%2Fa4e8e959j00tjeag7002gd000u000gom.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" alt="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0807%2Fa4e8e959j00tjeag7002gd000u000gom.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" /&gt;
+&lt;p&gt;　　随着“至暗之夜”第2赛季的开启，玩家将深入烈毒之渊，直面乌拉特克本尊。这只古老而强大的生物汇聚了仇恨、腐化与毒液，由于祖尔加的肆意妄为而被释放。这座全新的团队副本将包含八场全新的首领战，而你将在旅途的终点，与最终首领乌拉特克展开殊死搏斗。&lt;/p&gt;
+&lt;p&gt;　　勇闯三个全新地下堡，迎接全新的宿敌地下堡&lt;/p&gt;
+&lt;p&gt;　　荣耀之环&lt;/p&gt;
+&lt;img src="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0807%2F3e625ebbj00tjeag6000jd000h1009qm.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" alt="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0807%2F3e625ebbj00tjeag6000jd000h1009qm.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" /&gt;
+&lt;p&gt;　　纳拉多尔岛&lt;/p&gt;
+&lt;img src="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0807%2F42c311cbj00tjeag7000md000h8009nm.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" alt="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0807%2F42c311cbj00tjeag7000md000h8009nm.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" /&gt;
+&lt;p&gt;　　毒瀑深渊（宿敌地下堡）&lt;/p&gt;
+&lt;img src="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0807%2Fe8b41753j00tjeag6000pd000hm009hm.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" alt="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0807%2Fe8b41753j00tjeag6000pd000hm009hm.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" /&gt;
+&lt;p&gt;　　挑战三个全新地下堡，包含一个全新的宿敌地下堡。你将踏入荣耀之环、纳拉多尔岛以及毒瀑深渊宿敌地下堡，赢取全新奖励（以及一些无上荣耀）。随着8月20日“至暗之夜”第2赛季的开启，丰裕地下堡将会同步上线。届时，玩家将能够挑战超越7层的更高难度，不断突破自我，并直面全新的宿敌首领。&lt;/p&gt;
+&lt;p&gt;　　与此同时，玩家还将在现有的“至暗之夜”地下堡中，遭遇全新的蛇类和毒液变异敌人。&lt;/p&gt;
+&lt;img src="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0807%2F7d817d35j00tjeag7002dd000u000gvm.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" alt="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0807%2F7d817d35j00tjeag7002dd000u000gvm.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" /&gt;
+&lt;p&gt;　　备战“至暗之夜”第2赛季&lt;/p&gt;
+&lt;img src="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0807%2F487ab152j00tjeag6001dd000u000gqm.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" alt="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0807%2F487ab152j00tjeag6001dd000u000gqm.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" /&gt;
+&lt;p&gt;　　内容更新上线一周后，新赛季将正式拉开帷幕。届时将带来全新的史诗钥石地下城轮换、新团队副本、新PvP赛季以及更多的狩猎目标。同时，丰裕地下堡和钥匙也将开放获取。&lt;/p&gt;
+&lt;p&gt;　　史诗钥石地下城轮换池&lt;/p&gt;
+&lt;p&gt;　　新地下城：毒牙祭坛&lt;/p&gt;
+&lt;p&gt;　　密谋小径&lt;/p&gt;
+&lt;p&gt;　　纳洛拉克的洞穴&lt;/p&gt;
+&lt;p&gt;　　夺目谷&lt;/p&gt;
+&lt;p&gt;　　虚空之痕竞技场&lt;/p&gt;
+&lt;p&gt;　　回归地下城迎来设计调整及体验改进&lt;/p&gt;
+&lt;p&gt;　　诸王之眠&lt;/p&gt;
+&lt;p&gt;　　红玉新生法池&lt;/p&gt;
+&lt;p&gt;　　塞塔里斯神庙&lt;/p&gt;
+&lt;p&gt;　　在第2赛季中追踪全新猎物&lt;/p&gt;
+&lt;img src="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0807%2F65c9d383j00tjeag6000td000h6009jm.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" alt="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0807%2F65c9d383j00tjeag6000td000h6009jm.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" /&gt;
+&lt;p&gt;　　当第2赛季于8月20日开启后，玩家可以开始“蜿蜒的威胁”任务线。梦魇模式也将回归，带来四个全新的蛇类主题狩猎目标，并让玩家在盘卷蛇岛各地展开狩猎。&lt;/p&gt;
+&lt;p&gt;　　在盘卷蛇岛的梦魇模式中，你可以收集骨化圣物，激活散布在岛上的魂萦火盆，召唤拉尔卡拉并将其击败，以获取独特奖励。这项玩法需要与其他玩家合作完成。&lt;/p&gt;
+&lt;p&gt;　　第2赛季的狩猎旅程奖励路线提供了新的装饰、外观和坐骑。你还将解锁从地下堡中收集受难之魂和折磨之魂的能力。使用这些灵魂可以加快当前梦魇狩猎的进度，并获得额外奖励。&lt;/p&gt;
+&lt;p&gt;　　最后，“岛屿诅咒”将带来一种可随时开启的常驻梦魇模式。寻求更高难度挑战的玩家可以将其开启，大幅提升整个盘卷蛇岛的危险程度！&lt;/p&gt;
+&lt;p&gt;　　训练场拓展至竞技场&lt;/p&gt;
+&lt;img src="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0807%2F19e70eccj00tjeag7001qd000u000gym.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" alt="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0807%2F19e70eccj00tjeag7001qd000u000gym.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" /&gt;
+&lt;p&gt;　　训练场已经吸引了更多玩家加入PvP生态系统。继“与电脑对战的战场”之后，我们将为那些想要尝试3v3竞技场并学习基础技巧的玩家，推出全新的“与电脑对战的竞技场”模式。要体验这项新功能，请在队伍查找器的PvP选项卡中选择“训练场”。&lt;/p&gt;
+&lt;p&gt;　　家宅系统更新&lt;/p&gt;
+&lt;p&gt;　　善用图纸，打造你的完美住宅&lt;/p&gt;
+&lt;p&gt;　　如果你想与他人分享自己炫酷的住宅布置，现在你可以随心所欲地进行导出了！无论是整个室外和室内布置，还是仅导出室内、仅导出室外，甚至单独导出一个房间的布置，都能轻松实现。&lt;/p&gt;
+&lt;img src="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0807%2Fb411ee48j00tjeag70015d000u0008cm.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" alt="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0807%2Fb411ee48j00tjeag70015d000u0008cm.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" /&gt;
+&lt;p&gt;　　图纸可供玩家保存自己的住宅设计，随时切换使用或与其他玩家分享！&lt;/p&gt;
+&lt;p&gt;　　图纸代码可跨地区（国服除外）分享，其他玩家也能导入使用。&lt;/p&gt;
+&lt;p&gt;　　图纸可应用于整栋住宅（包括室内和室外）、仅室内、仅室外或单个房间。&lt;/p&gt;
+&lt;p&gt;　　导入时会显示所需的全部房间和装饰清单，包括需要占用的预算、目前缺少的物品等，让玩家提前了解导入会带来哪些变化、还需要准备什么。&lt;/p&gt;
+&lt;p&gt;　　导入功能还会妥善处理染色物品：优先使用颜色正确的物品，必要时为物品染色，但不会替换已经染色的物品等。&lt;/p&gt;
+&lt;p&gt;　　玩家最多可为不同布局设置50个“保存栏位”，另有10个“自动保存”栏位。&lt;/p&gt;
+&lt;p&gt;　　导入图纸时会自动建立存档，方便玩家轻松还原。&lt;/p&gt;
+&lt;p&gt;　　住宅权限中新增了“导出”选项，默认不向任何人开放。其他玩家造访住宅时，如果拥有这项权限，就能将该住宅导入自己的保存栏位。&lt;/p&gt;
+&lt;p&gt;　　新增“重置”按钮。想要从头开始时，可以重置整栋住宅，也可以只重置室内或室外区域。&lt;/p&gt;
+&lt;p&gt;　　图纸代码可以发送到聊天频道中，也可直接在聊天信息中查看。&lt;/p&gt;
+&lt;p&gt;　　现在可以举报图纸。&lt;/p&gt;
+&lt;p&gt;　　欢迎你的宠物回家&lt;/p&gt;
+&lt;img src="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0807%2F04024b94j00tjeag7001bd000u0008cm.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" alt="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0807%2F04024b94j00tjeag7001bd000u0008cm.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" /&gt;
+&lt;p&gt;　　通过添加宠物床这件装饰，你可以将非战斗小宠物安置在屋内，让它们在家中自由漫步。借助全新的寻路技术，你的爱宠还能够在你的住宅中四处闲逛，在各种装饰之间自如穿梭。&lt;/p&gt;
+&lt;p&gt;　　宠物床让玩家可以在住宅内外展示自己的宠物。&lt;/p&gt;
+&lt;p&gt;　　玩家最多可在室内放置10张宠物床，在室外放置5张。放置宠物床后，玩家可以选择一只宠物在此安家。&lt;/p&gt;
+&lt;p&gt;　　室内宠物可设为“静止”或“漫游”，目前放在室外的宠物只能设为“静止”。&lt;/p&gt;
+&lt;p&gt;　　出于种种原因，少量宠物暂时无法安置。&lt;/p&gt;
+&lt;p&gt;　　新住宅区文化节&lt;/p&gt;
+&lt;p&gt;　　随着阿曼尼巨魔、狗头人、欧恩哈拉半人马和始祖龟的加入，四个全新的文化节来到了你的住宅区。&lt;/p&gt;
+&lt;p&gt;　　阿曼尼巨魔：高仿阿曼尼&lt;/p&gt;
+&lt;img src="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0807%2F5adfa415j00tjeag60012d000h9009om.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" alt="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0807%2F5adfa415j00tjeag60012d000h9009om.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" /&gt;
+&lt;p&gt;　　格里伏塔和他手下的游商小队想来我们住宅区做买卖，推销所谓的“传统阿曼尼商品”。明眼人一看就知道这是假冒伪劣，但这丝毫不影响住宅区居民凑热闹的兴致。&lt;/p&gt;
+&lt;p&gt;　　狗头人：蜡烛文化&lt;/p&gt;
+&lt;img src="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0807%2F22be8a27j00tjeag6000zd000h4009om.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" alt="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0807%2F22be8a27j00tjeag6000zd000h4009om.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" /&gt;
+&lt;p&gt;　　住宅区里开始出现奇怪的蜡质沉积物。要说谁最懂得怎么利用这些东西，那非喧鸣深窟的狗头人莫属！去向他们请教照明的建议吧。&lt;/p&gt;
+&lt;p&gt;　　欧恩哈拉半人马：獒犬也有出头天&lt;/p&gt;
+&lt;img src="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0807%2F61f0e7fbj00tjeag70013d000hb009qm.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" alt="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0807%2F61f0e7fbj00tjeag70013d000hb009qm.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" /&gt;
+&lt;p&gt;　　住宅区的居民很爱他们的宠物，但在训练方面需要一些帮助。欧恩哈拉平原的马鲁克与他们的獒犬之间有着极深的羁绊，他们也许愿意传授一些训练技巧。&lt;/p&gt;
+&lt;p&gt;　　始祖龟：度假季&lt;/p&gt;
+&lt;img src="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0807%2F0440e32bj00tjeag6000rd000h6009um.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" alt="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0807%2F0440e32bj00tjeag6000rd000h6009um.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" /&gt;
+&lt;p&gt;　　始祖龟是一个见多识广的种族。事实上，他们如此见多识广，以至于根本不需要熟悉你的住宅区——早在你扎根于此之前，他们就已经在这里度假了！去分享他们休闲娱乐的智慧吧。&lt;/p&gt;
+&lt;p&gt;　　住宅区中还会根据已经完成的新旧文化节出现一些新变化。&lt;/p&gt;
+&lt;p&gt;　　其他家宅系统更新&lt;/p&gt;
+&lt;p&gt;　　住宅&lt;/p&gt;
+&lt;p&gt;　　住宅等级上限现已提升至12级，可解锁更高的数量上限、大型外观等内容。&lt;/p&gt;
+&lt;p&gt;　　现在可以向各个住宅区的总承包商NPC购买全新的匠心房间。兽人、人类、暗夜精灵和血精灵风格各新增四种房间，可使用社区礼券购买。跨阵营风格的房间需要向住宅区里的私运者购买。&lt;/p&gt;
+&lt;p&gt;　　住宅区新增更多可使用社区礼券购买的住宅物品。&lt;/p&gt;
+&lt;p&gt;　　玩家现在可以将入口房间移动到住宅中的任意位置，包括其他楼层！地下室的梦想终于可以实现了！&lt;/p&gt;
+&lt;p&gt;　　染料&lt;/p&gt;
+&lt;p&gt;　　染料制作流程经过简化，大幅减少了染料占用的背包空间。&lt;/p&gt;
+&lt;p&gt;　　新增多种染料颜色，其中包括可还原12.0.5内容更新前深色外观的颜色。&lt;/p&gt;
+&lt;p&gt;　　用户界面&lt;/p&gt;
+&lt;p&gt;　　新增两种装饰类别：&lt;/p&gt;
+&lt;p&gt;　　藤蔓与悬挂植物&lt;/p&gt;
+&lt;p&gt;　　宠物床&lt;/p&gt;
+&lt;p&gt;　　删除不含任何装饰的房间时，不再弹出多余的确认窗口。&lt;/p&gt;
+&lt;p&gt;　　冷却管理器与界面优化&lt;/p&gt;
+&lt;p&gt;　　更新后，冷却管理器可追踪饰品与药水，消耗品管理更省心。种族技能的冷却与持续时间也能一并纳入。&lt;/p&gt;
+&lt;img src="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0807%2F475d7e09j00tjeag7001rd000f300lbm.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" alt="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0807%2F475d7e09j00tjeag7001rd000f300lbm.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" /&gt;
+&lt;p&gt;　　为了方便管理其他资源，信号系统也得到了同步加强。玩家可直接在动作条或冷却管理器上发送信号，向队伍直接通报你的法术冷却状态。&lt;/p&gt;
+&lt;p&gt;　　玩家也可以给自己的单位框体打信号，向队伍同步生命值；治疗职责还可顺带报出法力值，开怪前不必再专门喊一声“没蓝了”。&lt;/p&gt;
+&lt;img src="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0807%2F3af325b1j00tjeag7000zd000u00087m.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" alt="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0807%2F3af325b1j00tjeag7000zd000u00087m.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" /&gt;
+&lt;p&gt;　　治疗者现在可以自行配置，甚至隐藏团队框体上的增益显示，让你最在意的那些治疗效果一直清楚可见。&lt;/p&gt;
+&lt;img src="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0807%2Fc6d504bfj00tjeag7001pd000u000s6m.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" alt="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0807%2Fc6d504bfj00tjeag7001pd000u000s6m.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" /&gt;
+&lt;p&gt;　　与阿拉托尔继续追猎萨拉塔斯&lt;/p&gt;
+&lt;p&gt;　　第2赛季开启时，我们将再次与阿拉托尔并肩作战，应对虚影尖塔带来的余波，并随他一同调查暮光之刃死灰复燃的真相，并继续展开对萨拉塔斯的追猎。&lt;/p&gt;
+&lt;img src="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0807%2F005edb1bj00tjeag70028d000u000gym.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" alt="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0807%2F005edb1bj00tjeag70028d000u000gym.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" /&gt;
+&lt;p&gt;　　角色&lt;/p&gt;
+&lt;p&gt;　　土灵&lt;/p&gt;
+&lt;p&gt;　　开发者注释：在“乌拉特克的诅咒”中，我们重新审视了探索区域时获得的经验值。这项调整对土灵角色的升级速度影响尤为明显，因为大开眼界种族技能会让他们通过探索获得更多经验值。为弥补区域探索经验值的下调，我们将提高土灵矿石摄入的增益效果。&lt;/p&gt;
+&lt;p&gt;　　探索区域获得的基础经验值降低60%。&lt;/p&gt;
+&lt;p&gt;　　探索低等级区域时，获得的经验值不再低于基础值。&lt;/p&gt;
+&lt;p&gt;　　通过矿石摄入获得的进食充分效果提高30%。&lt;/p&gt;
+&lt;p&gt;　　职业&lt;/p&gt;
+&lt;p&gt;　　满级玩家的生命值和生物伤害提高25%。治疗类消耗品的数值已根据新的生命值进行调整。&lt;/p&gt;
+&lt;p&gt;　　开发者注释：在“乌拉特克的诅咒”中，我们决定将满级玩家的生命值和敌人造成的伤害提高25%。我们曾在“至暗之夜”上线之初和“巨龙时代”早期进行过类似调整。我们希望借此缓和伤害峰值，并让治疗玩法带来更好的体验。如果治疗量过度集中于短时间爆发，敌人就必须造成峰值伤害，玩家也只能迅速反应才能存活。我们认为，这会让战斗体验缺乏乐趣，也更加紧张。虽然这项改动会提高生物的整体伤害，但我们也会逐项调整首领战技能，使其伤害与整体变动相称，并符合我们的设计目标。我们还会调整伤害输出和坦克专精的若干治疗及吸收技能，使它们仍能保持原有的相对作用。&lt;/p&gt;
+&lt;p&gt;　　所有职业的打断技能（例如脚踢、拳击和法术反制等）如果在目标未施法时使用，现在会在目标头顶显示“未命中”视觉效果。打断落空时还会播放一段独立的音效。即使没有成功打断法术，这也能帮助玩家察觉敌人或盟友是否使用了打断技能。&lt;/p&gt;
+&lt;p&gt;　　收益递减类别的重置时间调整为20秒（原为16秒）。&lt;/p&gt;
+&lt;p&gt;　　开发者注释：我们一直在关注第1赛季PvP群体控制效果递减机制的改动。玩家在免疫同类效果前可连续承受的控制次数由3次降至2次，我们对控制效果重复出现次数的减少感到满意。当时我们也缩短了免疫或减弱效果重置所需的时间。为了继续减少玩家失去角色控制权的总时长，我们决定进一步调整这部分机制。因此，第2赛季的重置时间将由16秒延长至20秒。&lt;/p&gt;
+&lt;p&gt;　　在“乌拉特克的诅咒”中，我们会降低多个专精主要伤害输出冷却技能在生效期间的伤害，同时提高其常态伤害。如果冷却技能生效期间造成的伤害远高于冷却期外，冷却期外的战斗节奏就会显得迟缓。我们的首要目标是让冷却技能继续带来强力而有趣的高光时刻，同时确保未开启冷却技能时的伤害依然有效，并维持各专精之间鲜明的特色。&lt;/p&gt;
+&lt;p&gt;　　死亡骑士&lt;/p&gt;
+&lt;p&gt;　　英雄天赋&lt;/p&gt;
+&lt;p&gt;　　萨莱因&lt;/p&gt;
+&lt;p&gt;　　血兽的自动攻击伤害提高1400%。&lt;/p&gt;
+&lt;p&gt;　　血染之地现在使受到的物理伤害降低8%（原为5%）。&lt;/p&gt;
+&lt;p&gt;　　鲜血&lt;/p&gt;
+&lt;p&gt;　　顶峰天赋：午夜舞步（等级2）已更新——每有一个激活的符文刃舞，受到的伤害降低6%（原为4%）。&lt;/p&gt;
+&lt;p&gt;　　近战伤害提高20%。&lt;/p&gt;
+&lt;p&gt;　　心脏打击的伤害提高25%。&lt;/p&gt;
+&lt;p&gt;　　骨髓分裂的伤害提高50%。&lt;/p&gt;
+&lt;p&gt;　　符文刃舞现在使招架提高30%（原为25%）。&lt;/p&gt;
+&lt;p&gt;　　永冻提供的护盾相当于所造成伤害的50%（原为40%）。&lt;/p&gt;
+&lt;p&gt;　　饮血提供15%的吸血（原为12%）。&lt;/p&gt;
+&lt;p&gt;　　猩红余味的治疗效果提高25%。&lt;/p&gt;
+&lt;p&gt;　　迅速凋零使血之疫病的治疗效果提高85%（原为50%）。&lt;/p&gt;
+&lt;p&gt;　　血腥爆裂为你恢复相当于所造成伤害18%的生命值（原为15%）。&lt;/p&gt;
+&lt;p&gt;　　永恒脐带吸收的伤害相当于血之疫病所造成伤害的6倍（原为5倍）。&lt;/p&gt;
+&lt;p&gt;　　消耗赤色天灾时，黑锋骑士团之毅现在使受到的伤害降低4%。持续时间延长至10秒（原为6秒）。&lt;/p&gt;
+&lt;p&gt;　　鲜血护盾激活期间，血箭现在还会使受到的伤害降低4%。&lt;/p&gt;
+&lt;p&gt;　　英雄天赋&lt;/p&gt;
+&lt;p&gt;　　死亡使者&lt;/p&gt;
+&lt;p&gt;　　死神印记对主要目标造成的伤害提高20%。&lt;/p&gt;
+&lt;p&gt;　　破灭对主要目标造成的伤害提高20%。&lt;/p&gt;
+&lt;p&gt;　　萨莱因&lt;/p&gt;
+&lt;p&gt;　　萨莱因之契现在会储存所造成全部暗影伤害的15%（原为10%）。&lt;/p&gt;
+&lt;p&gt;　　吸血鬼打击的伤害提高25%。&lt;/p&gt;
+&lt;p&gt;　　脏腑之力现在提供10%力量（原为12%）。&lt;/p&gt;
+&lt;p&gt;　　疯狂嗜血每层使灵界打击和凋零缠绕伤害提高的效果降低至5%（原为6%）。&lt;/p&gt;
+&lt;p&gt;　　血为命源现在会积蓄血兽所造成伤害的15%（原为25%）。&lt;/p&gt;
+&lt;p&gt;　　冰霜&lt;/p&gt;
+&lt;p&gt;　　开发者注释：我们将提高若干循环技能的强度，这些技能在整体伤害构成中的表现不及预期。此外，我们还会提高冰霜死亡骑士在冷却技能空档期的持续伤害。冰霜之柱期间的湮灭玩法和数值表现依然强势，因此我们可以将一部分强度重新分配给其他技能。&lt;/p&gt;
+&lt;p&gt;　　所有技能造成的伤害降低10%。&lt;/p&gt;
+&lt;p&gt;　　近战伤害降低20%。&lt;/p&gt;
+&lt;p&gt;　　冰霜之柱现在使力量提高20%（原为30%）。&lt;/p&gt;
+&lt;p&gt;　　凛风冲击的伤害提高100%。&lt;/p&gt;
+&lt;p&gt;　　符文武器增效的伤害提高30%。&lt;/p&gt;
+&lt;p&gt;　　冰川突进的伤害提高30%。&lt;/p&gt;
+&lt;p&gt;　　死亡寒潮的伤害提高30%。&lt;/p&gt;
+&lt;p&gt;　　冰霜疫病的伤害提高100%。&lt;/p&gt;
+&lt;p&gt;　　冷酷严冬的伤害提高40%。&lt;/p&gt;
+&lt;p&gt;　　冰霜之镰的伤害提高20%。&lt;/p&gt;
+&lt;p&gt;　　冰霜打击的伤害提高25%。该效果不影响冰霜灾祸。&lt;/p&gt;
+&lt;p&gt;　　湮灭的伤害降低12.5%。&lt;/p&gt;
+&lt;p&gt;　　冰龙吐息的伤害降低20%。&lt;/p&gt;
+&lt;p&gt;　　冰霜灾祸的伤害降低30%。&lt;/p&gt;
+&lt;p&gt;　　冰霜巨龙之怒的伤害降低20%。&lt;/p&gt;
+&lt;p&gt;　　永冻提供的护盾相当于所造成伤害的35%（原为30%）。&lt;/p&gt;
+&lt;p&gt;　　英雄天赋&lt;/p&gt;
+&lt;p&gt;　　死亡使者&lt;/p&gt;
+&lt;p&gt;　　枯败凋亡现在使冰霜疫病造成伤害的频率加快75%（原为100%）。&lt;/p&gt;
+&lt;p&gt;　　致命打击现在使冰霜打击的伤害提高35%（原为15%）。&lt;/p&gt;
+&lt;p&gt;　　死神印记的施放伤害和爆炸伤害降低25%。&lt;/p&gt;
+&lt;p&gt;　　破灭的伤害降低17%。&lt;/p&gt;
+&lt;p&gt;　　天启骑士&lt;/p&gt;
+&lt;p&gt;　　怀特迈恩的死灵伤害降低30%。&lt;/p&gt;
+&lt;p&gt;　　邪恶&lt;/p&gt;
+&lt;p&gt;　　开发者注释：在“乌拉特克的诅咒”中，我们希望缩小冷却技能生效期间与冷却期外的伤害差距。此外，我们也在重新审视邪恶死亡骑士目前召唤物过于密集的问题。在“至暗之夜”的重做中，邪恶死亡骑士被重新塑造成召唤天灾大军的职业，我们对最终效果十分满意。不过，再加上天启骑士英雄天赋树原有的召唤能力后，召唤物的数量已经超出我们认为合适的范围。为玩家提供清晰易读的战斗空间至关重要。我们认为，如果不违背这项核心原则，当前设计已没有余地继续增加召唤能力。&lt;/p&gt;
+&lt;p&gt;　　复苏更名为亡者之主，次要效果也经过重新设计——当你控制3名亡者魔导师时，将其献祭并召唤亡者之主，持续15秒。亡者之主会施放可在2名敌人之间弹射的寒冰箭。剩余持续时间越长的亡者魔导师，提供的强化效果越高。&lt;/p&gt;
+&lt;p&gt;　　顶峰天赋：禁断知识（等级3）已更新——亡者魔导师不再叠加提高死灵缠绕和灾殃坟茔的伤害。恐惧瘟疫触发腐化时，其效果提高至100%（原为60%）。&lt;/p&gt;
+&lt;p&gt;　　顶峰天赋：禁断知识——死灵缠绕的伤害降低6%，灾殃坟茔的伤害提高17.3%。&lt;/p&gt;
+&lt;p&gt;　　灵魂收割已更新——施放时不再消耗腐化的使用次数。现在会消耗最多3层次级食尸鬼，使其立即被召唤出来。&lt;/p&gt;
+&lt;p&gt;　　邪恶光环已更新——亡者魔导师出现时会提供急速增益，持续15秒。&lt;/p&gt;
+&lt;p&gt;　　亡者大军已更新——召唤或强化次级食尸鬼，组成一支数量为8、持续30秒的邪恶大军。亡者大军激活期间，你会通过天灾打击指挥大军，根据附近的敌人执行不同敕令，而不再召唤次级食尸鬼。&lt;/p&gt;
+&lt;p&gt;　　死亡敕令——次级食尸鬼会与你一同攻击，对目标造成暗影伤害。&lt;/p&gt;
+&lt;p&gt;　　传染敕令——次级食尸鬼爆裂成脏器碎片，对附近的敌人造成暗影伤害。目标数量超过5个后造成的伤害降低。&lt;/p&gt;
+&lt;p&gt;　　亡者大军的次级食尸鬼伤害降低25%。&lt;/p&gt;
+&lt;p&gt;　　阴险魔导师新增一项效果——亡者之主的寒冰箭现在还可弹射至另外3名敌人。&lt;/p&gt;
+&lt;p&gt;　　所有伤害降低3%。&lt;/p&gt;
+&lt;p&gt;　　自动攻击伤害提高100%。&lt;/p&gt;
+&lt;p&gt;　　次级食尸鬼造成的伤害降低6.5%。&lt;/p&gt;
+&lt;p&gt;　　扩散的伤害提高54%。该效果不影响灾殃坟茔。&lt;/p&gt;
+&lt;p&gt;　　亡者魔导师的伤害降低15%。&lt;/p&gt;
+&lt;p&gt;　　腐化的伤害降低15%。&lt;/p&gt;
+&lt;p&gt;　　腐化的范围伤害提高35%。&lt;/p&gt;
+&lt;p&gt;　　疫疾的伤害降低25%。&lt;/p&gt;
+&lt;p&gt;　　染疫之爪的伤害降低25%。&lt;/p&gt;
+&lt;p&gt;　　恶性病变造成的伤害提高2%。&lt;/p&gt;
+&lt;p&gt;　　亡者指挥官现在使黑暗突变令召唤生物造成的伤害提高10%/20%，持续30秒（原为15%/30%）。&lt;/p&gt;
+&lt;p&gt;　　爆裂脏器对超过5个目标造成的伤害降低。&lt;/p&gt;
+&lt;p&gt;　　永冻提供的护盾相当于所造成伤害的35%（原为30%）。&lt;/p&gt;
+&lt;p&gt;　　腐化喷射现在使腐化将疾病的持续时间延长3秒（原为4.5秒）。&lt;/p&gt;
+&lt;p&gt;　　符文能量消耗技能现在会将疾病的持续时间延长1秒（原为1.5秒）。&lt;/p&gt;
+&lt;p&gt;　　在死亡骑士40码范围内对新目标施加恐惧瘟疫时，会保留其已延长的持续时间。&lt;/p&gt;
+&lt;p&gt;　　修正了献祭亡者魔导师以召唤亡者之主时，纳兹戈林之征服会额外提供力量的问题。&lt;/p&gt;
+&lt;p&gt;　　纳兹戈林之征服不再能通过小动物和低等级目标提供力量。&lt;/p&gt;
+&lt;p&gt;　　死亡骑士以外的玩家现在最多只能同时看到3只次级食尸鬼。&lt;/p&gt;
+&lt;p&gt;　　英雄天赋&lt;/p&gt;
+&lt;p&gt;　　天启骑士&lt;/p&gt;
+&lt;p&gt;　　怀特迈恩的凋零缠绕伤害降低25%。&lt;/p&gt;
+&lt;p&gt;　　怀特迈恩的死灵伤害降低25%。&lt;/p&gt;
+&lt;p&gt;　　恶魔猎手&lt;/p&gt;
+&lt;p&gt;　　恶魔猎手现在可以装备匕首。&lt;/p&gt;
+&lt;p&gt;　　开发者注释：这项改动将使噬灭恶魔猎手可以获取并使用带有智力属性的匕首。&lt;/p&gt;
+&lt;p&gt;　　噬灭&lt;/p&gt;
+&lt;p&gt;　　开发者注释：我们将降低噬灭专精“精通：内在恶魔”的成长幅度，让其他属性更具竞争力，并通过提高所有技能伤害作为补偿。结合这项改动和其他几项针对性调整，我们预计虚空变形期间的伤害会略有降低，而恶魔变形以外的伤害会显著提高。&lt;/p&gt;
+&lt;p&gt;　　精通：内在恶魔已更新——虚空变形期间的伤害加成降低66%。&lt;/p&gt;
+&lt;p&gt;　　所有技能造成的伤害提高32%。&lt;/p&gt;
+&lt;p&gt;　　坍缩之星的伤害提高12%。&lt;/p&gt;
+&lt;p&gt;　　根除的伤害降低6%，对次要目标的伤害降低15%。&lt;/p&gt;
+&lt;p&gt;　　吞噬的伤害提高60%（该效果不影响噬灭）。&lt;/p&gt;
+&lt;p&gt;　　虚空变形现在使虚空射线的伤害提高40%（原为67%）。&lt;/p&gt;
+&lt;p&gt;　　天启将至现在使每颗坍缩之星令下一颗坍缩之星的伤害提高20%（原为30%）。&lt;/p&gt;
+&lt;p&gt;　　饥渴斩击现在会正确提供一次复仇回避的临时使用次数，而不再提供一次免费施放并同时重置其冷却时间。&lt;/p&gt;
+&lt;p&gt;　　英雄天赋&lt;/p&gt;
+&lt;p&gt;　　歼灭者&lt;/p&gt;
+&lt;p&gt;　　异界专注现在使坍缩之星和虚落流星对单个目标造成的伤害提高30%（原为35%）。&lt;/p&gt;
+&lt;p&gt;　　终末时刻现在使虚落的加成持续6秒（原为8秒）。&lt;/p&gt;
+&lt;p&gt;　　浩劫&lt;/p&gt;
+&lt;p&gt;　　开发者注释：以下狂怒生成调整会带来小幅整体提升，使资源获取更加平稳，并降低对献祭光环天赋效果的依赖。&lt;/p&gt;
+&lt;p&gt;　　恶魔之刃、刃舞和混乱打击现在需要装备战刃、斧、剑或拳套才能使用。&lt;/p&gt;
+&lt;p&gt;　　新天赋：永不言弃——生命值高于50%时，造成的伤害提高3%。生命值低于50%时，吸血提高5%。&lt;/p&gt;
+&lt;p&gt;　　毁灭之痕已更新——伤害现在会立即生效，不再于4秒内以持续伤害的形式造成。&lt;/p&gt;
+&lt;p&gt;　　锯齿战刃已更新——效果现在会作为增益施加给恶魔猎手，持续12秒；不再作为持续15秒的减益施加给敌方目标。&lt;/p&gt;
+&lt;p&gt;　　刃舞的伤害提高6%。&lt;/p&gt;
+&lt;p&gt;　　死亡横扫的伤害提高6%。&lt;/p&gt;
+&lt;p&gt;　　混乱打击的伤害提高6%。&lt;/p&gt;
+&lt;p&gt;　　毁灭的伤害提高6%。&lt;/p&gt;
+&lt;p&gt;　　恶魔追击的伤害提高12%。&lt;/p&gt;
+&lt;p&gt;　　献祭光环的伤害降低8%。&lt;/p&gt;
+&lt;p&gt;　　精华破碎的初始伤害提高49%。&lt;/p&gt;
+&lt;p&gt;　　燃烧之恨现在使献祭光环额外产生30点狂怒（原为40点）。&lt;/p&gt;
+&lt;p&gt;　　恶魔之刃现在每次攻击产生10至16点狂怒（原为8至15点）。&lt;/p&gt;
+&lt;p&gt;　　盲目之怒现在使眼棱每秒产生10/20点狂怒（原为15/30点）。&lt;/p&gt;
+&lt;p&gt;　　冲撞惯性现在使伤害提高12%，持续6秒（原为提高18%，持续5秒）。&lt;/p&gt;
+&lt;p&gt;　　内心之魔的位置已调整，现在与混沌理论组成选择节点（原本与混沌变身组成选择节点）。&lt;/p&gt;
+&lt;p&gt;　　混乱奔袭已被移除。&lt;/p&gt;
+&lt;p&gt;　　复仇&lt;/p&gt;
+&lt;p&gt;　　破裂和灵魂裂劈现在需要装备战刃、斧、剑或拳套才能使用。&lt;/p&gt;
+&lt;p&gt;　　锁链咒符现在于35级习得，不再是天赋。&lt;/p&gt;
+&lt;p&gt;　　锁链咒符的冷却时间缩短至60秒（原为90秒）。&lt;/p&gt;
+&lt;p&gt;　　锁链咒符不再取代悲苦咒符。&lt;/p&gt;
+&lt;p&gt;　　选择沉默咒符后，它现在会取代悲苦咒符。&lt;/p&gt;
+&lt;p&gt;　　强化悲苦咒符不再影响锁链咒符。&lt;/p&gt;
+&lt;p&gt;　　选择沉默咒符后，强化悲苦咒符现在会使沉默咒符的冷却时间缩短15秒。&lt;/p&gt;
+&lt;p&gt;　　所有伤害提高5.5%。&lt;/p&gt;
+&lt;p&gt;　　灵魂裂劈的治疗效果提高25%。&lt;/p&gt;
+&lt;p&gt;　　邪能毁灭的治疗效果提高25%。&lt;/p&gt;
+&lt;p&gt;　　焦油战刃现在会为你恢复相当于所造成火焰伤害5%的生命值（原为4%）。&lt;/p&gt;
+&lt;p&gt;　　脆弱使你恢复相当于对受其影响目标所造成伤害10%的生命值（原为8%）。&lt;/p&gt;
+&lt;p&gt;　　灵魂盛宴的治疗效果提高25%。&lt;/p&gt;
+&lt;p&gt;　　痛苦狂欢会将你所造成火焰伤害的6%转化为护盾（原为5%）。&lt;/p&gt;
+&lt;p&gt;　　更改了多个天赋在天赋树中的位置。&lt;/p&gt;
+&lt;p&gt;　　德鲁伊&lt;/p&gt;
+&lt;p&gt;　　蓬乱毛皮的吸收量提高25%。&lt;/p&gt;
+&lt;p&gt;　　野性之心强化的野性成长治疗效果提高25%。&lt;/p&gt;
+&lt;p&gt;　　撕碎和猎豹形态下横扫的伤害提高10%。&lt;/p&gt;
+&lt;p&gt;　　平衡&lt;/p&gt;
+&lt;p&gt;　　开发者注释：在“乌拉特克的诅咒”中，我们对平衡专精的调整目标是突出获取、消耗和积蓄星界能量这一核心玩法。在“至暗之夜”中，平衡专精获取星界能量的速度很快，而且有大量免费触发的能量消耗技能，因此施放这些技能后，几乎没有剩余的公共冷却时间可供安排其他操作。在“乌拉特克的诅咒”中，我们降低了星界能量的获取速度和免费能量消耗技能的触发次数，但提高了每个能量消耗技能的伤害。我们希望玩家有更多时间应对星界能量的增长，并让玩家在蚀盛之外积蓄星界能量、留到蚀盛期间消耗的策略更具影响力。我们还调整了部分天赋的强度，以增加配装选择的多样性。&lt;/p&gt;
+&lt;p&gt;　　42级习得新的被动技能：星辰护佑——如果月火术和阳炎术被驱散，则会对目标施加星辰耀斑。产生12点星界能量。&lt;/p&gt;
+&lt;p&gt;　　劲烈星影已更新——现在始终使愤怒和星火术的伤害提高12%。&lt;/p&gt;
+&lt;p&gt;　　顶峰天赋：蚀相升格（等级2）——阴燃星能的伤害降低至爆击伤害的10%/20%（原为12%/24%），持续时间延长至8秒（原为6秒）。&lt;/p&gt;
+&lt;p&gt;　　顶峰天赋：蚀相升格——阳炎箭的伤害提高27%，胧月箭的伤害提高10%。&lt;/p&gt;
+&lt;p&gt;　　造成的所有伤害提高8%。&lt;/p&gt;
+&lt;p&gt;　　月火术的伤害提高5%。&lt;/p&gt;
+&lt;p&gt;　　阳炎术的伤害提高5%。&lt;/p&gt;
+&lt;p&gt;　　愤怒的伤害提高10%。&lt;/p&gt;
+&lt;p&gt;　　星火术的伤害提高20%。&lt;/p&gt;
+&lt;p&gt;　　星涌术的伤害提高71%。&lt;/p&gt;
+&lt;p&gt;　　星辰坠落的伤害提高4%。&lt;/p&gt;
+&lt;p&gt;　　坠星的伤害提高10%。&lt;/p&gt;
+&lt;p&gt;　　陨星的伤害提高15%。&lt;/p&gt;
+&lt;p&gt;　　回春术的治疗效果提高25%。&lt;/p&gt;
+&lt;p&gt;　　野性成长的治疗效果提高25%。&lt;/p&gt;
+&lt;p&gt;　　愈合的治疗效果提高25%。&lt;/p&gt;
+&lt;p&gt;　　天界之火使月火术、阳炎术和坠星的伤害提高10%（原为8%）。&lt;/p&gt;
+&lt;p&gt;　　偏轨星月的效果降低至50%（原为60%）。&lt;/p&gt;
+&lt;p&gt;　　浩瀚之触由愤怒触发的几率降低至12%（原为15%），由星火术触发的几率降低至15%（原为20%）。&lt;/p&gt;
+&lt;p&gt;　　全蚀的触发几率提高至15%/30%（原为10%/20%）。&lt;/p&gt;
+&lt;p&gt;　　雕刻星辰和沟通星界在天赋树中的位置互换。&lt;/p&gt;
+&lt;p&gt;　　雕刻星辰使蚀盛的冷却时间缩短3秒（原为2秒）。&lt;/p&gt;
+&lt;p&gt;　　星辰强化现在只能施加给1个目标。&lt;/p&gt;
+&lt;p&gt;　　现在可以在冷却管理器中追踪偏轨星月光环。&lt;/p&gt;
+&lt;p&gt;　　修正了冷却管理器中的部分项目有时无法显示准确信息的问题，例如持续伤害计时器和增益追踪器。&lt;/p&gt;
+&lt;p&gt;　　英雄天赋&lt;/p&gt;
+&lt;p&gt;　　艾露恩钦选者&lt;/p&gt;
+&lt;p&gt;　　开发者注释：艾露恩钦选者应始终以星火术而非愤怒作为主要的能量获取技能。因此，我们恢复了星火术对单个目标的伤害加成，同时小幅降低星涌术的伤害，以削弱其单体伤害。&lt;/p&gt;
+&lt;p&gt;　　使用愤怒获得星界能量时不再触发星辰奔流。&lt;/p&gt;
+&lt;p&gt;　　星辰奔流有30%的几率发射一枚效果为50%的星涌术（原为40%的几率、70%的效果）。&lt;/p&gt;
+&lt;p&gt;　　开发者注释：第2赛季中，平衡专精施放的能量获取技能数量有所增加，导致这项天赋的表现超出预期。&lt;/p&gt;
+&lt;p&gt;　　沐浴月光使星涌术的伤害提高5%（原为10%）。&lt;/p&gt;
+&lt;p&gt;　　丛林守护者&lt;/p&gt;
+&lt;p&gt;　　丰裕之花现在会使自然之力树人的持续时间延长4秒，而不再额外召唤第4个树人。&lt;/p&gt;
+&lt;p&gt;　　塞纳留斯之力提供的急速降低至6%（原为8%）。&lt;/p&gt;
+&lt;p&gt;　　持久魔效提供的急速降低至6%（原为10%）。&lt;/p&gt;
+&lt;p&gt;　　森野感召树妖施放的星辰坠落伤害提高至250%效果（原为200%）。&lt;/p&gt;
+&lt;p&gt;　　林地仙灵使星辰坠落的伤害提高18%（原为12%）。&lt;/p&gt;
+&lt;p&gt;　　梦境爆发的伤害提高30%。&lt;/p&gt;
+&lt;p&gt;　　自然之威使树人的近战伤害提高300%（原为200%）。&lt;/p&gt;
+&lt;p&gt;　　野性&lt;/p&gt;
+&lt;p&gt;　　开发者注释：“乌拉特克的诅咒”中的野性专精调整旨在提高天赋选择的多样性。我们希望噬咬能在喜爱这项天赋的玩家手中发挥更强的效果，同时也会调整其他部分天赋，使其强度更为接近，并开放更多配装选择。此外，由于天赋选择受限，野性专精在团队副本中的范围和顺劈伤害难以与其他专精竞争。野性专精的大部分范围伤害来自野性难驯，但团队副本配装通常不会选择这项天赋。为了让团队副本配装更容易选择野性难驯，我们会将它与第1层的无情爪击互换位置。这会使部分配装更难选择无情爪击，因此我们会提高部分伤害，以补偿这项改动以及“乌拉特克的诅咒”中其他天赋强度的下调。&lt;/p&gt;
+&lt;p&gt;　　造成的所有伤害提高3%。&lt;/p&gt;
+&lt;p&gt;　　野性难驯的伤害提高25%。&lt;/p&gt;
+&lt;p&gt;　　剑齿利喉每点提供的伤害加成提高至60%（原为50%）。&lt;/p&gt;
+&lt;p&gt;　　专注狂乱的伤害加成降低至15%（原为20%）。&lt;/p&gt;
+&lt;p&gt;　　撕裂切割的伤害加成提高至20%（原为15%）。&lt;/p&gt;
+&lt;p&gt;　　噬咬的伤害提高30%。&lt;/p&gt;
+&lt;p&gt;　　顶级捕食者的渴望的基础触发几率降低至4%（原为5%）。&lt;/p&gt;
+&lt;p&gt;　　无情爪击使撕碎和横扫的伤害提高25%（原为20%）。&lt;/p&gt;
+&lt;p&gt;　　鲜血飞溅使凶猛撕咬的伤害提高8%（原为2%），但最多叠加6层（原为10层）。&lt;/p&gt;
+&lt;p&gt;　　血腥气息使凶猛撕咬的伤害提高16%（原为12%），猛虎之怒期间再提高8%（原为12%）。&lt;/p&gt;
+&lt;p&gt;　　回春术的治疗效果提高25%。&lt;/p&gt;
+&lt;p&gt;　　野性成长的治疗效果提高25%。&lt;/p&gt;
+&lt;p&gt;　　愈合的治疗效果提高25%。&lt;/p&gt;
+&lt;p&gt;　　冷却管理器已更新：斜掠和割裂等持续伤害效果被猛虎之怒强化后，对应项目会显示“已强化”版本的图标。&lt;/p&gt;
+&lt;p&gt;　　无情爪击和野性难驯在天赋树中的位置互换。&lt;/p&gt;
+&lt;p&gt;　　守护&lt;/p&gt;
+&lt;p&gt;　　开发者注释：这次守护德鲁伊更新主要旨在解决专精伤害构成和技能占比方面的问题。具体而言，我们将重做朔望，消除它对技能循环造成的不利压力；对血污毛皮和荒野守护者的调整则旨在让不同怒气消耗技能之间更加均衡，并将顶峰天赋的影响分摊到更长的持续时间和更多技能上。&lt;/p&gt;
+&lt;p&gt;　　血污毛皮已重新设计——铁鬃有一定几率使你的下一次重殴、摧折或毁灭不消耗怒气。重殴、摧折或毁灭有一定几率使你的下一次铁鬃不消耗怒气。&lt;/p&gt;
+&lt;p&gt;　　顶峰天赋：荒野守护者已重新设计——&lt;/p&gt;
+&lt;p&gt;　　等级1：消耗怒气有10%的几率唤醒一个守护之魂，持续8秒。施放痛击或裂伤时，守护之魂会攻击附近的一名敌人。&lt;/p&gt;
+&lt;p&gt;　　等级2：裂伤、毁灭、摧折和重殴会在12秒内额外造成20%/40%的自然伤害。你的精通提高3%/6%。&lt;/p&gt;
+&lt;p&gt;　　等级3：唤醒守护之魂时，痛击和裂伤的冷却时间会重置，并且在灵魂伴随你期间，这两个技能造成的伤害提高30%。守护之魂每次攻击都会使你额外产生8点怒气。施放狂暴或化身：乌索克的守护者后，获得1层荒野守护者：&lt;/p&gt;
+&lt;p&gt;　　荒野守护者：你下一次施放毁灭、摧折或重殴时必定唤醒一个守护之魂。&lt;/p&gt;
+&lt;p&gt;　　所有伤害提高8%。&lt;/p&gt;
+&lt;p&gt;　　刺藤的吸收量提高25%。&lt;/p&gt;
+&lt;p&gt;　　野火烧不尽的治疗效果提高25%。&lt;/p&gt;
+&lt;p&gt;　　明月普照的治疗效果提高25%。&lt;/p&gt;
+&lt;p&gt;　　朔望使明月普照的冷却时间缩短20秒（原为每个奥术技能缩短3秒）。&lt;/p&gt;
+&lt;p&gt;　　乌索克之怒提供的吸收效果提高至痛击和重殴伤害的35%（原为30%）。&lt;/p&gt;
+&lt;p&gt;　　艾露恩的青睐会为你恢复相当于所造成奥术伤害18%的生命值（原为15%）。&lt;/p&gt;
+&lt;p&gt;　　修正了重焕活力所施放的愈合会错误消耗梦境向导的问题。&lt;/p&gt;
+&lt;p&gt;　　英雄天赋&lt;/p&gt;
+&lt;p&gt;　　艾露恩钦选者&lt;/p&gt;
+&lt;p&gt;　　天涯共银辉——明月普照现在会使你从对受影响敌人所造成的伤害中获得12%吸血（原为10%）。&lt;/p&gt;
+&lt;p&gt;　　恢复&lt;/p&gt;
+&lt;p&gt;　　开发者注释：本次更新将对恢复德鲁伊进行多项便利性调整，旨在解决宁静、自然迅捷和化身：生命之树的易用性问题。我们还会调整迅捷治愈，使其重新具备强力单体治疗技能应有的效果。最后，我们希望通过重新设计丰饶，为其设定一个明确的阈值，让玩家清楚应在何时使用愈合，从而解决这项天赋目前存在的问题。&lt;/p&gt;
+&lt;p&gt;　　新天赋：过度生长——自然迅捷会使你的下一次愈合同时对一名盟友施加生命绽放、回春术和野性成长的持续治疗效果。&lt;/p&gt;
+&lt;p&gt;　　新天赋：明晰闪愈——清晰预兆使愈合的治疗效果提高40%。现在会出现在天赋树中栽培原先所在的位置。&lt;/p&gt;
+&lt;p&gt;　　栽培现在位于天赋树中明晰闪愈的下方。&lt;/p&gt;
+&lt;p&gt;　　激活已重新设计——现在会在8秒内为目标恢复其法力值上限25%的法力值，不再使法术在8秒内不消耗法力值。&lt;/p&gt;
+&lt;p&gt;　　丰饶已重新设计——当你同时维持至少5个回春术时，愈合的爆击几率提高50%，法力值消耗降低50%。&lt;/p&gt;
+&lt;p&gt;　　宁静已更新——现在会在你的脚下生长出保护性根须，吸收相当于你生命值60%的伤害，并使你免疫击退效果。&lt;/p&gt;
+&lt;p&gt;　　化身：生命之树已更新——初次变形时，会对附近最多3名受伤的盟友施放愈合。&lt;/p&gt;
+&lt;p&gt;　　迅捷治愈已更新——治疗量额外提高所消耗持续治疗效果的40%。&lt;/p&gt;
+&lt;p&gt;　　永茂（等级3）已更新——现在按下迅捷治愈时会触发其治疗效果（原为丛林之魂）。&lt;/p&gt;
+&lt;p&gt;　　翡翠灌注已更新——不再延长持续治疗效果。&lt;/p&gt;
+&lt;p&gt;　　萌芽已更新——不再使回春术的持续时间延长2秒。&lt;/p&gt;
+&lt;p&gt;　　伊瑟拉之赐已更新——如果其治疗会对德鲁伊产生过量治疗，则会将过量治疗量转移给附近的一名盟友。&lt;/p&gt;
+&lt;p&gt;　　精通：相生的治疗加成提高15%。&lt;/p&gt;
+&lt;p&gt;　　所有法术和技能的治疗效果提高6%。&lt;/p&gt;
+&lt;p&gt;　　野性成长的治疗效果提高20%，法力值消耗提高15%。&lt;/p&gt;
+&lt;p&gt;　　新绿的治疗效果提高40%。&lt;/p&gt;
+&lt;p&gt;　　回春术的法力值消耗降低10%。&lt;/p&gt;
+&lt;p&gt;　　愈合的治疗效果降低20%，法力值消耗降低10%。&lt;/p&gt;
+&lt;p&gt;　　生命绽放的法力值消耗降低20%。&lt;/p&gt;
+&lt;p&gt;　　季节变迁使自然迅捷的冷却时间缩短15秒（原为12秒）。&lt;/p&gt;
+&lt;p&gt;　　共生关系未激活时，现在会在动作条上高亮显示。&lt;/p&gt;
+&lt;p&gt;　　萌芽和新绿在天赋树中的位置互换。&lt;/p&gt;
+&lt;p&gt;　　自然的壮美已被移除。&lt;/p&gt;
+&lt;p&gt;　　唤魔师&lt;/p&gt;
+&lt;p&gt;　　万应灵药的治疗效果提高25%。&lt;/p&gt;
+&lt;p&gt;　　英雄天赋&lt;/p&gt;
+&lt;p&gt;　　鳞长&lt;/p&gt;
+&lt;p&gt;　　开发者注释：群龙之首的冷却缩减机制会强烈鼓励玩家将狂轰滥炸分散施加给多个目标。我们认为，单独来看这种玩法不够直观，还会引发一些不健康的操作方式，例如提前中断裂解，以及刻意积蓄群体裂解或喷发。这次重新设计旨在保留天赋对多目标战斗的侧重，同时解决上述问题。作为补偿，我们会提高鳞长部分范围伤害来源的伤害，以弥补新版群龙之首冷却缩减效果的降低。&lt;/p&gt;
+&lt;p&gt;　　群龙之首已重新设计——群体裂解/大规模喷发每命中一个目标，就会使深呼吸/亘古吐息的剩余冷却时间缩短0.5秒/1秒。&lt;/p&gt;
+&lt;p&gt;　　特遣动员的葬火伤害提高40%。&lt;/p&gt;
+&lt;p&gt;　　战术机动的持续伤害提高40%。&lt;/p&gt;
+&lt;p&gt;　　增辉&lt;/p&gt;
+&lt;p&gt;　　开发者注释：复制体施放地壳激变所产生的额外控制能力对地下城玩法的影响超出预期，而且由于触发时机无法控制，在某些情况下也会令人感到困扰。&lt;/p&gt;
+&lt;p&gt;　　顶峰天赋：复制——复制体施放的地壳激变不再将敌人击飞。&lt;/p&gt;
+&lt;p&gt;　　所有技能和宠物的伤害提高3%。&lt;/p&gt;
+&lt;p&gt;　　活化烈焰的治疗效果提高25%。&lt;/p&gt;
+&lt;p&gt;　　青翠之拥的治疗效果提高25%。&lt;/p&gt;
+&lt;p&gt;　　翡翠之花的治疗效果提高25%。&lt;/p&gt;
+&lt;p&gt;　　驳斥命运的治疗效果提高25%。&lt;/p&gt;
+&lt;p&gt;　　熔火血脉的治疗效果提高25%。&lt;/p&gt;
+&lt;p&gt;　　“至暗之夜”第1赛季的2件套装加成不再延长喷发对黑檀之力的持续时间。&lt;/p&gt;
+&lt;p&gt;　　英雄天赋&lt;/p&gt;
+&lt;p&gt;　　时空守卫&lt;/p&gt;
+&lt;p&gt;　　双倍速已更新——黑檀之力造成爆击时提供的额外属性现在持续15秒（受精通：时光旅行者影响）；如果黑檀之力在双倍速已激活时重新施加该效果，则会延长双倍速的持续时间。双倍速与先知先觉的互动方式保持不变。&lt;/p&gt;
+&lt;p&gt;　　鳞长&lt;/p&gt;
+&lt;p&gt;　　群龙之首现在会使亘古吐息的冷却时间每命中一个目标缩短1.5秒（原为1秒）。&lt;/p&gt;
+&lt;p&gt;　　湮灭&lt;/p&gt;
+&lt;p&gt;　　开发者注释：湮灭专精的顶峰天赋虽然十分强大，但对玩法的影响并未达到我们的预期。我们重新设计了等级3的效果：狂龙之怒结束后，它会被一种有使用次数限制的强力新法术释缚烈焰取代。此外，冲天怒火和渐怒已被整合为同一个增益效果。&lt;/p&gt;
+&lt;p&gt;　　顶峰天赋：冲天怒火（等级3）已重新设计——狂龙之怒结束时，冲天怒火的每层效果会继续持续4秒，并使狂龙之怒变为释缚烈焰。在狂龙之怒完成冷却前，可以施放4次释缚烈焰。&lt;/p&gt;
+&lt;p&gt;　　释缚烈焰——吐出毁灭烈焰，对目标及其附近的敌人造成必定爆击的火焰伤害。超过5个目标后伤害降低。触发1次精华迸发。瞬发，射程25码。&lt;/p&gt;
+&lt;p&gt;　　残暴已更新——现在会与释缚烈焰互动。无论目标的生命值如何，释缚烈焰始终会获得精通：巨人杀手的最高加成。&lt;/p&gt;
+&lt;p&gt;　　深呼吸的伤害提高30%。&lt;/p&gt;
+&lt;p&gt;　　葬火的伤害提高10%。&lt;/p&gt;
+&lt;p&gt;　　裂解造成的伤害提高40%。&lt;/p&gt;
+&lt;p&gt;　　活化烈焰的伤害提高50%，治疗效果提高25%。&lt;/p&gt;
+&lt;p&gt;　　青翠之拥的治疗效果提高25%。&lt;/p&gt;
+&lt;p&gt;　　翡翠之花的治疗效果提高25%。&lt;/p&gt;
+&lt;p&gt;　　碎裂星辰经由能量闪烁从永恒之涌中释放时，现在也会受到能量闪烁40%的效果倍率影响。&lt;/p&gt;
+&lt;p&gt;　　渐怒已被移除。&lt;/p&gt;
+&lt;p&gt;　　英雄天赋&lt;/p&gt;
+&lt;p&gt;　　塑焰者&lt;/p&gt;
+&lt;p&gt;　　孪生烈焰的伤害和治疗效果降低20%。&lt;/p&gt;
+&lt;p&gt;　　修正了孪生烈焰无法从精通中获得收益的问题。&lt;/p&gt;
+&lt;p&gt;　　鳞长&lt;/p&gt;
+&lt;p&gt;　　群龙之首现在会使深呼吸的冷却时间每命中一个目标缩短1秒（原为0.5秒）。&lt;/p&gt;
+&lt;p&gt;　　恩护&lt;/p&gt;
+&lt;p&gt;　　开发者注释：这项改动旨在让梦境吐息成为灵活的治疗法术，既能再次充当强力的持续治疗效果，也能在蓄力后提供爆发治疗。这还能进一步凸显它与青翠之拥、麦琳瑟拉的祝福等法术的区别，后两者同样可以随时提供爆发治疗。此外，我们将大幅提高吞噬烈焰的重要性和影响力，使其符合塑焰者终极天赋应有的地位。&lt;/p&gt;
+&lt;p&gt;　　顶峰天赋：麦琳瑟拉的祝福已更新——现在使梦境吐息的所有治疗效果提高60%（原为250%，且仅影响其即时治疗）。&lt;/p&gt;
+&lt;p&gt;　　魔法之泉已更新——现在还会使梦境吐息和火焰吐息的蓄力时间缩短20%。&lt;/p&gt;
+&lt;p&gt;　　梦境吐息的即时治疗效果降低50%。&lt;/p&gt;
+&lt;p&gt;　　梦境吐息的周期性治疗效果提高118%。&lt;/p&gt;
+&lt;p&gt;　　时光屏障的吸收量提高30%。&lt;/p&gt;
+&lt;p&gt;　　心灵之火使周期性治疗效果提高50%（原为60%）。&lt;/p&gt;
+&lt;p&gt;　　精神澄澈使梦境吐息的冷却时间缩短6秒（原为10秒）。&lt;/p&gt;
+&lt;p&gt;　　泰坦之赐现在也会提高婆娑幼苗的治疗效果。&lt;/p&gt;
+&lt;p&gt;　　修正了时间膨胀有时不会在死亡时清除已储存伤害的问题。&lt;/p&gt;
+&lt;p&gt;　　修正了吞噬烈焰的治疗效果不会被恩惠时刻或类似效果提高的问题。&lt;/p&gt;
+&lt;p&gt;　　英雄天赋&lt;/p&gt;
+&lt;p&gt;　　塑焰者&lt;/p&gt;
+&lt;p&gt;　　肺活猛增使梦境吐息的治疗效果提高20%（原为30%）。&lt;/p&gt;
+&lt;p&gt;　　烈焰导体使爆击几率提高10%（原为15%）。该效果不影响湮灭唤魔师。&lt;/p&gt;
+&lt;p&gt;　　迅雷咆哮使火焰吐息和梦境吐息造成伤害的频率加快15%（原为20%）。该效果不影响湮灭唤魔师。&lt;/p&gt;
+&lt;p&gt;　　婆娑幼苗现在可以触发吞噬烈焰。&lt;/p&gt;
+&lt;p&gt;　　选择吞噬烈焰天赋后，翡翠之花和婆娑幼苗现在会优先治疗身上带有梦境吐息效果的受伤盟友。&lt;/p&gt;
+&lt;p&gt;　　吞噬烈焰的治疗量提高至所消耗效果的240%（原为200%）。&lt;/p&gt;
+&lt;p&gt;　　修正了吞噬烈焰的治疗部分无法爆击的问题。&lt;/p&gt;
+&lt;p&gt;　　孪生烈焰的伤害和治疗效果降低20%。&lt;/p&gt;
+&lt;p&gt;　　修正了孪生烈焰无法从精通中获得收益的问题。&lt;/p&gt;
+&lt;p&gt;　　猎人&lt;/p&gt;
+&lt;p&gt;　　英雄天赋&lt;/p&gt;
+&lt;p&gt;　　黑暗游侠&lt;/p&gt;
+&lt;p&gt;　　黯然箭矢的伤害提高300%。&lt;/p&gt;
+&lt;p&gt;　　凋零射击的黑蚀箭伤害降低40%。&lt;/p&gt;
+&lt;p&gt;　　修正了千里猎目未能正确提高凋零射击伤害的问题。&lt;/p&gt;
+&lt;p&gt;　　野兽控制&lt;/p&gt;
+&lt;p&gt;　　开发者注释：野兽控制猎人在狂野怒火的伤害窗口之外表现稍显疲弱，因此我们会提高杀戮命令、眼镜蛇射击和倒刺射击的伤害，以增强其常态伤害。我们会将野兽顺劈的持续时间延长至10秒。只要在狂野鞭笞可用时及时使用，就能在范围伤害场合保持100%的覆盖率。&lt;/p&gt;
+&lt;p&gt;　　族群之心更名为锋锐射击并经过重新设计——使宠物的撕咬、爪击和拍击伤害提高100%。&lt;/p&gt;
+&lt;p&gt;　　刺骨之牙已重新设计——杀戮命令的爆击伤害提高15%。&lt;/p&gt;
+&lt;p&gt;　　血腥狂乱已更新——现在使倒刺射击周期性效果的频率加快33%（原为50%）。&lt;/p&gt;
+&lt;p&gt;　　杀戮顺劈已更新——野兽顺劈期间，杀戮命令现在只会顺劈造成其伤害的20%（原为40%）。&lt;/p&gt;
+&lt;p&gt;　　自动射击的伤害提高720%。&lt;/p&gt;
+&lt;p&gt;　　倒刺射击的伤害提高10%。&lt;/p&gt;
+&lt;p&gt;　　杀戮命令的伤害提高20%。&lt;/p&gt;
+&lt;p&gt;　　眼镜蛇射击的伤害提高25%。&lt;/p&gt;
+&lt;p&gt;　　野兽顺劈现在使宠物攻击附近的敌人，造成相当于所造成伤害55%的伤害（原为40%）。&lt;/p&gt;
+&lt;p&gt;　　野兽顺劈的持续时间延长至10秒（原为8秒），并且无法再被取消。&lt;/p&gt;
+&lt;p&gt;　　毒蛇打击现在使眼镜蛇射击的爆击伤害提高20%（原为50%）。&lt;/p&gt;
+&lt;p&gt;　　眼镜蛇感官现在使眼镜蛇射击的伤害提高10%（原为35%）。&lt;/p&gt;
+&lt;p&gt;　　凶暴野兽现在可以在冷却管理器上追踪。&lt;/p&gt;
+&lt;p&gt;　　狂野本能已被移除。&lt;/p&gt;
+&lt;p&gt;　　英雄天赋&lt;/p&gt;
+&lt;p&gt;　　黑暗游侠&lt;/p&gt;
+&lt;p&gt;　　黑暗猎犬现在可以在冷却管理器上追踪。&lt;/p&gt;
+&lt;p&gt;　　猎群领袖&lt;/p&gt;
+&lt;p&gt;　　猪突猛进现在使你的下一次眼镜蛇射击伤害提高100%（原为200%）。&lt;/p&gt;
+&lt;p&gt;　　铁蹄利刃现在使猪突猛进对眼镜蛇射击的伤害加成提高25%（原为50%）。&lt;/p&gt;
+&lt;p&gt;　　射击&lt;/p&gt;
+&lt;p&gt;　　开发者注释：射击猎人上一轮改动重新加入了可由玩家主动选择的爆炸射击，但它与专精现有玩法的衔接并不顺畅。在“至暗之夜”第2赛季中，我们会调整爆炸射击本身及其部分配套天赋的设计。一枪爆头天赋也一直令人感到困扰，因此我们会将其移除，并调整夺命打击的运作方式，让玩家更容易判断何时应在施放瞄准射击后接续夺命射击或黑蚀箭。最后，我们会调整射击专精的顶峰天赋节点，使瞄准射击不再必定爆击，降低玩法对瞄准射击增效效果的依赖。&lt;/p&gt;
+&lt;p&gt;　　新天赋：险变扳机——在3秒内再次使用爆炸射击，可以连续施放第二次。爆炸射击会纳入目标身上此前爆炸射击尚未造成的剩余伤害。&lt;/p&gt;
+&lt;p&gt;　　爆炸射击已重新设计——向目标射出一枚爆炸弹。目标会每1秒爆炸一次，持续3秒，对8码内的所有敌人造成火焰伤害。超过5个目标后伤害降低。再次施放爆炸射击时，会纳入目标身上此前爆炸射击尚未造成的剩余伤害。&lt;/p&gt;
+&lt;p&gt;　　开发者注释：我们大幅调整了爆炸射击的设计方向，希望为它塑造更鲜明的特色。爆炸射击本身及其相关天赋的改动，应该会让它与其他主要技能相比拥有截然不同的操作体验。&lt;/p&gt;
+&lt;p&gt;　　爆炸射击的视觉效果已更新。&lt;/p&gt;
+&lt;p&gt;　　爆炸射击的说明文字已更新；选择险变扳机天赋后，现在还会显示相应的情境说明。&lt;/p&gt;
+&lt;p&gt;　　精确引爆已重新设计——爆炸射击的持续时间延长1秒。&lt;/p&gt;
+&lt;p&gt;　　弹片射击更名为火力覆盖并经过重新设计——子弹风暴现在会影响你的下一次瞄准射击。&lt;/p&gt;
+&lt;p&gt;　　风行者箭袋已重新设计——急速射击的伤害提高10%。急速射击有30%的几率获得荷枪实弹效果。&lt;/p&gt;
+&lt;p&gt;　　顶峰天赋：凝神瞄准（等级2）已重新设计——你的爆击伤害提高5%/10%。你的远程技能造成的伤害提高3%/6%。&lt;/p&gt;
+&lt;p&gt;　　顶峰天赋：凝神瞄准（等级3）已更新——瞭望印记现在会使你下一次瞄准射击和急速射击对目标造成的伤害提高（原本仅影响瞄准射击）。&lt;/p&gt;
+&lt;p&gt;　　开发者注释：旧版射击专精顶峰天赋过于侧重瞄准射击及其爆击伤害增效效果。新版本应该能与专精中的更多技能形成更好的互动。&lt;/p&gt;
+&lt;p&gt;　　子弹风暴已重新设计——急速射击现在使你的下一次瞄准射击伤害提高20%。&lt;/p&gt;
+&lt;p&gt;　　夺命打击已更新——瞄准射击现在有一定几率使你的下一次瞄准射击获得夺命打击效果。&lt;/p&gt;
+&lt;p&gt;　　开发者注释：我们调整射击猎人的夺命打击，是希望明确告诉玩家何时应在瞄准射击后接续夺命射击或黑蚀箭，避免面对多个技能时无从判断。急速射击仍有100%的几率获得夺命打击效果，因此急速射击后始终可以接续夺命射击或黑蚀箭。&lt;/p&gt;
+&lt;p&gt;　　多头蛇守护已更新——奥术射击不再顺劈。&lt;/p&gt;
+&lt;p&gt;　　你的技能造成的所有伤害提高5%。&lt;/p&gt;
+&lt;p&gt;　　自动射击的伤害提高756%。&lt;/p&gt;
+&lt;p&gt;　　瞄准射击的伤害提高20%。&lt;/p&gt;
+&lt;p&gt;　　急速射击的伤害提高44%。&lt;/p&gt;
+&lt;p&gt;　　奥术射击伤害提高38%。&lt;/p&gt;
+&lt;p&gt;　　稳固射击的伤害提高50%。&lt;/p&gt;
+&lt;p&gt;　　多重射击伤害提高73%。&lt;/p&gt;
+&lt;p&gt;　　乱射的伤害提高20%。&lt;/p&gt;
+&lt;p&gt;　　夺命射击伤害提高50%。&lt;/p&gt;
+&lt;p&gt;　　鹰眼精准现在为1级天赋，使瞄准射击的伤害提高5%（原为10%），并使急速射击的伤害提高10%（原为20%）。&lt;/p&gt;
+&lt;p&gt;　　专注瞄准现在使瞄准射击的冷却时间缩短1秒（原为2秒）。&lt;/p&gt;
+&lt;p&gt;　　肋排猎人现在为2级天赋。数值保持不变。&lt;/p&gt;
+&lt;p&gt;　　瞄准射击有了新图标。&lt;/p&gt;
+&lt;p&gt;　　更改了多个天赋在天赋树中的位置。&lt;/p&gt;
+&lt;p&gt;　　以下天赋已被移除：&lt;/p&gt;
+&lt;p&gt;　　二连发&lt;/p&gt;
+&lt;p&gt;　　一枪爆头&lt;/p&gt;
+&lt;p&gt;　　英雄天赋&lt;/p&gt;
+&lt;p&gt;　　黑暗游侠&lt;/p&gt;
+&lt;p&gt;　　千里猎目已重新设计——使夺命射击和黑蚀箭的伤害提高10%。&lt;/p&gt;
+&lt;p&gt;　　黑蚀箭的伤害提高25%。&lt;/p&gt;
+&lt;p&gt;　　黑蚀箭的直接伤害降低40%。&lt;/p&gt;
+&lt;p&gt;　　黑蚀箭可对目标使用时，不再自动高亮显示。&lt;/p&gt;
+&lt;p&gt;　　乌黑弓弦现在使黑蚀箭有一定几率令你的下一次瞄准射击获得夺命打击效果。&lt;/p&gt;
+&lt;p&gt;　　黑暗爪牙现在可以在冷却管理器上追踪。&lt;/p&gt;
+&lt;p&gt;　　哨兵&lt;/p&gt;
+&lt;p&gt;　　月神之赐现在只会使瞄准射击的冷却时间缩短1秒（原为2秒）。&lt;/p&gt;
+&lt;p&gt;　　生存&lt;/p&gt;
+&lt;p&gt;　　新天赋：锋刃旋击——猛禽一击、猛禽横扫和杀戮命令的爆击几率提高10%，造成的爆击伤害提高10%。&lt;/p&gt;
+&lt;p&gt;　　新天赋：投弹手——野火炸弹的伤害、爆击几率和爆击伤害提高15%。&lt;/p&gt;
+&lt;p&gt;　　野火灌注已重新设计——投掷野火炸弹有一定几率为你的武器灌注烈焰，使你和宠物的自动攻击额外造成火焰伤害，持续10秒。&lt;/p&gt;
+&lt;p&gt;　　榴弹杂耍已重新设计——爆裂火铳使野火炸弹的冷却恢复速度提高60%，持续8秒。&lt;/p&gt;
+&lt;p&gt;　　榴弹杂耍现在可以在冷却管理器上追踪。&lt;/p&gt;
+&lt;p&gt;　　突刺现在使你的敏捷提高3%（原为2%）；双持武器时再额外提高1%（原为2%）。&lt;/p&gt;
+&lt;p&gt;　　野火弹药现在使野火炸弹的冷却时间缩短3秒（原为2秒）。&lt;/p&gt;
+&lt;p&gt;　　原初涌动在天赋树中的位置上移，现在更容易选到。&lt;/p&gt;
+&lt;p&gt;　　修正了猛禽横扫可能会对当前未选中的目标施加哨兵印记的问题。使用猛禽横扫时如果未选中目标，会从被猛禽横扫命中的目标中选择一个。&lt;/p&gt;
+&lt;p&gt;　　修正了猎人、当前宠物或族群领袖英雄天赋的其他召唤物所造成的多种周期性效果无法正确施加外域之毒的问题。&lt;/p&gt;
+&lt;p&gt;　　修正了精通：灵魂联结会错误地对族群领袖英雄天赋的部分召唤物生效两次的问题。&lt;/p&gt;
+&lt;p&gt;　　以下天赋已被移除：&lt;/p&gt;
+&lt;p&gt;　　燎焰沥青&lt;/p&gt;
+&lt;p&gt;　　浴血围猎&lt;/p&gt;
+&lt;p&gt;　　英雄天赋&lt;/p&gt;
+&lt;p&gt;　　猎群领袖&lt;/p&gt;
+&lt;p&gt;　　猪突猛进现在持续1分钟（原为20秒）。&lt;/p&gt;
+&lt;p&gt;　　开始团队副本首领战或史诗钥石地下城时，猪突猛进现在会被取消。&lt;/p&gt;
+&lt;p&gt;　　哨兵&lt;/p&gt;
+&lt;p&gt;　　破空枪鸣已重新设计——造成的火焰伤害提高5%。&lt;/p&gt;
+&lt;p&gt;　　致命倒钩已更新——自动攻击现在有极高几率产生3点集中值，不再是每次自动攻击产生1点集中值。&lt;/p&gt;
+&lt;p&gt;　　开发者注释：旧版致命倒钩天赋偏向于双持攻击速度最快的武器。我们将其改为有极高几率产生3点集中值，使集中值获取更加稳定，也让玩家可以使用自己偏好的武器类型。&lt;/p&gt;
+&lt;p&gt;　　使用伪装时，斥候警戒不再提高侦测潜行的范围。&lt;/p&gt;
+&lt;p&gt;　　月神之赐现在会在施加哨兵印记时使野火炸弹的冷却时间缩短6秒（原为4秒）。&lt;/p&gt;
+&lt;p&gt;　　哨兵印记的持续时间延长至16秒（原为12秒）。&lt;/p&gt;
+&lt;p&gt;　　法师&lt;/p&gt;
+&lt;p&gt;　　开发者注释：我们调整了法师的防御能力，旨在整体提高法师的生存能力。为实现这一目标，我们会统一强化屏障的功能，让所有专精的屏障法术都额外获得一次使用次数，同时各自附带一项专精特有的额外效果。&lt;/p&gt;
+&lt;p&gt;　　新天赋：强化结界——受到的范围攻击伤害降低4%。&lt;/p&gt;
+&lt;p&gt;　　强化棱光护体已重新设计——棱光护体额外获得一层充能，并使受到的魔法伤害进一步降低5%。&lt;/p&gt;
+&lt;p&gt;　　强化烈焰护体已重新设计——烈焰护体额外获得一层充能，并会烧灼你的伤口，为你恢复相当于其吸收伤害15%的生命值。&lt;/p&gt;
+&lt;p&gt;　　强化寒冰护体已重新设计——寒冰护体额外获得一层充能，并使你受到的物理伤害降低10%。&lt;/p&gt;
+&lt;p&gt;　　时光重组已更新——现在会立即恢复你20%的生命值，并在6秒内再恢复30%的生命值。&lt;/p&gt;
+&lt;p&gt;　　英雄天赋&lt;/p&gt;
+&lt;p&gt;　　疾咒师&lt;/p&gt;
+&lt;p&gt;　　调整了法术冰霜之训的说明文字，使其更加清晰。功能保持不变。&lt;/p&gt;
+&lt;p&gt;　　日怒&lt;/p&gt;
+&lt;p&gt;　　开发者注释：我们将重新设计辉圆火咒，使其侧重于强化现有的3颗法球，而不再提供5颗法球，这样更符合日怒的设计灵感，也能减少角色周围的视觉干扰。我们还会移除法力涌流的层数上限，使其与其他“多次施加可以重叠生效”的机制保持一致。&lt;/p&gt;
+&lt;p&gt;　　辉圆火咒已重新设计——产生法术火焰宝珠的几率提高6%/12%。法术火焰宝珠额外提供1%法术伤害。&lt;/p&gt;
+&lt;p&gt;　　灵感灰烬已重新设计——每次你的凤凰施放法术时，获得1层法力涌流。特殊法术额外提供1层。&lt;/p&gt;
+&lt;p&gt;　　奥之回忆已更新——燃烧和奥术涌动不再使法师获得双倍的法力涌流层数。&lt;/p&gt;
+&lt;p&gt;　　奥术法师产生法术火焰宝珠的几率降低至6%，火焰法师降低至12%（原为12%和25%）。&lt;/p&gt;
+&lt;p&gt;　　法力涌流不再有层数上限。&lt;/p&gt;
+&lt;p&gt;　　法师施放奥术脉冲或棱彩飞弹时，现在也会获得法力涌流。&lt;/p&gt;
+&lt;p&gt;　　修正了奥术专精会通过部分非预期法术获得法力涌流的问题。&lt;/p&gt;
+&lt;p&gt;　　奥术&lt;/p&gt;
+&lt;p&gt;　　开发者注释：我们很喜欢疾咒师法师不断掷出法球的玩法，也希望保留两个英雄专精在操作感受上的鲜明差异。然而，法球精通的重要性超过节能施法，甚至将奥术飞弹挤出技能循环，这会对整体天赋选择和游戏乐趣产生负面影响。这些改动旨在让奥术宝珠继续成为疾咒师玩法中的强力高光技能，同时让奥术飞弹仍是奥术法师职业特色中不可或缺的一环。此外，新的防御天赋折射镜像会为奥术法师提供独特的生存能力，与冰霜专精的极速冰冻/冰川壁垒以及火焰专精的灸灼相呼应。&lt;/p&gt;
+&lt;p&gt;　　我们还会重新设计奥术法师的顶峰天赋，使其带来更震撼的视觉时刻，并对天赋配装和技能循环产生更大影响。奥术脉冲也经过重新设计，进一步突出它作为强力范围伤害技能的定位，并让玩家能在范围战斗中迅速恢复奥术充能。&lt;/p&gt;
+&lt;p&gt;　　新顶峰天赋：棱彩飞弹&lt;/p&gt;
+&lt;p&gt;　　等级1：奥术弹幕每消耗一层奥术齐射，就有1%的几率触发棱彩飞弹。棱彩飞弹以压倒性的能量摧垮目标，对目标造成奥术伤害，并对附近的敌人造成较低的奥术伤害。超过5个目标后伤害降低。产生4层奥术充能。不受奥术冲击天赋或效果影响，其伤害和法力值消耗也不会随奥术充能层数提高。&lt;/p&gt;
+&lt;p&gt;　　等级2：棱彩飞弹有50%/100%的几率提供节能施法。奥术飞弹的伤害提高15%/30%。&lt;/p&gt;
+&lt;p&gt;　　等级3：奥术齐射额外提供1%的几率触发棱彩飞弹。奥术弹幕的伤害提高15%。&lt;/p&gt;
+&lt;p&gt;　　新天赋：折射镜像——你承受的伤害的10%改为在8秒内造成。施放镜像会使这一效果提高至30%，持续15秒。&lt;/p&gt;
+&lt;p&gt;　　奥术脉冲已重新设计——施法时间缩短至2秒（原为2.25秒）。范围扩大至8码（原为2码）。现在有15秒冷却时间，每命中一个敌人产生1层奥术充能，并消耗10%的基础法力值。施法时间、范围、法力值消耗和施法速度不再受奥术充能影响。&lt;/p&gt;
+&lt;p&gt;　　法球精通已重新设计——施放奥术宝珠时，会额外发射2颗效果为50%的法球。&lt;/p&gt;
+&lt;p&gt;　　心智洞开已更新——施放奥术宝珠会提供1层奥术齐射（原为2层）。施放棱彩飞弹现在会提供4层奥术齐射。&lt;/p&gt;
+&lt;p&gt;　　奥术冲击的伤害提高20%。&lt;/p&gt;
+&lt;p&gt;　　奥能动力不再影响奥术脉冲。&lt;/p&gt;
+&lt;p&gt;　　超凡专家不再影响奥术脉冲。&lt;/p&gt;
+&lt;p&gt;　　增效在天赋树中的位置移至气定神闲/气流下方。&lt;/p&gt;
+&lt;p&gt;　　强化节能施法在天赋树中的位置移至奥术脉冲上方，也就是增效原先所在的位置。&lt;/p&gt;
+&lt;p&gt;　　修正了说明文字在选择不同天赋时错误计算节能施法触发几率的问题。节能施法的功能保持不变。&lt;/p&gt;
+&lt;p&gt;　　大法师之抚已被移除。&lt;/p&gt;
+&lt;p&gt;　　英雄天赋&lt;/p&gt;
+&lt;p&gt;　　疾咒师&lt;/p&gt;
+&lt;p&gt;　　磨砺专注已更新——拥有至少20层奥术齐射时施放奥术弹幕，会返还3层奥术齐射（原为5层）。&lt;/p&gt;
+&lt;p&gt;　　裂片宝珠对奥术宝珠的伤害加成提高至50%（原为10%）。&lt;/p&gt;
+&lt;p&gt;　　日怒&lt;/p&gt;
+&lt;p&gt;　　白炽耀焰现在每消耗5层奥术齐射即召唤一颗流星（原为6</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>https://q9.itc.cn/q_70/images03/20260812/491cd26ac62b44a292bef25043de62d8.jpeg</t>
+          <t>https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0807%2Fc6ee7eafj00tjeai90014d000u0008am.jpg&amp;thumbnail=660x2147483647&amp;quality=80&amp;type=jpg</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>黑神话消退，谁能接棒悟空</t>
+          <t>魔兽：下周开始这些坐骑、幻化、成就去向未明!本周抓紧时间刷！</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
@@ -1421,51 +2155,76 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>《黑神话：悟空》对主机游戏市场的带动作用正在淡化。
-据ChinaJoy期间披露的中国游戏产业报告，今年上半年中国主机游戏市场收入下滑，主要原因是2024年推出的爆款产品《黑神话：悟空》降温，而过去两年间其他游戏均未能扛起大旗。
-一大批国内游戏开发企业受到黑神话成功的鼓舞，但复制黑神话的成功却没有那么容易。
-冷热不均
-主机游戏市场再度陷入沉寂。
-今年上半年，中国主机游戏市场实际销售收入9.61亿元，同比下降了7%。在ChinaJoy期间，中国音像与数字出版协会游戏工委主任委员张毅君表示，主机游戏市场下降的主因在于两年前的爆款黑神话逐渐降温，而后续新品跟进不足。
-黑神话是在2024年8月份全球上线的。这款开发成本超过3亿元的游戏，发售后成为一款现象级的作品，在全球市场销售了近3000万份。而且，它并非出自腾讯、网易等游戏大厂，而是来自游戏科学这样一家中小型企业。
-这款游戏的销售还在提升，游戏科学8月初宣布，黑神话全平台数字版本开启七折优惠活动。不过，它最高光的时刻确实已经过去了。
-过去两年里，中国没有一款单机游戏接近黑神话所取得的成绩。
-最近一款表现不错的单机游戏是《明末：渊虚之羽》，它在2025年面世之后，在Steam以及PS5等主机平台合计销售的套数超过200万。但它与黑神话接近3000万套的销售量相比还有较大差距。而且，这款游戏的开发制作组近期被曝已经解散，游戏制作人夏思源也离职了。
-星辰无双软件公司CEO濮冠楠对第一财经记者表示，从销售流水来看，目前接近黑神话的国产单机游戏还比较少。他也是受到黑神话影响，才开始着手开发单机游戏《时空低语》的。
-中国整体游戏市场的表现，与主机游戏细分市场截然不同。
-据游戏工委数据，今年上半年中国游戏行业增长明显，本土市场和出海游戏都是如此。国内游戏市场实际销售收入1884亿元，同比增长12%，主要得益于移动端基本盘的稳固。中国本土游戏表现尤佳：销售收入1633亿元，同比增长16%。
-自研游戏出海情况同样向好：上半年海外市场销售收入123亿美元，同比增长了30%，这得益于长线产品的持续运营及新品的稳定贡献。中国游戏出海收入中，美国、日本、韩国三国占比分别为32.31%、14.05%和7.48%，合计占比53.84%，是主要目标市场。
-据沛星互动CEO游直翰观察，中国游戏出海业务欣欣向荣，海外市占率越来越高。
-中国游戏出海，一开始不容易攻占欧美和日韩市场，是从东南亚国家先打开局面的。现在，游直翰则认为，中国企业已经掌握在欧美头部市场做好游戏的关键，而且这些能力正在众多中国游戏公司之间得到复制。
-“中国游戏出海已经逐渐从‘有没有能力进入海外市场’，进入‘如何持续扩大高质量增长’的新阶段。”游直翰认为，随着产品竞争力不断提高，游戏公司的核心问题也正在从单纯获取更多用户，转向如何找到更可能长期留存、持续付费的高价值玩家。
-人工智能的发展，也会普遍提升中国游戏制作能力。
-下一个悟空何时出现
-黑神话激励了大批游戏制作人。
-在黑神话成功之前，国内真正愿意投资单机游戏的资金非常少，中国单机游戏成功的先例也并不多。
-“目前只出现过一款大规模盈利的游戏就是《黑神话：悟空》。它投资3个多亿，流水大概90个亿，盈利40多亿，超过了大部分电影。但这是第一次。”濮冠楠说。
-他认为黑神话激励了不少人加入单机游戏开发，也极大的鼓舞了此前就开发单机游戏的同行。毕竟，如果不能实现盈利，单机游戏企业也难以为继。黑神话的崛起，也把很多玩家从手游市场带入单机游戏。
-高质量的单机游戏投资都不低。
-濮冠楠认为，一款单机游戏如果投资过小，比如3000万左右，反倒难以回本。因为这不足以保证画面质量，而游戏玩家也不会有好的付费意愿。
-“我个人认为合理的投资区间是2-3个亿，如果方向没选错、执行靠谱的话，大概率能做到2-3倍回本。”濮冠楠说。
-鉴于中国移动游戏的竞争烈度，濮冠楠认为现在做主机游戏的成功概率比移动游戏更高。目前中国存量单机游戏用户可能已达800万。
-人才储备是中国游戏的长板。
-《古神：风里希》的制作人刘洋对第一财经记者表示，全世界的游戏大作大部分都有中国员工的深度参与。这些游戏的核心IP掌握在海外游戏企业手中，而中国丰沛的人才补足了制作能力。
-这种合作模式里，中国在一定的程度上像是游戏产业的富士康，最有创意的部分还在苹果手里。
-人才是游戏产业最不可或缺的资源。相对人力资源的投入，一款游戏的硬件投入几乎可以忽略不计。据刘洋分析，中国游戏的人力成本，只相当于海外同等人力成本的三分之一，甚至是五分之一。这奠定了中国游戏长期发展的根基。
-悟空是中国传统文化的符号，现在不少游戏和电影是从传统文化里寻找灵感。未来会出现新的扛鼎之作吗？
-随着整体技术和审美的提升，刘洋相信长期来看会有越来越多好的作品。但中国游戏产业短期出现另一个黑神话的概率不高。
-“游戏行业将《黑神话：悟空》作为销量的参考，但我内心其实把它当作行业的天花板，那不是做好一个循规蹈矩的东西就能到达的位置。”刘洋说。
-黑神话不容易复现，原因还在于高质量的游戏开发周期漫长。比如，濮冠楠表示，他改编小说开发的单机游戏《时空低语》顺利的话2029年才会面世。
-黑神话是中国游戏市场的一颗种子，耐心是产业发展必不可少的部分。
-“就像《星球大战》出现之后，第二个科幻大制作的电影过了10年才出现。”濮冠楠说。返回搜狐，查看更多</t>
+          <t>&lt;img src="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0807%2Fc6ee7eafj00tjeai90014d000u0008am.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" alt="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0807%2Fc6ee7eafj00tjeai90014d000u0008am.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" /&gt;
+&lt;p&gt;　　距离12.1“乌拉特克的诅咒”上线只剩最后几天，躲猫猫玩法装饰对决也将随之关闭。&lt;/p&gt;
+&lt;p&gt;　　暴雪已经确认：玩法关闭后，玩家依然可以在银月城商人处购买家园装饰类奖励。但对于坐骑、玩具、武器幻化等非装饰奖励，官方目前没有说明后续获取方式。&lt;/p&gt;
+&lt;p&gt;　　想稳妥拿全奖励的玩家，最好趁最后这几天刷完。&lt;/p&gt;
+&lt;p&gt;　　最后冲刺：幻象硬币获取翻倍&lt;/p&gt;
+&lt;p&gt;　　为了让玩家赶上最后一班车，暴雪还对装饰对决进行了调整：&lt;/p&gt;
+&lt;p&gt;　　幻象硬币获取速度翻倍；&lt;/p&gt;
+&lt;p&gt;　　对局最后30秒，躲藏方不再被自动暴露；&lt;/p&gt;
+&lt;p&gt;　　躲藏方长时间停留在原地，不再会生成苍蝇提示；&lt;/p&gt;
+&lt;p&gt;　　寻找方能量获取速度降低20%。&lt;/p&gt;
+&lt;p&gt;　　现在不仅货币翻倍，躲藏方的生存环境也更好了。对于只想刷奖励的玩家而言，这几天是效率最高的窗口期。&lt;/p&gt;
+&lt;p&gt;　　最优先：500硬币坐骑&lt;/p&gt;
+&lt;p&gt;　　最需要优先兑换的，是售价500枚幻象硬币的坐骑：&lt;/p&gt;
+&lt;p&gt;　　魔导师的法术之蜂蜂巢&lt;/p&gt;
+&lt;img src="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0807%2F9760551aj00tjeai9000fd000iv004am.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" alt="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0807%2F9760551aj00tjeai9000fd000iv004am.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" /&gt;
+&lt;p&gt;　　玩具与武器幻化也别漏&lt;/p&gt;
+&lt;p&gt;　　其余非家园装饰奖励同样去向未明，包括3个玩具：&lt;/p&gt;
+&lt;p&gt;　　活化长椅：200幻象硬币&lt;/p&gt;
+&lt;p&gt;　　附魔沙漏：200幻象硬币&lt;/p&gt;
+&lt;p&gt;　　胜者领奖台：200幻象硬币&lt;/p&gt;
+&lt;p&gt;　　还有一批售价150幻象硬币的武器幻化：&lt;/p&gt;
+&lt;p&gt;　　破法者的刃杖&lt;/p&gt;
+&lt;img src="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0807%2Fafc4543aj00tjeai90002d0005n005km.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" alt="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0807%2Fafc4543aj00tjeai90002d0005n005km.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" /&gt;
+&lt;p&gt;　　破法者的凤凰战刃&lt;/p&gt;
+&lt;img src="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0807%2F2c2663d4j00tjeai90003d0005p004sm.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" alt="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0807%2F2c2663d4j00tjeai90003d0005p004sm.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" /&gt;
+&lt;p&gt;　　破法者的刃枪&lt;/p&gt;
+&lt;img src="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0807%2F5e1fd36cj00tjeai90002d0005n0059m.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" alt="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0807%2F5e1fd36cj00tjeai90002d0005n0059m.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" /&gt;
+&lt;p&gt;　　破法者的凤凰之剑&lt;/p&gt;
+&lt;img src="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0807%2Ff1910f06j00tjeai90003d0005s004tm.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" alt="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0807%2Ff1910f06j00tjeai90003d0005s004tm.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" /&gt;
+&lt;p&gt;　　法师卫队的精钢长剑&lt;/p&gt;
+&lt;img src="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0807%2F90c17f72j00tjeai90003d0005p0057m.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" alt="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0807%2F90c17f72j00tjeai90003d0005p0057m.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" /&gt;
+&lt;p&gt;　　法师卫队的魔刃&lt;/p&gt;
+&lt;img src="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0807%2F567c5c5bj00tjeai90003d0005w0056m.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" alt="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0807%2F567c5c5bj00tjeai90003d0005w0056m.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" /&gt;
+&lt;p&gt;　　破法者的神盾&lt;/p&gt;
+&lt;img src="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0807%2F2adca7dej00tjeai90003d0005k0050m.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" alt="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0807%2F2adca7dej00tjeai90003d0005k0050m.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" /&gt;
+&lt;p&gt;　　奥术游侠的魔弓&lt;/p&gt;
+&lt;img src="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0807%2F394bd3afj00tjeai90003d0005n005bm.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" alt="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0807%2F394bd3afj00tjeai90003d0005n005bm.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" /&gt;
+&lt;p&gt;　　废至信标裂隙引导杖&lt;/p&gt;
+&lt;img src="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0807%2Fa0aa9a5fj00tjeai90003d0005p005km.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" alt="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0807%2Fa0aa9a5fj00tjeai90003d0005p005km.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" /&gt;
+&lt;p&gt;　　废至信标裂隙重锤&lt;/p&gt;
+&lt;img src="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0807%2F4d1269dfj00tjeai90003d0005s005km.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" alt="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0807%2F4d1269dfj00tjeai90003d0005s005km.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" /&gt;
+&lt;p&gt;　　如果你的幻象硬币不够，建议兑换优先级为：&lt;/p&gt;
+&lt;p&gt;　　坐骑 &amp;gt; 喜欢的武器幻化 &amp;gt; 玩具 &amp;gt; 家园装饰。&lt;/p&gt;
+&lt;p&gt;　　因为家园装饰已经确认会在银月城商人处继续出售，其他奖励则暂时没有后续消息。&lt;/p&gt;
+&lt;p&gt;　　成就将随玩法关闭&lt;/p&gt;
+&lt;p&gt;　　除了物品，相关成就在玩法关闭后也将无法继续完成，包括：&lt;/p&gt;
+&lt;p&gt;　　百变大咖&lt;/p&gt;
+&lt;p&gt;　　全副武装&lt;/p&gt;
+&lt;p&gt;　　逮个正着！&lt;/p&gt;
+&lt;p&gt;　　插标卖首&lt;/p&gt;
+&lt;p&gt;　　现在你看不到我了……&lt;/p&gt;
+&lt;p&gt;　　虚空空降兵&lt;/p&gt;
+&lt;p&gt;　　影中寒蝉&lt;/p&gt;
+&lt;p&gt;　　藏影无踪&lt;/p&gt;
+&lt;p&gt;　　众里寻他千百度&lt;/p&gt;
+&lt;p&gt;　　你是“鬼”了&lt;/p&gt;
+&lt;p&gt;　　其中“百变大咖”要求完成全部装饰对决成就。&lt;/p&gt;
+&lt;p&gt;　　家园装饰以后还能买，但坐骑、玩具、幻化和成就都存在绝版风险。既然最后几天已经开放双倍幻象硬币，现在刷一刷最稳妥。&lt;/p&gt;</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="inlineStr"/>
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0801%2F83ba01acj00tj2lib0013d000u0008jm.jpg&amp;thumbnail=660x2147483647&amp;quality=80&amp;type=jpg</t>
+        </is>
+      </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>腾讯2026年第二季度网络游戏业务总收入同比增长11%</t>
+          <t>魔兽：重要！暴雪发布新蓝贴，12.1首周低保规则突变！</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
@@ -1475,27 +2234,60 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>本报讯 （记者李豪悦）8月12日，腾讯控股发布2026年第二季度财报。网络游戏业务总收入659亿元，同比增长11%，重回双位数增长态势。
-本土市场收入473亿元，同比增长17%。增长动力主要来自四款核心产品：《三角洲行动》《无畏契约》《无畏契约：源能行动》及《洛克王国：世界》。其中，本土长青游戏《三角洲行动》与《无畏契约》平均日活跃账户数均在本季度创下历史新高。《洛克王国：世界》在今年中国市场发布的所有新手游中，按平均日活跃账户数和流水计算均排名第一。
-国际市场游戏收入，在固定汇率下同比增长4%至186亿元，主要受《鸣潮》《VALORANT》驱动；同时，腾讯旗下Miniclip于国际市场获得突破性成功，掀起箭头解谜热潮的休闲游戏《Arrows-PuzzleEscape》在2026年第二季度成为全球下载量最高的手游，有望助力腾讯国际游戏业务打开新的市场增量。
-本土游戏业务收入持续发力
-在本土游戏业务方面，不同生命周期的产品共同贡献增量，进一步夯实了腾讯游戏业务的基本盘。
-第二季度，《王者荣耀》通过优化排位对局体验，上线小屋农场休闲玩法、英雄命格系统等新内容，并联动电影《哪吒2》等IP，借力五五开黑节等节点强化玩家活跃度、拓展泛用户触达。《三角洲行动》通过S9、S10连续版本迭代，以新干员、新地图、新玩法带来新鲜体验，先后联动古墓丽影、肯德基、《彩虹六号：围攻》等多圈层IP，宝藏月开启与景德镇的联动等，推动其平均日活跃账户数创新高。《无畏契约》与《无畏契约：源能行动》围绕竞技体验与泛用户拓展持续完善产品生态、拓展圈层影响力。
-新品方面，《洛克王国：世界》展现出持续运营的增长潜力。游戏围绕S2赛季更新，凡羽掠影活动及肯德基跨界联动，保持用户活跃与内容热度，并逐步形成稳定的商业化节奏，进一步验证了经典IP焕新后持续吸引用户、提升商业价值的能力，也为其成长为长青游戏奠定了基础。7月《失控进化》上线前全网预约量突破4000万，上线后迅速登顶iOS免费榜总榜，该产品虽不计入二季度收入，但作为下半年新品储备，与现有长青产品及成熟产品形成梯队，为后续业务增长提供新的产品支撑。
-腾讯于2015年完成对欧洲休闲游戏厂商Miniclip的收购，并通过国际游戏业务品牌Level Infinite助力多款产品实现跨区域持续增长与生态扩展，其海外休闲版图在十年间从单一的体育竞技，扩展到三消、益智、跑酷、塔防、模拟经营乃至主机平台，推动腾讯在国际游戏业务侧打开新的增量。
-AI成腾讯游戏业务驱动重要力量
-当前，AI已经成为推动腾讯游戏业务增长的重要力量，并已深入覆盖玩家体验、研发生产、运营服务等在内的全链路环节。比如，《三角洲行动》利用Agent（智能体）实现运营效能提升，并通过Hy3D能力进行场景端手一体化生产管线的提效。
-同时，AI与玩法的融合探索持续推进，《和平精英》AI NPC玩法累计体验用户数增加至1.67亿、最高日活跃用户数达1770万；新品《洛克王国：世界》也积极探索用游戏AI优化玩家体验，推出面向复杂玩法决策的游戏原生Coach Agent“斯嘉丽”，区别于通用大模型“百科全书式”的回答，“斯嘉丽”能够理解玩家的背包、阵容、对局环境，为玩家生成个性化、可执行的阵容与打法建议。自上线以来，“斯嘉丽”有效促进PVP破冰及活跃，PVP激活率增长20%，破冰用户使用功能后胜率也获得实质改善，提升了玩法体验。
-从长青游戏的持续发新芽，到休闲赛道的全球突破，再到游戏AI对玩家体验的深度重塑，腾讯游戏正稳步迈向更具确定性与想象力的增长空间。
-（编辑 张文玲）返回搜狐，查看更多</t>
+          <t>&lt;img src="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0801%2F83ba01acj00tj2lib0013d000u0008jm.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" alt="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0801%2F83ba01acj00tj2lib0013d000u0008jm.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" /&gt;
+&lt;p&gt;　　暴雪发布了更多关于第一赛季结束与第二赛季开启的说明，并确认：第二赛季第一次宏伟宝库无法选择晦暗虚空核心。&lt;/p&gt;
+&lt;p&gt;　　此前不少玩家的计划是，首周宏伟宝库装等较低，干脆不拿装备，改拿一次晦暗虚空核心留到后续再用。暴雪也发现了这个问题，现在这一方案行不通了，首周赛季宝库只能在装备中作出选择，玩家大概率只能期待套装部位或强力饰品。&lt;/p&gt;
+&lt;p&gt;　　以下为暴雪蓝贴：&lt;/p&gt;
+&lt;img src="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0801%2F2bfc6237j00tj2lib002pd000u000llm.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" alt="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0801%2F2bfc6237j00tj2lib002pd000u000llm.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" /&gt;
+&lt;p&gt;　　随着“乌拉特克的诅咒”内容更新临近，我们整理了第一赛季结束以及第二赛季开启时，玩家需要了解的重点信息。&lt;/p&gt;
+&lt;p&gt;　　和以往赛季一样，至暗之夜第一赛季的竞技PvP，将于各地区版本维护前一晚的22:00结束。第一赛季大秘境仍可进入，名人堂、引领潮流等成就也仍可获取，直至维护开始。&lt;/p&gt;
+&lt;p&gt;　　在8月13日当周维护期间，大秘境和PvP的百分比奖励门槛将进行结算。游戏随“乌拉特克的诅咒”更新重新开放后，至暗之夜第二赛季将以季前赛状态开始，部分内容与奖励暂未开放。&lt;/p&gt;
+&lt;p&gt;　　世界内容与地下堡&lt;/p&gt;
+&lt;p&gt;　　季前赛当周，地下堡1至11层开放，同时开放宿敌的“？”难度。丰裕地下堡不会在季前赛出现，地下堡可获得的最高奖励为冒险者3/6装备与老兵纹章。&lt;/p&gt;
+&lt;p&gt;　　新的户外内容，例如诅咒涌动和阿塔乌拉特克宝库，将在季前赛开放。巅峰宝箱会掉落第二赛季老兵装备；困难狩猎也会在季前赛开放，并掉落第二赛季老兵装备。&lt;/p&gt;
+&lt;p&gt;　　8月20日当周维护后：&lt;/p&gt;
+&lt;p&gt;　　丰裕地下堡开放；&lt;/p&gt;
+&lt;p&gt;　　宝匣钥匙开始掉落；&lt;/p&gt;
+&lt;p&gt;　　宿敌“？？”难度开放；&lt;/p&gt;
+&lt;p&gt;　　在赛季首周击败“？？”难度宿敌的玩家，可获得“传说：让我独自面对他 - 阿兹塔雷克”成就；&lt;/p&gt;
+&lt;p&gt;　　梦魇狩猎开放，奖励第二赛季勇士装备。&lt;/p&gt;
+&lt;p&gt;　　地下城&lt;/p&gt;
+&lt;p&gt;　　季前赛当周，第二赛季地下城池将启用，英雄难度和史诗0难度开放，其中包括新地下城毒牙祭坛。&lt;/p&gt;
+&lt;p&gt;　　这一周的史诗0地下城会掉落勇士1/6装备，但仅限每周一次拾取进度。&lt;/p&gt;
+&lt;p&gt;　　8月20日当周维护后：&lt;/p&gt;
+&lt;p&gt;　　玩家开始获得史诗钥石；&lt;/p&gt;
+&lt;p&gt;　　大秘境难度开放；&lt;/p&gt;
+&lt;p&gt;　　史诗0恢复为每日重置。&lt;/p&gt;
+&lt;p&gt;　　团本与巢穴&lt;/p&gt;
+&lt;p&gt;　　季前赛当周，潮缚洞窟巢穴的世界难度开放，掉落第二赛季老兵装备。&lt;/p&gt;
+&lt;p&gt;　　这类装备和团本装备一样为拾取后绑定。巢穴采用每周重置机制；晦暗虚空核心开放后，每周也只能在巢穴中使用一次。&lt;/p&gt;
+&lt;p&gt;　　8月20日当周维护后：&lt;/p&gt;
+&lt;p&gt;　　剧毒深渊团队副本开放普通、英雄与史诗难度；&lt;/p&gt;
+&lt;p&gt;　　团队查找器第一区开放；&lt;/p&gt;
+&lt;p&gt;　　潮缚洞窟巢穴的普通、英雄及弹性史诗难度开放。&lt;/p&gt;
+&lt;p&gt;　　PvP&lt;/p&gt;
+&lt;p&gt;　　季前赛开始后，新的“训练场：竞技场”开放，战场和野外的非评级PvP内容也可参与。&lt;/p&gt;
+&lt;p&gt;　　第二赛季于8月18日当周正式开始后，所有评级PvP开启。玩家可获取新的PvP装备、评级、头衔、成就、玩具，以及剧毒角斗士的血腥幼龙与邪恶光花野猪坐骑。&lt;/p&gt;
+&lt;p&gt;　　首个赛季宝库，不能换虚空核心&lt;/p&gt;
+&lt;p&gt;　　季前赛当周开启的宏伟宝库，提供的是第一赛季最后一周活动对应的奖励。&lt;/p&gt;
+&lt;p&gt;　　不过，从季前赛当周开始，玩家的活动已经会累计第二赛季宏伟宝库进度；这些奖励将在8月20日开放领取。&lt;/p&gt;
+&lt;p&gt;　　制造火花也会在季前赛当周开始掉落。&lt;/p&gt;
+&lt;p&gt;　　最重要的一点是：&lt;/p&gt;
+&lt;p&gt;　　第二赛季第一次宏伟宝库不提供晦暗虚空核心。&lt;/p&gt;
+&lt;p&gt;　　晦暗虚空核心将在第二赛季第二周，即8月27日当周，才会加入宏伟宝库选项。届时，解锁至少3个宝库格子的玩家才能选择它。&lt;/p&gt;
+&lt;p&gt;　　此外，第二赛季第一次宏伟宝库中，世界内容栏位最高只能提供勇士3/6装备；之后的宝库，世界内容栏位最高可提供英雄1/6装备。&lt;/p&gt;</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="inlineStr"/>
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0811%2Ff708eafej00tjkxy000lxd000o000dig.jpg&amp;thumbnail=660x2147483647&amp;quality=80&amp;type=jpg</t>
+        </is>
+      </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>腾讯2026年Q2财报发布：游戏业务双位数增长11% 海外休闲赛道取得突破性成功</t>
+          <t>海量财经 | 七局鏖战见高低 CFML S19总冠军诞生</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
@@ -1505,30 +2297,44 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>央广网北京8月12日消息（记者 陈越）8月12日，腾讯控股发布2026年第二季度财报。网络游戏业务总收入659亿元，同比增长11%，整体重回双位数增长态势。本土市场收入473亿元，同比增长17%。增长动力主要来自四款核心产品：《三角洲行动》《无畏契约》《无畏契约：源能行动》及《洛克王国：世界》。其中，本土长青游戏《三角洲行动》与《无畏契约》平均日活跃账户数均在本季度创下历史新高。《洛克王国：世界》在今年中国市场发布的所有新手游中，按平均日活跃账户数和流水计算均排名第一。
-国际市场游戏收入，固定汇率下同比增长4%至人民币186亿元，主要受《鸣潮》《VALORANT》驱动；同时，腾讯旗下Miniclip于国际市场获得突破性成功，掀起箭头解谜热潮的休闲游戏《Arrows – Puzzle Escape》在2026年Q2成为全球下载量最高的手游，有望助力腾讯国际游戏业务打开新的市场增量。
-本土游戏业务双位数增长17% 海外休闲赛道取得突破性成功
-腾讯Q2本土游戏业务的双位数增长主要得益于《王者荣耀》《三角洲行动》《无畏契约》《无畏契约：源能行动》《洛克王国：世界》等核心产品的业绩表现。不同生命周期的产品共同贡献增量，进一步夯实了腾讯游戏业务的基本盘，在射击品类与竞技赛道上，腾讯游戏持续保持领先位置。
-其中，第二季度，《王者荣耀》通过优化排位对局体验，上线小屋农场休闲玩法、英雄命格系统等新内容，并联动电影《哪吒2》等IP，借力五五开黑节等节点强化玩家活跃、拓展泛用户触达。《三角洲行动》通过S9、S10连续版本迭代，以新干员、新地图、新玩法带来新鲜体验，先后联动古墓丽影、肯德基、《彩虹六号：围攻》等多圈层IP，宝藏月开启与景德镇的联动等，推动其平均日活跃账户数创新高。《无畏契约》与《无畏契约：源能行动》围绕竞技体验与泛用户拓展持续完善产品生态、拓展圈层影响力。
-新品方面，《洛克王国：世界》展现出持续运营的增长潜力。游戏围绕S2赛季更新，凡羽掠影活动及肯德基跨界联动，保持用户活跃与内容热度，并逐步形成稳定的商业化节奏，进一步验证了经典IP焕新后持续吸引用户、提升商业价值的能力，也为其成长为长青奠定了基础。7月上线的《失控进化》上线前全网预约量突破4000万，上线后迅速登顶iOS免费榜总榜，虽不计入二季度收入，但作为下半年新品储备，与现有长青产品及成熟产品形成梯队，为后续业务增长提供新的产品支撑。
-国际市场方面，固定汇率下同比增长4%至人民币186亿元，主要受《鸣潮》《VALORANT》驱动； 同时，腾讯旗下Miniclip于国际市场获得突破性成功，掀起箭头解谜热潮的休闲游戏《Arrows – Puzzle Escape》在2026年Q2成为全球下载量最高的手游，并带来强劲的应用内广告收入。
-腾讯于2015年完成对欧洲休闲游戏厂商Miniclip的收购，并通过国际游戏业务品牌Level Infinite助力多款产品实现跨区域持续增长与生态扩展，其海外休闲版图在十年间从单一的体育竞技，扩展到三消、益智、跑酷、塔防、模拟经营乃至主机平台，推动腾讯在国际游戏业务侧打开新的增量。
-游戏AI持续提升玩家体验 成腾讯游戏业务驱动重要力量
-当前，AI已经成为推动腾讯游戏业务增长的重要力量，并已深入覆盖玩家体验、研发生产、运营服务等在内的全链路环节。比如，《三角洲行动》利用Agent实现运营效能提升，并通过Hy3D能力进行场景端手一体化生产管线的提效。
-同时，AI与玩法的融合探索持续推进，《和平精英》AI NPC 玩法累计体验用户数增加至1.67亿、最高日活跃用户数达 1770 万；新品《洛克王国：世界》也积极探索用游戏AI优化玩家体验，推出面向复杂玩法决策的游戏原生Coach Agent“斯嘉丽”，区别于通用大模型“百科全书式”的回答，“斯嘉丽”能够理解玩家的背包、阵容、对局环境，为玩家生成个性化、可执行的阵容与打法建议。自上线以来，“斯嘉丽”有效促进PVP破冰及活跃，期间PVP激活率增幅20%，破冰用户使用功能后胜率也获得实质改善，提升了玩法体验。
-从长青游戏的持续发新芽，到休闲赛道的全球突破，再到游戏AI对玩家体验的深度重塑，腾讯游戏正稳步迈向更具确定性与想象力的增长空间。返回搜狐，查看更多</t>
+          <t>&lt;p&gt;　　海报新闻首席记者 周凌峰 报道&lt;/p&gt;
+&lt;p&gt;　　8月9日，2026穿越火线IP嘉年华进入第二天。当天的重头戏是CFML（穿越火线手游职业联赛）S19总决赛。经过七局比赛，“白鲨战队”以“4∶3”的总比分战胜“KZ.斗鱼战队”，捧起2026 CFML夏季赛总冠军奖杯，队内选手“时涯.白鲨”当选总决赛FMVP。&lt;/p&gt;
+&lt;img src="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0811%2Ff708eafej00tjkxy000lxd000o000dig.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" alt="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0811%2Ff708eafej00tjkxy000lxd000o000dig.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" /&gt;
+&lt;p&gt;　　据了解，连续两日的赛事均设在济南融创国际体育中心。前一天，端游项目的CFPL夏季赛总决赛已在此落幕，CNCF赛区五支战队随后出征巴黎EWC电竞世俱杯。手游总决赛的加入，让这届嘉年华在同一座场馆里完成了两个项目的收官。&lt;/p&gt;
+&lt;p&gt;　　从年度发布到评论席定调&lt;/p&gt;
+&lt;p&gt;　　腾讯游戏工作人员介绍，CFML是穿越火线手游最高规格的职业联赛，S19为第19个赛季。记者在现场注意到，本届总决赛延续了嘉年华“品牌发布+职业对抗”的节奏：白天做内容发布与预热，晚间进行正式比赛。当天下午，品牌开幕式率先举行。手游策划“老王”登台，介绍CFM新一阶段的版本规划与生态安排，内容涉及新赛季的地图、武器与赛事体系调整。&lt;/p&gt;
+&lt;img src="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0811%2F3be2a9f7j00tjkxy000ohd000o000dig.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" alt="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0811%2F3be2a9f7j00tjkxy000ohd000o000dig.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" /&gt;
+&lt;p&gt;　　随后进行的赛前评论席与总决赛开幕式，由解说潇逸、花瓣、婉瑜与战舞共同担任场间分析嘉宾，从专业研判和粉丝视角两个层面，为决赛做了铺垫。&lt;/p&gt;
+&lt;p&gt;　　七局鏖战，实力见真章&lt;/p&gt;
+&lt;p&gt;　　当天的总决赛采用BO7（七局四胜）赛制。每局开始前，双方需要进行武器BP（禁用与选用），这是CFML本赛季沿用的枪械全局BP模式。赛事方给出的统计显示，2026年夏季赛期间，受这一赛制带动，职业选手对新枪的使用率较此前提升20.9%。选手的武器选择因此更宽，战队之间的战术也比过去更多样。&lt;/p&gt;
+&lt;img src="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0811%2F09f48621j00tjkxy000had000o000dig.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" alt="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0811%2F09f48621j00tjkxy000had000o000dig.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" /&gt;
+&lt;p&gt;　　值得注意的是，决胜图为“新港口”，所有队员集体发力，白鲨势如破竹，半场取得8:1的梦幻开局。攻守互换，白鲨乘胜追击再拿两分，以10:1的比分拿下图7，以总比分4:3获得CFMLS19总冠军。&lt;/p&gt;
+&lt;img src="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0811%2Fe4f761f2j00tjkxy000pfd000o000dig.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" alt="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0811%2Fe4f761f2j00tjkxy000pfd000o000dig.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" /&gt;
+&lt;p&gt;　　然而，KZ与白鲨出现在决赛中，有一点值得记录：不久前的端游CFPL S28总决赛，两支战队刚完成一次交手；此番在CFML总决赛再次相遇，意味着同一对阵在端游、手游两个项目里都打进了决赛。按赛事方统计，这种双端同对阵闯入决赛的概率约为2.22%。&lt;/p&gt;
+&lt;p&gt;　　七局比赛里，双方在地图控制、残局处理和道具配合上互有攻守。现场观众的反应随局势起伏，关键回合出现时，看台上的加油声明显集中。当白鲨集体爆发拿下冠军点的刹那，选手相拥而泣，全场沸腾！CFer为白鲨队史首夺CFML联赛冠军尖叫、呐喊。&lt;/p&gt;
+&lt;img src="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0811%2F351f476bj00tjkxy000ndd000o000dig.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" alt="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0811%2F351f476bj00tjkxy000ndd000o000dig.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" /&gt;
+&lt;p&gt;　　在局间休息期间，赛事方还邀请了eStar、EDG、XROCK、成都AG、LGD、TLG、Q9、EP等俱乐部的KOL登台，与现场观众做互动，内容涵盖战术讲解和趣味挑战。&lt;/p&gt;
+&lt;img src="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0811%2Fc78e8831j00tjkxy000p8d000o000dig.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" alt="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0811%2Fc78e8831j00tjkxy000p8d000o000dig.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" /&gt;
+&lt;p&gt;　　CFML趣味派对拉近玩家距离&lt;/p&gt;
+&lt;p&gt;　　在场馆外，CFML趣味派对与场馆内的比赛同步进行。玩家自发组织的应援打卡和Cosplay巡游在场地外围展开，主办方设置了手游专属的迷你对抗体验区、周边市集和抽奖互动区。不少平时只在手机上看比赛的年轻人，这天也走到了线下的场馆里。&lt;/p&gt;
+&lt;img src="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0811%2Fa90b8d09j00tjkxy000nrd000o000dig.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" alt="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0811%2Fa90b8d09j00tjkxy000nrd000o000dig.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" /&gt;
+&lt;p&gt;　　记者从腾讯游戏官方了解到，CFM接下来的国际赛事安排也已经明确。手游表演赛将进入EWC（电竞世俱杯）的日程，踏上世界舞台。赛事方表示，这一步要把CFM的赏金爆破模式推到世界赛场，在爆破电竞里确立自己的位置，也让CFM这个IP在海外有更多声音。&lt;/p&gt;
+&lt;img src="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0811%2Fff13048bj00tjkxy000kxd000o000dig.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" alt="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0811%2Fff13048bj00tjkxy000kxd000o000dig.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" /&gt;
+&lt;p&gt;　　连续两日的嘉年华虽已落幕，但穿越火线与济南的故事仍在延续。从端游的“枪响正当燃”到手游的“巅峰对决”，从职业赛场到全民狂欢，现场观众得以近距离观看职业对抗，周边的消费和互动也随之增加，而泉城也见证了又一段电竞记忆的诞生。&lt;/p&gt;
+&lt;p&gt;　　责编：宋　玉&lt;/p&gt;
+&lt;p&gt;　　审签：张达伟&lt;/p&gt;</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>https://q2.itc.cn/q_70/images03/20260812/60c10b7dbd4147efa0874238aa509c83.jpeg</t>
+          <t>https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0803%2F083cb295j00tj5gg00005d000460046g.jpg&amp;thumbnail=660x2147483647&amp;quality=80&amp;type=jpg</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>腾讯第二季度财报，本土游戏收入达473亿元人民币</t>
+          <t>144人同台竞技，让《三角洲行动》又多了一张电竞牌"/&gt; 主站 商城 论坛 自运营 登录 注册 144人同台竞技，让《三角洲行动》又多了一张...</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
@@ -1538,27 +2344,88 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>据财联社报道，腾讯发布2026年第二季度财报。
-财报显示，腾讯二季度增值服务业务收入环比增长2%至人民币984亿元。本土市场游戏收入环比增长4%至人民币473亿元，主要得益于《王者荣耀》收入增长以及近期发布的《洛克王国：世界》的贡献。
-财报中提到，本土长青游戏《三角洲行动》及《无畏契约》的平均日活跃账户数量创下新高。《洛克王国：世界》在今年中国市场发布的所有新手游中，按平均日活跃账户数和按流水计算均排名第一。
-另据财经网科技，腾讯国际市场游戏收入环比下降0.7%至人民币186亿元，乃由于《VALORANT》及《PUBG MOBILE》的收入增长被Supercell旗下部分游戏收入下降部分所抵消。社交网络收入环比增长2%，达到人民币325亿元，主要得益于手机游戏应用的道具销售收入增长。
-腾讯控股最新财报显示，第二季度营收2,047.9亿元人民币，预估2,028.4亿元人民币，去年同期1845.04亿元；第二季度NON-IFRS净利润684亿人民币，同比增9%。第二季度资本支出527.8亿元人民币，预估321.4亿元人民币。腾讯控股：第二季度录得负自由现金流人民币138亿元，若剔除算力采购的预付款项，自由现金流为人民币376亿元
-财报还显示，第二季，腾讯控股录得负自由现金流人民币138亿元，此乃由于经营活动所产生的现金净额人民币527亿元，被资本开支付款人民币593亿元、媒体内容付款人民币50亿元及租赁负债付款人民币22亿元超额抵销。腾讯控股的经营现金流包括大额AI相关预付款项，用于提供基础设施以支持Hy模型升级、WorkBuddy及CodeBuddy推理的需求、微信AI举措，以及我们各项产品与服务的AI能力建设，同时满足外部客户对我们的云服务持续增长的需求。若剔除算力采购的预付款项，腾讯控股的自由现金流为人民币376亿元。
-编辑：江砚辞
-审核：十月
-【来源：财联社、财经网科技】返回搜狐，查看更多</t>
+          <t>&lt;p&gt;　　144人同台竞技，让《三角洲行动》又多了一张电竞牌&lt;/p&gt;
+&lt;img src="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0803%2F083cb295j00tj5gg00005d000460046g.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" alt="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0803%2F083cb295j00tj5gg00005d000460046g.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" /&gt;
+&lt;p&gt;　　廉颇&lt;/p&gt;
+&lt;p&gt;　　2026-08-05&lt;/p&gt;
+&lt;p&gt;　　返回专栏首页&lt;/p&gt;
+&lt;p&gt;　　作者：廉颇&lt;/p&gt;
+&lt;p&gt;　　原创投稿&lt;/p&gt;
+&lt;p&gt;　　评论：&lt;/p&gt;
+&lt;p&gt;　　商城特卖&lt;/p&gt;
+&lt;p&gt;　　漫威蜘蛛侠2&lt;/p&gt;
+&lt;img src="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0803%2F6a7f5c57j00tj5gg0000ad000cs005zg.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" alt="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0803%2F6a7f5c57j00tj5gg0000ad000cs005zg.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" /&gt;
+&lt;p&gt;　　¥316&lt;/p&gt;
+&lt;p&gt;　　¥398&lt;/p&gt;
+&lt;p&gt;　　-21%&lt;/p&gt;
+&lt;p&gt;　　前往购买&lt;/p&gt;
+&lt;p&gt;　　艾尔登法环&lt;/p&gt;
+&lt;img src="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0803%2F3ba70e6aj00tj5gg0000cd000cs005zg.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" alt="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0803%2F3ba70e6aj00tj5gg0000cd000cs005zg.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" /&gt;
+&lt;p&gt;　　¥198&lt;/p&gt;
+&lt;p&gt;　　¥298&lt;/p&gt;
+&lt;p&gt;　　-34%&lt;/p&gt;
+&lt;p&gt;　　前往购买&lt;/p&gt;
+&lt;p&gt;　　绝地潜兵2&lt;/p&gt;
+&lt;img src="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0803%2F27751cf7j00tj5gg0000ld000cs005zg.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" alt="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0803%2F27751cf7j00tj5gg0000ld000cs005zg.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" /&gt;
+&lt;p&gt;　　¥135&lt;/p&gt;
+&lt;p&gt;　　¥198&lt;/p&gt;
+&lt;p&gt;　　-32%&lt;/p&gt;
+&lt;p&gt;　　前往购买&lt;/p&gt;
+&lt;p&gt;　　风灵月影VIP&lt;/p&gt;
+&lt;img src="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0805%2Fed9f5514j00tj95s0000rd000ia0099g.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" alt="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0805%2Fed9f5514j00tj95s0000rd000ia0099g.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" /&gt;
+&lt;p&gt;　　¥19.9&lt;/p&gt;
+&lt;p&gt;　　前往购买&lt;/p&gt;
+&lt;p&gt;　　绿色地狱&lt;/p&gt;
+&lt;img src="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0803%2Fecf4eabaj00tj5gg0000md000cs005zg.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" alt="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0803%2Fecf4eabaj00tj5gg0000md000cs005zg.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" /&gt;
+&lt;p&gt;　　¥14.9&lt;/p&gt;
+&lt;p&gt;　　¥80&lt;/p&gt;
+&lt;p&gt;　　-81%&lt;/p&gt;
+&lt;p&gt;　　前往购买&lt;/p&gt;
+&lt;p&gt;　　你廉颇老师已经在准备明年参赛了&lt;/p&gt;
+&lt;p&gt;　　《三角洲行动》这次“主播巅峰赛”线下总决赛的氛围很不一般。它不同于以往我去过的任何一个《三角洲行动》赛事，甚至可以说，它与绝大多数目前已有的电竞赛事都不一样。&lt;/p&gt;
+&lt;p&gt;　　当你就坐在选手身后，看着他们电脑屏幕上的对枪画面，听着此起彼伏的报点、战术讨论，以及纯粹情绪宣泄的呐喊时，你会自然而然地感觉，自己身处的不是电竞赛场，而是玩家们同样很熟悉的另一个场景：&lt;/p&gt;
+&lt;p&gt;　　网吧。&lt;/p&gt;
+&lt;img src="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0805%2Fd19fbc5fj00tj9vce0021d000u000fvg.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" alt="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0805%2Fd19fbc5fj00tj9vce0021d000u000fvg.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" /&gt;
+&lt;p&gt;　　其实，去年《三角洲行动》第一届“主播巅峰赛”，就很不平常——500余名主播参加，为期超过一个半月的总赛程，不但打破了人们心目中“电竞赛事”的刻板印象，还诞生了无数让人津津乐道的游戏名场面。像林树卡点极限救援、老飞宇躲过猎杀围剿百万撤离、杨齐家被人“反向扶贫”等等，至今回想起来，依然历历在目，很有画面感。&lt;/p&gt;
+&lt;img src="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0805%2F98b6d13ej00tj9vce00djd000mg00f3g.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" alt="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0805%2F98b6d13ej00tj9vce00djd000mg00f3g.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" /&gt;
+&lt;p&gt;　　而且，由于每个主播的参赛全过程都能被平台直播和切片完整记录，赛程中发生的任何故事，都能在第一时间在互联网上传播、扩散。比如在这次“主播巅峰赛”的预选过程中，小叮当在同平台“父老乡亲”三把千万局的托举之下晋级、贱徐在全程130上下心率的情况下18进1艰难打赢复活赛“地狱归来”等等，既创造了全新的“主播巅峰赛”集体记忆，也在无数讨论中进一步拉高了观众对决赛的期待值。&lt;/p&gt;
+&lt;img src="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0805%2F738a0fe6j00tj9vcf001xd000u000gvg.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" alt="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0805%2F738a0fe6j00tj9vcf001xd000u000gvg.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" /&gt;
+&lt;p&gt;　　可以说，除了电竞赛事本身的观赏性，“主播巅峰赛”还给了“高手在民间”的广大《三角洲行动》主播和玩家们一次“一搏成名”的机会。而这种具有“真人秀”属性的元素，也大幅提升了“主播巅峰赛”本身的观赏性与娱乐性。&lt;/p&gt;
+&lt;img src="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0805%2F033b598fj00tj9vcf002ud000sz007og.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" alt="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0805%2F033b598fj00tj9vcf002ud000sz007og.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" /&gt;
+&lt;p&gt;　　与此同时，在赛制层面，这次的“主播巅峰赛”相比第一次也进行了很大幅度的革新。而这一举措，也更加突出了“主播巅峰赛”的“真人秀”属性。&lt;/p&gt;
+&lt;p&gt;　　在初次举办“主播巅峰赛”时，《三角洲行动》官方采用的是类似后来的“烽火杯”以及“烽火职业联赛”的“夺砖赛制”，一砖开启赛点，两砖拿下比赛，这也使得“主播巅峰赛”首次总决赛的规模被限制在了18个选手、六支固定队伍。&lt;/p&gt;
+&lt;p&gt;　　但在今年的“主播巅峰赛”流程中，为了更好地契合“主播巅峰赛”电竞硬核性与真人秀娱乐性并存的调性，《三角洲行动》官方取消了硬性的组队限制，要求各个参赛主播必须单人“混匹”入局。到了线下总决赛，本次“主播巅峰赛”更是以36位争冠选手与108位“赏金猎人”踢馆主播共同入赛，144台电脑同时匹配的“大乱斗”环境，把“主播巅峰赛”改版后“一人入局，一搏成名”的看点发挥到了极致。&lt;/p&gt;
+&lt;p&gt;　　与《三角洲行动》高度要求战术策略和团队配合的专业比赛“烽火职业联赛”相比，“主播巅峰赛”的赛制，不仅更加突出了每个选手的综合个人能力，也与普通玩家在《三角洲行动》“烽火地带”模式里的游戏体验完全相同，这无疑进一步拓展了“主播巅峰赛”的观赏性和话题度。&lt;/p&gt;
+&lt;img src="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0805%2F9917969bj00tj9vcg0025d000u000njg.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" alt="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0805%2F9917969bj00tj9vcg0025d000u000njg.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" /&gt;
+&lt;p&gt;　　关于这一点，在观赛过程中其实有很多个瞬间，让我感受到了“主播巅峰赛”具体的“观赏性”——比如说，与“烽火职业联赛”不同，“主播巅峰赛”没有空投等高质量装备获取机制，也没有无砖局等为选手提供缓冲空间的设计。为了在规定时间内更多“得吃”，在排行榜和击杀榜上取得更高的名次，参赛选手必须不断进入匹配，一点空闲时间也没有。&lt;/p&gt;
+&lt;p&gt;　　而这也使得，他们必须不断优化自己的装备配置，在尽可能拉高自己战力的同时，还要保证一旦出现失误，损失在自己的可接受范围之内，也就是说要实现极致的性价比。所以在比赛开始之后，从大屏幕转播画面可以明显看到，很多选手不仅打的都是四级弹，而且经常有从保险箱现场扣子弹装填的情况出现。在装备方面，许多选手也选用了“强袭战术背心+两格绿手术包”这种普通玩家在游戏中经常选用的配置，非常具有亲切感。&lt;/p&gt;
+&lt;img src="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0805%2F360b12cbj00tj9vcg001gd000u000gvg.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" alt="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0805%2F360b12cbj00tj9vcg001gd000u000gvg.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" /&gt;
+&lt;p&gt;　　再比如，比赛开始后不久，导播就把镜头切给了“整活型主播”王浩宇。而曾经创造了“比赛打暗号第一人”“比赛找指挥部要物资第一人”等神人操作的他，这次也没有辜负导播和所有观众的期待。&lt;/p&gt;
+&lt;p&gt;　　在发现自己“上电视”之后，他不仅马上对着镜头表示“不要看我，看技术主播去”，还在一波中控沙地PEEK险些被抽死之后，一边打药一边站起来对着全场大喊：“我穿的五套，气不气”，一举把整场比赛的节目效果抬高到了一个新的层次。&lt;/p&gt;
+&lt;img src="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0805%2F143c4e58j00tj9vcg001ud000u000gvg.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" alt="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0805%2F143c4e58j00tj9vcg001ud000u000gvg.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" /&gt;
+&lt;img src="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0805%2F119024a1j00tj9vcg000jd000u000adg.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" alt="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0805%2F119024a1j00tj9vcg000jd000u000adg.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" /&gt;
+&lt;p&gt;　　不过，虽然现场的氛围非常欢乐，但这次“主播巅峰赛”线下总决赛的比赛环境节奏还是非常激烈的。毕竟，在场的36位决赛争冠选手，谁都想拿下最终的冠军，在《三角洲行动》的发展史上刻下自己的名字；而剩下的108名赏金猎人，也在“干员击败榜”的激励下，用各种手段不断刷新着自己的击杀纪录。&lt;/p&gt;
+&lt;p&gt;　　位于击杀榜前列的昊天、小向等人，平均一局游戏能拿下三到四个人头，对争冠选手造成了很大的压力。其中原本粉丝数量并不多的小向，更是在这次的比赛中做到了“一搏成名”，用实力证明了自己。&lt;/p&gt;
+&lt;img src="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0805%2F3973bc23j00tj9vch001nd000u000dvg.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" alt="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0805%2F3973bc23j00tj9vch001nd000u000dvg.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" /&gt;
+&lt;p&gt;　　除此之外，在预选赛过程中曾多次出现的“温情时刻”，也同样发生在了这次“主播巅峰赛”的线下决赛当中。在决赛匹配倒计时的末尾阶段，魔王PP运气爆发搜出一张蓝室核心，取得争冠资格，此时他的两名“野排”队友为了帮助他夺冠，直接投喂了包括两个4格红在内的大量物资，还主动断后为他争取了前往丢包撤离点的时间。在对局结束后，被队友的无私支持感动的魔王PP直接泪洒比赛当场。&lt;/p&gt;
+&lt;p&gt;　　但是，百人线下总决赛的环境永远是瞬息万变的。在比赛的最后阶段，eStar.Aqing压哨匹配进场，赶上了最后一趟末班车。此时的他，正在与另一场对局中的争冠选手展开一场没有硝烟的战争，双方都在竭尽全力搜刮更多的物资。最后，同样是在队友的帮助下，eStar.Aqing实现了千万撤离，再结合他本来就领先的击败数和破砖数，一举实现了惊天逆转，夺得了本次“主播巅峰赛”的冠军。&lt;/p&gt;
+&lt;img src="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0805%2F093f1903j00tj9vch0025d000u000gvg.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" alt="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0805%2F093f1903j00tj9vch0025d000u000gvg.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" /&gt;
+&lt;p&gt;　　虽然比赛就此结束了，但从在决赛镜头前整活的王浩宇，到无情的屠杀机器昊天、小向，再到激烈争冠的魔王PP、eStar.Aqing……所有参赛主播的各种高光操作，此时依然在我的脑海中不断重播。特别是在最后一把对局用自身经历贯彻了《三角洲行动》“团队搜打撤”游戏本质的魔王PP，虽然他最终没有夺冠，但我还是记住了那一局中出现的，令人感动至深的时刻——正如官方对这次“主播巅峰赛”的定义：在这里，用各种方式让观众看到你，就是赢。&lt;/p&gt;
+&lt;p&gt;　　而在更理性的层面上，“主播巅峰赛”赛事期间话题整体播放量已突破40亿，总决赛当晚话题位列抖音热榜第4、快手热榜第23、B站平台热榜第13等，抖音平台官方直播间最高在线达76.6万（PCU），成成大王、昊天等5位主播直播间同时在线突破10万人，Xleft小叮当直播间人气超500万等等肉眼可见的大数字，也在不断证明，“主播巅峰赛”的确做到了让玩家们看到每一名主播的风采，而刷新了电子竞技和游戏综艺环境的“主播巅峰赛”本身，也正在被越来越多的玩家看到。&lt;/p&gt;
+&lt;img src="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0805%2F4defe062j00tj9vch002qd000u000i3g.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" alt="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0805%2F4defe062j00tj9vch002qd000u000i3g.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" /&gt;
+&lt;p&gt;　　或许，在不久的将来，“主播巅峰赛”也将如同《三角洲行动》在游戏业界的表现一样，在游戏衍生的娱乐赛事领域，引领起一波新的潮流。&lt;/p&gt;</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>https://q9.itc.cn/q_70/images03/20260801/f5e1410b85f344768d468a423e79189b.jpeg</t>
+          <t>https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0805%2F79ccb9acj00tja9x000mqd002yo01o0g.jpg&amp;thumbnail=660x2147483647&amp;quality=80&amp;type=jpg</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>老牌厂商突围求变，《异环》闯关出海，完美世界寻找竞争新支点</t>
+          <t>V26无畏巡回成都站启动 城市文旅活动同步开启</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
@@ -1568,33 +2435,18 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>国产开放世界赛道竞争白热化，叠加出海环境迭代、AI技术浪潮冲击，老牌游戏厂商亟待搭建可持续的系统性竞争力。
-在“2026中国国际数字娱乐产业大会（CDEC）高峰论坛”期间，完美世界集团高级副总裁、总编辑伊迪在接受包括《每日经济新闻》记者在内的媒体群访时，对公司当下战略路径进行了拆解。
-伊迪 图片来源：企业供图
-放眼完美世界近两年的布局，今年4月上线的自研开放世界RPG《异环》，是其产品端最重要的一次尝试。业务层面，自2024年开始，公司加大电竞生态建设投入，同时推动AI技术渗透游戏、影视、电竞多条业务线。
-而今年上半年，完美世界业绩再度承压。根据业绩预告，完美世界2026年上半年预计净亏损8000万元至1.2亿元，阶段性亏损原因之一是旗舰产品《异环》公测推广投入与收入确认存在时间错配。
-一边是新游投入带来短期财务压力，另一边是开放世界、全球化、数智化多重赛道机遇，完美世界如何依托产品储备与技术积累破局？
-《异环》承压长跑，全球一体化出海模式落地试验
-2026年的国产二次元开放世界早已告别蓝海。《原神》《鸣潮》等游戏持续长线运营巩固基本盘，网易《无限大》、诗悦《望月》等都市题材新品蓄势待发，赛道拥挤、玩家审美阈值持续抬高。
-作为完美世界押注的年度核心旗舰，《异环》自诞生起就背负着沉甸甸的期待。上线前全网预约突破3500万，市场期待其承接《幻塔》经验，打通国产都市开放世界全球市场。
-但其现实开局却充满波折。4月23日国服公测开启后，游戏迅速暴露移动端优化不足、角色设计、剧情叙事等多重短板。接着官方发布公开致歉公告，承诺全方位优化调整。而从伊迪披露的游戏成绩来看，直面争议之后，这款产品还是交出了一份合格的成绩单。
-据伊迪介绍，《异环》4月底启动全球公测，覆盖180多个国家和地区，截至6月30日全球累计流水突破14亿元人民币，官方PC、官方安卓渠道流水占比超六成。海外市场表现尤为亮眼，多次跻身iOS游戏畅销榜前五，在日本市场登顶PS主机热门榜单。
-从这份数据可以看出产品独特的用户结构，PC与主机玩家构成收入基本盘，区别于传统手游依赖移动端的商业模式。
-但出海层面，完美世界仍有明显短板。2025年年报显示，公司海外收入4.34亿元，同比下滑16.67%，海外营收占比仅6.51%，出海业务长期处于疲软状态。《异环》自主发行出海，成为完美世界新模式的试验田。
-“我们的出海经历代理发行、海外设立分公司自建团队多个阶段。随着全球产业升级和市场环境变化，尤其是手游市场的变化，我们对原有出海模式进行升级。”伊迪解释说，完美世界正在推行全球一体化出海策略。
-伊迪表示，这套模式并非全球市场一套方案简单复制，而是将全球市场视作统一大盘，统一调配人力、资金、研发节奏，根据不同区域市场特征精细化运营。本次《异环》在日韩、欧美等主要区域全部由公司自主发行。
-在行业红利消退、海外监管趋严、用户口味分化的背景下，游戏出海需要更为精细化的统筹能力。
-伊迪透露，未来完美世界多款新品将采取“先海外、后国内”的市场顺序，借助全球化研发发行框架打开增长空间。短期来看，《异环》前期高额营销投入造成财报阶段性承压，公司判断，产品业绩贡献将从三季度开始逐步释放。
-“没有技术焦虑，将AI视作工具”
-2026年，生成式AI全面渗透数字文创行业，而本届ChinaJoy（中国国际数码互动娱乐展览会）也将“释放数智能量”定为核心议题。游戏行业作为AI最早落地的场景之一，已经实现了一定的落地成果。
-根据中国音数协游戏工委与清华大学的专项调研，AI在中国游戏研发端的整体普及率已达86.36%。AIGC美术、智能NPC、数字人动画从概念走向常态化应用，腾讯、网易相继推出自研AI平台，行业技术竞赛持续升温。面对汹涌而来的技术浪潮，完美世界有着不一样的判断。
-伊迪认为，游戏与人工智能本就是双向赋能、相伴共生。早年OpenAI依托《DOTA2》电竞场景训练AI模型，游戏为AI提供训练土壤。反过来，AI如今持续推动游戏产业工业化升级。
-他指出，当前游戏行业AI应用清晰地划分为两大方向：一端面向生产管线，依靠AIGC工具降低美术、动画、内容制作成本；另一端面向玩家消费端，智能NPC打破固定剧本限制，依据玩家对话、行为做出差异化反馈，拉升大世界沉浸感。
-而在具体实践上，伊迪对完美世界的AI应用进行了回顾。他表示，完美世界早在2017年便在内容安全、客服机器人等基础场景落地相关技术。而近两年来，AI工具则嵌入游戏研发全流程，自研完美AIGC平台整合生图、大模型角色扮演、数字人视频、2D转3D工具。2025年，进一步升级大模型智能体平台，支持私有化大模型部署。落地成果已经体现在《诛仙世界》等产品中。
-面对行业普遍存在的技术焦虑，伊迪认为：“AI对游戏的研发制作更多处于单点提效状态，并没有完全颠覆性改变整个技术环境和工作流。这对整个游戏行业也是如此。”
-在他看来，AI更像是一件持续迭代的工具，厂商跟随技术更新更换趁手工具即可，不必过度恐慌。而且，比起技术焦虑，玩家是否接受AI技术是更应该关注的落点。“在拥抱AI的过程中，我们也会审慎考虑玩家对AI创作的态度，因为对大部分游戏厂商来说，游戏质量和玩家喜爱才是第一位的。”
-视线放得更远，伊迪认为，游戏的定义正在被时代改写，游戏不止于娱乐，而是一种工具和方式。“AI+游戏、游戏化思维赋能千行百业。比如，在教育、数字孪生、工业制造、自动驾驶等领域，游戏化的组织管理，都可以广泛地应用。”
-每日经济新闻返回搜狐，查看更多</t>
+          <t>&lt;p&gt;　　来源：环球网&lt;/p&gt;
+&lt;p&gt;　　【环球网互娱综合报道】V26无畏巡回成都站暨2026无畏契约冠军巡回赛VCT CN联赛第二赛段入围赛&amp;amp;季后赛将于8月5日至8月23日在成都举办。首次来到成都的无畏巡回和VCT CN联赛，将带着无畏巡回的完整体验，为全国观众、广大市民和电竞爱好者奉上一场集竞技、潮流、文化于一体的暑期观赛新体验！&lt;/p&gt;
+&lt;img src="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0805%2F79ccb9acj00tja9x000mqd002yo01o0g.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" alt="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0805%2F79ccb9acj00tja9x000mqd002yo01o0g.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" /&gt;
+&lt;p&gt;　　作为无畏巡回成都站的竞技主轴，VCT CN联赛第二赛段季后赛将分为两个阶段。8月5日至8月16日，2026 VCT CN联赛第二赛段季后赛入围赛&amp;amp;季后赛前三日将在成都城北体育馆举办。&lt;/p&gt;
+&lt;p&gt;　　EDG、AG、FPX、WOL、DRG、JDG、TE、TEC八支VCT CN联赛队伍与KBG、AT两支全国大赛专业赛道队伍，将通过双败淘汰赛，争夺4个晋级第二赛段季后赛的资格。这4支队伍将与在常规赛中直接晋级季后赛正赛的NOVA、BLG、XLG、TYL四支队伍，展开季后赛前三日的首轮较量。&lt;/p&gt;
+&lt;img src="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0805%2Ffa2e9577j00tja9x000a6d001hc00u0g.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" alt="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0805%2Ffa2e9577j00tja9x000a6d001hc00u0g.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" /&gt;
+&lt;p&gt;　　8月19日至8月23日，VCT CN联赛第二赛段季后赛后五日将在成都金融城演艺中心举办。首轮季后赛角逐出的6支队伍，将在此进行剩余季后赛比拼。最后仅有一支队伍能脱颖而出，捧起代表VCT CN最高荣耀的“花火”奖杯，成为2026 VCT CN联赛年度总冠军。本次季后赛除败者组决赛与年度总决赛为BO5外，其余比赛均为BO3。获得冠军与亚军的队伍将直接晋级全球冠军赛！&lt;/p&gt;
+&lt;img src="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0805%2F0ba96fd2j00tja9x0009pd001hc00u0g.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" alt="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0805%2F0ba96fd2j00tja9x0009pd001hc00u0g.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" /&gt;
+&lt;p&gt;　　VCT CN联赛第二赛段季后赛举办期间，赛场内外将举办丰富联动活动，同时12支VCT CN联赛队伍还将举办俱乐部见面会等活动。&lt;/p&gt;
+&lt;p&gt;　　赛事之余，此次无畏巡回成都站更有丰富多彩的城市活动待观众解锁。首个沉浸式手瓦一周年主题乐园将落地成都东郊记忆。现场将带来诸多互动体验、主题打卡、趣味挑战等精彩内容，更有神秘嘉宾惊喜亮相，带来精彩纷呈的互动环节，与众多瓦友共同开启周年狂欢。&lt;/p&gt;
+&lt;p&gt;　　除此之外，首次来到成都的无畏巡回和VCT CN联赛，将保持“潮流文化+热血竞技+城市文旅”的IP属性，积极探索与成都文旅、商业、体育等领域的深度融合。&lt;/p&gt;
+&lt;p&gt;　　赛事期间，观众可前往现场观赛助威，沉浸式感受无畏巡回潮流竞技魅力。（古雨）&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -1602,7 +2454,7 @@
       <c r="A35" s="2" t="inlineStr"/>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>虎牙：第二季度营收17.4亿元，同比增长11%</t>
+          <t>三角洲S2总决赛大结局，19岁青训小将Aqing极限翻盘，夺冠高喊“我是新的王！”</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
@@ -1612,24 +2464,19 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>中证报中证网讯（记者 杨梓岩）8月11日，虎牙公布了2026年第二季度财报。财报显示，该季度，虎牙总收入同比增长11%至17.4亿元，连续6个季度同比增长。其中，游戏相关服务、广告及其他收入同比增长54.1%至6.4亿元，占总收入比例提高至36.7%。
-虎牙公司CEO黄俊洪表示：“2026年第二季度，虎牙战略转型继续取得积极进展，游戏相关服务、广告及其他收入延续强劲增长势头。虎牙沿游戏产业价值链不断向上延伸，从游戏联运、道具销售、广告营销到游戏发行，逐步在产业链各环节构建起差异化能力，并日益获得合作伙伴和市场的认可与验证。”
-从最新业务进展来看，游戏发行业务方面，7月份，《鹅鸭杀》手游进入App Store免费游戏排行榜前五。《鹅鸭杀》围绕对局语音环境加强治理，并联动经典IP《西游记》、同步推出聚会场景玩法，获得良好反响。
-新游储备方面，虎牙将独家发行经典武侠MMORPG游戏《剑侠情缘：重逢》和3D消除手游《消消奇遇》。虎牙首款自研游戏《这岛有幻兽》7月获批版号，目前正筹备测试。
-广告业务方面，《炉石传说》成为第二季度重要的新广告主。直播业务方面，进入下半年，公司持续优化主播合作及签约体系，提升内容投入产出效能。在赛事内容上，2026年二季度虎牙平台带来超过100项版权赛事、约20档自制赛事。
-产品与AI领域，围绕《三角洲行动》《英雄联盟》《云顶之弈》等热门游戏品类，虎牙已上线地图导航、战斗辅助等AI游戏工具。7月，公司发布了自研的实时多模态数字人模型VAM 1.0，可快速生成兼具自然语音、歌唱与肢体表达能力的AI数字人，实现实时互动。返回搜狐，查看更多</t>
+          <t>&lt;p&gt;　　8月2日晚，三角洲行动S2主播巅峰总决赛，eStar青训小将游戏主播Aqing多次极限1vN绝境突围，收官局更是极限翻盘，完成积分反超登顶。拿下总冠军，他本人高喊“我是新的王！”还有6旬电竞老太小two姐姐以赏金猎人身份同台对战一众年轻高手，多次拿下击杀。而主播昊天更是打出最高43杀，碾压职业选手。还有解说嘉宾陈泽，一边整活吐槽一边专业分析，看点直接刷屏。封面新闻记者 谢杰 编辑 周珂冰&lt;/p&gt;</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>https://q2.itc.cn/q_70/images03/20260702/4b21e1d1287f451e85b0b3f23733f39e.jpeg</t>
+          <t>https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0811%2F4001f560j00tjkatu001td200u000gwg01hc00u0.jpg&amp;thumbnail=660x2147483647&amp;quality=80&amp;type=jpg</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>借势世界杯 EA寻找第二曲线</t>
+          <t>一款爽到耳鸣的打炮游戏，在Steam轰下了98%好评率</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
@@ -1639,24 +2486,68 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>上一届世界杯结束之后，Electronic Arts Incorporated（以下简称“EA”）与FIFA合作了将近30年的独家授权正式取消，但EA不仅没有关停足球游戏产品线，更是推出更名作品FC系列，完成品牌转型。根据EA发布的官方新闻稿，在FC 24上线首日就有220万人安装该应用，打破了EA SPORTS移动足球系列的纪录，上线10天内，超过1120万新用户下载。
-EA官方公布的资料显示，截至2026年，FC系列全平台累计注册玩家破1.5亿，核心的球员卡包付费收入保持稳定，整体足球品类年度营收规模和此前FIFA联名时期基本持平。EA依旧手握英超、西甲、德甲等全球主流联赛、俱乐部与球员独立肖像版权，仅剥离FIFA冠名、世界杯官方赛事标识使用权，同时持续升级游戏画面、对战玩法与电竞赛事体系，玩家核心游玩需求并未因品牌更名受到影响。借助本届世界杯全球流量，FC系列同步上线原创足球赛事主题活动，持续拉动游戏用户活跃度。
-根据EA发布的四季度及2026财年业绩报告，2026财政年度的净收入为75.31亿美元，较前一年度增长了1%，该季度经营活动产生的净现金为5.8亿美元，整个财政年度的经营活动产生的净现金为25.53亿美元，同比分别增长6%和23%。在2026财年，EA全球足球游戏品类净预订量增长了中位数，包括FC 26、FC Online和FC Mobile。
-“玩家选择足球游戏的核心是看重真实联赛、球员内容，而非单一FIFA标识，EA拥有完整赛事版权的同时，其足球系列多年沉淀的手感、AI系统、线上社区以及Ultimate Team模式，都形成了比较深的用户习惯，品牌变更不会轻易动摇核心收入。独家授权取消后，EA获得了更大的战略主动权，但关键还是看它如何重新配置这些资源。虽然短期来看，FIFA的授权取消对EA的影响相对有限，但长此以往是否会对EA形成竞争冲击，则取决于FIFA能否真正建立新的数字生态。”数码行业从业人员石明坤如是说。
-就在2026年世界杯赛事期间，EA依托旗下FC系列落地规模化游戏内广告布局，试图打造区别于游戏买断、道具内购的全新增长曲线。EA明确发布的公告称，正式推出EA广告，将品牌直接引入游戏。
-根据EA官方公告数据，在主机、移动端和PC平台，其游戏和服务在2026财年每月触达超过1.2亿玩家，其粉丝们在FC系列中每月完成超过10亿场比赛。在EA看来，这种规模和频率共同为品牌通过真实互动体验与观众建立联系创造了机会与平台。
-EA相关负责人曾在公开访谈中表示，脱离FIFA独家合作框架后，EA不再受FIFA官方赞助商排他条款约束，拥有自主对接、筛选广告品牌的完整权限，这也是独立广告业务能够全面铺开的关键基础。
-在EA的规划中，此次上线的独立广告业务集中在体育游戏赛道，核心载体为原FIFA系列迭代而来的FC系列，同时覆盖《麦登橄榄球》《NHL冰球》等自有头部体育IP。EA宣称，其广告形式将贴合真实赛场环境，不会强制弹窗打断对局体验。
-“世界杯的热度势必会带来的短期流量红利，使不少品牌都会咨询EA游戏广告投放方案，整体商业合作意向热度较高。但在各大游戏厂商均承压的当下，EA同样存在存储、引擎开发等各类运营成本困境，无法独善其身压低广告投放门槛。”北京市社会科学院研究员沈望舒进一步解释道，“且玩家对游戏内商业植入的容忍度往往有限，频繁插入大量广告可能会引发口碑下滑，从而失去高黏性用户。长远来看，游戏厂商想要长期站稳市场，不能过度依靠硬件与广告衍生业务，深耕原创优质游戏内容才是核心根基。”
-北京商报记者 卢扬 实习生 王祺姝返回搜狐，查看更多</t>
+          <t>&lt;img src="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0811%2F4001f560j00tjkatu001td200u000gwg01hc00u0.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" alt="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0811%2F4001f560j00tjkatu001td200u000gwg01hc00u0.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" /&gt;
+&lt;p&gt;　　怪物马戏团 | 文&lt;/p&gt;
+&lt;p&gt;　　这几天，一个模拟打炮的独立游戏成为了黑马，名叫《铁巢重炮》，非常有意思。现在游戏Steam好评率维持在98%，有五千多个评价，高得惊人。&lt;/p&gt;
+&lt;img src="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0811%2F61419698j00tjkatu0026d200kk00mlg00kk00ml.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" alt="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0811%2F61419698j00tjkatu0026d200kk00mlg00kk00ml.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" /&gt;
+&lt;p&gt;　　《铁巢重炮》是一个很特殊的游戏，它让你模拟当一个炮兵，掌控一门机械巨炮，而你就住在大炮碉堡的内部。&lt;/p&gt;
+&lt;img src="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0811%2F58d9a519j00tjkatu001pd200u000gwg01hc00u0.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" alt="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0811%2F58d9a519j00tjkatu001pd200u000gwg01hc00u0.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" /&gt;
+&lt;p&gt;　　因为这是个模拟游戏，所以它也带有一点硬核色彩，而且涉及不少重复劳作。然而神奇的就是，这游戏还是很能让你上头，因为它把氛围和各种操作的质感做得极为出色。&lt;/p&gt;
+&lt;p&gt;　　游戏设定在一个架空的1920年，所以你只能依靠传统的炮兵手段开炮。也就是，当你靠电传打字机获得情报和命令后，得先在地图上标记目标和测距，然后计算弹道、发射角度和装药量。接着，还得操控液压系统，最后开火。&lt;/p&gt;
+&lt;img src="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0811%2Fbbf0aa63j00tjkatu002cd200u000gwg01hc00u0.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" alt="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0811%2Fbbf0aa63j00tjkatu002cd200u000gwg01hc00u0.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" /&gt;
+&lt;p&gt;　　开火后，你会得到轰炸地的照片，以判断是否命中目标，需不需要重射。整个过程中，任何错误都能导致炮弹的弹道完全偏离，炸到计划外的目标。&lt;/p&gt;
+&lt;img src="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0811%2Ff5245102j00tjkatu002od200u000irg01hc00xc.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" alt="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0811%2Ff5245102j00tjkatu002od200u000irg01hc00xc.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" /&gt;
+&lt;p&gt;　　游戏的打击感是顶级的，当你开炮的那一瞬间，整座数千吨的巨炮都会在震耳欲聋的咆哮中颤动起来，屏幕摇晃，音箱爆炸，给人极大的满足感。&lt;/p&gt;
+&lt;img src="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0811%2Fe48526dfj00tjkatu0013d200u000gwg01hc00u0.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" alt="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0811%2Fe48526dfj00tjkatu0013d200u000gwg01hc00u0.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" /&gt;
+&lt;p&gt;　　而且打击感不限于开炮的瞬间，在你操控的每个环节，都能获得出色的反馈，比如装填炮弹和火药时，你会看到一个个齿轮驱动机械支架，以复杂但有序的运作，将一颗颗炮弹送进炮膛。&lt;/p&gt;
+&lt;img src="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0811%2Fa46950baj00tjkatu0022d200u000gwg01hc00u0.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" alt="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0811%2Fa46950baj00tjkatu0022d200u000gwg01hc00u0.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" /&gt;
+&lt;p&gt;　　同时，游戏的美术风格也很不错，充满重工金属味，仪器和炮弹的质感上乘，我尤其喜欢看机械装置将一个个白色的火药桶装入炮膛。你如果看过《环太平洋》，应该会对里面重型机甲移动时，关节处的各种液压和机械细节印象深刻，这游戏的操控过程，就充满这种细节。&lt;/p&gt;
+&lt;img src="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0811%2F98bf21b1j00tjkatv001kd200u000gwg01hc00u0.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" alt="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0811%2F98bf21b1j00tjkatv001kd200u000gwg01hc00u0.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" /&gt;
+&lt;p&gt;　　总之，游戏方方面面都能给你上乘的操控反馈，比如你会发现碉堡内吊着很多灯，我觉得这些灯应该不止是照明用的，它们会根据炮体的震动，乃至你操作时的一些行为摇晃，让光影也跟着一起晃动，增强整体打击感。制作组应该打磨了很久游戏的开炮手感。&lt;/p&gt;
+&lt;p&gt;　　控制一门数千吨的巨炮，还有什么比这更让人满足的呢。&lt;/p&gt;
+&lt;img src="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0811%2F0259ef54j00tjkatv001dd200u000gwg01hc00u0.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" alt="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0811%2F0259ef54j00tjkatv001dd200u000gwg01hc00u0.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" /&gt;
+&lt;p&gt;　　此外，游戏会循序渐进为你安排新内容，你可以陆续选择不同的炮弹，从反人类的白磷弹，到催泪弹和威力十足的高爆弹，应对不同的情况。同时，敌方也会出现反重炮的手段，而你检测开炮目标的方式也在改变，一开始只是单纯获取坐标，后来得依靠数位观测员的情报，结合起来推理出位置，乃至更复杂。&lt;/p&gt;
+&lt;img src="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0811%2F8af4b415j00tjkatv002kd200u000gwg01hc00u0.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" alt="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0811%2F8af4b415j00tjkatv002kd200u000gwg01hc00u0.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" /&gt;
+&lt;p&gt;　　到后期，开炮的很多环节都会出毛病，从机械本身到指挥体系，你也得想办法处理。&lt;/p&gt;
+&lt;img src="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0811%2Fbe1a942dj00tjkatv0018d200u000gwg01hc00u0.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" alt="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0811%2Fbe1a942dj00tjkatv0018d200u000gwg01hc00u0.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" /&gt;
+&lt;p&gt;　　当然，我觉得游戏最有意思的地方，还是它的氛围营造和剧情。这游戏是有剧情的，虽然你只能依靠电报，和开炮后获得的报纸来侧面了解到底发生了什么，但这反而给了人一种与世隔绝的氛围：你的世界就是巨炮，但这门巨炮却能影响世界。&lt;/p&gt;
+&lt;img src="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0811%2Fca5c6bbbj00tjkatw001id200u000gwg01z40141.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" alt="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0811%2Fca5c6bbbj00tjkatw001id200u000gwg01z40141.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" /&gt;
+&lt;p&gt;　　游戏设定在一个架空世界，大致等于西班牙内战被提前了十多年，而共和国派和国民军正在内战，你则为维护君主主义的国王军战斗。&lt;/p&gt;
+&lt;img src="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0811%2F8b00ce61j00tjkatw0030d200u000gwg01hc00u0.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" alt="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0811%2F8b00ce61j00tjkatw0030d200u000gwg01hc00u0.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" /&gt;
+&lt;p&gt;　　西班牙内战，实际上是一场非常出名，影响深远的战争。它是在1936年到1939年，导致西班牙内部分裂的冲突，一方是支持独裁统治和法西斯主义的国民军，另一方则是拥护共和制和共产主义的共和国派。&lt;/p&gt;
+&lt;p&gt;　　整个欧洲文艺圈处处都是西班牙内战的影子，比如毕加索最著名的《格尔尼卡》，画的就是西班牙内战。同时达利那幅同样很著名的《内战的预感》，也是影射西班牙内战，搞笑的是，这画其实原名叫《豆角和菜豆》，后来被达利改名了。&lt;/p&gt;
+&lt;img src="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0811%2Fe98bd5c8j00tjkatw002ad200u000ddg00xc00eu.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" alt="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0811%2Fe98bd5c8j00tjkatw002ad200u000ddg00xc00eu.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" /&gt;
+&lt;p&gt;　　格尔尼卡&lt;/p&gt;
+&lt;img src="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0811%2F289e9ae9j00tjkatw0049d200u000tzg014u014s.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" alt="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0811%2F289e9ae9j00tjkatw0049d200u000tzg014u014s.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" /&gt;
+&lt;p&gt;　　内战的预感&lt;/p&gt;
+&lt;p&gt;　　世界上最著名的战地记者罗伯特·卡帕，拍的最著名的照片，就是一名中弹的共和派士兵。只是这照片的摆拍争议很大，基本已经被确认为根本不是在战场上拍的了。&lt;/p&gt;
+&lt;img src="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0811%2F7a6dd884j00tjkatw000jd200ah007cg00ah007c.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" alt="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0811%2F7a6dd884j00tjkatw000jd200ah007cg00ah007c.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" /&gt;
+&lt;p&gt;　　《倒下的士兵》&lt;/p&gt;
+&lt;p&gt;　　现在的电竞圈，总喜欢用“国际纵队”这个词，而它就是源自西班牙内战的。当时苏联为了支援共和国派对抗法西斯，向西班牙派兵，同时世界各地大量的左翼人士自愿成立军队，以国际纵队的名义同弗朗西斯科将军，以及德国、意大利的纳粹战斗。&lt;/p&gt;
+&lt;p&gt;　　当时中国也有参与国际纵队的战士，一些人认为这是现代战争史上最悲壮光荣的战斗之一。因为共和国派虽然有很多支援者，但最后纳粹却胜利了，导致弗朗西斯科对西班牙进行了长久的独裁统治。后来西班牙因此陷入长期的衰退和恐怖时代，只是在后期又迎来了高速发展，所以让弗朗西斯科成了个评价复杂的人。&lt;/p&gt;
+&lt;img src="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0811%2Fa64d3cf4j00tjkatx00e5d200m800cfg00m800cf.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" alt="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0811%2Fa64d3cf4j00tjkatx00e5d200m800cfg00m800cf.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" /&gt;
+&lt;p&gt;　　而在这个游戏里，你扮演的差不多就等于弗朗西斯科手下的士兵（虽然实际是架空的），所以你要干的事，绝对不是什么光荣的东西。&lt;/p&gt;
+&lt;p&gt;　　在游戏第一关，你要轰炸一个“敌方目标”，可炮打出去后，你才发现这其实是自己家的医院。而第二天的报纸竟把这出惨剧，报道成了敌方的恐袭。你的上司炸掉一座医院，只为甩锅给敌人操控舆论——没有什么比这更弗朗西斯科了。&lt;/p&gt;
+&lt;img src="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0811%2F9cb9cc79j00tjkatx0026d200u000gwg01hc00u0.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" alt="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0811%2F9cb9cc79j00tjkatx0026d200u000gwg01hc00u0.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" /&gt;
+&lt;p&gt;　　所以，你会逐渐开始关注战况和剧情，战报和现实也会越来越对不上，命令愈发可疑。很多时候，你都需要自己做决策，判断该怎么做。所有的敌人、平民、我方建筑和敌方碉堡，都只是地图上的标识，而你要选择是否麻木应对所有的残忍。&lt;/p&gt;
+&lt;img src="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0811%2F0a0fe141j00tjkaty003nd200u000gwg01hc00u0.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" alt="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0811%2F0a0fe141j00tjkaty003nd200u000gwg01hc00u0.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" /&gt;
+&lt;p&gt;　　在游戏最后，你会得到前所未有的自由度，而你最后开的那一炮，则会导向不同结局。它就像在漫长思考后，最后让你做下的那个关键决策，像一面镜子一样照出你对整场战争的态度。&lt;/p&gt;
+&lt;img src="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0811%2F4f60fbb1j00tjkaty0039d200u000gwg01z40141.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" alt="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0811%2F4f60fbb1j00tjkaty0039d200u000gwg01z40141.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" /&gt;
+&lt;p&gt;　　总而言之，《铁巢重炮》是一个非常特别，质量很高，而且充满对战争黑色幽默讽刺的独立佳作。但就像之前说的，因为它是一个模拟游戏，所以无法避免会让人后期产生上班的感觉，虽然有些人就是吃这一套。&lt;/p&gt;
+&lt;p&gt;　　对了，顺带一提，游戏里还有猫、咖啡机和唱片收集，因为这毕竟不是个压抑的游戏。单纯作为游戏来说，它其实也是很有意思的。&lt;/p&gt;
+&lt;img src="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0811%2Fbe091237j00tjkaty0029d200u000irg01z4018g.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" alt="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0811%2Fbe091237j00tjkaty0029d200u000irg01z4018g.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" /&gt;</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="inlineStr"/>
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0811%2F6fb7654aj00tjlojb00f6d000k000b9p.jpg&amp;thumbnail=660x2147483647&amp;quality=80&amp;type=jpg</t>
+        </is>
+      </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>虎牙26Q2业绩会实录：游戏相关服务持续扩张 游戏发行迈入独家发行新阶段</t>
+          <t>独立游戏《Big Walk》发售6天销量破百万，开发商致谢玩家</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
@@ -1666,35 +2557,20 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>北京时间2026年8月11日下午，虎牙公司（NYSE:HUYA）公布了2026年第二季度财报。财报显示，该季度，虎牙公司总收入同比增长11.0%至17.4亿元，连续六个季度同比增长。其中，游戏相关服务、广告及其他收入同比增长54.1%至6.4亿元，占总收入比例提高至36.7%。同时，虎牙公司董事会批准将“2026年股票回购计划”授权额度由5000万美元提升至1亿美元。
-财报发布后，虎牙公司CEO黄俊洪、CFO雷鹏等公司高管出席了随后举行的财报电话会议，解读财报要点。
-以下为电话会上黄俊洪演讲全文：
-大家好，感谢大家参加今天的财报会。
-首先分享一下本季度的整体业绩。第二季度，公司总收入同比增长11%至17.4亿元，再次实现稳健增长。其中，游戏相关服务、广告与其他收入延续强劲增长势头，同比增长54%至6.4亿元，占总收入约37%。这一增长的背后，是虎牙沿着游戏产业链的长期布局，正在稳步兑现为可持续的增长动能。
-过去三年以来，虎牙沿游戏产业价值链不断向上延伸，从游戏联运、道具销售到广告营销，再到现在的游戏发行，逐步在产业链各环节建立起差异化能力，并日益获得合作伙伴和市场的认可和验证。游戏发行业务的推进，是这一进程中又一重要的里程碑。它推动虎牙从游戏产业链的渠道角色进一步向外延伸，使我们能够更加深入地参与游戏产品的全生命周期运营。我们坚持以内容为核心、而非依赖付费买量的差异化发行策略。依托平台在内容创作、主播生态和用户社区方面的深厚积累，引导优质UGC内容产出，形成覆盖抖音、小红书、视频号等外部平台的全域声量。这一差异化发行模式有助于我们更高效地获取用户，同时降低对传统付费流量渠道的依赖。
-《鹅鸭杀》的市场表现，印证了虎牙这套内容营销打法的有效性，也为后续新游戏的发行沉淀了方法论和运营经验。
-新游储备方面，我们接下来将独家发行两款游戏：经典武侠MMORPG《剑侠情缘：重逢》和3D消除手游《消消奇遇》。从联合发行迈向独家发行，标志着虎牙发行战略再上新台阶。
-《剑侠情缘：重逢》由西山居经典IP授权，承载“剑侠情缘”系列二十余年的武侠积淀，由《剑侠世界》端游原班核心团队打造，支持APP、PC客户端及小程序三端互通。目前游戏已完成首轮测试并收获积极用户反馈，我们希望凭借虎牙在内容营销和主播生态上的优势，在原汁原味传承经典武侠体验的同时，将其带给更广泛的用户群体，延续其多年来深受玩家喜爱的魅力。
-《消消奇遇》是正版Zanmang Loopy IP的3D消除类手游，是虎牙在消除品类上的重磅落子。该游戏与虎牙以内容为驱动的发行模式高度契合，有望在直播和短视频平台激发大量用户创作内容、社交互动和自然流量。
-自研产品上，我们很高兴看到首个自研游戏《这岛有幻兽》于7月获得版号，这是一款以海岛和宠物收集为核心的轻度SLG游戏，也是虎牙建设内部游戏研发能力的又一重要进展。目前，我们正在积极准备游戏的后续测试，并期待随着研发推进分享更多进展。
-广告业务上，本季度我们继续深化以内容驱动的游戏整合营销服务，广告主覆盖面不断拓宽。值得一提的是，《炉石传说》已成为我们重要的新广告主。围绕炉石IP，我们联动头部主播打造了包括“大安庄园全球邀请赛”在内的多项赛事与内容合作，其中“大安庄园赛事”作为炉石酒馆战棋首个第三方全球性平台赛事，首次落地中国，赛事期间全网总曝光超2亿，赢得客户的高度认可。
-道具销售方面，收入保持同比三位数增长，《和平精英》、《PUBG Mobile》、《原神》、《暗区突围》等游戏道具驱动增长。以《和平精英》为例，我们持续开展生态投入，特别是通过PEL赛事解说吸引了大量观众关注和互动，进一步提升了游戏道具供给的吸引力，并推动相关销售持续增长。
-直播业务方面，户外娱乐品类本季度延续了良好的表现，公会与主播生态保持稳健。我们也在积极探索游戏主播与娱乐板块的联动，激活头部主播给平台的收入增量。进入下半年以来，我们已主动优化与主播的合作与签约成本，以进一步提升内容投入产出效率，推动直播生态更健康、可持续地发展。
-赛事内容上，本季度我们在虎牙平台提供了超过100项版权赛事和约20档自制赛事。其中，自办赛事进一步IP化、规模化，“CF宗师杯”联合穿越火线官方打造国际邀请赛，集结8支职业战队与4支海外劲旅同台竞技，并创新性地融合《功夫》电影IP，实现赛事与泛娱乐内容的深度联动；“DOTA2不朽杯S2”引爆全网热度，收获超25亿曝光量；7月“三角洲行动主播巅峰赛”、“和平精英猛男超星杯”先后开赛，覆盖核心射击品类，形成自制赛事矩阵，有效提升了平台在核心玩家中的内容吸引力。此外，我们参与承办了《无畏契约》全国大赛，承办能力进一步得到游戏厂商认可。
-产品与AI领域，我们不断以AI技术反哺游戏内容生态，推动产品和平台体验迭代升级。围绕《三角洲行动》《英雄联盟》《云顶之弈》等热门游戏品类，我们已上线地图导航、战斗辅助等系列AI游戏工具，用户使用粘性和留存表现良好，在虎牙平台的活跃度、观看时长和用户价值上均呈现出明显的正向贡献，进一步印证了AI游戏工具能够持续反哺直播生态，并创造长期价值的产品逻辑。
-7月，我们发布了自研的实时多模态数字人模型VAM 1.0，可快速生成兼具自然语音、歌唱与肢体表达能力的AI数字人，实现较高拟真度的实时互动。我们认为VAM有望从根本上优化内容生产的成本结构，突破传统直播对真人主播数量和时间的限制，以更高效率实现内容供给的规模化扩张。随着部署规模不断扩大，其规模效应将持续释放，内容生产的边际成本也将进一步下降。
-回顾本季度，虎牙围绕长期战略持续稳步推进，并在游戏发行、自主研发、AI创新及游戏相关服务等领域进一步夯实能力，不断拓展在游戏产业价值链中的布局与参与深度。
-展望未来，我们将继续坚持内容驱动的发展策略，深化与游戏产业生态伙伴的合作，并持续投入建设支撑下一阶段增长的核心能力。我们相信，这些努力将进一步巩固虎牙的竞争优势，为股东创造长期、可持续的价值。谢谢大家。
-（电话会财务数据阐述详见业绩公告）
-推广返回搜狐，查看更多</t>
+          <t>&lt;p&gt;　　据GameDeveloper报道，《Untitled Goose Game》开发商House House推出的多人步行模拟游戏《Big Walk》在发售不到一周内销量突破100万份。 发行商Panic在Bluesky上确认了这一消息，并晒出了一份完整的线上工作人员名单，向参与该项目的每一位成员致谢。 《Big Walk》于8月4日正式登陆PC、Nintendo Switch 2和PlayStation 5平台。同时，该作也被纳入PlayStation Plus当月的免费游戏阵容，供订阅用户领取。 Panic在声明中写道：“在短短六天内，已有超过100万人购买了《Big Walk》——这款以聊天和散步为核心的合作冒险游戏。我们非常感谢有这么多人愿意花时间游玩我们的作品，也深深感激大家的粉丝创作、直播、故事分享和精彩瞬间。感谢你们游玩。”&lt;/p&gt;
+&lt;img src="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0811%2F6fb7654aj00tjlojb00f6d000k000b9p.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" alt="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0811%2F6fb7654aj00tjlojb00f6d000k000b9p.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" /&gt;</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="inlineStr"/>
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0812%2Fbc19b526j00tjmuay000jd000cs005zg.jpg&amp;thumbnail=660x2147483647&amp;quality=80&amp;type=jpg</t>
+        </is>
+      </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>腾讯Q2游戏收入双位数增长《三角洲行动》《无畏契约》平均日活跃用户齐创新高</t>
+          <t>《差不多起飞》正式推出 好评宇宙飞船定制冒险</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
@@ -1704,20 +2580,25 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>央广网北京8月12日消息（记者 陈越）8月12日，腾讯控股发布2026年第二季度财报。网络游戏业务总收入659亿元，同比增长11%，整体重回双位数增长态势。本土市场收入473亿元，同比增长17%。增长动力主要来自四款核心产品：《三角洲行动》、《无畏契约》、《无畏契约：能源行动》及《洛克王国：世界》。其中本土长青游戏《三角洲行动》与《无畏契约》平均日活跃用户均在本季度创下历史新高。腾讯持续在射击品类与竞技赛道上保持领先位置。《洛克王国：世界》在今年中国市场发布的所有新手游中，按平均日活跃账户数和流水计算均排名第一。
-国际市场收入186亿元，按固定汇率计算同比增长4%，主要受《鸣潮》《VALORANT》驱动; 同时，腾讯旗下Miniclip于国际市场获得突破性成功，产品《Arrows - Puzzle Escape》在2026年Q2成为全球下载量最高的手游。返回搜狐，查看更多</t>
+          <t>&lt;p&gt;　　Approximately Games工作室制作并发行，一款宇宙飞船定制冒险新游《差不多起飞》登陆Steam正式推出，现已收获特别好评。&lt;/p&gt;
+&lt;img src="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0812%2Fbc19b526j00tjmuay000jd000cs005zg.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" alt="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0812%2Fbc19b526j00tjmuay000jd000cs005zg.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" /&gt;
+&lt;p&gt;　　《差不多起飞》：Steam地址&lt;/p&gt;
+&lt;p&gt;　　《差不多起飞》是一款横跨行星间的第一人称视点探索游戏。支持单人或最多4人的多人游戏。玩家们将打造属于自己风格的模块化宇宙飞船，探索行星并挑战任务。然后为了前往下一个行星，下一个要建造的更大更全面宇宙飞船。完成各种各样的任务是本作品的目标。&lt;/p&gt;
+&lt;img src="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0812%2F590a3356j00tjmuaz0022d000u000gwg.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" alt="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0812%2F590a3356j00tjmuaz0022d000u000gwg.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" /&gt;
+&lt;img src="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0812%2F8edbf945j00tjmuaz0020d000u000gwg.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" alt="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0812%2F8edbf945j00tjmuaz0020d000u000gwg.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" /&gt;
+&lt;img src="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0812%2F93ef2266j00tjmub00034d0016o00o0g.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" alt="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0812%2F93ef2266j00tjmub00034d0016o00o0g.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" /&gt;</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
+          <t>https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0811%2Fe5d1b901j00tjkz8q00ydd002yo01o0p.jpg&amp;thumbnail=660x2147483647&amp;quality=80&amp;type=jpg</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>《无人深空》开发商新作，开发进度超预期了</t>
+          <t>《大步行》发售仅6天销量破百万：一款“对话走路游戏”凭什么爆火？</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
@@ -1727,10 +2608,8 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>IT之家 8 月 10 日消息，据游戏媒体 Eurogamer 今天报道，由 Hello Games 开发的《无人深空》发售至今已有十年，该工作室负责人 Sean Murray 最近透露，他们的新作《无火之光》已经在路上。
-谈到《无火之光》时，Sean Murray 表示：“我已经吸取了非常重要的教训，就是不要提前讨论一些事情。我们现在做出的东西，已经远远超过了本应公布的阶段。我们会在某个时候让玩家看到更多内容。”
-不过这名负责人并没有给出更多信息，只是表示“肯定会公开”。
-IT之家了解到，《无火之光》最初公布于 2023 年，是一款主打多人合作的开放世界冒险游戏，以幻想星球为背景。虽然 Hello Games 曾在 2024 年提过这款游戏，但此后工作室一直保持低调。</t>
+          <t>&lt;p&gt;　　由《Untitled Goose Game》开发商House House打造、Panic发行的合作冒险游戏《大步行（Big Walk）》自8月4日正式发售后，仅用6天时间便突破了100万份销量，成为了这个夏天独立游戏领域最亮眼的一匹黑马。 Panic官方表示：“在发售六天内，《大步行》这款以对话和行走为主题的合作冒险游戏就吸引了超过一百万玩家购买。我们非常感谢大家抽出时间来体验这款游戏。我们也由衷感谢你们的单人模式、直播、视频以及所有陪伴我们度过的美好时光。感谢你们的游玩。” 这款游戏目前登陆了PS5、Switch 2以及PC（Steam和Epic），同时也在发售首日加入了PS+每月游戏阵容。在Steam上，本作获得了“特别好评”的评价，玩家的热情可见一斑。 《Big Walk》是一款围绕团队合作与幽默感的合作多人冒险游戏。玩家将结伴穿越一个充满趣味、谜题与发现的广阔开放世界。你们需要一起辨别方向，利用各种工具和玩具保持联系；当你突然变得“口齿伶俐”时，还想出新的沟通暗语。 除了冒险，还有大量时间可以用在闲逛上。一起看看风景，或者走走停停的小径，甚至踢进海里。一起共度时光，是这部作品最核心的乐趣。 游戏特色方面，《Big Walk》采用了独特的空间音频系统，声音会随距离渐渐消散，走散后通过传呼机和对讲机机制传递消息，让沟通本身成为玩法的一部分。玩家可以按照自己的节奏在开放世界中探索，当无法开口说话时，只需要制造噪音、点头或用各种动作来交流，甚至干脆乱来一通。 工具与玩具也是本作的一大乐趣所在：对讲机、激光笔、扬声器、信号弹、白板、锁，甚至一个巨大的黄色头颅——这些五花八门的道具将陪伴玩家完成整个旅程。 更灵活的是，游戏最少2人即可开始游玩，最多支持12人合作，人数越多场面就越混乱。同时，《Big Walk》支持跨平台联机，你可以与好友——无论对方在哪个平台上——随时随地开始游戏。 作为一款“纯走路聊天”的游戏，《大步行》的成功证明了：只要把对话和行走做到极致，也能打动数百万玩家。如果你还没试过，不妨拉上朋友，一起走进这个混乱又治愈的开放世界。&lt;/p&gt;
+&lt;img src="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0811%2Fe5d1b901j00tjkz8q00ydd002yo01o0p.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" alt="https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0811%2Fe5d1b901j00tjkz8q00ydd002yo01o0p.jpg&amp;amp;thumbnail=660x2147483647&amp;amp;quality=80&amp;amp;type=jpg" /&gt;</t>
         </is>
       </c>
     </row>
@@ -1738,7 +2617,7 @@
       <c r="A40" s="2" t="inlineStr"/>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>TMT热度回升，游戏ETF国泰（516010）逆市收涨近2%</t>
+          <t>腾讯2026年Q2财报发布：游戏业务双位数增长11% 海外休闲赛道取得突破性成功</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
@@ -1748,26 +2627,30 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>每经编辑：肖芮冬
-8月10日，A股市场主要指数表现分化，截至收盘，上证指数上涨0.67%，而深证成指微涨0.04%，创业板指则收跌0.73%。在市场震荡调整的格局中，游戏板块展现出较强韧性，相关ETF产品受到市场关注。其中，游戏ETF国泰（516010）表现亮眼，逆市收涨1.96%，全天成交额达1.12亿元。
-尽管近期市场波动加剧，但资金仍在积极寻找结构性机会。数据显示，资金对游戏板块的布局意愿不减，游戏ETF国泰（516010）近30日累计获得3.50亿元的资金净流入，推动其最新基金规模达到27.04亿元，显示出投资者对该赛道后市表现的信心。
-从行业层面看，游戏板块作为TMT领域的重要组成部分，其市场热度正逐步回升。中信建投在其最新报告中指出，成长与小盘风格强势反弹，TMT交易热度回升至48%高位，市场偏好前期回调较多的科技成长方向。这一观点为游戏板块的强势表现提供了注脚。在市场风格轮动中，具备成长属性且前期经历调整的科技方向，正重新获得资金青睐。
-与此同时，当前游戏板块的估值水平也为其提供了较高的安全边际和投资性价比。最新数据显示，游戏ETF国泰（516010）所跟踪的中证动漫游戏指数当前市盈率（PE）为25.17倍，处于近一年来20%的历史分位点，估值相对偏低。在政策面持续释放稳市场信号的背景下，中金公司认为，在稳市机制作用下A股企稳修复，A股修复行情有望延续。在此宏观背景下，估值处于低位且具备成长弹性的游戏板块，有望在市场修复行情中获得更好的表现。
-作为投资者布局动漫游戏产业的便捷工具，游戏ETF国泰（516010）紧密跟踪中证动漫游戏指数，该指数选取主营业务涉及动画、漫画、游戏等相关细分娱乐产业的上市公司作为样本，旨在反映动漫游戏产业的整体表现，能够较好地分享产业发展带来的红利。
-风险提示：提及个股仅用于行业事件分析，不构成任何个股推荐或投资建议。指数等短期涨跌仅供参考，不代表其未来表现，亦不构成对基金业绩的承诺或保证。观点可能随市场环境变化而调整，不构成投资建议或承诺。提及基金风险收益特征各不相同，敬请投资者仔细阅读基金法律文件，充分了解产品要素、风险等级及收益分配原则，选择与自身风险承受能力匹配的产品，谨慎投资。涉及基金费率请查阅法律文件。
-每日经济新闻</t>
+          <t>&lt;p&gt;　　央广网北京8月12日消息（记者 陈越）8月12日，腾讯控股发布2026年第二季度财报。网络游戏业务总收入659亿元，同比增长11%，整体重回双位数增长态势。本土市场收入473亿元，同比增长17%。增长动力主要来自四款核心产品：《三角洲行动》《无畏契约》《无畏契约：源能行动》及《洛克王国：世界》。其中，本土长青游戏《三角洲行动》与《无畏契约》平均日活跃账户数均在本季度创下历史新高。《洛克王国：世界》在今年中国市场发布的所有新手游中，按平均日活跃账户数和流水计算均排名第一。&lt;/p&gt;
+&lt;p&gt;　　国际市场游戏收入，固定汇率下同比增长4%至人民币186亿元，主要受《鸣潮》《VALORANT》驱动；同时，腾讯旗下Miniclip于国际市场获得突破性成功，掀起箭头解谜热潮的休闲游戏《Arrows – Puzzle Escape》在2026年Q2成为全球下载量最高的手游，有望助力腾讯国际游戏业务打开新的市场增量。&lt;/p&gt;
+&lt;p&gt;　　本土游戏业务双位数增长17% 海外休闲赛道取得突破性成功&lt;/p&gt;
+&lt;p&gt;　　腾讯Q2本土游戏业务的双位数增长主要得益于《王者荣耀》《三角洲行动》《无畏契约》《无畏契约：源能行动》《洛克王国：世界》等核心产品的业绩表现。不同生命周期的产品共同贡献增量，进一步夯实了腾讯游戏业务的基本盘，在射击品类与竞技赛道上，腾讯游戏持续保持领先位置。&lt;/p&gt;
+&lt;p&gt;　　其中，第二季度，《王者荣耀》通过优化排位对局体验，上线小屋农场休闲玩法、英雄命格系统等新内容，并联动电影《哪吒2》等IP，借力五五开黑节等节点强化玩家活跃、拓展泛用户触达。《三角洲行动》通过S9、S10连续版本迭代，以新干员、新地图、新玩法带来新鲜体验，先后联动古墓丽影、肯德基、《彩虹六号：围攻》等多圈层IP，宝藏月开启与景德镇的联动等，推动其平均日活跃账户数创新高。《无畏契约》与《无畏契约：源能行动》围绕竞技体验与泛用户拓展持续完善产品生态、拓展圈层影响力。&lt;/p&gt;
+&lt;p&gt;　　新品方面，《洛克王国：世界》展现出持续运营的增长潜力。游戏围绕S2赛季更新，凡羽掠影活动及肯德基跨界联动，保持用户活跃与内容热度，并逐步形成稳定的商业化节奏，进一步验证了经典IP焕新后持续吸引用户、提升商业价值的能力，也为其成长为长青奠定了基础。7月上线的《失控进化》上线前全网预约量突破4000万，上线后迅速登顶iOS免费榜总榜，虽不计入二季度收入，但作为下半年新品储备，与现有长青产品及成熟产品形成梯队，为后续业务增长提供新的产品支撑。&lt;/p&gt;
+&lt;p&gt;　　国际市场方面，固定汇率下同比增长4%至人民币186亿元，主要受《鸣潮》《VALORANT》驱动； 同时，腾讯旗下Miniclip于国际市场获得突破性成功，掀起箭头解谜热潮的休闲游戏《Arrows – Puzzle Escape》在2026年Q2成为全球下载量最高的手游，并带来强劲的应用内广告收入。&lt;/p&gt;
+&lt;p&gt;　　腾讯于2015年完成对欧洲休闲游戏厂商Miniclip的收购，并通过国际游戏业务品牌Level Infinite助力多款产品实现跨区域持续增长与生态扩展，其海外休闲版图在十年间从单一的体育竞技，扩展到三消、益智、跑酷、塔防、模拟经营乃至主机平台，推动腾讯在国际游戏业务侧打开新的增量。&lt;/p&gt;
+&lt;p&gt;　　游戏AI持续提升玩家体验 成腾讯游戏业务驱动重要力量&lt;/p&gt;
+&lt;p&gt;　　当前，AI已经成为推动腾讯游戏业务增长的重要力量，并已深入覆盖玩家体验、研发生产、运营服务等在内的全链路环节。比如，《三角洲行动》利用Agent实现运营效能提升，并通过Hy3D能力进行场景端手一体化生产管线的提效。&lt;/p&gt;
+&lt;p&gt;　　同时，AI与玩法的融合探索持续推进，《和平精英》AI NPC 玩法累计体验用户数增加至1.67亿、最高日活跃用户数达 1770 万；新品《洛克王国：世界》也积极探索用游戏AI优化玩家体验，推出面向复杂玩法决策的游戏原生Coach Agent“斯嘉丽”，区别于通用大模型“百科全书式”的回答，“斯嘉丽”能够理解玩家的背包、阵容、对局环境，为玩家生成个性化、可执行的阵容与打法建议。自上线以来，“斯嘉丽”有效促进PVP破冰及活跃，期间PVP激活率增幅20%，破冰用户使用功能后胜率也获得实质改善，提升了玩法体验。&lt;/p&gt;
+&lt;p&gt;　　从长青游戏的持续发新芽，到休闲赛道的全球突破，再到游戏AI对玩家体验的深度重塑，腾讯游戏正稳步迈向更具确定性与想象力的增长空间。返回搜狐，查看更多&lt;/p&gt;</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
+          <t>https://q8.itc.cn/images01/20260811/f9d573175c5c4e40879495ba4f7f9927.jpeg</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>官宣已8年：微软XBOX夏尔马试玩《上古卷轴6》游戏</t>
+          <t>史玉柱实控平台套现5亿！老牌游戏巨头能扛住吗？</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
@@ -1777,23 +2660,44 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>IT之家 8 月 12 日消息，微软 XBOX 首席执行官阿莎 · 夏尔马（Asha Sharma）今天（8 月 12 日）在 X 平台发布推文，表示其试玩了《上古卷轴 6》游戏，评价称游戏叙事宏大，气势磅礴，令人叹为观止，游戏剧情更是精彩绝伦。
-游戏媒体 gamesradar 今天发布博文，指出本次“现场演示”具备重要意义，很可能是 Bethesda 开发团队（可能包括首席执行官 Todd Howard）向夏尔马以及其他 XBOX 高管展示游戏最新动态，但现阶段不清楚演示版本的开发进度。
-微软 XBOX 首席创意官马特 · 布蒂（Matt Booty）今年 6 月向粉丝表示，《上古卷轴 6》自官宣（2018 年 E3 游戏展上公布）以来已过去 8 年时间，目前游戏开发进展顺利。
-布蒂此前表示：“我目前可以透露的信息是我已经去过 Bethesda，和 Todd 坐在一起，也看过《上古卷轴 6》的试玩，它看起来棒极了，而且进展顺利”。
-IT之家查询社交平台，消息称《上古卷轴 6》游戏副标题可能为《哨兵》（Sentinel）：</t>
+          <t>&lt;p&gt;　　若爆款游戏后续热度出现下滑，巨人网络未来业绩或将面临较大考验&lt;/p&gt;
+&lt;img src="https://q8.itc.cn/images01/20260811/f9d573175c5c4e40879495ba4f7f9927.jpeg" alt="https://q8.itc.cn/images01/20260811/f9d573175c5c4e40879495ba4f7f9927.jpeg" /&gt;
+&lt;p&gt;　　投资时间网、标点财经研究员 董琳&lt;/p&gt;
+&lt;p&gt;　　日前，巨人网络集团股份有限公司（下称巨人网络，002558.SZ）披露股东减持进展公告，公司第二大股东上海腾澎投资合伙企业（有限合伙）（下称腾澎投资）在2026年7月16日至8月7日期间，通过集中竞价方式合计减持公司股份约1893.56万股，占公司总股本比例约1%，减持计划中集中竞价部分已减持完成。&lt;/p&gt;
+&lt;p&gt;　　从股权关系来看，腾澎投资与公司控股股东巨人投资为一致行动人。工商信息显示，腾澎投资背后股东包含巨人投资、巨人投资集团等主体，实际控制人为巨人网络董事长史玉柱。&lt;/p&gt;
+&lt;p&gt;　　2026年5月16日，巨人网络披露公告，因归还银行贷款，腾澎投资拟通过集中竞价、大宗交易两种方式合计减持公司股份不超过5680.70万股，对应总股本比例约2.99%。若以8月7日收盘价29.34元/股（不复权，下同）测算，腾澎投资已完成减持金额超5亿元，后续仍存在约11亿元规模的减持空间。&lt;/p&gt;
+&lt;p&gt;　　从二级市场表现来看，虽然半年报预告利润实现翻倍增长，但巨人网络股价并未随之同步走高。&lt;/p&gt;
+&lt;p&gt;　　2026年年初，因公司加速落地游戏垂类AI大模型，AI NPC、美术自动生成进入规模化应用，市场给予“传统游戏+AI降本增效”的估值溢价。1月20日，巨人网络股价触及年内高点53.35元/股，市值一度突破千亿元大关。&lt;/p&gt;
+&lt;p&gt;　　此后，受监管警示函、股东减持预期、市场情绪走弱等多重利空因素影响，公司股价持续震荡回调，阶段低位一度跌破24元/股。截至2026年8月11日收盘，巨人网络报28.7元/股，年内累计跌幅为33.22%，最新市值回落至545亿元。&lt;/p&gt;
+&lt;p&gt;　　2026年以来巨人网络股价走势情况（元/股）&lt;/p&gt;
+&lt;img src="https://q1.itc.cn/images01/20260811/6d9ec31468dc42c29d67978cdfbc6164.png" alt="https://q1.itc.cn/images01/20260811/6d9ec31468dc42c29d67978cdfbc6164.png" /&gt;
+&lt;p&gt;　　数据来源：Wind&lt;/p&gt;
+&lt;p&gt;　　从业绩维度来看，2025年，巨人网络实现营业收入50.47亿元，同比增长72.69%；归母净利润为17.55亿元，同比增长23.13%，营收与净利润双双创下上市以来新高。而公司近五年经营状况实现从低谷向高点逆转，《超自然行动组》功不可没。该游戏于2025年1月上线，以“中式微恐+搜打撤”的差异化玩法，迅速成为手游市场现象级爆款。截至2026年一季度末，《超自然行动组》的累计注册用户已突破2亿，DAU（日活跃用户数）突破千万。&lt;/p&gt;
+&lt;p&gt;　　在本轮股东减持实施前，巨人网络披露了半年度业绩预告，公司预计2026年上半年归母净利润为20亿元至22亿元，同比增长157.38%至183.12%；预计扣非净利润为22亿元至24亿元，同比增长172.74%至197.54%。&lt;/p&gt;
+&lt;p&gt;　　招商证券研报表示，巨人网络上半年营业收入及利润均实现同比大幅增长，核心驱动力仍为《超自然行动组》持续贡献较高水平收入。该游戏在春节期间单日、单月流水均创历史新高，进入二季度后仍保持稳定运营，并通过“摸金节”等活动持续补充内容供给。&lt;/p&gt;
+&lt;p&gt;　　海外市场方面，巨人网络披露，《超自然行动组》海外版《TombBusters》已于5月27日正式登陆日本、韩国、美国市场，同步覆盖iOS、Android及PC三大平台，首日冲上iOS游戏免费榜日本第3名、韩国第7名，全球化布局取得良好开局。&lt;/p&gt;
+&lt;p&gt;　　2021年至2025年巨人网络归母净利润及同比情况（亿元、%）&lt;/p&gt;
+&lt;img src="https://q1.itc.cn/images01/20260811/48bac88cdbb846b281ba7a39dffcd81f.png" alt="https://q1.itc.cn/images01/20260811/48bac88cdbb846b281ba7a39dffcd81f.png" /&gt;
+&lt;p&gt;　　数据来源：Wind&lt;/p&gt;
+&lt;p&gt;　　为公司贡献主要业绩增量的同时，《超自然行动组》也让巨人网络的业务结构承受一定压力。&lt;/p&gt;
+&lt;p&gt;　　在这款产品走红之前，巨人网络留给市场的深刻印象是《征途》，这款2006年上线的作品开创了国内网游免费付费模式，长期作为公司的营收基本盘。而上一次公司产出具备全民影响力的爆款，还要追溯至2015年推出的《球球大作战》。&lt;/p&gt;
+&lt;p&gt;　　从现有产品管线来看，巨人网络暂未培育出体量与《超自然行动组》相当的第二款核心产品，随着赛道竞争日趋白热化，若该游戏后续热度出现下滑，公司未来业绩或将面临较大考验。&lt;/p&gt;
+&lt;p&gt;　　从市场布局来看，该款游戏产品收入主要来自国内市场，其海外版本虽已在部分地区上线，但现阶段收入贡献仍然有限，海外业务整体占比不高。相较于行业内头部企业成熟的出海布局，公司在海外市场拓展方面仍有提升空间。&lt;/p&gt;
+&lt;p&gt;　　投资时间网、标点财经研究员注意到，面对单品依赖的现实约束，巨人网络也在通过AI产业投资，尝试打开技术层面的增长空间。6月，公司参与光轮智能新一轮融资，布局物理AI的数据、仿真及评测基础设施；同月参投硅基流动B轮融资，将版图拓展到大模型推理、异构算力调度领域；7月，公司又参投了AI 3D大模型与通用世界模型企业VAST，补足游戏3D资产快速生成的技术储备。&lt;/p&gt;
+&lt;p&gt;　　当爆款红利逐步褪去，面对腾讯（0700.HK）、网易（9999.HK）等头部玩家持续加码AI游戏研发，巨人网络能否借助外部AI布局补齐管线短板、摆脱对单一爆款的依赖，把阶段性业绩高光转化为长期稳定的经营能力？&lt;/p&gt;
+&lt;p&gt;　　投时关键词：巨人网络（002558.SZ）返回搜狐，查看更多&lt;/p&gt;</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
+          <t>https://q9.itc.cn/q_70/images03/20260812/6d3089662d89427aba099b61cab19cb6.jpeg</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>上海烛龙单机新作《古剑》公布战斗实机</t>
+          <t>上场即燃！二次元养成新游《篮球少女：飞越巅峰》抢先下载今日开启，教练们请就位！</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
@@ -1803,21 +2707,41 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>IT之家 6 月 6 日消息，上海烛龙单机新作《古剑》今日在夏日游戏节公布 3 分钟战斗实机，线下试玩会将于 2026 年 7 月 18 日-19 日在上海举办，现场将提供多个首领对决与独立关卡片段试玩，Steam 商店页面现已同步上线。
-IT之家附游戏介绍：
-《古剑》是古剑奇谭系列单机新作。这是一款由上海烛龙工作室开发的动作角色扮演游戏。本作融合中国上古神话与志怪传说要素，基于虚幻引擎 5 开发，未来将以单机买断制形式登陆 PC 及主机平台。</t>
+          <t>&lt;p&gt;　　阿里巴巴灵犀互娱旗下游戏平台&lt;/p&gt;
+&lt;p&gt;　　提到篮球手游，大家脑子里第一时间蹦出来的是啥？&lt;/p&gt;
+&lt;p&gt;　　是那种得背战术、记跑位、练投篮时机，手残党进去就是被对手按在地上摩擦的硬核2K竞技游戏？还是经理人模拟器，全程看数据跑表，跟看财报似的，却感受不到竞技体育活力的模拟经营游戏。&lt;/p&gt;
+&lt;p&gt;　　不过，今天九酱给大家带来的则是一款画风完全不一样的二次元养成篮球游戏《篮球少女：飞越巅峰》。它有美少女、有羁绊、有热血番式的成长剧情，但偏偏不搞硬核操作那一套。&lt;/p&gt;
+&lt;img src="https://q9.itc.cn/q_70/images03/20260812/6d3089662d89427aba099b61cab19cb6.jpeg" alt="https://q9.itc.cn/q_70/images03/20260812/6d3089662d89427aba099b61cab19cb6.jpeg" /&gt;
+&lt;p&gt;　　《篮球少女：飞越巅峰》巅峰测试将于8月13日正式开启，九游APP现已开放抢先下载通道！&lt;/p&gt;
+&lt;p&gt;　　在这里，你将接手一支刚刚惨败的女子高中篮球队，带着一群天赋异禀的少女，从地区预选赛一路打进全国大赛。&lt;/p&gt;
+&lt;p&gt;　　拒绝宏大叙事 体验夏日汽水般的二次元画风&lt;/p&gt;
+&lt;p&gt;　　不知道从何时开始，市面上的许多二游，都以世界末日、种族存亡这种沉重的背景展开，玩久了，难免有点喘不过气。&lt;/p&gt;
+&lt;p&gt;　　《篮球少女：飞越巅峰》则完全回归了二游最初带给大家的感觉——没有宏大的宿命论，只有球场上少女们奔跑的身影和汗水，以及青春特有的明亮气息。&lt;/p&gt;
+&lt;img src="https://q5.itc.cn/q_70/images03/20260812/f3aa58730e9944deb4d3a4425e925ca1.jpeg" alt="https://q5.itc.cn/q_70/images03/20260812/f3aa58730e9944deb4d3a4425e925ca1.jpeg" /&gt;
+&lt;p&gt;　　队内的这群少女们性格迥异，都有着自己的成长故事。她们中有天赋异禀但不合群的王牌，有努力但天赋平平的替补，有嘴上说“无所谓”其实比谁都在意输赢的傲娇怪……你得搞清楚每个人的特点，安排合适的训练、搭配合理的阵容、激活她们的羁绊！&lt;/p&gt;
+&lt;p&gt;　　自由面板养成 每一次选择都是全新的剧本&lt;/p&gt;
+&lt;p&gt;　　如果说“二次元美少女+篮球”的题材混搭已经足够特别，那游戏在养成系统里引入的自由面板养成元素，则是一次更大胆的尝试。&lt;/p&gt;
+&lt;img src="https://q9.itc.cn/q_70/images03/20260812/32e98cd7dd1646baa251b12522922c49.jpeg" alt="https://q9.itc.cn/q_70/images03/20260812/32e98cd7dd1646baa251b12522922c49.jpeg" /&gt;
+&lt;p&gt;　　每场比赛开始前，你需要组队、配备训练器材。训练过程中会触发各种随机事件，需要你做出选择，不同的选择导向不同的成长路径。每一次育成都是一场全新的剧本，而不是机械重复的“点确定→等进度条”。&lt;/p&gt;
+&lt;p&gt;　　这大概就是“教练”这个身份最真实的体验——你永远不知道明天会遇到哪些突发状况。&lt;/p&gt;
+&lt;p&gt;　　策略比赛 率队登顶全国大赛&lt;/p&gt;
+&lt;p&gt;　　《篮球少女：飞越巅峰》采用自动演算机制，配合红、蓝、黄三色卡牌克制系统。进攻或防守时，根据提示打出对应颜色卡牌形成属性压制，就能获取战术优势。角色能量积满后还会释放专属大招卡，对关键回合产生决定性影响。&lt;/p&gt;
+&lt;img src="https://q2.itc.cn/q_70/images03/20260812/31314a9d3ec0483fa2867e079d3c21f5.jpeg" alt="https://q2.itc.cn/q_70/images03/20260812/31314a9d3ec0483fa2867e079d3c21f5.jpeg" /&gt;
+&lt;p&gt;　　编队需要严格遵循PG（控球后卫）、SG（得分后卫）、SF（小前锋）、PF（大前锋）、C（中锋） 的标准五人篮球架构。内线角色得确保弹跳属性达标才能抢到篮板，PG需要重点强化运控能力降低被抢断风险。前期先把位置补齐，后期再根据羁绊关系微调优化。&lt;/p&gt;
+&lt;img src="https://q8.itc.cn/q_70/images03/20260812/7a3bb3f27241422888955fc099b4cb19.jpeg" alt="https://q8.itc.cn/q_70/images03/20260812/7a3bb3f27241422888955fc099b4cb19.jpeg" /&gt;
+&lt;p&gt;　　说白了，玩家无需为了进球而一遍遍练习出手时机、不需要背战术板、研究球员的数值。操作门槛极低，但策略深度在线，这或许就是教练视角带来的最大优势。返回搜狐，查看更多&lt;/p&gt;</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
+          <t>https://q1.itc.cn/q_70/images03/20260813/d6d8039d0036430b8cdbb18df8656304.jpeg</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>2026ChinaJoy前瞻：新作云集！今年厂商们又整出了哪些“狠活”？</t>
+          <t>腾讯游戏+1：《无畏契约：源能行动》华为鸿蒙版正式上线</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
@@ -1827,66 +2751,22 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>随着7月临近尾声，备受玩家们期待的年度盛会，2026年ChinaJoy就要来啦！
-今年ChinaJoy在规模上又创新高，根据官方数据，7月31日至8月3日期间，将会有近900家参展企业来到现场，相比去年的743家涨幅达20%。
-自2004年举办首届展会以来，已经22岁的ChinaJoy还在以全盛之姿，见证着中国乃至全球数字娱乐产业的蓬勃发展。
-那么今年的CJ又有哪些值得一看的亮点呢？在正式开馆前，我们不妨老规矩，再从BtoC场馆开始“云逛”一圈吧～
-N1场馆——新游齐聚，单机盛宴
-今年的N1馆，依然是想要了解热门游戏厂商动态的好去处。
-完美世界这边就为新公测的都市开放世界游戏《异环》准备了丰富的现场活动，并带来了《P5X》《DOTA2》《CS》等游戏的现场试玩。
-于今年4月开启删档测试的诛仙系列MMO新作《梦幻新诛仙：轻享》届时也将和玩家们见面，诛仙IP的粉丝们可以重点关注一波。
-在今年7月凭借1.0正式版拿下4000万玩家和Steam85万同时在线的《幻兽帕鲁》，这次也带着新内容和丰富的周边抽奖活动来到了现场。不知那只四处游荡，贯穿多个大型展会的捣蛋猫，这次会不会也在CJ来个“惊喜返场”。
-开发商Pocketpair这次还特地一口气拿出了《乡野奇运》《Clicky Islands》《钓了个诡》三款新游戏的DEMO，说不定下一个爆款，就能从这些游戏中诞生呢。
-还有参展者们休憩时必去的“云网吧”顺网科技，这次也集结了4Divinity、Game Freak、Fictions、白玉京工作室、古神实验室、苍墨工作室、剑猫熊、Story Taco 等知名团队。如果你想体验《猿公剑》《古神： 风里希》《锦衣卫》《轮回之兽》这些精彩佳作，兴许可以找个时间在这里坐一坐。
-当然，我还强烈建议你看看位于VIP入口处的ChinaJoy Express试玩区。
-今年试玩区足足云集了88款来自国内外工作室的佳作和新作，同时还和3i计划合作，带来了八款精选独立游戏的最新试玩DEMO。
-“3i计划”是由法国3i游戏工作室Evil Empire牵头，全球顶尖游戏工作室合力打造的游戏线上发布会，且在之前已经为全球玩家带来了《武士零》《寻找伪人》《吸血鬼幸存者》《杀戮尖塔2》等独立佳作的最新消息。
-而这次参展的独游中也有不少值得一提的小众精品，像是在23年发售，Steam好评率高达94%的轻量肉鸽射击游戏《土豆兄弟》，这次就端上来了新DLC“史前惧兽”的抢先试玩。
-节奏地牢系列续作《节奏裂隙》更是直接开放了本体、DLC和联动曲等近乎全部的游戏内容，现场就能无限爽玩。
-相信在3i游戏的带队下，今年体验ChinaJoy Express游戏试玩区的长龙，一定比之前还要壮观。
-除了上面提到的参展展商和游戏，N1馆还有不少游戏新作等待大家前往体验。由于数量实在太多，这里就放一张图让各位感受一下吧。
-N2场馆——有料，而且不少
-和N1一样，N2场馆这边也入驻了不少我们颇为熟悉的老朋友。
-360游戏这次就带来了《坦克世界》和《战舰世界》两款经典游戏。为了展现对CJ的重视，官方不仅要在现场首次公布下一届WCI（坦克世界国际冠军赛）的更多关键信息，还准备了专门的联动体验区、定制周边和舞台节目。
-不仅如此，360游戏还在CJ上首次亮相了他们的新作《坦克世界：征程》。据悉，这部作品跳出了历史还原的思路，在保留以坦克为主体载具设计的基础上，新增了特工、技能等全新设定，帮助玩家打出远超想象的超常规操作。这种将钢铁巨兽和技能搭配组合的新设定，说不定能吸引到不少新玩家。
-巨人网络这边也拿出了他们的“全家桶”。除了《征途》系列、《球球大作战》这类经典外，还有《名将杀》《超自然行动组》这样在各自领域的新兴爆款。
-顺带一提，去年巨人网络就把《超自然行动组》的古城实景搬到了CJ，我还挺期待他们今年又能整出什么大活。
-金山世游今年为展区准备了“社交江湖×萌趣治愈×经典怀旧”的三核主题，它们分别对应《鹅鸭杀》《猫咪和汤》和《愤怒的小鸟：经典归来》三个重磅IP。
-其中《鹅鸭杀》这边和剑侠情缘IP联动，打造了“鹅鸭群侠共赴江湖”国风推理主题区，《猫咪和汤》则是构筑了一个“魔法书屋”，内置各种趣味互动和集章抽奖。相信这种和去年截然不同的复刻游戏场景，一定还会成为展会上最适合打卡的好去处。
-至于B站这边呢？别看BW结束不久，bilibili游戏为了这届CJ，可是拿出了自己的多张“王炸”。其中既包括刚刚度过两周年的热门SLG《三国：谋定天下》，也有前段时间开哥亲自复出背书的《三国：百将牌》。
-B站旗下光荣正版授权的新作《三国志：王道天下》，也将在展会开启线下首秀。这款游戏在玩法上改善了许多传统策略游戏的痛点，比如用更加多维的策略体系来弱化数值权重、用动态地图规则调整环境等等，大有成为赛道改革者的架势。
-4399为“造梦西游”正统续作《造梦西游之黎尤浩劫篇》设置了专属特殊展台，另一款自研游戏《童话师》也将一同亮相现场。
-旗下的4399游戏盒更是与十余款优质游戏合作参展，现场集章打卡还有周边奖励，想打游戏和薅羊毛的玩家都可以去看看。
-除了上面提到的这些，N2馆还有许多值得一看的好去处。比如二次元射击游戏《卡拉比丘》，以及《仙境传说3》《植物大战僵尸2》之类经典IP续作等等。只要你稍微细逛一下，N2馆一定能像去年一样，轻松耗掉你的一天时间。
-以下是N2馆可以玩到的游戏，数量之多，一屏已经装不下了。
-N3、N4场馆——依旧神仙打架
-相比之下，N3和N4场馆这边则主打一个“少而精”，入驻的厂商个个都是重量级。
-网易和腾讯依然分别占据着N3和N4馆的半壁江山。网易游戏这次带来了30余款精品力作亮相现场，并为《第五人格》《燕云十六声》《逆水寒》《永劫无间》《遗忘之海》《天下万象》六大IP产品打造独立场景体验区。有了去年
-直接把水族馆搬到现场搞美人鱼表演的前车之鉴，相信网易今年整的活也一定不会差。
-值得一提的是，网易今年热度颇高的两款新作《诡影藏锋》《山海奇旅》届时也将和大家见面。
-其中《诡影藏锋》是以中式恐怖冷兵器为题材的搜打撤，参展者很可能会在8月7日首次内测之前，拿到先行体验的机会。
-《山海奇旅》则主打奇幻生活模拟，节奏轻快、玩法自由。游戏于7月24日刚刚开启测试，想同期体验的小伙伴一定不要错过。
-与网易游戏紧邻的，则是大家最熟悉的暴雪展台。暴雪这次将带来《魔兽世界》《炉石传说》《守望先锋》《暗黑破坏神Ⅳ》《星际争霸Ⅱ》等五款经典IP，并会和去年一样放出经典巨型雕塑供大家打卡。谁不想站在五米高的巨型巫妖王旁边，大声喊出那些平日里想想都脸红的中二台词呢？
-腾讯这边虽然目前没放出什么具体消息，但就去年和前年的参展情况来看，他们很有可能为王者IP公测不久的《王者荣耀：世界》和结束终测的《王者万象棋》准备点大动作，顺道再通过《英雄联盟》《无畏契约》这样的国民网游来一手梅开三度，重现万人空巷的名场面。
-华为游戏中心则是与五十余款鸿蒙游戏一同，在现场打造了一座1000+平方米的赛博游乐场。这里既有《王者荣耀》《王者万象棋》《和平精英》《鸣潮》《鹅鸭杀》《夜幕之下》《太吾绘卷》等精选佳作携手打造的热门游戏展区，也有可供参展者打卡的全场景体验区、游戏试玩区和舞台互动区。就是不知道继语音操控和无缝切换过后，今年的他们又会带来哪些令人惊喜的黑科技。
-字节游戏旗下的朝夕光年，今年又推出了更加空前的豪华联合阵容前来参展。其中不仅包括了《境·界 刀鸣》《初音未来：缤纷舞台》《航海王热血航线》《星球：重启》《镭明闪击》五款热门线上游戏，还有《代号：对决》《SlashZero》《毛仔别打啦》《集合！浆果镇》《托托比亚》《不问凡尘》《雾影猎人》等七款神秘新品。看得出来，他们这次是真的想在CJ现场放出一波大的。
-最后放出N3&amp;N4馆部分参展游戏：
-结语
-好了，受限于篇幅，今年的BtoC前瞻就先说到这里。
-作为国内综合性和影响力最强的展会之一，ChinaJoy上值得说的东西实在太多了，无论是N5的骁龙主题馆，还是位于E区的AI前沿科技、潮流模玩、舞台表演，它们都值得你在出行前做好详细规划，细细品味和游览。
-最后17173祝大家少排队，多出片，集章顺利，盲盒出金！</t>
+          <t>&lt;p&gt;　　IT之家 8 月 13 日消息，腾讯旗下手游《无畏契约：源能行动》鸿蒙版今日正式上线华为应用市场 App Gallery。&lt;/p&gt;
+&lt;img src="https://q1.itc.cn/q_70/images03/20260813/d6d8039d0036430b8cdbb18df8656304.jpeg" alt="https://q1.itc.cn/q_70/images03/20260813/d6d8039d0036430b8cdbb18df8656304.jpeg" /&gt;
+&lt;p&gt;　　IT之家注：《无畏契约：源能行动》是拳头出品、腾讯代理的一款手游，上线于去年 8 月。最低配置仅需骁龙 430、麒麟 710 或苹果 A9 处理器，安卓设备内存至少 3GB 即可运行。但若想获得最佳竞技体验，则需要更高的配置。&lt;/p&gt;
+&lt;img src="https://q3.itc.cn/q_70/images03/20260813/5c60810195e34309b58a0a6e076c844e.jpeg" alt="https://q3.itc.cn/q_70/images03/20260813/5c60810195e34309b58a0a6e076c844e.jpeg" /&gt;</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
+          <t>https://q5.itc.cn/q_70/images03/20260813/7006754c9f8d472594ffe04dca9cfc14.jpeg</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>世嘉携五款新作亮相科隆游戏展2026，现场开放试玩</t>
+          <t>江湖有约，砺剑试锋！武侠RPG手游《古龙群侠录》今日开测，陆小凤、楚留香百位侠客等你集结！</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
@@ -1896,21 +2776,44 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>IT之家 7 月 17 日消息，世嘉官方昨天在 YouTube 平台宣布参展科隆游戏展 2026（Gamescom 2026），至少带来五款可试玩游戏。
-视频显示，《女神异闻录 4：Revival》《异形：隔离 2》《异于天堂》《疯狂出租车：极速环游》和《全面战争：战锤 40K》等游戏将在科隆游戏展 2026 亮相，玩家可在现场试玩。
-作为参考，科隆游戏展 2026 将于 8 月 26 日-8 月 30 日在德国举行，汇集全球 1000 多家游戏企业，各家大厂都将在展会上发布新作或带来实机试玩。IT之家将持续关注，第一时间带来最新消息。</t>
+          <t>&lt;p&gt;　　阿里巴巴灵犀互娱旗下游戏平台&lt;/p&gt;
+&lt;p&gt;　　大家记忆中古龙的江湖，到底长什么样？&lt;/p&gt;
+&lt;p&gt;　　是李寻欢的飞刀、陆小凤的灵犀一指、楚留香的踏月留香、西门吹雪的剑神一笑，还是花满楼那双看不见却比谁都通透的眼睛？&lt;/p&gt;
+&lt;p&gt;　　古龙创作了56部小说，塑造了上百个让人念念不忘的侠客。如今，这个江湖也终于有了一个可以“逛”的地方。今天（8月13日）上午10:00，《古龙群侠录》「砺剑」测试正式开启。&lt;/p&gt;
+&lt;p&gt;　　本作是一款根据“古龙武侠系列小说”正版授权改编的开放式3D武侠冒险RPG，玩家将扮演初入江湖的少年侠客，与古龙笔下的经典角色邂逅相逢、共同成长。李寻欢、陆小凤、楚留香、西门吹雪——上百位经典侠客，都在这个江湖里等你。&lt;/p&gt;
+&lt;img src="https://q5.itc.cn/q_70/images03/20260813/7006754c9f8d472594ffe04dca9cfc14.jpeg" alt="https://q5.itc.cn/q_70/images03/20260813/7006754c9f8d472594ffe04dca9cfc14.jpeg" /&gt;
+&lt;p&gt;　　开放式3D探索武侠 一个可以逛的江湖&lt;/p&gt;
+&lt;p&gt;　　跟之前不少古龙IP改编游戏走卡牌对战的路线不同，《古龙群侠录》做了一个不太一样的选择——把古龙的江湖做成了一个开放式3D探索武侠RPG游戏。&lt;/p&gt;
+&lt;p&gt;　　在这里，你可以踏遍万里山河，与李寻欢共饮，看叶孤城问剑，伴陆小凤探案。西门吹雪和叶孤城在紫禁之巅的那场对决，不再只是书里的一段描写，而是你可以亲身经历的名场面。&lt;/p&gt;
+&lt;img src="https://q3.itc.cn/q_70/images03/20260813/9615a3d3b2ac46e98034304f375f062b.jpeg" alt="https://q3.itc.cn/q_70/images03/20260813/9615a3d3b2ac46e98034304f375f062b.jpeg" /&gt;
+&lt;p&gt;　　城中的楼顶、酒家的房梁、山岗的石狮像，处处暗藏玄机。无名山洞、山区脉矿，不为人知的密宝在等待探索。&lt;/p&gt;
+&lt;p&gt;　　九酱觉得，这或许才是大部分人想象中古龙江湖该有的样子——不只是一个推图刷副本的战场，更是一个真正可以逛、会迷路、但在某个不起眼的角落却能遇到故人的活生生的江湖。&lt;/p&gt;
+&lt;p&gt;　　百派武学随心配 招式由你定&lt;/p&gt;
+&lt;p&gt;　　古龙小说中的武功，从来不是靠等级堆出来的。李寻欢的飞刀例不虚发，靠的是“心”。西门吹雪的剑快到了极致，靠的是“专注”。陆小凤的灵犀一指，能夹住天下任何兵器，靠的是“巧”。&lt;/p&gt;
+&lt;img src="https://q7.itc.cn/q_70/images03/20260813/62de15cb037441f982cbce7cbcdbe5de.jpeg" alt="https://q7.itc.cn/q_70/images03/20260813/62de15cb037441f982cbce7cbcdbe5de.jpeg" /&gt;
+&lt;p&gt;　　《古龙群侠录》在武学系统上，走了一条类似的思路。游戏内置了刀剑、拳掌、暗器等百派武学，可以自由学习搭配。没有职业限制，没有固定套路。因此甭管是想走李寻欢的飞刀流，还是学陆小凤的空手入白刃？全由你决定。&lt;/p&gt;
+&lt;p&gt;　　更关键的是，绝技、连击、连携技，群侠共助战。这不是一个人单打独斗的江湖——你招募的侠客会跟你并肩作战，打出组合招式。用古龙的话说，“以柔克刚，以力破巧”，招式之间没有绝对强弱，只有用得对不对。&lt;/p&gt;
+&lt;img src="https://q7.itc.cn/q_70/images03/20260813/189fccbb6e7a40ba841e64a98953614c.jpeg" alt="https://q7.itc.cn/q_70/images03/20260813/189fccbb6e7a40ba841e64a98953614c.jpeg" /&gt;
+&lt;p&gt;　　主阵容最多上阵4名侠客，还有支援位8名侠客提供额外战力加成。主阵容中上阵3名或以上同派系侠客（刀、剑、奇门等），即可激活对应派系的“阵法”，为全体上阵侠客提供大量属性加成。这套机制在前期能让你的策略搭配有实实在在的回报，不只是凑战力数值。&lt;/p&gt;
+&lt;p&gt;　　不止打打杀杀 江湖还有另一面&lt;/p&gt;
+&lt;p&gt;　　古龙的江湖里，除了刀光剑影，还有酒、有茶、有钓鱼、有说不完的闲话。&lt;/p&gt;
+&lt;p&gt;　　《古龙群侠录》也没把江湖简单理解成“打打杀杀”，更有“人情世故”。游戏里你可以在碧溪间垂钓，在山野间采矿，接取跑商任务，触发隐藏支线。与他人猜拳论剑夺奇宝，赠礼结缘传神功——那些古龙笔下侠客们的日常，你也可以体验一把。&lt;/p&gt;
+&lt;img src="https://q4.itc.cn/q_70/images03/20260813/594563f6f1cc4bebaf0f424bd2a5182b.jpeg" alt="https://q4.itc.cn/q_70/images03/20260813/594563f6f1cc4bebaf0f424bd2a5182b.jpeg" /&gt;
+&lt;p&gt;　　这也难怪有玩家在专区里留言，希望游戏把重点放在剧情和角色上，尽量还原古龙作品里的人物性格和故事。这种对角色还原的期待，在古龙粉丝里其实挺普遍的。毕竟古龙的魅力，从来不只在武功有多强，而在于那些人物本身。&lt;/p&gt;
+&lt;p&gt;　　「砺剑」测试不限名额 服满就关&lt;/p&gt;
+&lt;p&gt;　　最后，九酱把测试信息给各位少侠划个重点：&lt;/p&gt;</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
+          <t>https://q5.itc.cn/images01/20260813/cf7b11e3973b4a37bd773c35813c9d73.png</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>国产游戏《昭和米国物语》配置要求公布</t>
+          <t>《无畏契约：源能行动》鸿蒙版上线：数据互通，多端玩家无缝切换</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
@@ -1920,18 +2823,23 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>IT之家 8 月 10 日消息，开发商铃空游戏现已公布了《昭和米国物语》游戏配置需求信息，本作要求的配置较低，推荐使用 i7-4770K + GTX1660Ti 游玩，IT之家附游戏系统需求如下：
-参考IT之家先前报道，本作将参加 8 月 26 日至 30 日的 2026 科隆游戏展，将带来现场试玩和全新预告。
-《昭和米国物语》游戏充分融合 80 年代美国和日本的文化特性，创造了一个打破常规、充满颠覆性的全新世界，死而复生的少女蝶子将在此展开她的冒险之旅。游戏将登陆 PlayStation 5 和 PC 平台。
-该游戏的上一支预告片还是在 2024 年 11 月，游戏原定 2025 年发售。到了 2025 年 11 月，开发商铃空游戏宣布，随着开发进入最终的打磨阶段，为了不留遗憾地把作品呈现在玩家的面前，经过再三思考，决定调整发售计划。《昭和米国物语》的发售时间将由 2025 年调整至 2026 年。</t>
+          <t>&lt;p&gt;　　PChome 8月13日消息，腾讯旗下5V5战术竞技射击手游《无畏契约：源能行动》鸿蒙版正式在华为应用市场App Gallery上线。这款由拳头游戏开发、腾讯代理的《无畏契约》IP正版手游，去年8月已登陆安卓与iOS平台。最低配置仅需骁龙430、麒麟710或苹果A9处理器，3GB内存即可运行。&lt;/p&gt;
+&lt;img src="https://q5.itc.cn/images01/20260813/cf7b11e3973b4a37bd773c35813c9d73.png" alt="https://q5.itc.cn/images01/20260813/cf7b11e3973b4a37bd773c35813c9d73.png" /&gt;
+&lt;p&gt;　　鸿蒙版最大的亮点是支持多端数据互通。玩家已有的游戏账号数据可直接在鸿蒙端继承，无需重新开始；同时支持跨平台匹配竞技。也就是说，无论你此前在安卓还是iOS设备上玩过，切换到鸿蒙设备后都能无缝接续原有战斗进程，继续与好友组队开黑。游戏延续了经典的5V5战术射击玩法，将英雄技能与枪战竞技结合，每一回合都充满博弈。&lt;/p&gt;
+&lt;img src="https://q2.itc.cn/images01/20260813/63963f16d8b54b2780f709c8af29edbb.png" alt="https://q2.itc.cn/images01/20260813/63963f16d8b54b2780f709c8af29edbb.png" /&gt;
+&lt;p&gt;　　此次上线正值鸿蒙生态快速扩张期。此前鸿蒙版已于6月25日至7月3日进行过删档尝鲜测试。如今正式版本上线，玩家可前往华为游戏中心搜索下载。在腾讯Q2财报中，《无畏契约：源能行动》被点名表扬为本土市场游戏收入增长的核心动力之一。鸿蒙版的加入，意味着这款热门射击手游完成了对三大主流移动操作系统的全面覆盖。返回搜狐，查看更多&lt;/p&gt;</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="inlineStr"/>
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>https://q9.itc.cn/q_70/images03/20260805/f2e6ccbd05bd4d30b7fcacc9010c7fcc.png</t>
+        </is>
+      </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>任天堂数字版游戏占比突破六成，销售额猛增九成至1327亿日元</t>
+          <t>盗墓笔记、诡秘之主、怪物猎人领衔：8月定档手游扎堆，谁能成爆款？</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
@@ -1941,24 +2849,78 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>IT之家 8 月 6 日消息，围绕游戏行业是否会全面转向数字发行的讨论近来持续升温，索尼、Xbox 和任天堂都被卷入数字化浪潮之中。任天堂最新财报显示，Switch 玩家正越来越多地转向数字版游戏，数字渠道贡献的软件销售额占比已经超过 60%。
-据外媒 Inside Gaming 今天（6 日）报道，索尼计划从 2028 年起告别实体光盘，Xbox 据称也在探索把实体盘转换为数字版的服务。任天堂一度被视为最有可能长期保留实体游戏的最后几家大厂之一，但数字销售持续攀升意味着，任天堂同样很难逆转行业方向。
-最新财报显示，任天堂 Switch 2 累计销量已经突破 2300 万台，整个 Switch 生态系统仍拥有约 1.3 亿年活跃玩家。庞大的用户规模正在不断放大数字业务的重要性。任天堂 2027 财年第一季度的软件销售额中，61.5% 来自数字渠道，较上一季度的 59.3% 上升 2.2 个百分点。
-占比增幅只有 2.2 个百分点的同时，数字销售额却几乎翻了一番，从上一季度的 698 亿日元（IT之家注：现汇率约合 29.92 亿元人民币）增至 1,327 亿日元（现汇率约合 56.88 亿元人民币），增幅约 90%。
-任天堂称，数字销售额同比大幅增长，主要得益于盒装游戏对应下载版销量增加，同时也受到日元贬值推动。
-具体到游戏表现，《Tomodachi Life 朋友收集：梦想生活》成为任天堂近期的重要畅销作品，截至 2026 年 8 月 5 日销量已经超过 800 万套。《Pokémon Pokopia》则创下新纪录，成为史上销量最高的《宝可梦》衍生游戏。</t>
+          <t>&lt;img src="https://q9.itc.cn/q_70/images03/20260805/f2e6ccbd05bd4d30b7fcacc9010c7fcc.png" alt="https://q9.itc.cn/q_70/images03/20260805/f2e6ccbd05bd4d30b7fcacc9010c7fcc.png" /&gt;
+&lt;p&gt;　　今年暑期档下半程，游戏圈战火延续。&lt;/p&gt;
+&lt;p&gt;　　据陀螺君统计，8月超20款新游定档上线或明确公测节点，至少18款产品启动测试，数量与7月持平，热度不减。&lt;/p&gt;
+&lt;p&gt;　　从排期看，8月上旬尤为密集，仅8月6日便有《魂坠深境》《航海王：集结》《群星征途2117》《丹墨三国：弈》等多款集中发力。&lt;/p&gt;
+&lt;p&gt;　　品类上，卡牌RPG与策略仍是基本盘，“搜打撤”赛道迎来多款新品，二次元音游、中式志怪恐怖、派对社交等细分领域亦有重磅入局。腾讯、网易、B站、朝夕光年、恺英网络等厂商均在本月“上新”或进行关键新游测试。&lt;/p&gt;
+&lt;img src="https://q4.itc.cn/q_70/images03/20260805/281937ce063e41d9bd255897c1c87dde.png" alt="https://q4.itc.cn/q_70/images03/20260805/281937ce063e41d9bd255897c1c87dde.png" /&gt;
+&lt;p&gt;　　注：新游档期信息主要采集自官方、TapTap、好游快爆及App Store预订页面，标“*”者为App Store预定信息，官方尚未正式定档，实际上线时间请以厂商公告为准。&lt;/p&gt;
+&lt;p&gt;　　本月，腾讯预计有4款产品进入关键测试节点，覆盖暗黑MMO、开放世界狩猎、休闲派对、经典移植四大品类，堪称全赛道出击。&lt;/p&gt;
+&lt;p&gt;　　网易以中式志怪“搜打撤”新作《诡影藏锋》差异化入局。B站在二次元音游与经典MMO两端同时落子。朝夕光年携《航海王：集结》重启归来。恺英网络、快手、凉屋游戏等厂商同样颇具看点。&lt;/p&gt;
+&lt;p&gt;　　具体来看，8月上线的重点产品介绍：&lt;/p&gt;
+&lt;p&gt;　　凉屋游戏——《魂坠深境》（8月6日上线）&lt;/p&gt;
+&lt;img src="https://q1.itc.cn/q_70/images03/20260805/a8202fa6c3ff487ea4cca671327a8d2a.png" alt="https://q1.itc.cn/q_70/images03/20260805/a8202fa6c3ff487ea4cca671327a8d2a.png" /&gt;
+&lt;p&gt;　　《魂坠深境》是凉屋游戏推出的卡牌Roguelike新作，定档8月6日上线。&lt;/p&gt;
+&lt;p&gt;　　游戏以策略构筑与序列式卡牌对战为核心玩法，辅以暗黑西幻风格的美术基调与克系诡异氛围，主打的是一套围绕“取舍”展开的深度博弈机制：战斗序列中，玩家每打出一张卡牌，需以牺牲其后若干张卡牌为代价，出牌顺序与牺牲决策共同构成策略内核。&lt;/p&gt;
+&lt;p&gt;　　在内容体量上，游戏现已开放700余张特色卡牌、170余种祝福、50种印记及85种护符供玩家自由构筑，四大职业与十七位出战者各自拥有独立卡池和专属天赋树，彼此之间的搭配组合具备可观的策略纵深。&lt;/p&gt;
+&lt;p&gt;　　恺英网络——《盗墓笔记：启程》（8月11日公测）&lt;/p&gt;
+&lt;img src="https://q5.itc.cn/q_70/images03/20260805/99b70967965b40d7b98170d7d0be62e7.png" alt="https://q5.itc.cn/q_70/images03/20260805/99b70967965b40d7b98170d7d0be62e7.png" /&gt;
+&lt;p&gt;　　《盗墓笔记：启程》由南派三叔正版授权，虚幻4研发的寻宝盗墓探险手游。&lt;/p&gt;
+&lt;p&gt;　　玩家以“九门后人”身份随铁三角深入鲁王宫、西王母宫等原著古墓，箱庭式地宫中以星图推演、铭文比对等考古逻辑解谜，搭配六大职业与ARPG+策略+Roguelike战斗。&lt;/p&gt;
+&lt;p&gt;　　游戏“地下探险+雨村闲居”双线并行，支持种田钓鱼送礼等休闲玩法。6月份官宣全平台预约破500万。&lt;/p&gt;
+&lt;p&gt;　　延趣网络——《赘婿》（8月12日首发）&lt;/p&gt;
+&lt;img src="https://q6.itc.cn/q_70/images03/20260805/93e85ce7f51042cdacdca69d490d5743.png" alt="https://q6.itc.cn/q_70/images03/20260805/93e85ce7f51042cdacdca69d490d5743.png" /&gt;
+&lt;p&gt;　　《赘婿》获同名小说及剧版正版授权，三七互娱运营的游戏。&lt;/p&gt;
+&lt;p&gt;　　玩家化身宁毅从苏家赘婿起步，以“拼刀刀砍价、直播带货”等现代商业思维经营古代商场，走“经营赚钱→养门客红颜→商战打脸→身份晋升”的模拟经营+放置养成闭环，复刻大婚、掌印争夺等名场面，穿插斗鸭、抓大鹅等轻量休闲玩法。&lt;/p&gt;
+&lt;p&gt;　　快手弹指宇宙——《诡秘之主》（8月21日上线）&lt;/p&gt;
+&lt;img src="https://q3.itc.cn/q_70/images03/20260805/0244313f3a654a2daf643f411d0e8a82.png" alt="https://q3.itc.cn/q_70/images03/20260805/0244313f3a654a2daf643f411d0e8a82.png" /&gt;
+&lt;p&gt;　　《诡秘之主》是一款UE5研发的欧式古风神秘学MMORPG游戏，改编自同名网络小说。&lt;/p&gt;
+&lt;p&gt;　　玩家从22条神之途径中选择，通过服用魔药与“扮演法”晋升（序列9至序列0），内置SAN值精神机制，理智归零将失控异变。包含原著向剧情线与个人主线双线叙事，支持千人同屏阵营混战。&lt;/p&gt;
+&lt;p&gt;　　据悉该团队超过600人，项目研发时间超过四年，累计投入超10亿元。&lt;/p&gt;
+&lt;p&gt;　　金山世游——《猫咪和汤：魔法与美食》（8月27日上线）&lt;/p&gt;
+&lt;img src="https://q1.itc.cn/q_70/images03/20260805/103760d8d0d545faae270b5c22e6949d.png" alt="https://q1.itc.cn/q_70/images03/20260805/103760d8d0d545faae270b5c22e6949d.png" /&gt;
+&lt;p&gt;　　《猫咪和汤：魔法与美食》（英文名：《Cats &amp;amp; Soup》）是一款由Neowiz 运营，Hidea 开发的治愈系猫咪魔法合成装扮类手游，金山世游负责其国服代理。&lt;/p&gt;
+&lt;p&gt;　　游戏的全球累计下载次数突破7000万，并持续保持高人气。简单的游戏方式与可爱的画风等疗愈要素是该游戏的主要特点，目前游戏在好游快爆平台评分达8.2分。&lt;/p&gt;
+&lt;p&gt;　　已定档产品之外，8月预计有18款游戏进入测试阶段，其激烈程度不亚于正式上线潮。&lt;/p&gt;
+&lt;img src="https://q5.itc.cn/q_70/images03/20260805/21b4d1144ab54a9faa0943d342e0a982.png" alt="https://q5.itc.cn/q_70/images03/20260805/21b4d1144ab54a9faa0943d342e0a982.png" /&gt;
+&lt;p&gt;　　重点测试产品有：&lt;/p&gt;
+&lt;p&gt;　　腾讯游戏——《天堂：血统》《怪物猎人：旅人》《奥星热浪》&lt;/p&gt;
+&lt;p&gt;　　《天堂：血统》（8月5日限量计费删档测试）：天堂IP正版硬核MMO，高清还原亚丁大陆与血盟攻城，支持PC/手机双端互通与自由交易，主打经典打宝与挂机减负。&lt;/p&gt;
+&lt;p&gt;　　《怪物猎人：旅人》（8月7日限量删档测试）：怪猎系列首款移动端开放世界狩猎手游，由天美研发、卡普空监修。以埃索岛无缝大地图、融光种独占怪物、四人共斗与太刀/大剑/弓等经典武器还原为核心，单局压缩至15-25分钟。&lt;/p&gt;
+&lt;p&gt;　　《奥星热浪》（8月14日限量删档测试）：光子工作室出品，以“梗文化+轻量搜打撤+派对社交”拼装出哈基镇、来财行动与家园循环，法棍当武器，主打年轻玩家的抽象整活与解压。&lt;/p&gt;
+&lt;img src="https://q7.itc.cn/q_70/images03/20260805/52a1051112754df6972a4f877ff3fdb2.png" alt="https://q7.itc.cn/q_70/images03/20260805/52a1051112754df6972a4f877ff3fdb2.png" /&gt;
+&lt;p&gt;　　网易游戏——《诡影藏锋》（8月7日“藏锋测试”）&lt;/p&gt;
+&lt;p&gt;　　这是雷火工作室用虚幻5打造的首款中式志怪第一人称“搜打撤”新作。&lt;/p&gt;
+&lt;p&gt;　　玩家扮通玄院探客潜入荒村、废庙、古宅等禁地，15分钟内搜奇珍、破机关、斗纸人傀儡与缢死女鬼，赶在时限前找生门撤离。&lt;/p&gt;
+&lt;p&gt;　　游戏战斗弃用枪械，以刀剑枪扇戟等冷兵近身格挡闪避，辅以结印咒术驱鬼，单排或三排（含PvPvE）并行，暗黑水墨写实美术搭配浓雾烛影，Steam页面已挂“免费开玩”。&lt;/p&gt;
+&lt;img src="https://q9.itc.cn/q_70/images03/20260805/ac98742639914d2794908eab3ae00184.png" alt="https://q9.itc.cn/q_70/images03/20260805/ac98742639914d2794908eab3ae00184.png" /&gt;
+&lt;p&gt;　　B站——《BanG Dream! Our Notes》《仙境传说3》&lt;/p&gt;
+&lt;p&gt;　　《BanG Dream! Our Notes》（8月6日海外β测试）：B站代理海外发行，围绕五支乐队展开叙事，延续动画世界观，引入“电影叙事系统”强化角色表情与镜头语言。保留竖版下落式玩法，新增“辅助模式”降低门槛，新增“激奏演出”及最多五人同台的派对联机。&lt;/p&gt;
+&lt;p&gt;　　《仙境传说3》（8月27日PC端不限量删档“重逢测试”）：B站独家代理，Gravity与欢乐互娱联合研发，RO正统续作。PC原生架构+多端互通，次世代2.5D俯视视角MMO，延续普隆德拉摆摊、转职BD、MVP与百人GVG攻城、自由交易等经典元素。&lt;/p&gt;
+&lt;img src="https://q3.itc.cn/q_70/images03/20260805/092096ae06754a6e809a2de6e4a08123.png" alt="https://q3.itc.cn/q_70/images03/20260805/092096ae06754a6e809a2de6e4a08123.png" /&gt;
+&lt;p&gt;　　朝夕光年——《航海王：集结》（8月6日限量删档“集结测试”）&lt;/p&gt;
+&lt;p&gt;　　东映动画正版授权的3D动作冒险手游，原《代号：伙伴》重启。以多人协作PVE团本为核心，主打六人分两队兵分两路联动作战、三角色轮切与输出/特攻/辅助分工，将草帽团经典战役做成赛季制副本，以“猜拳式”攻防克制兼顾团战配合与PVP策略。&lt;/p&gt;
+&lt;p&gt;　　此外，8月新品矩阵中还有《全职掌门》《鸡械绿洲》《三国将魂》《满庭芳·宋上繁华》《大侠闯天下》等值得关注的面孔。&lt;/p&gt;
+&lt;p&gt;　　纵观8月产品阵容，三大趋势尤为突出：&lt;/p&gt;
+&lt;p&gt;　　其一，“搜打撤”玩法从战术射击向国风恐怖、休闲派对快速外溢，《诡影藏锋》《奥星热浪》分别以东方惊悚和抽象整活切入细分赛道。&lt;/p&gt;
+&lt;p&gt;　　其二，IP改编仍是重头戏，从《盗墓笔记》《诡秘之主》到《怪物猎人》《航海王》《天堂》《仙境传说》，文学、动漫、经典端游IP全面开花，移动端价值持续深挖。&lt;/p&gt;
+&lt;p&gt;　　其三，头部厂商排兵布阵层次分明，腾讯三款产品覆盖三种截然不同的用户画像，B站兼顾二次元核心与经典MMO两端，网易以风格化单品寻求突破，多端互通已成为中大型产品标配。&lt;/p&gt;
+&lt;p&gt;　　结语：&lt;/p&gt;
+&lt;p&gt;　　8月竞争压力不仅来自新品扎堆，还有多款长青产品在暑期后半程的版本攻势。在大厂新品密集轰炸、经典IP集中变现与存量市场三方角力下，谁能在8月真正承接住暑期档后半段用户的注意力，成为今夏最后的赢家？拭目以待。&lt;/p&gt;
+&lt;img src="https://q1.itc.cn/q_70/images03/20260805/3d057977f75841f8939abdc31cc7c688.jpeg" alt="https://q1.itc.cn/q_70/images03/20260805/3d057977f75841f8939abdc31cc7c688.jpeg" /&gt;</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>data:image/gif;base64,R0lGODlhAQABAIAAAAAAAP///yH5BAEAAAAALAAAAAABAAEAAAIBRAA7</t>
+          <t>https://q9.itc.cn/q_70/images03/20260802/c2f0b49761a74fc38ad0530425b41359.jpeg</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>“中国（成都）动漫游戏消费季”在成都高新区举办</t>
+          <t>首款中式志怪搜打撤游戏，网易《诡影藏锋》已开启全网预约</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
@@ -1968,24 +2930,24 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>8月8日-9日，“2026中国（成都）动漫游戏消费季COMIDAY30”在成都高新区世纪城新国际会展中心举办。作为西南地区影响力突出的原创动漫交流展会，本届活动吸引数万名ACG（动画、动漫、游戏）爱好者到场参与逛展、互动体验，通过搭建线上线下文创交流平台，丰富青年文化消费场景，推动数字文创产业加快发展。
-记者了解到，本届活动参展规模较往届实现扩容升级，场内设立超4000个展位。展会整体划分国创同人、热门IP、独立游戏三大核心板块，打造《无期迷途》《燕云十六声》等多条专属主题街区，适配不同爱好者的观展需求。
-“我专门从重庆赶来参加这次漫展，活动现场打造的主题街区内容特别丰富，光是挨个摊位集章打卡，就能在现场玩上一整天。”来自重庆的观展市民张女士说，整场展会氛围浓厚，场景布置也都十分用心，沉浸式体验感十足。
-此外，企业馆区域则集结多家知名游戏厂商、模型品牌与同人创作社团，海量展会限定周边、独家原画手稿、限量手办现货集中发售，为收藏爱好者提供丰富选择。本届展会还创新增设展区，陈列数百件模型参赛作品，搭建起面向模型创作者、收藏爱好者的专业展示、交流分享平台，填补了西南地区线下模型专业交流场景空白。
-游戏体验专区是本次展会另一大热门亮点。据主办方相关负责人介绍，今年游戏展区完成全面扩容，《无限机兵》《猿公剑》等多款国产独立新作开放线下实机试玩，同步配套电竞挑战赛、行业开发者沙龙等活动，“我们希望让到场玩家能够在线下沉浸式体验国产游戏全新内容，同时搭建创作者直面玩家的线下沟通渠道，倾听市场反馈，助力本土独立游戏创作发展。”
-记者 吴怡霏 图据受访单位 责任编辑 蔺虹豆 编辑 王奕然 审核 曹宇阳</t>
+          <t>&lt;p&gt;　　IT之家 8 月 2 日消息，今日，网易雷火工作室宣布全新作品《诡影藏锋》现已开启全网预约，这部首款中式志怪搜打撤游戏将于 8 月 7 日开启藏锋测试（删档测试）。&lt;/p&gt;
+&lt;img src="https://q9.itc.cn/q_70/images03/20260802/c2f0b49761a74fc38ad0530425b41359.jpeg" alt="https://q9.itc.cn/q_70/images03/20260802/c2f0b49761a74fc38ad0530425b41359.jpeg" /&gt;
+&lt;p&gt;　　据介绍，本作是一款主打中式志怪题材的第一视角搜打撤游戏，玩家将在充满诡异氛围的东方志怪世界里搜寻宝物、破解机关、直面邪祟，并赶在时间耗尽前寻得生门撤离。&lt;/p&gt;
+&lt;p&gt;　　IT之家注意到，《诡影藏锋》于 7 月 8 日开启藏锋测试招募，报名现已结束。本次测试预计于 2026 年 8 月 7 日上午 10:00 开启，2026 年 8 月 10 日晚 23:59:59 结束，为期四天。首批测试资格将于 8 月 3 日中午 12:00 起，通过短信陆续向获得资格的玩家发送提醒。本次测试内容包括PvP 争锋模式、PvE 共御模式。&lt;/p&gt;
+&lt;p&gt;　　《诡影藏锋》使用虚幻 5 打造，支持三排（4 队，上限 12 人）与单排（8 队，上限 8 人）两种模式。目前游戏已在 Steam 上开放愿望单功能，添加即可获得专属永久限定“金满华堂”桃木剑皮肤。&lt;/p&gt;
+&lt;img src="https://q2.itc.cn/q_70/images03/20260802/903179d36c4043309b962cf41c4e6257.jpeg" alt="https://q2.itc.cn/q_70/images03/20260802/903179d36c4043309b962cf41c4e6257.jpeg" /&gt;</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0810%2F385ecb33j00tjj7kf000od000fa008lg.jpg&amp;thumbnail=660x2147483647&amp;quality=80&amp;type=jpg</t>
+          <t>https://q1.itc.cn/q_70/images03/20260805/66ee9e8f44834de98cd6fd35518eebfc.jpeg</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>《匹诺曹谎言2》已进入全面开发阶段！保证非常有趣</t>
+          <t>网易首款“吃打撤手游”《雾海之下》8月17日开启首测</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
@@ -1995,23 +2957,24 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>据VG Times报道，《匹诺曹的谎言》开发商Round8 Studio表示，游戏的续作《匹诺曹的谎言2》已经进入正式开发阶段，而游戏总监Choi Jiwon也已经向玩家请求耐心等待，希望团队能够全力打造这款续作。工作室表示，他们希望下一款作品能够真正成为一款与众不同的游戏。
-游戏总监Choi Jiwon表示，团队希望下一款作品能够真正令人感到有趣，并在情感层面打动玩家。他同时请求粉丝再等待一段时间，让团队能够尽最大努力将游戏打造得更加优秀。
-他说：“我们正在制作的下一款作品将会非常有趣，我也希望它能够触及你的内心深处。我们正在尽一切努力，让它变得尽可能优秀。所以，请再等待一段时间。你不会感到失望。这是真的，不是谎言。”
-艺术总监Cha Byung-joon表示，团队感受到了压力，但他们正在努力回归制作第一款《匹诺曹的谎言》时的心态。他补充称，开发团队仍然坚持“由玩家为玩家打造游戏”的理念，并且会继续对项目进行测试和调整，在不妥协的情况下不断完善作品。
-发行商Neowiz还表示，续作的所有前期准备工作已经完成，目前工作人员正专注于游戏内容的制作。公司指出，在内部测试过程中，一些团队成员甚至无法完成原版《匹诺曹的谎言》一半的流程，因此游戏中加入了难度选项。</t>
+          <t>&lt;p&gt;　　IT之家 8 月 5 日消息，网易宣布旗下雷火工作室推出的首款“吃打撤”玩法手游《雾海之下》将于 8 月 17 日开启首测“大狩猎测试”。&lt;/p&gt;
+&lt;img src="https://q1.itc.cn/q_70/images03/20260805/66ee9e8f44834de98cd6fd35518eebfc.jpeg" alt="https://q1.itc.cn/q_70/images03/20260805/66ee9e8f44834de98cd6fd35518eebfc.jpeg" /&gt;
+&lt;p&gt;　　据介绍，本作采用西幻魔物题材，核心玩法为“吃打撤”：开局前，玩家通过“吃下魔物料理”获得对应的魔物能力，以此替代传统装备系统；进入对局后与两名队友在迷雾中探索、狩猎、抢夺资源；最后必须在迷雾完全吞没区域前成功撤离。&lt;/p&gt;
+&lt;p&gt;　　官方表示，本次测试时间从 2026 年 8 月 17 日至 8 月 23 日（共 7 天），测试平台包含安卓、iOS 双端，为限号、删档、不计费模式，测试资格从 8 月 14 日起陆续发放。&lt;/p&gt;
+&lt;img src="https://q8.itc.cn/q_70/images03/20260805/791c7a4b322841468a06252a9177a029.jpeg" alt="https://q8.itc.cn/q_70/images03/20260805/791c7a4b322841468a06252a9177a029.jpeg" /&gt;
+&lt;img src="https://q9.itc.cn/q_70/images03/20260805/03c6f7001a0348d2810d52d2c3b0e092.jpeg" alt="https://q9.itc.cn/q_70/images03/20260805/03c6f7001a0348d2810d52d2c3b0e092.jpeg" /&gt;</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>https://q4.itc.cn/q_70/images03/20260810/205dc7f708344499a0443edc8e9d52e2.jpeg</t>
+          <t>https://q2.itc.cn/q_70/images01/20260813/f472f984112b42b7ac2afaf3b8448ee4.jpeg</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>Epic喜加一：原价31元恐怖游戏《Cat Named Mojave》免费领</t>
+          <t>《BanG Dream! 交织的乐章》封测实机影片曝光 一窥全新「激奏演出」与「ANON TOKYO」模拟经营玩法</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
@@ -2021,23 +2984,20 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>IT之家 8 月 10 日消息，独立开发团队 Stargazers Studios 制作并发行的心理恐怖游戏《Cat Named Mojave》即日起在 Epic Games Store 开启限时免费领取“喜加一”活动，游戏在国区定价为 31 元，活动将持续至 8 月 15 日上午 11 点结束。
-需要注意的是，本次限免并非 Epic 官方活动，而是由开发团队自行发起的特别促销，IT之家附游戏商品页（https://store.epicgames.com/p/cat-named-mojave-7e06ad）。
-本作最初于 2025 年 12 月 8 日在 PC 平台发布，目前 Steam 玩家评价维持在 95% 的“特别好评”。在游戏中，玩家将扮演一名因汽车电池耗尽而被困在荒漠中的角色。此时，一个诡异的猫人“Mojave”突然出现，并成为主角逃离沙漠的唯一希望。
-然而，Mojave 提出的要求十分异常。他要求玩家猎杀各种超现实生物，剥下它们的皮、进行切割，并将这些动物战利品带回地下室，作为自己的收藏品。因此玩家必须在“狩猎、剥皮、切割以及生存”之间不断做出选择。
-游戏图赏：</t>
+          <t>&lt;p&gt;　　由 BILIBILI GAME（哔哩哔哩游戏）代理发行（台湾地区由艾瑞尔网路股份有限公司代理）的《BanG Dream! 交织的乐章》于近期开放国际服封闭测试（CBT），巴哈姆特电玩疯也参与了本次测试，为玩家带来实机影片。&lt;/p&gt;
+&lt;img src="https://q2.itc.cn/q_70/images01/20260813/f472f984112b42b7ac2afaf3b8448ee4.jpeg" alt="https://q2.itc.cn/q_70/images01/20260813/f472f984112b42b7ac2afaf3b8448ee4.jpeg" /&gt;</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>https://inews.gtimg.com/om_bt/OaFYur_vJ9hlQuAk3iJo5dfilyDGlmuPa7X-2nqgFzFtgAA/641</t>
+          <t>https://q6.itc.cn/images01/20260808/03b1cfe29c954f98b238d3ee98c1fe60.jpeg</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>《DOTA2》国际邀请赛TI15首轮赛程公布，8月13日上海开战</t>
+          <t>LPL第三赛段：痛失好局，AL连下两城横扫LGD</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
@@ -2047,25 +3007,30 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>IT之家 8 月 10 日消息，《DOTA2》2026 年国际邀请赛将于 8 月 13 日开始，时隔多年重返上海。官方今日公布第一轮对阵图，每场比赛均为 BO3，中国赛区 XG、VG、TR 作为东道主出战。
-A 路直播
-B 路直播
-C 路直播
-D 路直播
-2026 年国际邀请赛将于 8 月 13 日-23 日在中国上海举行，来自全世界的 16 支顶尖职业战队将在上海争夺冠军之神盾。
-IT之家注意到，本届赛事的小组赛将于 8 月 13 日至 16 日进行，所有参赛战队将通过瑞士轮赛制的小组赛较量，决出八支战队进入国际邀请赛主赛事。8 月 20 日至 23 日，最终晋级主赛事的八支战队将进入浦发银行东方体育中心，向 DOTA2 最高荣誉发起冲击。</t>
+          <t>&lt;img src="https://q6.itc.cn/images01/20260808/03b1cfe29c954f98b238d3ee98c1fe60.jpeg" alt="https://q6.itc.cn/images01/20260808/03b1cfe29c954f98b238d3ee98c1fe60.jpeg" /&gt;
+&lt;p&gt;　　按照赛程，8月8日的比赛，由WBG对阵LNG，LGD对阵AL，以及BLG对阵EDG组成。这几场比赛，除了WBG这一场，略有悬念之外，其余两场基本没有悬念。在先结束的第一场比赛中，WBG零封LNG，拿下赛季首胜。那么，LGD和AL，他们究竟谁能赢下比赛，一切都交给赛场了。&lt;/p&gt;
+&lt;img src="https://q6.itc.cn/images01/20260808/1d31f7c8c809407a98260874a93af8fa.jpeg" alt="https://q6.itc.cn/images01/20260808/1d31f7c8c809407a98260874a93af8fa.jpeg" /&gt;
+&lt;p&gt;　　第一局比赛，AL蓝色方，禁用：梦魇，慎，阿卡丽，飞机，泰坦，选用：Breathe奥拉夫，Tarzan潘森，Shanks发条，Hope韦鲁斯，Kael波比；LGD红色方，禁用：皇子，EZ，卢锡安，卡密尔，萨勒芬妮，选用：Burdol薇恩，Heng纳亚菲利，Tangyuan瑞兹，Shaoye希维尔，Crisp巴德&lt;/p&gt;
+&lt;img src="https://q8.itc.cn/images01/20260808/0d0cc4ef6b6140cc8e0180af0b2db5e0.jpeg" alt="https://q8.itc.cn/images01/20260808/0d0cc4ef6b6140cc8e0180af0b2db5e0.jpeg" /&gt;
+&lt;p&gt;　　结果第一局比赛，LGD屡次脱节痛失好局，AL首局艰难击败LGD。4分钟，LGD野辅GANK上路，Heng纳亚菲利击败奥拉夫，拿下一血；19分钟，中路处，Tarzan潘森大招进场切入LGD后排，Hope韦鲁斯跟上输出拿到双杀，随后AL持续追击打出一换四；35分钟，LGD试图开团，但AL迅速反打，Shanks奥莉安娜击败瑞兹，Tarzan潘森大招追击LGD野辅帮助队友完成击败，AL打出零换四；最终39分32秒，Kael波比控住希维尔，Breathe奥拉夫将其击败，Tarzan潘森进场控住瑞兹并击败，AL打出零换三，顺势一波推平基地，赢下比赛。&lt;/p&gt;
+&lt;img src="https://q3.itc.cn/images01/20260808/0aa5bfa4c5f1402bbed70ec402b1fa74.jpeg" alt="https://q3.itc.cn/images01/20260808/0aa5bfa4c5f1402bbed70ec402b1fa74.jpeg" /&gt;
+&lt;p&gt;　　第二局比赛，AL蓝色方，禁用：梦魇，慎，阿卡丽，飞机，泰坦，选用：Breathe奥拉夫，Tarzan潘森，Shanks发条，Hope韦鲁斯，Kael波比；LGD红色方，禁用：皇子，EZ，卢锡安，卡密尔，萨勒芬妮，选用：Burdol薇恩，Heng纳亚菲利，Tangyuan瑞兹，Shaoye希维尔，Crisp巴德&lt;/p&gt;
+&lt;img src="https://q9.itc.cn/images01/20260808/a87fdcb7eaf44185bc7c774320246abf.jpeg" alt="https://q9.itc.cn/images01/20260808/a87fdcb7eaf44185bc7c774320246abf.jpeg" /&gt;
+&lt;p&gt;　　结果第二局比赛，LGD貌似没有灵魂，被AL打出了碾压局。3分钟，LGD三人越塔下路，Hope烬塔下击败库奇，拿下一血；28分钟，中路处，Tarzan蔚先手开团控住库奇，Hope烬将其击败，Shanks卡西奥佩娅侧面进场击败芮尔，AL打出零换二；最终33分钟整，野区处，LGD试图开团，但AL众人及时赶到，Shanks卡西奥佩娅打出高额伤害拿下双杀，AL打出零换三后一波推平基地，赢下比赛。&lt;/p&gt;
+&lt;img src="https://q0.itc.cn/images01/20260808/ee5d9d4726734ad286fb90e3d45a99de.jpeg" alt="https://q0.itc.cn/images01/20260808/ee5d9d4726734ad286fb90e3d45a99de.jpeg" /&gt;
+&lt;p&gt;　　最终AL零封LGD，赢下比赛。其实看过比赛的，大抵都是知道的，LGD输掉第一局之后，就有些太夸张了，后面一个一个上去送，真的有意思吗？返回搜狐，查看更多&lt;/p&gt;</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2026%2F0812%2Fc923a05fj00tjnp0w008td000fa008hg.jpg&amp;thumbnail=660x2147483647&amp;quality=80&amp;type=jpg</t>
+          <t>https://q1.itc.cn/images01/20260808/d60eab248cad448ca273026eef7da7f9.jpeg</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>PS+8月二三档首款游戏敲定！《绝地潜兵2》来了</t>
+          <t>LPL第三赛段：集体冲阵一往无前，WBG横扫LNG，取得赛段首胜</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
@@ -2075,9 +3040,18 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>就在刚刚，索尼官方通过PlayStation Blog提前放出重磅福利，《绝地潜兵2》于今日全球同步加入PS Plus二档与三档游戏目录，英、美、日等所有地区的二三档订阅用户均可立刻免费入库游玩，不用等待月度完整阵容公布。
-按照官方计划，索尼将在今日晚些时候正式官宣2026年8月份PS+ Extra与Premium档位的全部入库游戏清单，完整内容后续会第一时间为大家跟进报道。
-值得一提的是，游戏今日还同步上线了大型版本更新，推出全新战区、新敌人、全新任务等海量内容，玩家可以直接体验完整版新内容。</t>
+          <t>&lt;img src="https://q1.itc.cn/images01/20260808/d60eab248cad448ca273026eef7da7f9.jpeg" alt="https://q1.itc.cn/images01/20260808/d60eab248cad448ca273026eef7da7f9.jpeg" /&gt;
+&lt;p&gt;　　按照赛程，8月8日的比赛，由WBG对阵LNG，LGD对阵AL，以及BLG对阵EDG组成。这几场比赛，除了WBG这一场，略有悬念之外，其余两场基本没有悬念。他们究竟谁能赢下比赛，一切都交给赛场了。&lt;/p&gt;
+&lt;img src="https://q2.itc.cn/images01/20260808/e62965143818434ea858a21f7e1ce08a.jpeg" alt="https://q2.itc.cn/images01/20260808/e62965143818434ea858a21f7e1ce08a.jpeg" /&gt;
+&lt;p&gt;　　第一局比赛，WBG蓝色方，禁用：蛇女、发条、波比、VN、纳尔，选用：Zeka奥拉夫、Xiaohao 皇子、Xiaohu兔子、Elk炸弹人、Moham慎；LNG红色方，禁用：EZ、卡密尔、瑞兹、兰博、阿卡丽，选用：Sheer亚恒、Weiwei NOC、Nia加里奥、1xn卢锡安、Missing米利欧&lt;/p&gt;
+&lt;img src="https://q1.itc.cn/images01/20260808/afb0b7a195d74c62819d6482d790858c.jpeg" alt="https://q1.itc.cn/images01/20260808/afb0b7a195d74c62819d6482d790858c.jpeg" /&gt;
+&lt;p&gt;　　结果第一局比赛，WBG很少见的打出了碾压局。3分钟，Xiaohao嘉文四世GANK下路，在队友的帮助下击败米利欧，拿下一血；25分钟，野区处，WBG三人先集火击败亚恒，Xiaohao嘉文四世进场收割拿下双杀，WBG打出一换四；最终31分钟整，河道处，Xiaohu阿萝拉绕后进场击败米利欧，Elk吉格斯跟上伤害击败魔腾，WBG打出零换四后一波推平基地，赢下比赛。&lt;/p&gt;
+&lt;img src="https://q2.itc.cn/images01/20260808/ce46dafefb9246d38246564997e9f67b.jpeg" alt="https://q2.itc.cn/images01/20260808/ce46dafefb9246d38246564997e9f67b.jpeg" /&gt;
+&lt;p&gt;　　第二局比赛，WBG蓝色方，禁用：蛇女、发条、卡牌、兰博、奇亚娜，选用：Zeka奎桑提、Xiaohao狼狗、Xiaohu辛德拉、Elk卡莎、Moham日女；LNG红色方，禁用：卡密尔、瑞兹、韦鲁斯、阿卡丽、鳄鱼，选用：Sheer掘墓、Weiwei潘森、Nia洛克、1xn EZ、Ycx泰坦&lt;/p&gt;
+&lt;img src="https://q8.itc.cn/images01/20260808/07d1d15fda4d4f64ba5e3a49b3e9dad2.jpeg" alt="https://q8.itc.cn/images01/20260808/07d1d15fda4d4f64ba5e3a49b3e9dad2.jpeg" /&gt;
+&lt;p&gt;　　结果第二局比赛，两队在前中期争夺的比较厉害，到了后期，集体冲阵一往无前，WBG横扫LNG取得赛段首胜。5分钟，河道处，Moham蕾欧娜控住诺提勒斯，Zika奎桑提将其击败拿下一血，但后续LNG更占优势，sheer约里克拿下双杀，LNG打出一换三；22分钟，小龙团，Elk卡莎大招切入LNG后排击败诺提勒斯，Xiaohao纳亚菲利跟上输出拿下双杀，WBG打出零换五并拿下小龙；最终32分23秒，河道处，Zika奎桑提先手开团控住诺提勒斯，Elk卡莎输出爆炸拿下四杀，WBG团灭LNG后一波推平基地，赢下比赛。&lt;/p&gt;
+&lt;img src="https://q1.itc.cn/images01/20260808/1b3396e0e5f54e19bddd793d13a2dcf7.jpeg" alt="https://q1.itc.cn/images01/20260808/1b3396e0e5f54e19bddd793d13a2dcf7.jpeg" /&gt;
+&lt;p&gt;　　最终WBG零封LNG，赢得了自己第三赛段的首胜。老实说，这场比赛能赢，更换Jiejie，确实取得了很大的成效。呵呵，大家都喷厂长不行，但是厂长动用自己关系把jiejie换回EDG，伟大无需多言好吧！返回搜狐，查看更多&lt;/p&gt;</t>
         </is>
       </c>
     </row>
